--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.273</v>
+        <v>2.275</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.939</v>
+        <v>2.944</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.618</v>
+        <v>-0.617</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>65096.738</v>
+        <v>64936.363</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44235,16 +44235,16 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.553</v>
+        <v>1.5532</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8365</v>
+        <v>1.8373</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2728</v>
+        <v>2.2753</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9389</v>
+        <v>2.9442</v>
       </c>
       <c r="G262" t="n">
         <v>4.0239</v>
@@ -44259,13 +44259,13 @@
         <v>2.6</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.147</v>
+        <v>-1.1468</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6181</v>
+        <v>-0.6167</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3389</v>
+        <v>0.3442</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>65096.7378</v>
+        <v>64936.363</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.2049</v>
+        <v>10.1887</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.085</v>
+        <v>1.0797</v>
       </c>
     </row>
   </sheetData>
@@ -44479,7 +44479,7 @@
         <v>-0.3691</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6313</v>
+        <v>-0.6314</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5615</v>
@@ -44529,7 +44529,7 @@
         <v>0.1587</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6147</v>
+        <v>-0.6148</v>
       </c>
       <c r="F4" t="n">
         <v>0.1587</v>
@@ -44541,7 +44541,7 @@
         <v>-0.0185</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5647</v>
+        <v>-0.5648</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6133</v>
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4299</v>
+        <v>-0.43</v>
       </c>
       <c r="C5" t="n">
         <v>-0.2012</v>
@@ -44643,7 +44643,7 @@
         <v>0.1507</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4971</v>
+        <v>-0.4972</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3579</v>
@@ -45731,7 +45731,7 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4142</v>
+        <v>-0.4143</v>
       </c>
       <c r="J39" t="n">
         <v>0.1332</v>
@@ -45901,7 +45901,7 @@
         <v>-0.4994</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5681</v>
+        <v>-0.5682</v>
       </c>
       <c r="J44" t="n">
         <v>0.5029</v>
@@ -45969,7 +45969,7 @@
         <v>-0.9858</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6514</v>
+        <v>-0.6515</v>
       </c>
       <c r="J46" t="n">
         <v>0.5853</v>
@@ -46003,7 +46003,7 @@
         <v>-0.9858</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8368</v>
+        <v>-0.8369</v>
       </c>
       <c r="J47" t="n">
         <v>0.7472</v>
@@ -46037,7 +46037,7 @@
         <v>-0.9858</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9304</v>
+        <v>-0.9305</v>
       </c>
       <c r="J48" t="n">
         <v>0.7558</v>
@@ -46173,7 +46173,7 @@
         <v>-3.3944</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.015</v>
+        <v>-1.0151</v>
       </c>
       <c r="J52" t="n">
         <v>0.3951</v>
@@ -46275,7 +46275,7 @@
         <v>-2.8207</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9871</v>
+        <v>-0.9872</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1714</v>
@@ -46390,7 +46390,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1675</v>
+        <v>-1.1676</v>
       </c>
       <c r="C59" t="n">
         <v>0.7284</v>
@@ -46445,7 +46445,7 @@
         <v>-2.3735</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1119</v>
+        <v>-1.112</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9777</v>
@@ -46547,7 +46547,7 @@
         <v>-2.1899</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0956</v>
+        <v>-1.0957</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4633</v>
@@ -46581,7 +46581,7 @@
         <v>-1.8257</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0808</v>
+        <v>-1.0809</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6948</v>
@@ -46683,7 +46683,7 @@
         <v>-1.3608</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0877</v>
+        <v>-1.0878</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1309</v>
@@ -46717,7 +46717,7 @@
         <v>-1.3608</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1551</v>
+        <v>-1.1552</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0795</v>
@@ -46785,7 +46785,7 @@
         <v>-1.0927</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2022</v>
+        <v>-1.2023</v>
       </c>
       <c r="J70" t="n">
         <v>-1.986</v>
@@ -46819,7 +46819,7 @@
         <v>-1.0927</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2266</v>
+        <v>-1.2267</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9281</v>
@@ -46989,7 +46989,7 @@
         <v>-0.7026</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2228</v>
+        <v>-1.2229</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7015</v>
@@ -47023,7 +47023,7 @@
         <v>-0.7026</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.2029</v>
+        <v>-1.203</v>
       </c>
       <c r="J77" t="n">
         <v>-1.639</v>
@@ -47079,7 +47079,7 @@
         <v>0.1228</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9381</v>
+        <v>-0.9382</v>
       </c>
       <c r="F79" t="n">
         <v>0.1228</v>
@@ -47091,7 +47091,7 @@
         <v>-0.7729</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2489</v>
+        <v>-1.249</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5259</v>
@@ -47444,7 +47444,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.527</v>
+        <v>-0.5271</v>
       </c>
       <c r="C90" t="n">
         <v>-0.2617</v>
@@ -47546,7 +47546,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4618</v>
+        <v>-0.4619</v>
       </c>
       <c r="C93" t="n">
         <v>-0.3887</v>
@@ -47635,7 +47635,7 @@
         <v>-0.4521</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2934</v>
+        <v>-1.2935</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6674</v>
@@ -47771,7 +47771,7 @@
         <v>-0.5034999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.965</v>
+        <v>-0.9651</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5256</v>
@@ -47793,7 +47793,7 @@
         <v>0.09180000000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.3743</v>
+        <v>-0.3744</v>
       </c>
       <c r="F100" t="n">
         <v>0.09180000000000001</v>
@@ -48145,7 +48145,7 @@
         <v>-0.019</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5558</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J110" t="n">
         <v>-0.2578</v>
@@ -48179,7 +48179,7 @@
         <v>-0.019</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5802</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2946</v>
@@ -49709,7 +49709,7 @@
         <v>1.1222</v>
       </c>
       <c r="I156" t="n">
-        <v>0.079</v>
+        <v>0.0791</v>
       </c>
       <c r="J156" t="n">
         <v>0.6891</v>
@@ -49913,7 +49913,7 @@
         <v>1.1736</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0392</v>
+        <v>0.0393</v>
       </c>
       <c r="J162" t="n">
         <v>1.0094</v>
@@ -50049,7 +50049,7 @@
         <v>1.1085</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1162</v>
+        <v>0.1163</v>
       </c>
       <c r="J166" t="n">
         <v>1.2102</v>
@@ -50287,7 +50287,7 @@
         <v>1.0356</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0453</v>
+        <v>-0.0452</v>
       </c>
       <c r="J173" t="n">
         <v>1.4545</v>
@@ -50389,7 +50389,7 @@
         <v>0.9648</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1521</v>
+        <v>-0.152</v>
       </c>
       <c r="J176" t="n">
         <v>1.6164</v>
@@ -50411,7 +50411,7 @@
         <v>0.7198</v>
       </c>
       <c r="E177" t="n">
-        <v>0.7536</v>
+        <v>0.7537</v>
       </c>
       <c r="F177" t="n">
         <v>0.7198</v>
@@ -50491,7 +50491,7 @@
         <v>0.9367</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1903</v>
+        <v>-0.1902</v>
       </c>
       <c r="J179" t="n">
         <v>1.7188</v>
@@ -50797,7 +50797,7 @@
         <v>-0.1333</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.19</v>
+        <v>-0.1899</v>
       </c>
       <c r="J188" t="n">
         <v>1.9294</v>
@@ -50887,7 +50887,7 @@
         <v>0.0825</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3593</v>
+        <v>0.3594</v>
       </c>
       <c r="F191" t="n">
         <v>0.0825</v>
@@ -51023,7 +51023,7 @@
         <v>0.1951</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2358</v>
+        <v>0.2359</v>
       </c>
       <c r="F195" t="n">
         <v>0.1951</v>
@@ -51035,7 +51035,7 @@
         <v>-0.0002</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1022</v>
+        <v>0.1023</v>
       </c>
       <c r="J195" t="n">
         <v>0.2299</v>
@@ -51103,7 +51103,7 @@
         <v>0.2023</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2123</v>
+        <v>0.2124</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2066</v>
@@ -51137,7 +51137,7 @@
         <v>0.2023</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2148</v>
+        <v>0.2149</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4525</v>
@@ -51205,7 +51205,7 @@
         <v>0.2926</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2704</v>
+        <v>0.2705</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6339</v>
@@ -51273,7 +51273,7 @@
         <v>0.3596</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3653</v>
+        <v>0.3654</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6061</v>
@@ -51465,7 +51465,7 @@
         <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3036</v>
+        <v>0.3037</v>
       </c>
       <c r="F208" t="n">
         <v>0.7243000000000001</v>
@@ -51490,7 +51490,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5601</v>
+        <v>0.5602</v>
       </c>
       <c r="C209" t="n">
         <v>-1.483</v>
@@ -51817,7 +51817,7 @@
         <v>0.0131</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7103</v>
       </c>
       <c r="J218" t="n">
         <v>0.0018</v>
@@ -51851,7 +51851,7 @@
         <v>0.0131</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.7627</v>
       </c>
       <c r="J219" t="n">
         <v>0.1819</v>
@@ -51885,7 +51885,7 @@
         <v>-0.0495</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7849</v>
       </c>
       <c r="J220" t="n">
         <v>0.1814</v>
@@ -51953,7 +51953,7 @@
         <v>-0.0495</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8982</v>
+        <v>0.8983</v>
       </c>
       <c r="J222" t="n">
         <v>0.1996</v>
@@ -51975,7 +51975,7 @@
         <v>1.7748</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5514</v>
+        <v>0.5515</v>
       </c>
       <c r="F223" t="n">
         <v>1.7748</v>
@@ -51987,7 +51987,7 @@
         <v>0.0545</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0118</v>
+        <v>1.0119</v>
       </c>
       <c r="J223" t="n">
         <v>0.3149</v>
@@ -52021,7 +52021,7 @@
         <v>0.0545</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0399</v>
+        <v>1.04</v>
       </c>
       <c r="J224" t="n">
         <v>0.3625</v>
@@ -52077,7 +52077,7 @@
         <v>1.4774</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5159</v>
+        <v>0.516</v>
       </c>
       <c r="F226" t="n">
         <v>1.4774</v>
@@ -52089,7 +52089,7 @@
         <v>-0.0499</v>
       </c>
       <c r="I226" t="n">
-        <v>1.191</v>
+        <v>1.1911</v>
       </c>
       <c r="J226" t="n">
         <v>0.3581</v>
@@ -52123,7 +52123,7 @@
         <v>-0.0499</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2308</v>
+        <v>1.2309</v>
       </c>
       <c r="J227" t="n">
         <v>0.3104</v>
@@ -52179,7 +52179,7 @@
         <v>1.4513</v>
       </c>
       <c r="E229" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6105</v>
       </c>
       <c r="F229" t="n">
         <v>1.4513</v>
@@ -52191,7 +52191,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2136</v>
+        <v>1.2137</v>
       </c>
       <c r="J229" t="n">
         <v>0.4323</v>
@@ -52204,7 +52204,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.7776</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="C230" t="n">
         <v>-1.991</v>
@@ -52225,7 +52225,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3266</v>
+        <v>1.3267</v>
       </c>
       <c r="J230" t="n">
         <v>0.5399</v>
@@ -52259,7 +52259,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4489</v>
+        <v>1.449</v>
       </c>
       <c r="J231" t="n">
         <v>0.4733</v>
@@ -52293,7 +52293,7 @@
         <v>0.0287</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5127</v>
+        <v>1.5128</v>
       </c>
       <c r="J232" t="n">
         <v>0.4327</v>
@@ -52327,7 +52327,7 @@
         <v>0.0287</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5833</v>
+        <v>1.5834</v>
       </c>
       <c r="J233" t="n">
         <v>0.5769</v>
@@ -52340,7 +52340,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8867</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52349,7 +52349,7 @@
         <v>1.2978</v>
       </c>
       <c r="E234" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7839</v>
       </c>
       <c r="F234" t="n">
         <v>1.2978</v>
@@ -52395,7 +52395,7 @@
         <v>0.0287</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7062</v>
+        <v>1.7063</v>
       </c>
       <c r="J235" t="n">
         <v>0.5726</v>
@@ -52417,7 +52417,7 @@
         <v>1.3711</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7235</v>
+        <v>0.7236</v>
       </c>
       <c r="F236" t="n">
         <v>1.3711</v>
@@ -52442,7 +52442,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.8586</v>
+        <v>0.8587</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
@@ -52451,7 +52451,7 @@
         <v>1.4207</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7181</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="F237" t="n">
         <v>1.4207</v>
@@ -52463,7 +52463,7 @@
         <v>0.0287</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5314</v>
+        <v>1.5315</v>
       </c>
       <c r="J237" t="n">
         <v>0.6664</v>
@@ -52476,7 +52476,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7267</v>
+        <v>0.7268</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
@@ -52497,7 +52497,7 @@
         <v>0.0542</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4966</v>
+        <v>1.4967</v>
       </c>
       <c r="J238" t="n">
         <v>0.6374</v>
@@ -52565,7 +52565,7 @@
         <v>0.0542</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7355</v>
+        <v>1.7356</v>
       </c>
       <c r="J240" t="n">
         <v>0.7241</v>
@@ -52612,7 +52612,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.7977</v>
+        <v>0.7978</v>
       </c>
       <c r="C242" t="n">
         <v>-1.726</v>
@@ -52633,7 +52633,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8325</v>
+        <v>1.8326</v>
       </c>
       <c r="J242" t="n">
         <v>0.7882</v>
@@ -52667,7 +52667,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7557</v>
+        <v>1.7558</v>
       </c>
       <c r="J243" t="n">
         <v>0.8135</v>
@@ -52701,7 +52701,7 @@
         <v>-0.115</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7227</v>
+        <v>1.7228</v>
       </c>
       <c r="J244" t="n">
         <v>0.7667</v>
@@ -52769,7 +52769,7 @@
         <v>-0.115</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6932</v>
+        <v>1.6933</v>
       </c>
       <c r="J246" t="n">
         <v>0.9795</v>
@@ -52803,7 +52803,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7216</v>
+        <v>1.7217</v>
       </c>
       <c r="J247" t="n">
         <v>0.8564000000000001</v>
@@ -52837,7 +52837,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I248" t="n">
-        <v>1.818</v>
+        <v>1.8181</v>
       </c>
       <c r="J248" t="n">
         <v>0.921</v>
@@ -52905,7 +52905,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9759</v>
+        <v>1.976</v>
       </c>
       <c r="J250" t="n">
         <v>0.9868</v>
@@ -52939,7 +52939,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1378</v>
+        <v>2.1379</v>
       </c>
       <c r="J251" t="n">
         <v>0.9752999999999999</v>
@@ -52961,7 +52961,7 @@
         <v>1.2102</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6694</v>
+        <v>0.6695</v>
       </c>
       <c r="F252" t="n">
         <v>1.2102</v>
@@ -52973,7 +52973,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2469</v>
+        <v>2.247</v>
       </c>
       <c r="J252" t="n">
         <v>1.0513</v>
@@ -53007,7 +53007,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I253" t="n">
-        <v>2.302</v>
+        <v>2.3021</v>
       </c>
       <c r="J253" t="n">
         <v>0.9856</v>
@@ -53041,7 +53041,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3947</v>
+        <v>2.3949</v>
       </c>
       <c r="J254" t="n">
         <v>1.0285</v>
@@ -53063,7 +53063,7 @@
         <v>0.4423</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6083</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="F255" t="n">
         <v>0.4423</v>
@@ -53075,7 +53075,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4614</v>
+        <v>2.4615</v>
       </c>
       <c r="J255" t="n">
         <v>1.1598</v>
@@ -53088,7 +53088,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4696</v>
+        <v>0.4697</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53109,7 +53109,7 @@
         <v>-0.172</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4835</v>
+        <v>2.4836</v>
       </c>
       <c r="J256" t="n">
         <v>1.1299</v>
@@ -53122,7 +53122,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4907</v>
+        <v>0.4908</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53143,7 +53143,7 @@
         <v>-0.172</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6066</v>
+        <v>2.6067</v>
       </c>
       <c r="J257" t="n">
         <v>1.1806</v>
@@ -53177,7 +53177,7 @@
         <v>-0.172</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7561</v>
+        <v>2.7562</v>
       </c>
       <c r="J258" t="n">
         <v>1.1695</v>
@@ -53190,7 +53190,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5333</v>
+        <v>0.5334</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53199,7 +53199,7 @@
         <v>0.3237</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5857</v>
+        <v>0.5858</v>
       </c>
       <c r="F259" t="n">
         <v>0.3237</v>
@@ -53211,7 +53211,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9453</v>
+        <v>2.9455</v>
       </c>
       <c r="J259" t="n">
         <v>1.2103</v>
@@ -53245,7 +53245,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9912</v>
+        <v>2.9913</v>
       </c>
       <c r="J260" t="n">
         <v>1.2358</v>
@@ -53258,13 +53258,13 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.6172</v>
+        <v>0.6173</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
       </c>
       <c r="E261" t="n">
-        <v>0.6172</v>
+        <v>0.6173</v>
       </c>
       <c r="G261" t="n">
         <v>-1.5813</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9892</v>
+        <v>2.9894</v>
       </c>
       <c r="J261" t="n">
         <v>1.2076</v>
@@ -53286,13 +53286,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6112</v>
+        <v>0.6105</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6112</v>
+        <v>0.6105</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53301,7 +53301,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9652</v>
+        <v>2.9623</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.837</v>
+        <v>1.838</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.275</v>
+        <v>2.278</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.944</v>
+        <v>2.949</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.024</v>
+        <v>4.025</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.617</v>
+        <v>-0.616</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.344</v>
+        <v>0.349</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>1.9976</v>
       </c>
       <c r="F260" t="n">
-        <v>2.7734</v>
+        <v>2.79</v>
       </c>
       <c r="G260" t="n">
         <v>3.93</v>
@@ -43957,7 +43957,7 @@
         <v>-0.9668</v>
       </c>
       <c r="M260" t="n">
-        <v>0.1734</v>
+        <v>0.19</v>
       </c>
       <c r="N260" t="n">
         <v>-1.722</v>
@@ -43969,7 +43969,7 @@
         <v>-0.1589</v>
       </c>
       <c r="Q260" t="n">
-        <v>0.9812</v>
+        <v>0.9979</v>
       </c>
       <c r="R260" t="n">
         <v>1.706</v>
@@ -44065,10 +44065,10 @@
         <v>22.0243</v>
       </c>
       <c r="AW260" t="n">
-        <v>10.3951</v>
+        <v>10.4066</v>
       </c>
       <c r="AX260" t="n">
-        <v>1.1567</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="261">
@@ -44090,7 +44090,7 @@
         <v>2.1399</v>
       </c>
       <c r="F261" t="n">
-        <v>2.8706</v>
+        <v>2.94</v>
       </c>
       <c r="G261" t="n">
         <v>4.0149</v>
@@ -44111,7 +44111,7 @@
         <v>-0.7833</v>
       </c>
       <c r="M261" t="n">
-        <v>0.2706</v>
+        <v>0.34</v>
       </c>
       <c r="N261" t="n">
         <v>-1.723</v>
@@ -44123,7 +44123,7 @@
         <v>-0.1589</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.9812</v>
+        <v>0.9979</v>
       </c>
       <c r="R261" t="n">
         <v>1.706</v>
@@ -44219,10 +44219,10 @@
         <v>21.0724</v>
       </c>
       <c r="AW261" t="n">
-        <v>10.2998</v>
+        <v>10.3669</v>
       </c>
       <c r="AX261" t="n">
-        <v>1.1442</v>
+        <v>1.0749</v>
       </c>
     </row>
     <row r="262">
@@ -44238,16 +44238,16 @@
         <v>1.5532</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8373</v>
+        <v>1.8377</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2753</v>
+        <v>2.278</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9442</v>
+        <v>2.9486</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0239</v>
+        <v>4.0255</v>
       </c>
       <c r="H262" t="n">
         <v>2.7</v>
@@ -44262,10 +44262,10 @@
         <v>-1.1468</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6167</v>
+        <v>-0.6155</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3442</v>
+        <v>0.3486</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
@@ -44277,7 +44277,7 @@
         <v>-0.1589</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.9812</v>
+        <v>0.9979</v>
       </c>
       <c r="R262" t="n">
         <v>1.706</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.1887</v>
+        <v>10.608</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0797</v>
+        <v>1.0769</v>
       </c>
     </row>
   </sheetData>
@@ -45002,13 +45002,13 @@
         <v>-0.4936</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.031</v>
+        <v>-0.0309</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3461</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.031</v>
+        <v>-0.0309</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7669</v>
@@ -45138,13 +45138,13 @@
         <v>-0.4462</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1092</v>
+        <v>0.1093</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4144</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1092</v>
+        <v>0.1093</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0986</v>
@@ -45274,13 +45274,13 @@
         <v>-0.4461</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0387</v>
+        <v>-0.0386</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3996</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0387</v>
+        <v>-0.0386</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4308</v>
@@ -45750,13 +45750,13 @@
         <v>-0.3972</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6105</v>
       </c>
       <c r="E40" t="n">
         <v>-0.5867</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6105</v>
       </c>
       <c r="G40" t="n">
         <v>-1.7501</v>
@@ -45954,13 +45954,13 @@
         <v>-0.6071</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="E46" t="n">
         <v>-0.7231</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9775</v>
+        <v>0.9776</v>
       </c>
       <c r="G46" t="n">
         <v>-1.8405</v>
@@ -46838,13 +46838,13 @@
         <v>0.3843</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1504</v>
+        <v>-0.1503</v>
       </c>
       <c r="E72" t="n">
         <v>-1.0992</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1504</v>
+        <v>-0.1503</v>
       </c>
       <c r="G72" t="n">
         <v>-0.2368</v>
@@ -47518,13 +47518,13 @@
         <v>-0.3907</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1327</v>
+        <v>0.1328</v>
       </c>
       <c r="E92" t="n">
         <v>-0.6891</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1327</v>
+        <v>0.1328</v>
       </c>
       <c r="G92" t="n">
         <v>-0.1028</v>
@@ -48572,13 +48572,13 @@
         <v>-0.992</v>
       </c>
       <c r="D123" t="n">
-        <v>1.2434</v>
+        <v>1.2435</v>
       </c>
       <c r="E123" t="n">
         <v>0.1951</v>
       </c>
       <c r="F123" t="n">
-        <v>1.2434</v>
+        <v>1.2435</v>
       </c>
       <c r="G123" t="n">
         <v>0.6432</v>
@@ -48810,13 +48810,13 @@
         <v>-0.786</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2582</v>
+        <v>0.2583</v>
       </c>
       <c r="E130" t="n">
         <v>0.3563</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2582</v>
+        <v>0.2583</v>
       </c>
       <c r="G130" t="n">
         <v>0.6417</v>
@@ -48912,13 +48912,13 @@
         <v>-0.62</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3667</v>
+        <v>0.3668</v>
       </c>
       <c r="E133" t="n">
         <v>0.3661</v>
       </c>
       <c r="F133" t="n">
-        <v>0.3667</v>
+        <v>0.3668</v>
       </c>
       <c r="G133" t="n">
         <v>0.5727</v>
@@ -49286,13 +49286,13 @@
         <v>-0.359</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3332</v>
+        <v>0.3333</v>
       </c>
       <c r="E144" t="n">
         <v>0.5261</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3332</v>
+        <v>0.3333</v>
       </c>
       <c r="G144" t="n">
         <v>0.8556</v>
@@ -51354,7 +51354,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5749</v>
+        <v>0.575</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8159999999999999</v>
@@ -51632,13 +51632,13 @@
         <v>-2.07</v>
       </c>
       <c r="D213" t="n">
-        <v>1.5661</v>
+        <v>1.5662</v>
       </c>
       <c r="E213" t="n">
         <v>0.4863</v>
       </c>
       <c r="F213" t="n">
-        <v>1.5661</v>
+        <v>1.5662</v>
       </c>
       <c r="G213" t="n">
         <v>0.9696</v>
@@ -52516,13 +52516,13 @@
         <v>-1.795</v>
       </c>
       <c r="D239" t="n">
-        <v>1.1456</v>
+        <v>1.1457</v>
       </c>
       <c r="E239" t="n">
         <v>0.6533</v>
       </c>
       <c r="F239" t="n">
-        <v>1.1456</v>
+        <v>1.1457</v>
       </c>
       <c r="G239" t="n">
         <v>0.2812</v>
@@ -52918,7 +52918,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.707</v>
+        <v>0.7071</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53128,13 +53128,13 @@
         <v>-1.517</v>
       </c>
       <c r="D257" t="n">
-        <v>0.3213</v>
+        <v>0.3214</v>
       </c>
       <c r="E257" t="n">
         <v>0.5331</v>
       </c>
       <c r="F257" t="n">
-        <v>0.3213</v>
+        <v>0.3214</v>
       </c>
       <c r="G257" t="n">
         <v>-1.4828</v>
@@ -53224,19 +53224,19 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5818</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
       </c>
       <c r="D260" t="n">
-        <v>0.4117</v>
+        <v>0.41</v>
       </c>
       <c r="E260" t="n">
         <v>0.6248</v>
       </c>
       <c r="F260" t="n">
-        <v>0.4117</v>
+        <v>0.41</v>
       </c>
       <c r="G260" t="n">
         <v>-1.5813</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-0.317</v>
+        <v>-0.318</v>
       </c>
     </row>
     <row r="15">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-0.29</v>
+        <v>-0.291</v>
       </c>
     </row>
     <row r="16">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-0.327</v>
+        <v>-0.328</v>
       </c>
     </row>
     <row r="27">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.183</v>
+        <v>-1.184</v>
       </c>
     </row>
     <row r="57">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>-1.218</v>
+        <v>-1.219</v>
       </c>
     </row>
     <row r="58">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>-1.032</v>
+        <v>-1.033</v>
       </c>
     </row>
     <row r="68">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>-1.03</v>
+        <v>-1.031</v>
       </c>
     </row>
     <row r="69">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>-0.909</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="73">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>-0.777</v>
+        <v>-0.778</v>
       </c>
     </row>
     <row r="77">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>-0.55</v>
+        <v>-0.551</v>
       </c>
     </row>
     <row r="90">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="115">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="116">
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="117">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>0.395</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="118">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="121">
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>0.654</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="213">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="218">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="247">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.617</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.609</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.555</v>
+        <v>1.557</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.841</v>
+        <v>1.843</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.286</v>
+        <v>2.288</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.959</v>
+        <v>2.962</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.036</v>
+        <v>4.037</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.145</v>
+        <v>-1.143</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.611</v>
+        <v>-0.609</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64685.152</v>
+        <v>64708.995</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -44117,13 +44117,13 @@
         <v>-1.723</v>
       </c>
       <c r="O261" t="n">
-        <v>-0.5886</v>
+        <v>-0.3883</v>
       </c>
       <c r="P261" t="n">
-        <v>-0.1589</v>
+        <v>0.0246</v>
       </c>
       <c r="Q261" t="n">
-        <v>0.9979</v>
+        <v>1.1479</v>
       </c>
       <c r="R261" t="n">
         <v>1.706</v>
@@ -44177,7 +44177,7 @@
         <v>0.53</v>
       </c>
       <c r="AI261" t="n">
-        <v>-0.8141</v>
+        <v>-0.8151</v>
       </c>
       <c r="AJ261" t="n">
         <v>2.1286</v>
@@ -44235,19 +44235,19 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.555</v>
+        <v>1.557</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8408</v>
+        <v>1.8429</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2856</v>
+        <v>2.2884</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9593</v>
+        <v>2.9619</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0363</v>
+        <v>4.0372</v>
       </c>
       <c r="H262" t="n">
         <v>2.7</v>
@@ -44259,25 +44259,25 @@
         <v>2.6</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.145</v>
+        <v>-1.143</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6109</v>
+        <v>-0.6086</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3593</v>
+        <v>0.3619</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
       </c>
       <c r="O262" t="n">
-        <v>-0.5886</v>
+        <v>-0.3883</v>
       </c>
       <c r="P262" t="n">
-        <v>-0.1589</v>
+        <v>0.0246</v>
       </c>
       <c r="Q262" t="n">
-        <v>0.9979</v>
+        <v>1.1479</v>
       </c>
       <c r="R262" t="n">
         <v>1.706</v>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>64685.1523</v>
+        <v>64708.995</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44331,7 +44331,7 @@
         <v>0.53</v>
       </c>
       <c r="AI262" t="n">
-        <v>-0.8141</v>
+        <v>-0.8151</v>
       </c>
       <c r="AJ262" t="n">
         <v>2.1779</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.5275</v>
+        <v>10.5092</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.077</v>
+        <v>1.0752</v>
       </c>
     </row>
   </sheetData>
@@ -44464,16 +44464,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5763</v>
+        <v>-0.5764</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2568</v>
+        <v>0.2564</v>
       </c>
       <c r="E2" t="n">
         <v>-0.854</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2568</v>
+        <v>0.2564</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3691</v>
@@ -44492,16 +44492,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5238</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1073</v>
+        <v>0.1068</v>
       </c>
       <c r="E3" t="n">
         <v>-0.734</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1073</v>
+        <v>0.1068</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0659</v>
@@ -44520,19 +44520,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4601</v>
+        <v>-0.4602</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1587</v>
+        <v>0.1583</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1587</v>
+        <v>0.1583</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2624</v>
@@ -44560,13 +44560,13 @@
         <v>-0.2012</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2207</v>
+        <v>0.2203</v>
       </c>
       <c r="E5" t="n">
         <v>-0.5926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2207</v>
+        <v>0.2203</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2787</v>
@@ -44588,19 +44588,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4313</v>
+        <v>-0.4314</v>
       </c>
       <c r="C6" t="n">
         <v>-0.2012</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2696</v>
+        <v>0.2692</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6066</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2696</v>
+        <v>0.2692</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3296</v>
@@ -44609,7 +44609,7 @@
         <v>-0.0185</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.533</v>
+        <v>-0.5329</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5452</v>
@@ -44622,19 +44622,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3826</v>
+        <v>-0.3827</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1462</v>
+        <v>0.1458</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1462</v>
+        <v>0.1458</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3549</v>
@@ -44656,19 +44656,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3947</v>
+        <v>-0.3948</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2098</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1284</v>
+        <v>0.1279</v>
       </c>
       <c r="E8" t="n">
         <v>-0.5255</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1284</v>
+        <v>0.1279</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3883</v>
@@ -44677,7 +44677,7 @@
         <v>0.1507</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4152</v>
+        <v>-0.4151</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4492</v>
@@ -44690,19 +44690,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3761</v>
+        <v>-0.3762</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2098</v>
       </c>
       <c r="D9" t="n">
-        <v>0.105</v>
+        <v>0.1045</v>
       </c>
       <c r="E9" t="n">
         <v>-0.4963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.105</v>
+        <v>0.1045</v>
       </c>
       <c r="G9" t="n">
         <v>-0.337</v>
@@ -44724,19 +44724,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3546</v>
+        <v>-0.3547</v>
       </c>
       <c r="C10" t="n">
         <v>-0.4074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0924</v>
+        <v>0.0919</v>
       </c>
       <c r="E10" t="n">
         <v>-0.4663</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0924</v>
+        <v>0.0919</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3831</v>
@@ -44758,19 +44758,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3699</v>
+        <v>-0.37</v>
       </c>
       <c r="C11" t="n">
         <v>-0.4074</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="E11" t="n">
         <v>-0.4883</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5374</v>
@@ -44792,19 +44792,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3171</v>
+        <v>-0.3172</v>
       </c>
       <c r="C12" t="n">
         <v>-0.4074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.101</v>
+        <v>0.1005</v>
       </c>
       <c r="E12" t="n">
         <v>-0.4216</v>
       </c>
       <c r="F12" t="n">
-        <v>0.101</v>
+        <v>0.1005</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4148</v>
@@ -44826,19 +44826,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2949</v>
+        <v>-0.295</v>
       </c>
       <c r="C13" t="n">
         <v>-0.4636</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1008</v>
+        <v>0.1003</v>
       </c>
       <c r="E13" t="n">
         <v>-0.3938</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1008</v>
+        <v>0.1003</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5713</v>
@@ -44860,19 +44860,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3174</v>
+        <v>-0.3175</v>
       </c>
       <c r="C14" t="n">
         <v>-0.4636</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>-0.421</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7282999999999999</v>
@@ -44894,19 +44894,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2905</v>
+        <v>-0.2906</v>
       </c>
       <c r="C15" t="n">
         <v>-0.4636</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1058</v>
+        <v>0.1053</v>
       </c>
       <c r="E15" t="n">
         <v>-0.3896</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1058</v>
+        <v>0.1053</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6925</v>
@@ -44928,19 +44928,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2315</v>
+        <v>-0.2316</v>
       </c>
       <c r="C16" t="n">
         <v>-0.5116000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0902</v>
+        <v>0.0897</v>
       </c>
       <c r="E16" t="n">
         <v>-0.3119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0902</v>
+        <v>0.0897</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5736</v>
@@ -44962,19 +44962,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2627</v>
+        <v>-0.2628</v>
       </c>
       <c r="C17" t="n">
         <v>-0.5116000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0541</v>
+        <v>-0.0547</v>
       </c>
       <c r="E17" t="n">
         <v>-0.3149</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0541</v>
+        <v>-0.0547</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6897</v>
@@ -44996,19 +44996,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2831</v>
+        <v>-0.2832</v>
       </c>
       <c r="C18" t="n">
         <v>-0.4936</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0309</v>
+        <v>-0.0315</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3461</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0309</v>
+        <v>-0.0315</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7669</v>
@@ -45030,19 +45030,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3057</v>
+        <v>-0.3058</v>
       </c>
       <c r="C19" t="n">
         <v>-0.534</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0359</v>
+        <v>0.0354</v>
       </c>
       <c r="E19" t="n">
         <v>-0.391</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0359</v>
+        <v>0.0354</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9392</v>
@@ -45064,19 +45064,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3299</v>
+        <v>-0.33</v>
       </c>
       <c r="C20" t="n">
         <v>-0.415</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0136</v>
+        <v>0.013</v>
       </c>
       <c r="E20" t="n">
         <v>-0.4158</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0136</v>
+        <v>0.013</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1006</v>
@@ -45098,19 +45098,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2921</v>
+        <v>-0.2922</v>
       </c>
       <c r="C21" t="n">
         <v>-0.32</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1089</v>
+        <v>0.1084</v>
       </c>
       <c r="E21" t="n">
         <v>-0.3924</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1089</v>
+        <v>0.1084</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9939</v>
@@ -45132,19 +45132,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3097</v>
+        <v>-0.3098</v>
       </c>
       <c r="C22" t="n">
         <v>-0.4462</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1093</v>
+        <v>0.1088</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4144</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1093</v>
+        <v>0.1088</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0986</v>
@@ -45166,19 +45166,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3657</v>
+        <v>-0.3658</v>
       </c>
       <c r="C23" t="n">
         <v>-0.4532</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0243</v>
+        <v>0.0237</v>
       </c>
       <c r="E23" t="n">
         <v>-0.4632</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0243</v>
+        <v>0.0237</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3674</v>
@@ -45200,19 +45200,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3516</v>
+        <v>-0.3517</v>
       </c>
       <c r="C24" t="n">
         <v>-0.4502</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0527</v>
+        <v>0.0522</v>
       </c>
       <c r="E24" t="n">
         <v>-0.4526</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0527</v>
+        <v>0.0522</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2861</v>
@@ -45234,19 +45234,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.329</v>
+        <v>-0.3291</v>
       </c>
       <c r="C25" t="n">
         <v>-0.4581</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0983</v>
+        <v>0.0978</v>
       </c>
       <c r="E25" t="n">
         <v>-0.4358</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0983</v>
+        <v>0.0978</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3963</v>
@@ -45268,19 +45268,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3274</v>
+        <v>-0.3276</v>
       </c>
       <c r="C26" t="n">
         <v>-0.4461</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0386</v>
+        <v>-0.0392</v>
       </c>
       <c r="E26" t="n">
         <v>-0.3996</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0386</v>
+        <v>-0.0392</v>
       </c>
       <c r="G26" t="n">
         <v>-1.4308</v>
@@ -45302,19 +45302,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3372</v>
+        <v>-0.3374</v>
       </c>
       <c r="C27" t="n">
         <v>-0.3561</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0774</v>
+        <v>-0.078</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4022</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0774</v>
+        <v>-0.078</v>
       </c>
       <c r="G27" t="n">
         <v>-1.4643</v>
@@ -45336,19 +45336,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3852</v>
+        <v>-0.3853</v>
       </c>
       <c r="C28" t="n">
         <v>-0.1935</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1715</v>
+        <v>-0.1722</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4386</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1715</v>
+        <v>-0.1722</v>
       </c>
       <c r="G28" t="n">
         <v>-1.5157</v>
@@ -45370,19 +45370,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3839</v>
+        <v>-0.384</v>
       </c>
       <c r="C29" t="n">
         <v>-0.1915</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0901</v>
+        <v>-0.0907</v>
       </c>
       <c r="E29" t="n">
         <v>-0.4573</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0901</v>
+        <v>-0.0907</v>
       </c>
       <c r="G29" t="n">
         <v>-1.7602</v>
@@ -45404,19 +45404,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3895</v>
+        <v>-0.3897</v>
       </c>
       <c r="C30" t="n">
         <v>-0.1815</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1164</v>
+        <v>-0.1171</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4578</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1164</v>
+        <v>-0.1171</v>
       </c>
       <c r="G30" t="n">
         <v>-1.7011</v>
@@ -45438,19 +45438,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3578</v>
+        <v>-0.358</v>
       </c>
       <c r="C31" t="n">
         <v>-0.3423</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1817</v>
+        <v>-0.1824</v>
       </c>
       <c r="E31" t="n">
         <v>-0.4019</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1817</v>
+        <v>-0.1824</v>
       </c>
       <c r="G31" t="n">
         <v>-1.7304</v>
@@ -45472,19 +45472,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3848</v>
+        <v>-0.385</v>
       </c>
       <c r="C32" t="n">
         <v>-0.3533</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1743</v>
+        <v>-0.175</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4375</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1743</v>
+        <v>-0.175</v>
       </c>
       <c r="G32" t="n">
         <v>-1.9586</v>
@@ -45506,19 +45506,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3642</v>
+        <v>-0.3644</v>
       </c>
       <c r="C33" t="n">
         <v>-0.3673</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1093</v>
+        <v>-0.1099</v>
       </c>
       <c r="E33" t="n">
         <v>-0.428</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1093</v>
+        <v>-0.1099</v>
       </c>
       <c r="G33" t="n">
         <v>-1.7904</v>
@@ -45540,19 +45540,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3839</v>
+        <v>-0.384</v>
       </c>
       <c r="C34" t="n">
         <v>-0.4155</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0979</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="E34" t="n">
         <v>-0.4554</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0979</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="G34" t="n">
         <v>-1.7757</v>
@@ -45574,19 +45574,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3902</v>
+        <v>-0.3903</v>
       </c>
       <c r="C35" t="n">
         <v>-0.4195</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0022</v>
+        <v>-0.0027</v>
       </c>
       <c r="E35" t="n">
         <v>-0.4872</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0022</v>
+        <v>-0.0027</v>
       </c>
       <c r="G35" t="n">
         <v>-1.9623</v>
@@ -45608,19 +45608,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2979</v>
+        <v>-0.298</v>
       </c>
       <c r="C36" t="n">
         <v>-0.4255</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1658</v>
+        <v>0.1653</v>
       </c>
       <c r="E36" t="n">
         <v>-0.4138</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1658</v>
+        <v>0.1653</v>
       </c>
       <c r="G36" t="n">
         <v>-1.6592</v>
@@ -45642,19 +45642,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.2864</v>
+        <v>-0.2865</v>
       </c>
       <c r="C37" t="n">
         <v>-0.4583</v>
       </c>
       <c r="D37" t="n">
-        <v>0.487</v>
+        <v>0.4868</v>
       </c>
       <c r="E37" t="n">
         <v>-0.4798</v>
       </c>
       <c r="F37" t="n">
-        <v>0.487</v>
+        <v>0.4868</v>
       </c>
       <c r="G37" t="n">
         <v>-1.7741</v>
@@ -45676,19 +45676,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2659</v>
+        <v>-0.266</v>
       </c>
       <c r="C38" t="n">
         <v>-0.4533</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4011</v>
+        <v>0.4008</v>
       </c>
       <c r="E38" t="n">
         <v>-0.4327</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4011</v>
+        <v>0.4008</v>
       </c>
       <c r="G38" t="n">
         <v>-1.6171</v>
@@ -45716,13 +45716,13 @@
         <v>-0.4513</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4918</v>
+        <v>0.4916</v>
       </c>
       <c r="E39" t="n">
         <v>-0.4708</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4918</v>
+        <v>0.4916</v>
       </c>
       <c r="G39" t="n">
         <v>-1.6682</v>
@@ -45744,19 +45744,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3472</v>
+        <v>-0.3473</v>
       </c>
       <c r="C40" t="n">
         <v>-0.3972</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6105</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="E40" t="n">
         <v>-0.5867</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6105</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G40" t="n">
         <v>-1.7501</v>
@@ -45778,19 +45778,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.3676</v>
+        <v>-0.3677</v>
       </c>
       <c r="C41" t="n">
         <v>-0.4022</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4135</v>
+        <v>0.4132</v>
       </c>
       <c r="E41" t="n">
         <v>-0.5629</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4135</v>
+        <v>0.4132</v>
       </c>
       <c r="G41" t="n">
         <v>-1.7083</v>
@@ -45818,13 +45818,13 @@
         <v>-0.4032</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5653</v>
+        <v>0.5652</v>
       </c>
       <c r="E42" t="n">
         <v>-0.5174</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5653</v>
+        <v>0.5652</v>
       </c>
       <c r="G42" t="n">
         <v>-1.6266</v>
@@ -45880,19 +45880,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.2397</v>
+        <v>-0.2396</v>
       </c>
       <c r="C44" t="n">
         <v>-0.506</v>
       </c>
       <c r="D44" t="n">
-        <v>1.0013</v>
+        <v>1.0016</v>
       </c>
       <c r="E44" t="n">
         <v>-0.5499000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0013</v>
+        <v>1.0016</v>
       </c>
       <c r="G44" t="n">
         <v>-1.6351</v>
@@ -45914,19 +45914,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.2118</v>
+        <v>-0.2117</v>
       </c>
       <c r="C45" t="n">
         <v>-0.505</v>
       </c>
       <c r="D45" t="n">
-        <v>1.0381</v>
+        <v>1.0383</v>
       </c>
       <c r="E45" t="n">
         <v>-0.5243</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0381</v>
+        <v>1.0383</v>
       </c>
       <c r="G45" t="n">
         <v>-1.648</v>
@@ -45948,19 +45948,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.383</v>
+        <v>-0.3829</v>
       </c>
       <c r="C46" t="n">
         <v>-0.6071</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9776</v>
+        <v>0.9778</v>
       </c>
       <c r="E46" t="n">
         <v>-0.7231</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9776</v>
+        <v>0.9778</v>
       </c>
       <c r="G46" t="n">
         <v>-1.8405</v>
@@ -45988,13 +45988,13 @@
         <v>-0.6151</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7933</v>
+        <v>0.7934</v>
       </c>
       <c r="E47" t="n">
         <v>-0.7078</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7933</v>
+        <v>0.7934</v>
       </c>
       <c r="G47" t="n">
         <v>-1.7557</v>
@@ -46022,13 +46022,13 @@
         <v>-0.8011</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4544</v>
+        <v>0.4542</v>
       </c>
       <c r="E48" t="n">
         <v>-0.6563</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4544</v>
+        <v>0.4542</v>
       </c>
       <c r="G48" t="n">
         <v>-1.4647</v>
@@ -46050,19 +46050,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.823</v>
+        <v>-0.8232</v>
       </c>
       <c r="C49" t="n">
         <v>-0.2307</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0877</v>
+        <v>-0.0883</v>
       </c>
       <c r="E49" t="n">
         <v>-1.0069</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0877</v>
+        <v>-0.0883</v>
       </c>
       <c r="G49" t="n">
         <v>-1.6193</v>
@@ -46071,7 +46071,7 @@
         <v>-2.1632</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0562</v>
+        <v>-1.0561</v>
       </c>
       <c r="J49" t="n">
         <v>0.8112</v>
@@ -46084,19 +46084,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7482</v>
+        <v>-0.7483</v>
       </c>
       <c r="C50" t="n">
         <v>-0.3217</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1314</v>
+        <v>0.1309</v>
       </c>
       <c r="E50" t="n">
         <v>-0.9681</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1314</v>
+        <v>0.1309</v>
       </c>
       <c r="G50" t="n">
         <v>-1.3497</v>
@@ -46118,19 +46118,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7765</v>
+        <v>-0.7766</v>
       </c>
       <c r="C51" t="n">
         <v>-0.3307</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1171</v>
+        <v>0.1167</v>
       </c>
       <c r="E51" t="n">
         <v>-0.9999</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1171</v>
+        <v>0.1167</v>
       </c>
       <c r="G51" t="n">
         <v>-1.2809</v>
@@ -46152,19 +46152,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.064</v>
+        <v>-1.0641</v>
       </c>
       <c r="C52" t="n">
         <v>0.2794</v>
       </c>
       <c r="D52" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E52" t="n">
         <v>-1.3473</v>
       </c>
       <c r="F52" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G52" t="n">
         <v>-1.3749</v>
@@ -46186,19 +46186,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.0582</v>
+        <v>-1.0583</v>
       </c>
       <c r="C53" t="n">
         <v>0.2834</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0615</v>
+        <v>0.061</v>
       </c>
       <c r="E53" t="n">
         <v>-1.3382</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0615</v>
+        <v>0.061</v>
       </c>
       <c r="G53" t="n">
         <v>-1.0984</v>
@@ -46220,19 +46220,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.1478</v>
+        <v>-1.148</v>
       </c>
       <c r="C54" t="n">
         <v>0.2814</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3301</v>
+        <v>-0.331</v>
       </c>
       <c r="E54" t="n">
         <v>-1.3522</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.3301</v>
+        <v>-0.331</v>
       </c>
       <c r="G54" t="n">
         <v>-0.9942</v>
@@ -46254,19 +46254,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1458</v>
+        <v>-1.146</v>
       </c>
       <c r="C55" t="n">
         <v>0.9249000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5716</v>
+        <v>-0.5726</v>
       </c>
       <c r="E55" t="n">
         <v>-1.2894</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.5716</v>
+        <v>-0.5726</v>
       </c>
       <c r="G55" t="n">
         <v>-1.1783</v>
@@ -46288,19 +46288,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.1835</v>
+        <v>-1.1837</v>
       </c>
       <c r="C56" t="n">
         <v>0.9229000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.8158</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="E56" t="n">
         <v>-1.2754</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.8158</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="G56" t="n">
         <v>-0.9691</v>
@@ -46322,19 +46322,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2184</v>
+        <v>-1.2186</v>
       </c>
       <c r="C57" t="n">
         <v>0.9268999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.8938</v>
+        <v>-0.895</v>
       </c>
       <c r="E57" t="n">
         <v>-1.2996</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.8938</v>
+        <v>-0.895</v>
       </c>
       <c r="G57" t="n">
         <v>-0.963</v>
@@ -46356,19 +46356,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-1.1846</v>
+        <v>-1.1849</v>
       </c>
       <c r="C58" t="n">
         <v>0.7244</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.8337</v>
+        <v>-0.8349</v>
       </c>
       <c r="E58" t="n">
         <v>-1.2724</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.8337</v>
+        <v>-0.8349</v>
       </c>
       <c r="G58" t="n">
         <v>-0.9639</v>
@@ -46390,19 +46390,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1676</v>
+        <v>-1.1678</v>
       </c>
       <c r="C59" t="n">
         <v>0.7284</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8126</v>
+        <v>-0.8138</v>
       </c>
       <c r="E59" t="n">
         <v>-1.2563</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.8126</v>
+        <v>-0.8138</v>
       </c>
       <c r="G59" t="n">
         <v>-0.7393</v>
@@ -46424,19 +46424,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1389</v>
+        <v>-1.1391</v>
       </c>
       <c r="C60" t="n">
         <v>0.7274</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5419</v>
+        <v>-0.5429</v>
       </c>
       <c r="E60" t="n">
         <v>-1.2882</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5419</v>
+        <v>-0.5429</v>
       </c>
       <c r="G60" t="n">
         <v>-0.6896</v>
@@ -46458,19 +46458,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1046</v>
+        <v>-1.1048</v>
       </c>
       <c r="C61" t="n">
         <v>0.5718</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3879</v>
+        <v>-0.3888</v>
       </c>
       <c r="E61" t="n">
         <v>-1.2838</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3879</v>
+        <v>-0.3888</v>
       </c>
       <c r="G61" t="n">
         <v>-0.7181999999999999</v>
@@ -46479,7 +46479,7 @@
         <v>-2.1899</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0855</v>
+        <v>-1.0854</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1416</v>
@@ -46492,19 +46492,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.0661</v>
+        <v>-1.0663</v>
       </c>
       <c r="C62" t="n">
         <v>0.5668</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.2602</v>
+        <v>-0.2609</v>
       </c>
       <c r="E62" t="n">
         <v>-1.2676</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2602</v>
+        <v>-0.2609</v>
       </c>
       <c r="G62" t="n">
         <v>-0.5569</v>
@@ -46526,19 +46526,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.109</v>
+        <v>-1.1091</v>
       </c>
       <c r="C63" t="n">
         <v>0.5718</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.2135</v>
+        <v>-0.2142</v>
       </c>
       <c r="E63" t="n">
         <v>-1.3329</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2135</v>
+        <v>-0.2142</v>
       </c>
       <c r="G63" t="n">
         <v>-0.5825</v>
@@ -46560,19 +46560,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.1017</v>
+        <v>-1.1018</v>
       </c>
       <c r="C64" t="n">
         <v>0.5042</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.2624</v>
+        <v>-0.2631</v>
       </c>
       <c r="E64" t="n">
         <v>-1.3115</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2624</v>
+        <v>-0.2631</v>
       </c>
       <c r="G64" t="n">
         <v>-0.6447000000000001</v>
@@ -46594,19 +46594,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.0456</v>
+        <v>-1.0458</v>
       </c>
       <c r="C65" t="n">
         <v>0.5002</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.3024</v>
+        <v>-0.3032</v>
       </c>
       <c r="E65" t="n">
         <v>-1.2314</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3024</v>
+        <v>-0.3032</v>
       </c>
       <c r="G65" t="n">
         <v>-0.303</v>
@@ -46628,19 +46628,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0548</v>
+        <v>-1.0549</v>
       </c>
       <c r="C66" t="n">
         <v>0.4982</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.2086</v>
+        <v>-0.2093</v>
       </c>
       <c r="E66" t="n">
         <v>-1.2664</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2086</v>
+        <v>-0.2093</v>
       </c>
       <c r="G66" t="n">
         <v>-0.268</v>
@@ -46662,19 +46662,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0324</v>
+        <v>-1.0325</v>
       </c>
       <c r="C67" t="n">
         <v>0.454</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1876</v>
+        <v>-0.1883</v>
       </c>
       <c r="E67" t="n">
         <v>-1.2436</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1876</v>
+        <v>-0.1883</v>
       </c>
       <c r="G67" t="n">
         <v>-0.395</v>
@@ -46696,19 +46696,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0305</v>
+        <v>-1.0306</v>
       </c>
       <c r="C68" t="n">
         <v>0.453</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2734</v>
+        <v>-0.2742</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2198</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2734</v>
+        <v>-0.2742</v>
       </c>
       <c r="G68" t="n">
         <v>-0.2835</v>
@@ -46730,19 +46730,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0236</v>
+        <v>-1.0238</v>
       </c>
       <c r="C69" t="n">
         <v>0.454</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.2619</v>
+        <v>-0.2627</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2141</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.2619</v>
+        <v>-0.2627</v>
       </c>
       <c r="G69" t="n">
         <v>-0.3374</v>
@@ -46764,19 +46764,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9832</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="C70" t="n">
         <v>0.3843</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.2931</v>
+        <v>-0.2939</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1557</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.2931</v>
+        <v>-0.2939</v>
       </c>
       <c r="G70" t="n">
         <v>-0.3418</v>
@@ -46798,19 +46798,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8999</v>
+        <v>-0.9</v>
       </c>
       <c r="C71" t="n">
         <v>0.3843</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.1104</v>
+        <v>-0.111</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0972</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1104</v>
+        <v>-0.111</v>
       </c>
       <c r="G71" t="n">
         <v>-0.1414</v>
@@ -46832,19 +46832,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9095</v>
+        <v>-0.9096</v>
       </c>
       <c r="C72" t="n">
         <v>0.3843</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.1503</v>
+        <v>-0.151</v>
       </c>
       <c r="E72" t="n">
         <v>-1.0992</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1503</v>
+        <v>-0.151</v>
       </c>
       <c r="G72" t="n">
         <v>-0.2368</v>
@@ -46866,19 +46866,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.8628</v>
+        <v>-0.863</v>
       </c>
       <c r="C73" t="n">
         <v>0.301</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.1177</v>
+        <v>-0.1183</v>
       </c>
       <c r="E73" t="n">
         <v>-1.0491</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1177</v>
+        <v>-0.1183</v>
       </c>
       <c r="G73" t="n">
         <v>-0.2512</v>
@@ -46900,19 +46900,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8394</v>
       </c>
       <c r="C74" t="n">
         <v>0.299</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.1687</v>
+        <v>-0.1694</v>
       </c>
       <c r="E74" t="n">
         <v>-1.0069</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1687</v>
+        <v>-0.1694</v>
       </c>
       <c r="G74" t="n">
         <v>-0.1458</v>
@@ -46934,19 +46934,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.8238</v>
+        <v>-0.8239</v>
       </c>
       <c r="C75" t="n">
         <v>0.307</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.1839</v>
+        <v>-0.1846</v>
       </c>
       <c r="E75" t="n">
         <v>-0.9837</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1839</v>
+        <v>-0.1846</v>
       </c>
       <c r="G75" t="n">
         <v>-0.0709</v>
@@ -46968,19 +46968,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7774</v>
+        <v>-0.7775</v>
       </c>
       <c r="C76" t="n">
         <v>0.13</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0872</v>
       </c>
       <c r="E76" t="n">
         <v>-0.9500999999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0872</v>
       </c>
       <c r="G76" t="n">
         <v>-0.1733</v>
@@ -47002,19 +47002,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.74</v>
+        <v>-0.7402</v>
       </c>
       <c r="C77" t="n">
         <v>0.107</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0526</v>
+        <v>0.0521</v>
       </c>
       <c r="E77" t="n">
         <v>-0.9382</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0526</v>
+        <v>0.0521</v>
       </c>
       <c r="G77" t="n">
         <v>-0.2082</v>
@@ -47036,19 +47036,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.6931</v>
       </c>
       <c r="C78" t="n">
         <v>0.114</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1135</v>
+        <v>0.113</v>
       </c>
       <c r="E78" t="n">
         <v>-0.8946</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1135</v>
+        <v>0.113</v>
       </c>
       <c r="G78" t="n">
         <v>-0.0613</v>
@@ -47070,19 +47070,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.726</v>
+        <v>-0.7261</v>
       </c>
       <c r="C79" t="n">
         <v>-0.0368</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1228</v>
+        <v>0.1224</v>
       </c>
       <c r="E79" t="n">
         <v>-0.9382</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1228</v>
+        <v>0.1224</v>
       </c>
       <c r="G79" t="n">
         <v>-0.2048</v>
@@ -47110,13 +47110,13 @@
         <v>-0.0328</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2633</v>
+        <v>0.263</v>
       </c>
       <c r="E80" t="n">
         <v>-0.9018</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2633</v>
+        <v>0.263</v>
       </c>
       <c r="G80" t="n">
         <v>-0.0266</v>
@@ -47138,19 +47138,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6248</v>
+        <v>-0.6249</v>
       </c>
       <c r="C81" t="n">
         <v>-0.0248</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3198</v>
+        <v>0.3194</v>
       </c>
       <c r="E81" t="n">
         <v>-0.8609</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3198</v>
+        <v>0.3194</v>
       </c>
       <c r="G81" t="n">
         <v>-0.0153</v>
@@ -47178,13 +47178,13 @@
         <v>-0.0573</v>
       </c>
       <c r="D82" t="n">
-        <v>0.326</v>
+        <v>0.3257</v>
       </c>
       <c r="E82" t="n">
         <v>-0.8247</v>
       </c>
       <c r="F82" t="n">
-        <v>0.326</v>
+        <v>0.3257</v>
       </c>
       <c r="G82" t="n">
         <v>-0.0064</v>
@@ -47206,19 +47206,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6974</v>
+        <v>-0.6975</v>
       </c>
       <c r="C83" t="n">
         <v>-0.0563</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1817</v>
+        <v>0.1813</v>
       </c>
       <c r="E83" t="n">
         <v>-0.9172</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1817</v>
+        <v>0.1813</v>
       </c>
       <c r="G83" t="n">
         <v>-0.3784</v>
@@ -47240,19 +47240,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.622</v>
+        <v>-0.6221</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0603</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1347</v>
+        <v>0.1343</v>
       </c>
       <c r="E84" t="n">
         <v>-0.8112</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1347</v>
+        <v>0.1343</v>
       </c>
       <c r="G84" t="n">
         <v>-0.0224</v>
@@ -47274,19 +47274,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.5903</v>
+        <v>-0.5904</v>
       </c>
       <c r="C85" t="n">
         <v>-0.1757</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1894</v>
+        <v>0.1889</v>
       </c>
       <c r="E85" t="n">
         <v>-0.7852</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1894</v>
+        <v>0.1889</v>
       </c>
       <c r="G85" t="n">
         <v>-0.0122</v>
@@ -47308,19 +47308,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5913</v>
+        <v>-0.5914</v>
       </c>
       <c r="C86" t="n">
         <v>-0.1737</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2363</v>
+        <v>0.2359</v>
       </c>
       <c r="E86" t="n">
         <v>-0.7982</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2363</v>
+        <v>0.2359</v>
       </c>
       <c r="G86" t="n">
         <v>-0.07140000000000001</v>
@@ -47348,13 +47348,13 @@
         <v>-0.1687</v>
       </c>
       <c r="D87" t="n">
-        <v>0.285</v>
+        <v>0.2847</v>
       </c>
       <c r="E87" t="n">
         <v>-0.7082000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>0.285</v>
+        <v>0.2847</v>
       </c>
       <c r="G87" t="n">
         <v>0.1654</v>
@@ -47376,19 +47376,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5211</v>
+        <v>-0.5212</v>
       </c>
       <c r="C88" t="n">
         <v>-0.2617</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3315</v>
+        <v>0.3312</v>
       </c>
       <c r="E88" t="n">
         <v>-0.7343</v>
       </c>
       <c r="F88" t="n">
-        <v>0.3315</v>
+        <v>0.3312</v>
       </c>
       <c r="G88" t="n">
         <v>0.035</v>
@@ -47416,13 +47416,13 @@
         <v>-0.2707</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3377</v>
+        <v>0.3374</v>
       </c>
       <c r="E89" t="n">
         <v>-0.7725</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3377</v>
+        <v>0.3374</v>
       </c>
       <c r="G89" t="n">
         <v>-0.1414</v>
@@ -47450,13 +47450,13 @@
         <v>-0.2617</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="E90" t="n">
         <v>-0.712</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="G90" t="n">
         <v>0.1491</v>
@@ -47484,13 +47484,13 @@
         <v>-0.3987</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1758</v>
+        <v>0.1753</v>
       </c>
       <c r="E91" t="n">
         <v>-0.6465</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1758</v>
+        <v>0.1753</v>
       </c>
       <c r="G91" t="n">
         <v>0.0725</v>
@@ -47512,19 +47512,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5248</v>
       </c>
       <c r="C92" t="n">
         <v>-0.3907</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1328</v>
+        <v>0.1323</v>
       </c>
       <c r="E92" t="n">
         <v>-0.6891</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1328</v>
+        <v>0.1323</v>
       </c>
       <c r="G92" t="n">
         <v>-0.1028</v>
@@ -47552,13 +47552,13 @@
         <v>-0.3887</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1761</v>
+        <v>0.1757</v>
       </c>
       <c r="E93" t="n">
         <v>-0.6214</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1761</v>
+        <v>0.1757</v>
       </c>
       <c r="G93" t="n">
         <v>0.1025</v>
@@ -47580,19 +47580,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4375</v>
+        <v>-0.4376</v>
       </c>
       <c r="C94" t="n">
         <v>-0.4527</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2713</v>
+        <v>0.271</v>
       </c>
       <c r="E94" t="n">
         <v>-0.6147</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2713</v>
+        <v>0.271</v>
       </c>
       <c r="G94" t="n">
         <v>0.1361</v>
@@ -47614,19 +47614,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.4219</v>
+        <v>-0.422</v>
       </c>
       <c r="C95" t="n">
         <v>-0.4527</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2715</v>
+        <v>0.2712</v>
       </c>
       <c r="E95" t="n">
         <v>-0.5953000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2715</v>
+        <v>0.2712</v>
       </c>
       <c r="G95" t="n">
         <v>0.0319</v>
@@ -47648,19 +47648,19 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3902</v>
+        <v>-0.3903</v>
       </c>
       <c r="C96" t="n">
         <v>-0.4517</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2768</v>
+        <v>0.2764</v>
       </c>
       <c r="E96" t="n">
         <v>-0.5570000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2768</v>
+        <v>0.2764</v>
       </c>
       <c r="G96" t="n">
         <v>0.2279</v>
@@ -47688,13 +47688,13 @@
         <v>-0.6221</v>
       </c>
       <c r="D97" t="n">
-        <v>0.5887</v>
+        <v>0.5886</v>
       </c>
       <c r="E97" t="n">
         <v>-0.5829</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5887</v>
+        <v>0.5886</v>
       </c>
       <c r="G97" t="n">
         <v>0.0779</v>
@@ -47716,19 +47716,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.379</v>
+        <v>-0.3791</v>
       </c>
       <c r="C98" t="n">
         <v>-0.6211</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1387</v>
+        <v>0.1382</v>
       </c>
       <c r="E98" t="n">
         <v>-0.5084</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1387</v>
+        <v>0.1382</v>
       </c>
       <c r="G98" t="n">
         <v>0.0558</v>
@@ -47750,19 +47750,19 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3008</v>
+        <v>-0.3009</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1589</v>
+        <v>0.1585</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.4158</v>
+        <v>-0.4157</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1589</v>
+        <v>0.1585</v>
       </c>
       <c r="G99" t="n">
         <v>0.3311</v>
@@ -47784,19 +47784,19 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2811</v>
+        <v>-0.2812</v>
       </c>
       <c r="C100" t="n">
         <v>-0.6868</v>
       </c>
       <c r="D100" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0914</v>
       </c>
       <c r="E100" t="n">
         <v>-0.3744</v>
       </c>
       <c r="F100" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0914</v>
       </c>
       <c r="G100" t="n">
         <v>0.3136</v>
@@ -47818,19 +47818,19 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.3329</v>
+        <v>-0.333</v>
       </c>
       <c r="C101" t="n">
         <v>-0.6928</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1066</v>
+        <v>0.1061</v>
       </c>
       <c r="E101" t="n">
         <v>-0.4428</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1066</v>
+        <v>0.1061</v>
       </c>
       <c r="G101" t="n">
         <v>0.0522</v>
@@ -47852,19 +47852,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1902</v>
+        <v>-0.1903</v>
       </c>
       <c r="C102" t="n">
         <v>-0.6918</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2464</v>
+        <v>0.246</v>
       </c>
       <c r="E102" t="n">
         <v>-0.2994</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2464</v>
+        <v>0.246</v>
       </c>
       <c r="G102" t="n">
         <v>0.3619</v>
@@ -47892,13 +47892,13 @@
         <v>-0.7114</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3909</v>
+        <v>0.3906</v>
       </c>
       <c r="E103" t="n">
         <v>-0.2817</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3909</v>
+        <v>0.3906</v>
       </c>
       <c r="G103" t="n">
         <v>0.3909</v>
@@ -47926,13 +47926,13 @@
         <v>-0.7124</v>
       </c>
       <c r="D104" t="n">
-        <v>0.5313</v>
+        <v>0.5312</v>
       </c>
       <c r="E104" t="n">
         <v>-0.2782</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5313</v>
+        <v>0.5312</v>
       </c>
       <c r="G104" t="n">
         <v>0.207</v>
@@ -47954,19 +47954,19 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0561</v>
+        <v>-0.0562</v>
       </c>
       <c r="C105" t="n">
         <v>-0.7124</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5886</v>
+        <v>0.5885</v>
       </c>
       <c r="E105" t="n">
         <v>-0.2173</v>
       </c>
       <c r="F105" t="n">
-        <v>0.5886</v>
+        <v>0.5885</v>
       </c>
       <c r="G105" t="n">
         <v>0.4685</v>
@@ -47994,13 +47994,13 @@
         <v>-0.8269</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5482</v>
+        <v>0.5481</v>
       </c>
       <c r="E106" t="n">
         <v>-0.2279</v>
       </c>
       <c r="F106" t="n">
-        <v>0.5482</v>
+        <v>0.5481</v>
       </c>
       <c r="G106" t="n">
         <v>0.2791</v>
@@ -48028,13 +48028,13 @@
         <v>-0.8289</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6534</v>
+        <v>0.6533</v>
       </c>
       <c r="E107" t="n">
         <v>-0.2558</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6534</v>
+        <v>0.6533</v>
       </c>
       <c r="G107" t="n">
         <v>0.1929</v>
@@ -48062,13 +48062,13 @@
         <v>-0.8259</v>
       </c>
       <c r="D108" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7899</v>
       </c>
       <c r="E108" t="n">
         <v>-0.1903</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7899</v>
       </c>
       <c r="G108" t="n">
         <v>0.4313</v>
@@ -48090,19 +48090,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.1715</v>
+        <v>0.1716</v>
       </c>
       <c r="C109" t="n">
         <v>-0.8532999999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>1.5002</v>
+        <v>1.5008</v>
       </c>
       <c r="E109" t="n">
         <v>-0.1607</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5002</v>
+        <v>1.5008</v>
       </c>
       <c r="G109" t="n">
         <v>0.3082</v>
@@ -48130,13 +48130,13 @@
         <v>-0.8542999999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>0.8837</v>
+        <v>0.8839</v>
       </c>
       <c r="E110" t="n">
         <v>-0.1488</v>
       </c>
       <c r="F110" t="n">
-        <v>0.8837</v>
+        <v>0.8839</v>
       </c>
       <c r="G110" t="n">
         <v>0.2374</v>
@@ -48164,13 +48164,13 @@
         <v>-0.8502999999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="E111" t="n">
         <v>-0.0956</v>
       </c>
       <c r="F111" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="G111" t="n">
         <v>0.5115</v>
@@ -48198,13 +48198,13 @@
         <v>-1.037</v>
       </c>
       <c r="D112" t="n">
-        <v>0.8885</v>
+        <v>0.8887</v>
       </c>
       <c r="E112" t="n">
         <v>-0.0616</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8885</v>
+        <v>0.8887</v>
       </c>
       <c r="G112" t="n">
         <v>0.4516</v>
@@ -48226,19 +48226,19 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.2479</v>
+        <v>0.248</v>
       </c>
       <c r="C113" t="n">
         <v>-1.044</v>
       </c>
       <c r="D113" t="n">
-        <v>1.6989</v>
+        <v>1.6996</v>
       </c>
       <c r="E113" t="n">
         <v>-0.1149</v>
       </c>
       <c r="F113" t="n">
-        <v>1.6989</v>
+        <v>1.6996</v>
       </c>
       <c r="G113" t="n">
         <v>0.2597</v>
@@ -48260,19 +48260,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3535</v>
+        <v>0.3537</v>
       </c>
       <c r="C114" t="n">
         <v>-1.041</v>
       </c>
       <c r="D114" t="n">
-        <v>1.7459</v>
+        <v>1.7467</v>
       </c>
       <c r="E114" t="n">
         <v>0.0054</v>
       </c>
       <c r="F114" t="n">
-        <v>1.7459</v>
+        <v>1.7467</v>
       </c>
       <c r="G114" t="n">
         <v>0.6358</v>
@@ -48294,19 +48294,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3444</v>
+        <v>0.3445</v>
       </c>
       <c r="C115" t="n">
         <v>-1.072</v>
       </c>
       <c r="D115" t="n">
-        <v>1.7497</v>
+        <v>1.7505</v>
       </c>
       <c r="E115" t="n">
         <v>-0.0069</v>
       </c>
       <c r="F115" t="n">
-        <v>1.7497</v>
+        <v>1.7505</v>
       </c>
       <c r="G115" t="n">
         <v>0.3826</v>
@@ -48328,19 +48328,19 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.3535</v>
+        <v>0.3536</v>
       </c>
       <c r="C116" t="n">
         <v>-1.073</v>
       </c>
       <c r="D116" t="n">
-        <v>1.7561</v>
+        <v>1.7569</v>
       </c>
       <c r="E116" t="n">
         <v>0.0028</v>
       </c>
       <c r="F116" t="n">
-        <v>1.7561</v>
+        <v>1.7569</v>
       </c>
       <c r="G116" t="n">
         <v>0.3818</v>
@@ -48362,19 +48362,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.3954</v>
+        <v>0.3955</v>
       </c>
       <c r="C117" t="n">
         <v>-1.07</v>
       </c>
       <c r="D117" t="n">
-        <v>1.6653</v>
+        <v>1.6661</v>
       </c>
       <c r="E117" t="n">
         <v>0.0779</v>
       </c>
       <c r="F117" t="n">
-        <v>1.6653</v>
+        <v>1.6661</v>
       </c>
       <c r="G117" t="n">
         <v>0.6306</v>
@@ -48396,19 +48396,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3912</v>
+        <v>0.3913</v>
       </c>
       <c r="C118" t="n">
         <v>-1.093</v>
       </c>
       <c r="D118" t="n">
-        <v>1.6179</v>
+        <v>1.6186</v>
       </c>
       <c r="E118" t="n">
         <v>0.08450000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>1.6179</v>
+        <v>1.6186</v>
       </c>
       <c r="G118" t="n">
         <v>0.4575</v>
@@ -48430,19 +48430,19 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4043</v>
+        <v>0.4044</v>
       </c>
       <c r="C119" t="n">
         <v>-1.1</v>
       </c>
       <c r="D119" t="n">
-        <v>1.5829</v>
+        <v>1.5836</v>
       </c>
       <c r="E119" t="n">
         <v>0.1096</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5829</v>
+        <v>1.5836</v>
       </c>
       <c r="G119" t="n">
         <v>0.5199</v>
@@ -48464,19 +48464,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.3964</v>
+        <v>0.3965</v>
       </c>
       <c r="C120" t="n">
         <v>-1.094</v>
       </c>
       <c r="D120" t="n">
-        <v>1.4576</v>
+        <v>1.4582</v>
       </c>
       <c r="E120" t="n">
         <v>0.1311</v>
       </c>
       <c r="F120" t="n">
-        <v>1.4576</v>
+        <v>1.4582</v>
       </c>
       <c r="G120" t="n">
         <v>0.4793</v>
@@ -48504,13 +48504,13 @@
         <v>-1</v>
       </c>
       <c r="D121" t="n">
-        <v>0.353</v>
+        <v>0.3528</v>
       </c>
       <c r="E121" t="n">
         <v>0.1709</v>
       </c>
       <c r="F121" t="n">
-        <v>0.353</v>
+        <v>0.3528</v>
       </c>
       <c r="G121" t="n">
         <v>0.5171</v>
@@ -48532,19 +48532,19 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4086</v>
+        <v>0.4087</v>
       </c>
       <c r="C122" t="n">
         <v>-0.994</v>
       </c>
       <c r="D122" t="n">
-        <v>1.3545</v>
+        <v>1.355</v>
       </c>
       <c r="E122" t="n">
         <v>0.1722</v>
       </c>
       <c r="F122" t="n">
-        <v>1.3545</v>
+        <v>1.355</v>
       </c>
       <c r="G122" t="n">
         <v>0.5208</v>
@@ -48566,19 +48566,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4048</v>
+        <v>0.4049</v>
       </c>
       <c r="C123" t="n">
         <v>-0.992</v>
       </c>
       <c r="D123" t="n">
-        <v>1.2435</v>
+        <v>1.2439</v>
       </c>
       <c r="E123" t="n">
         <v>0.1951</v>
       </c>
       <c r="F123" t="n">
-        <v>1.2435</v>
+        <v>1.2439</v>
       </c>
       <c r="G123" t="n">
         <v>0.6432</v>
@@ -48600,19 +48600,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5019</v>
+        <v>0.502</v>
       </c>
       <c r="C124" t="n">
         <v>-0.9419999999999999</v>
       </c>
       <c r="D124" t="n">
-        <v>1.28</v>
+        <v>1.2804</v>
       </c>
       <c r="E124" t="n">
         <v>0.3074</v>
       </c>
       <c r="F124" t="n">
-        <v>1.28</v>
+        <v>1.2804</v>
       </c>
       <c r="G124" t="n">
         <v>0.6111</v>
@@ -48640,13 +48640,13 @@
         <v>-0.951</v>
       </c>
       <c r="D125" t="n">
-        <v>0.522</v>
+        <v>0.5219</v>
       </c>
       <c r="E125" t="n">
         <v>0.3119</v>
       </c>
       <c r="F125" t="n">
-        <v>0.522</v>
+        <v>0.5219</v>
       </c>
       <c r="G125" t="n">
         <v>0.6157</v>
@@ -48668,19 +48668,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3379</v>
+        <v>0.3378</v>
       </c>
       <c r="C126" t="n">
         <v>-0.9429999999999999</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4297</v>
+        <v>0.4295</v>
       </c>
       <c r="E126" t="n">
         <v>0.3149</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4297</v>
+        <v>0.4295</v>
       </c>
       <c r="G126" t="n">
         <v>0.6761</v>
@@ -48702,19 +48702,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3369</v>
+        <v>0.3368</v>
       </c>
       <c r="C127" t="n">
         <v>-0.9389999999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3786</v>
+        <v>0.3784</v>
       </c>
       <c r="E127" t="n">
         <v>0.3264</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3786</v>
+        <v>0.3784</v>
       </c>
       <c r="G127" t="n">
         <v>0.5066000000000001</v>
@@ -48736,19 +48736,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3267</v>
+        <v>0.3266</v>
       </c>
       <c r="C128" t="n">
         <v>-0.9370000000000001</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2945</v>
+        <v>0.2942</v>
       </c>
       <c r="E128" t="n">
         <v>0.3347</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2945</v>
+        <v>0.2942</v>
       </c>
       <c r="G128" t="n">
         <v>0.5534</v>
@@ -48770,19 +48770,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.3702</v>
+        <v>0.3701</v>
       </c>
       <c r="C129" t="n">
         <v>-0.9350000000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2553</v>
+        <v>0.2549</v>
       </c>
       <c r="E129" t="n">
         <v>0.3989</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2553</v>
+        <v>0.2549</v>
       </c>
       <c r="G129" t="n">
         <v>0.75</v>
@@ -48804,19 +48804,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3367</v>
+        <v>0.3366</v>
       </c>
       <c r="C130" t="n">
         <v>-0.786</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2583</v>
+        <v>0.2579</v>
       </c>
       <c r="E130" t="n">
         <v>0.3563</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2583</v>
+        <v>0.2579</v>
       </c>
       <c r="G130" t="n">
         <v>0.6417</v>
@@ -48838,19 +48838,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.329</v>
+        <v>0.3289</v>
       </c>
       <c r="C131" t="n">
         <v>-0.783</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2221</v>
+        <v>0.2217</v>
       </c>
       <c r="E131" t="n">
         <v>0.3558</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2221</v>
+        <v>0.2217</v>
       </c>
       <c r="G131" t="n">
         <v>0.7066</v>
@@ -48872,19 +48872,19 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3425</v>
+        <v>0.3424</v>
       </c>
       <c r="C132" t="n">
         <v>-0.781</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3561</v>
+        <v>0.3558</v>
       </c>
       <c r="E132" t="n">
         <v>0.3391</v>
       </c>
       <c r="F132" t="n">
-        <v>0.3561</v>
+        <v>0.3558</v>
       </c>
       <c r="G132" t="n">
         <v>0.5545</v>
@@ -48906,19 +48906,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3662</v>
+        <v>0.3661</v>
       </c>
       <c r="C133" t="n">
         <v>-0.62</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3668</v>
+        <v>0.3665</v>
       </c>
       <c r="E133" t="n">
         <v>0.3661</v>
       </c>
       <c r="F133" t="n">
-        <v>0.3668</v>
+        <v>0.3665</v>
       </c>
       <c r="G133" t="n">
         <v>0.5727</v>
@@ -48946,13 +48946,13 @@
         <v>-0.621</v>
       </c>
       <c r="D134" t="n">
-        <v>0.3864</v>
+        <v>0.3861</v>
       </c>
       <c r="E134" t="n">
         <v>0.3664</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3864</v>
+        <v>0.3861</v>
       </c>
       <c r="G134" t="n">
         <v>0.7548</v>
@@ -48980,13 +48980,13 @@
         <v>-0.662</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4548</v>
+        <v>0.4546</v>
       </c>
       <c r="E135" t="n">
         <v>0.3786</v>
       </c>
       <c r="F135" t="n">
-        <v>0.4548</v>
+        <v>0.4546</v>
       </c>
       <c r="G135" t="n">
         <v>0.7607</v>
@@ -49014,13 +49014,13 @@
         <v>-0.503</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3204</v>
+        <v>0.3201</v>
       </c>
       <c r="E136" t="n">
         <v>0.4224</v>
       </c>
       <c r="F136" t="n">
-        <v>0.3204</v>
+        <v>0.3201</v>
       </c>
       <c r="G136" t="n">
         <v>0.9045</v>
@@ -49048,13 +49048,13 @@
         <v>-0.537</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2951</v>
+        <v>0.2948</v>
       </c>
       <c r="E137" t="n">
         <v>0.3936</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2951</v>
+        <v>0.2948</v>
       </c>
       <c r="G137" t="n">
         <v>0.8308</v>
@@ -49082,13 +49082,13 @@
         <v>-0.5590000000000001</v>
       </c>
       <c r="D138" t="n">
-        <v>0.308</v>
+        <v>0.3077</v>
       </c>
       <c r="E138" t="n">
         <v>0.4389</v>
       </c>
       <c r="F138" t="n">
-        <v>0.308</v>
+        <v>0.3077</v>
       </c>
       <c r="G138" t="n">
         <v>0.9073</v>
@@ -49116,13 +49116,13 @@
         <v>-0.421</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3253</v>
+        <v>0.325</v>
       </c>
       <c r="E139" t="n">
         <v>0.4204</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3253</v>
+        <v>0.325</v>
       </c>
       <c r="G139" t="n">
         <v>0.8671</v>
@@ -49150,13 +49150,13 @@
         <v>-0.409</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3009</v>
+        <v>0.3006</v>
       </c>
       <c r="E140" t="n">
         <v>0.4471</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3009</v>
+        <v>0.3006</v>
       </c>
       <c r="G140" t="n">
         <v>0.8431</v>
@@ -49178,19 +49178,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4011</v>
+        <v>0.401</v>
       </c>
       <c r="C141" t="n">
         <v>-0.409</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2426</v>
+        <v>0.2423</v>
       </c>
       <c r="E141" t="n">
         <v>0.4407</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2426</v>
+        <v>0.2423</v>
       </c>
       <c r="G141" t="n">
         <v>0.8559</v>
@@ -49212,19 +49212,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4043</v>
+        <v>0.4042</v>
       </c>
       <c r="C142" t="n">
         <v>-0.362</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2577</v>
+        <v>0.2574</v>
       </c>
       <c r="E142" t="n">
         <v>0.4409</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2577</v>
+        <v>0.2574</v>
       </c>
       <c r="G142" t="n">
         <v>0.8164</v>
@@ -49252,13 +49252,13 @@
         <v>-0.347</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3536</v>
+        <v>0.3533</v>
       </c>
       <c r="E143" t="n">
         <v>0.4544</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3536</v>
+        <v>0.3533</v>
       </c>
       <c r="G143" t="n">
         <v>0.7828000000000001</v>
@@ -49280,19 +49280,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4876</v>
+        <v>0.4875</v>
       </c>
       <c r="C144" t="n">
         <v>-0.359</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3333</v>
+        <v>0.333</v>
       </c>
       <c r="E144" t="n">
         <v>0.5261</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3333</v>
+        <v>0.333</v>
       </c>
       <c r="G144" t="n">
         <v>0.8556</v>
@@ -49314,7 +49314,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5885</v>
+        <v>0.5884</v>
       </c>
       <c r="C145" t="n">
         <v>-0.438</v>
@@ -49348,19 +49348,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5411</v>
+        <v>0.541</v>
       </c>
       <c r="C146" t="n">
         <v>-0.439</v>
       </c>
       <c r="D146" t="n">
-        <v>0.5053</v>
+        <v>0.5052</v>
       </c>
       <c r="E146" t="n">
         <v>0.55</v>
       </c>
       <c r="F146" t="n">
-        <v>0.5053</v>
+        <v>0.5052</v>
       </c>
       <c r="G146" t="n">
         <v>0.7677</v>
@@ -49382,19 +49382,19 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5911</v>
+        <v>0.591</v>
       </c>
       <c r="C147" t="n">
         <v>-0.432</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5476</v>
+        <v>0.5475</v>
       </c>
       <c r="E147" t="n">
         <v>0.6019</v>
       </c>
       <c r="F147" t="n">
-        <v>0.5476</v>
+        <v>0.5475</v>
       </c>
       <c r="G147" t="n">
         <v>0.9043</v>
@@ -49422,13 +49422,13 @@
         <v>-0.456</v>
       </c>
       <c r="D148" t="n">
-        <v>0.6009</v>
+        <v>0.6008</v>
       </c>
       <c r="E148" t="n">
         <v>0.5772</v>
       </c>
       <c r="F148" t="n">
-        <v>0.6009</v>
+        <v>0.6008</v>
       </c>
       <c r="G148" t="n">
         <v>0.7965</v>
@@ -49456,13 +49456,13 @@
         <v>-0.468</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5851</v>
+        <v>0.585</v>
       </c>
       <c r="E149" t="n">
         <v>0.5599</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5851</v>
+        <v>0.585</v>
       </c>
       <c r="G149" t="n">
         <v>0.7799</v>
@@ -49490,13 +49490,13 @@
         <v>-0.467</v>
       </c>
       <c r="D150" t="n">
-        <v>0.614</v>
+        <v>0.6139</v>
       </c>
       <c r="E150" t="n">
         <v>0.6309</v>
       </c>
       <c r="F150" t="n">
-        <v>0.614</v>
+        <v>0.6139</v>
       </c>
       <c r="G150" t="n">
         <v>0.9247</v>
@@ -49524,13 +49524,13 @@
         <v>-0.547</v>
       </c>
       <c r="D151" t="n">
-        <v>0.5951</v>
+        <v>0.595</v>
       </c>
       <c r="E151" t="n">
         <v>0.6359</v>
       </c>
       <c r="F151" t="n">
-        <v>0.5951</v>
+        <v>0.595</v>
       </c>
       <c r="G151" t="n">
         <v>0.7832</v>
@@ -49592,13 +49592,13 @@
         <v>-0.54</v>
       </c>
       <c r="D153" t="n">
-        <v>0.7339</v>
+        <v>0.734</v>
       </c>
       <c r="E153" t="n">
         <v>0.6584</v>
       </c>
       <c r="F153" t="n">
-        <v>0.7339</v>
+        <v>0.734</v>
       </c>
       <c r="G153" t="n">
         <v>0.8381</v>
@@ -49660,13 +49660,13 @@
         <v>-0.408</v>
       </c>
       <c r="D155" t="n">
-        <v>0.7769</v>
+        <v>0.777</v>
       </c>
       <c r="E155" t="n">
         <v>0.6345</v>
       </c>
       <c r="F155" t="n">
-        <v>0.7769</v>
+        <v>0.777</v>
       </c>
       <c r="G155" t="n">
         <v>0.6347</v>
@@ -49694,13 +49694,13 @@
         <v>-0.419</v>
       </c>
       <c r="D156" t="n">
-        <v>0.8369</v>
+        <v>0.837</v>
       </c>
       <c r="E156" t="n">
         <v>0.6259</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8369</v>
+        <v>0.837</v>
       </c>
       <c r="G156" t="n">
         <v>0.6131</v>
@@ -49722,19 +49722,19 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6942</v>
       </c>
       <c r="C157" t="n">
         <v>-0.527</v>
       </c>
       <c r="D157" t="n">
-        <v>0.7795</v>
+        <v>0.7796</v>
       </c>
       <c r="E157" t="n">
         <v>0.6728</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7795</v>
+        <v>0.7796</v>
       </c>
       <c r="G157" t="n">
         <v>0.6994</v>
@@ -49762,13 +49762,13 @@
         <v>-0.525</v>
       </c>
       <c r="D158" t="n">
-        <v>0.7729</v>
+        <v>0.773</v>
       </c>
       <c r="E158" t="n">
         <v>0.71</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7729</v>
+        <v>0.773</v>
       </c>
       <c r="G158" t="n">
         <v>0.719</v>
@@ -49777,7 +49777,7 @@
         <v>1.1559</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0772</v>
+        <v>0.0771</v>
       </c>
       <c r="J158" t="n">
         <v>0.8881</v>
@@ -49796,13 +49796,13 @@
         <v>-0.527</v>
       </c>
       <c r="D159" t="n">
-        <v>0.8692</v>
+        <v>0.8693</v>
       </c>
       <c r="E159" t="n">
         <v>0.7010999999999999</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8692</v>
+        <v>0.8693</v>
       </c>
       <c r="G159" t="n">
         <v>0.8106</v>
@@ -49830,13 +49830,13 @@
         <v>-0.5669999999999999</v>
       </c>
       <c r="D160" t="n">
-        <v>0.7827</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="E160" t="n">
         <v>0.7102000000000001</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7827</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="G160" t="n">
         <v>0.7661</v>
@@ -49898,13 +49898,13 @@
         <v>-0.5659999999999999</v>
       </c>
       <c r="D162" t="n">
-        <v>0.7341</v>
+        <v>0.7342</v>
       </c>
       <c r="E162" t="n">
         <v>0.75</v>
       </c>
       <c r="F162" t="n">
-        <v>0.7341</v>
+        <v>0.7342</v>
       </c>
       <c r="G162" t="n">
         <v>0.7776</v>
@@ -49926,19 +49926,19 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.7335</v>
+        <v>0.7336</v>
       </c>
       <c r="C163" t="n">
         <v>-0.615</v>
       </c>
       <c r="D163" t="n">
-        <v>0.777</v>
+        <v>0.7771</v>
       </c>
       <c r="E163" t="n">
         <v>0.7227</v>
       </c>
       <c r="F163" t="n">
-        <v>0.777</v>
+        <v>0.7771</v>
       </c>
       <c r="G163" t="n">
         <v>0.5893</v>
@@ -49994,19 +49994,19 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7473</v>
+        <v>0.7474</v>
       </c>
       <c r="C165" t="n">
         <v>-0.603</v>
       </c>
       <c r="D165" t="n">
-        <v>0.8058</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="E165" t="n">
         <v>0.7327</v>
       </c>
       <c r="F165" t="n">
-        <v>0.8058</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="G165" t="n">
         <v>0.5364</v>
@@ -50034,13 +50034,13 @@
         <v>-0.472</v>
       </c>
       <c r="D166" t="n">
-        <v>0.8032</v>
+        <v>0.8033</v>
       </c>
       <c r="E166" t="n">
         <v>0.7669</v>
       </c>
       <c r="F166" t="n">
-        <v>0.8032</v>
+        <v>0.8033</v>
       </c>
       <c r="G166" t="n">
         <v>0.6328</v>
@@ -50062,19 +50062,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.7597</v>
+        <v>0.7598</v>
       </c>
       <c r="C167" t="n">
         <v>-0.473</v>
       </c>
       <c r="D167" t="n">
-        <v>0.8495</v>
+        <v>0.8496</v>
       </c>
       <c r="E167" t="n">
         <v>0.7373</v>
       </c>
       <c r="F167" t="n">
-        <v>0.8495</v>
+        <v>0.8496</v>
       </c>
       <c r="G167" t="n">
         <v>0.5076000000000001</v>
@@ -50102,13 +50102,13 @@
         <v>-0.483</v>
       </c>
       <c r="D168" t="n">
-        <v>0.8164</v>
+        <v>0.8165</v>
       </c>
       <c r="E168" t="n">
         <v>0.7743</v>
       </c>
       <c r="F168" t="n">
-        <v>0.8164</v>
+        <v>0.8165</v>
       </c>
       <c r="G168" t="n">
         <v>0.663</v>
@@ -50238,13 +50238,13 @@
         <v>-0.463</v>
       </c>
       <c r="D172" t="n">
-        <v>0.7993</v>
+        <v>0.7994</v>
       </c>
       <c r="E172" t="n">
         <v>0.7703</v>
       </c>
       <c r="F172" t="n">
-        <v>0.7993</v>
+        <v>0.7994</v>
       </c>
       <c r="G172" t="n">
         <v>0.6287</v>
@@ -50266,19 +50266,19 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.7651</v>
+        <v>0.7652</v>
       </c>
       <c r="C173" t="n">
         <v>-0.487</v>
       </c>
       <c r="D173" t="n">
-        <v>0.8366</v>
+        <v>0.8367</v>
       </c>
       <c r="E173" t="n">
         <v>0.7473</v>
       </c>
       <c r="F173" t="n">
-        <v>0.8366</v>
+        <v>0.8367</v>
       </c>
       <c r="G173" t="n">
         <v>0.5442</v>
@@ -50306,13 +50306,13 @@
         <v>-0.469</v>
       </c>
       <c r="D174" t="n">
-        <v>0.7541</v>
+        <v>0.7542</v>
       </c>
       <c r="E174" t="n">
         <v>0.7972</v>
       </c>
       <c r="F174" t="n">
-        <v>0.7541</v>
+        <v>0.7542</v>
       </c>
       <c r="G174" t="n">
         <v>0.7018</v>
@@ -50476,13 +50476,13 @@
         <v>-0.346</v>
       </c>
       <c r="D179" t="n">
-        <v>0.6655</v>
+        <v>0.6654</v>
       </c>
       <c r="E179" t="n">
         <v>0.7351</v>
       </c>
       <c r="F179" t="n">
-        <v>0.6655</v>
+        <v>0.6654</v>
       </c>
       <c r="G179" t="n">
         <v>0.4753</v>
@@ -50544,13 +50544,13 @@
         <v>-0.307</v>
       </c>
       <c r="D181" t="n">
-        <v>0.5618</v>
+        <v>0.5617</v>
       </c>
       <c r="E181" t="n">
         <v>0.7447</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5618</v>
+        <v>0.5617</v>
       </c>
       <c r="G181" t="n">
         <v>0.4245</v>
@@ -50680,13 +50680,13 @@
         <v>-0.044</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3989</v>
+        <v>0.3986</v>
       </c>
       <c r="E185" t="n">
         <v>0.7437</v>
       </c>
       <c r="F185" t="n">
-        <v>0.3989</v>
+        <v>0.3986</v>
       </c>
       <c r="G185" t="n">
         <v>0.6528</v>
@@ -50714,13 +50714,13 @@
         <v>-0.055</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3986</v>
+        <v>0.3984</v>
       </c>
       <c r="E186" t="n">
         <v>0.7654</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3986</v>
+        <v>0.3984</v>
       </c>
       <c r="G186" t="n">
         <v>0.7107</v>
@@ -50742,19 +50742,19 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5366</v>
+        <v>0.5365</v>
       </c>
       <c r="C187" t="n">
         <v>0.119</v>
       </c>
       <c r="D187" t="n">
-        <v>0.3924</v>
+        <v>0.3922</v>
       </c>
       <c r="E187" t="n">
         <v>0.5726</v>
       </c>
       <c r="F187" t="n">
-        <v>0.3924</v>
+        <v>0.3922</v>
       </c>
       <c r="G187" t="n">
         <v>0.4566</v>
@@ -50776,19 +50776,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.4863</v>
+        <v>0.4862</v>
       </c>
       <c r="C188" t="n">
         <v>0.139</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4358</v>
+        <v>0.4356</v>
       </c>
       <c r="E188" t="n">
         <v>0.4989</v>
       </c>
       <c r="F188" t="n">
-        <v>0.4358</v>
+        <v>0.4356</v>
       </c>
       <c r="G188" t="n">
         <v>0.3895</v>
@@ -50810,19 +50810,19 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.4069</v>
+        <v>0.4068</v>
       </c>
       <c r="C189" t="n">
         <v>0.132</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2499</v>
+        <v>0.2496</v>
       </c>
       <c r="E189" t="n">
         <v>0.4462</v>
       </c>
       <c r="F189" t="n">
-        <v>0.2499</v>
+        <v>0.2496</v>
       </c>
       <c r="G189" t="n">
         <v>0.4397</v>
@@ -50844,19 +50844,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3733</v>
+        <v>0.3732</v>
       </c>
       <c r="C190" t="n">
         <v>0.067</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2573</v>
+        <v>0.257</v>
       </c>
       <c r="E190" t="n">
         <v>0.4022</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2573</v>
+        <v>0.257</v>
       </c>
       <c r="G190" t="n">
         <v>0.3498</v>
@@ -50878,19 +50878,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.304</v>
+        <v>0.3039</v>
       </c>
       <c r="C191" t="n">
         <v>0.101</v>
       </c>
       <c r="D191" t="n">
-        <v>0.0825</v>
+        <v>0.082</v>
       </c>
       <c r="E191" t="n">
         <v>0.3594</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0825</v>
+        <v>0.082</v>
       </c>
       <c r="G191" t="n">
         <v>0.3937</v>
@@ -50912,19 +50912,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.348</v>
+        <v>0.3479</v>
       </c>
       <c r="C192" t="n">
         <v>0.089</v>
       </c>
       <c r="D192" t="n">
-        <v>0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="E192" t="n">
         <v>0.4349</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0002</v>
+        <v>-0.0004</v>
       </c>
       <c r="G192" t="n">
         <v>0.8068</v>
@@ -50946,19 +50946,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2879</v>
+        <v>0.2878</v>
       </c>
       <c r="C193" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1266</v>
+        <v>0.1261</v>
       </c>
       <c r="E193" t="n">
         <v>0.3283</v>
       </c>
       <c r="F193" t="n">
-        <v>0.1266</v>
+        <v>0.1261</v>
       </c>
       <c r="G193" t="n">
         <v>0.5551</v>
@@ -50980,19 +50980,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2862</v>
+        <v>0.2861</v>
       </c>
       <c r="C194" t="n">
         <v>0.093</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1212</v>
+        <v>0.1208</v>
       </c>
       <c r="E194" t="n">
         <v>0.3274</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1212</v>
+        <v>0.1208</v>
       </c>
       <c r="G194" t="n">
         <v>0.7625999999999999</v>
@@ -51014,19 +51014,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.2277</v>
+        <v>0.2276</v>
       </c>
       <c r="C195" t="n">
         <v>0.094</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1951</v>
+        <v>0.1947</v>
       </c>
       <c r="E195" t="n">
         <v>0.2359</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1951</v>
+        <v>0.1947</v>
       </c>
       <c r="G195" t="n">
         <v>0.6114000000000001</v>
@@ -51048,19 +51048,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2639</v>
+        <v>0.2638</v>
       </c>
       <c r="C196" t="n">
         <v>-0.08500000000000001</v>
       </c>
       <c r="D196" t="n">
-        <v>0.2427</v>
+        <v>0.2423</v>
       </c>
       <c r="E196" t="n">
         <v>0.2692</v>
       </c>
       <c r="F196" t="n">
-        <v>0.2427</v>
+        <v>0.2423</v>
       </c>
       <c r="G196" t="n">
         <v>0.628</v>
@@ -51082,19 +51082,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2049</v>
+        <v>0.2048</v>
       </c>
       <c r="C197" t="n">
         <v>-0.08</v>
       </c>
       <c r="D197" t="n">
-        <v>0.0731</v>
+        <v>0.0726</v>
       </c>
       <c r="E197" t="n">
         <v>0.2378</v>
       </c>
       <c r="F197" t="n">
-        <v>0.0731</v>
+        <v>0.0726</v>
       </c>
       <c r="G197" t="n">
         <v>0.7431</v>
@@ -51116,19 +51116,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.2157</v>
+        <v>0.2156</v>
       </c>
       <c r="C198" t="n">
         <v>-0.08500000000000001</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1602</v>
+        <v>0.1598</v>
       </c>
       <c r="E198" t="n">
         <v>0.2295</v>
       </c>
       <c r="F198" t="n">
-        <v>0.1602</v>
+        <v>0.1598</v>
       </c>
       <c r="G198" t="n">
         <v>0.9534</v>
@@ -51150,19 +51150,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1667</v>
+        <v>0.1666</v>
       </c>
       <c r="C199" t="n">
         <v>-0.283</v>
       </c>
       <c r="D199" t="n">
-        <v>0.2048</v>
+        <v>0.2044</v>
       </c>
       <c r="E199" t="n">
         <v>0.1572</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2048</v>
+        <v>0.2044</v>
       </c>
       <c r="G199" t="n">
         <v>0.6985</v>
@@ -51190,13 +51190,13 @@
         <v>-0.29</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3394</v>
+        <v>0.3391</v>
       </c>
       <c r="E200" t="n">
         <v>0.1787</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3394</v>
+        <v>0.3391</v>
       </c>
       <c r="G200" t="n">
         <v>0.7856</v>
@@ -51218,19 +51218,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2451</v>
+        <v>0.245</v>
       </c>
       <c r="C201" t="n">
         <v>-0.288</v>
       </c>
       <c r="D201" t="n">
-        <v>0.429</v>
+        <v>0.4287</v>
       </c>
       <c r="E201" t="n">
         <v>0.1991</v>
       </c>
       <c r="F201" t="n">
-        <v>0.429</v>
+        <v>0.4287</v>
       </c>
       <c r="G201" t="n">
         <v>0.8132</v>
@@ -51258,13 +51258,13 @@
         <v>-0.388</v>
       </c>
       <c r="D202" t="n">
-        <v>0.4631</v>
+        <v>0.4629</v>
       </c>
       <c r="E202" t="n">
         <v>0.217</v>
       </c>
       <c r="F202" t="n">
-        <v>0.4631</v>
+        <v>0.4629</v>
       </c>
       <c r="G202" t="n">
         <v>0.749</v>
@@ -51292,13 +51292,13 @@
         <v>-0.393</v>
       </c>
       <c r="D203" t="n">
-        <v>0.5001</v>
+        <v>0.5</v>
       </c>
       <c r="E203" t="n">
         <v>0.2521</v>
       </c>
       <c r="F203" t="n">
-        <v>0.5001</v>
+        <v>0.5</v>
       </c>
       <c r="G203" t="n">
         <v>0.7614</v>
@@ -51326,13 +51326,13 @@
         <v>-0.406</v>
       </c>
       <c r="D204" t="n">
-        <v>0.6373</v>
+        <v>0.6372</v>
       </c>
       <c r="E204" t="n">
         <v>0.3099</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6373</v>
+        <v>0.6372</v>
       </c>
       <c r="G204" t="n">
         <v>0.8678</v>
@@ -51354,19 +51354,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.575</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8159999999999999</v>
       </c>
       <c r="D205" t="n">
-        <v>1.7563</v>
+        <v>1.7571</v>
       </c>
       <c r="E205" t="n">
         <v>0.2796</v>
       </c>
       <c r="F205" t="n">
-        <v>1.7563</v>
+        <v>1.7571</v>
       </c>
       <c r="G205" t="n">
         <v>0.7884</v>
@@ -51394,13 +51394,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="D206" t="n">
-        <v>0.526</v>
+        <v>0.5259</v>
       </c>
       <c r="E206" t="n">
         <v>0.2687</v>
       </c>
       <c r="F206" t="n">
-        <v>0.526</v>
+        <v>0.5259</v>
       </c>
       <c r="G206" t="n">
         <v>0.7327</v>
@@ -51428,13 +51428,13 @@
         <v>-0.8080000000000001</v>
       </c>
       <c r="D207" t="n">
-        <v>0.6431</v>
+        <v>0.643</v>
       </c>
       <c r="E207" t="n">
         <v>0.3529</v>
       </c>
       <c r="F207" t="n">
-        <v>0.6431</v>
+        <v>0.643</v>
       </c>
       <c r="G207" t="n">
         <v>0.9666</v>
@@ -51490,19 +51490,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5602</v>
+        <v>0.5603</v>
       </c>
       <c r="C209" t="n">
         <v>-1.483</v>
       </c>
       <c r="D209" t="n">
-        <v>1.2981</v>
+        <v>1.2986</v>
       </c>
       <c r="E209" t="n">
         <v>0.3757</v>
       </c>
       <c r="F209" t="n">
-        <v>1.2981</v>
+        <v>1.2986</v>
       </c>
       <c r="G209" t="n">
         <v>0.9678</v>
@@ -51524,19 +51524,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.574</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="C210" t="n">
         <v>-1.489</v>
       </c>
       <c r="D210" t="n">
-        <v>1.2952</v>
+        <v>1.2956</v>
       </c>
       <c r="E210" t="n">
         <v>0.3937</v>
       </c>
       <c r="F210" t="n">
-        <v>1.2952</v>
+        <v>1.2956</v>
       </c>
       <c r="G210" t="n">
         <v>1.014</v>
@@ -51558,19 +51558,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.5879</v>
+        <v>0.588</v>
       </c>
       <c r="C211" t="n">
         <v>-2.09</v>
       </c>
       <c r="D211" t="n">
-        <v>1.3414</v>
+        <v>1.3419</v>
       </c>
       <c r="E211" t="n">
         <v>0.3995</v>
       </c>
       <c r="F211" t="n">
-        <v>1.3414</v>
+        <v>1.3419</v>
       </c>
       <c r="G211" t="n">
         <v>0.7933</v>
@@ -51592,19 +51592,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6544</v>
+        <v>0.6545</v>
       </c>
       <c r="C212" t="n">
         <v>-2.064</v>
       </c>
       <c r="D212" t="n">
-        <v>1.4357</v>
+        <v>1.4363</v>
       </c>
       <c r="E212" t="n">
         <v>0.4591</v>
       </c>
       <c r="F212" t="n">
-        <v>1.4357</v>
+        <v>1.4363</v>
       </c>
       <c r="G212" t="n">
         <v>0.9588</v>
@@ -51626,19 +51626,19 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7023</v>
+        <v>0.7025</v>
       </c>
       <c r="C213" t="n">
         <v>-2.07</v>
       </c>
       <c r="D213" t="n">
-        <v>1.5662</v>
+        <v>1.5668</v>
       </c>
       <c r="E213" t="n">
         <v>0.4864</v>
       </c>
       <c r="F213" t="n">
-        <v>1.5662</v>
+        <v>1.5668</v>
       </c>
       <c r="G213" t="n">
         <v>0.9696</v>
@@ -51660,19 +51660,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.7237</v>
+        <v>0.7239</v>
       </c>
       <c r="C214" t="n">
         <v>-2.284</v>
       </c>
       <c r="D214" t="n">
-        <v>1.7317</v>
+        <v>1.7325</v>
       </c>
       <c r="E214" t="n">
         <v>0.4717</v>
       </c>
       <c r="F214" t="n">
-        <v>1.7317</v>
+        <v>1.7325</v>
       </c>
       <c r="G214" t="n">
         <v>0.8554</v>
@@ -51694,19 +51694,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.7722</v>
+        <v>0.7724</v>
       </c>
       <c r="C215" t="n">
         <v>-2.285</v>
       </c>
       <c r="D215" t="n">
-        <v>1.8952</v>
+        <v>1.8962</v>
       </c>
       <c r="E215" t="n">
         <v>0.4915</v>
       </c>
       <c r="F215" t="n">
-        <v>1.8952</v>
+        <v>1.8962</v>
       </c>
       <c r="G215" t="n">
         <v>0.9341</v>
@@ -51728,19 +51728,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8099</v>
+        <v>0.8101</v>
       </c>
       <c r="C216" t="n">
         <v>-2.302</v>
       </c>
       <c r="D216" t="n">
-        <v>1.9742</v>
+        <v>1.9752</v>
       </c>
       <c r="E216" t="n">
         <v>0.5188</v>
       </c>
       <c r="F216" t="n">
-        <v>1.9742</v>
+        <v>1.9752</v>
       </c>
       <c r="G216" t="n">
         <v>1.0459</v>
@@ -51762,19 +51762,19 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.6284</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="C217" t="n">
         <v>-2.379</v>
       </c>
       <c r="D217" t="n">
-        <v>1.5625</v>
+        <v>1.5631</v>
       </c>
       <c r="E217" t="n">
         <v>0.3949</v>
       </c>
       <c r="F217" t="n">
-        <v>1.5625</v>
+        <v>1.5631</v>
       </c>
       <c r="G217" t="n">
         <v>0.7469</v>
@@ -51796,19 +51796,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.7315</v>
+        <v>0.7317</v>
       </c>
       <c r="C218" t="n">
         <v>-2.333</v>
       </c>
       <c r="D218" t="n">
-        <v>2.1405</v>
+        <v>2.1416</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3793</v>
+        <v>0.3792</v>
       </c>
       <c r="F218" t="n">
-        <v>2.1405</v>
+        <v>2.1416</v>
       </c>
       <c r="G218" t="n">
         <v>0.7917999999999999</v>
@@ -51830,19 +51830,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.7095</v>
+        <v>0.7097</v>
       </c>
       <c r="C219" t="n">
         <v>-2.332</v>
       </c>
       <c r="D219" t="n">
-        <v>1.6766</v>
+        <v>1.6773</v>
       </c>
       <c r="E219" t="n">
         <v>0.4678</v>
       </c>
       <c r="F219" t="n">
-        <v>1.6766</v>
+        <v>1.6773</v>
       </c>
       <c r="G219" t="n">
         <v>0.9134</v>
@@ -51864,19 +51864,19 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6942</v>
       </c>
       <c r="C220" t="n">
         <v>-2.405</v>
       </c>
       <c r="D220" t="n">
-        <v>1.74</v>
+        <v>1.7408</v>
       </c>
       <c r="E220" t="n">
         <v>0.4326</v>
       </c>
       <c r="F220" t="n">
-        <v>1.74</v>
+        <v>1.7408</v>
       </c>
       <c r="G220" t="n">
         <v>0.8136</v>
@@ -51898,19 +51898,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.7123</v>
+        <v>0.7125</v>
       </c>
       <c r="C221" t="n">
         <v>-2.403</v>
       </c>
       <c r="D221" t="n">
-        <v>1.811</v>
+        <v>1.8118</v>
       </c>
       <c r="E221" t="n">
         <v>0.4376</v>
       </c>
       <c r="F221" t="n">
-        <v>1.811</v>
+        <v>1.8118</v>
       </c>
       <c r="G221" t="n">
         <v>0.827</v>
@@ -51919,7 +51919,7 @@
         <v>-0.0495</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7992</v>
+        <v>0.7991</v>
       </c>
       <c r="J221" t="n">
         <v>0.1739</v>
@@ -51932,19 +51932,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.7568</v>
       </c>
       <c r="C222" t="n">
         <v>-2.439</v>
       </c>
       <c r="D222" t="n">
-        <v>1.7246</v>
+        <v>1.7254</v>
       </c>
       <c r="E222" t="n">
         <v>0.5145999999999999</v>
       </c>
       <c r="F222" t="n">
-        <v>1.7246</v>
+        <v>1.7254</v>
       </c>
       <c r="G222" t="n">
         <v>1.0101</v>
@@ -51966,19 +51966,19 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.7961</v>
+        <v>0.7963</v>
       </c>
       <c r="C223" t="n">
         <v>-2.155</v>
       </c>
       <c r="D223" t="n">
-        <v>1.7748</v>
+        <v>1.7757</v>
       </c>
       <c r="E223" t="n">
         <v>0.5515</v>
       </c>
       <c r="F223" t="n">
-        <v>1.7748</v>
+        <v>1.7757</v>
       </c>
       <c r="G223" t="n">
         <v>0.8245</v>
@@ -52000,19 +52000,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8148</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
       </c>
       <c r="D224" t="n">
-        <v>1.6971</v>
+        <v>1.6979</v>
       </c>
       <c r="E224" t="n">
         <v>0.5942</v>
       </c>
       <c r="F224" t="n">
-        <v>1.6971</v>
+        <v>1.6979</v>
       </c>
       <c r="G224" t="n">
         <v>0.9198</v>
@@ -52034,19 +52034,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.8156</v>
+        <v>0.8157</v>
       </c>
       <c r="C225" t="n">
         <v>-2.152</v>
       </c>
       <c r="D225" t="n">
-        <v>1.6708</v>
+        <v>1.6715</v>
       </c>
       <c r="E225" t="n">
         <v>0.6018</v>
       </c>
       <c r="F225" t="n">
-        <v>1.6708</v>
+        <v>1.6715</v>
       </c>
       <c r="G225" t="n">
         <v>0.9356</v>
@@ -52068,19 +52068,19 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.7083</v>
+        <v>0.7084</v>
       </c>
       <c r="C226" t="n">
         <v>-2.088</v>
       </c>
       <c r="D226" t="n">
-        <v>1.4774</v>
+        <v>1.478</v>
       </c>
       <c r="E226" t="n">
         <v>0.516</v>
       </c>
       <c r="F226" t="n">
-        <v>1.4774</v>
+        <v>1.478</v>
       </c>
       <c r="G226" t="n">
         <v>0.5645</v>
@@ -52102,19 +52102,19 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.7618</v>
+        <v>0.7619</v>
       </c>
       <c r="C227" t="n">
         <v>-2.054</v>
       </c>
       <c r="D227" t="n">
-        <v>1.5261</v>
+        <v>1.5267</v>
       </c>
       <c r="E227" t="n">
         <v>0.5707</v>
       </c>
       <c r="F227" t="n">
-        <v>1.5261</v>
+        <v>1.5267</v>
       </c>
       <c r="G227" t="n">
         <v>0.7912</v>
@@ -52123,7 +52123,7 @@
         <v>-0.0499</v>
       </c>
       <c r="I227" t="n">
-        <v>1.231</v>
+        <v>1.2309</v>
       </c>
       <c r="J227" t="n">
         <v>0.3104</v>
@@ -52136,19 +52136,19 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.8063</v>
+        <v>0.8064</v>
       </c>
       <c r="C228" t="n">
         <v>-2.049</v>
       </c>
       <c r="D228" t="n">
-        <v>1.3816</v>
+        <v>1.3821</v>
       </c>
       <c r="E228" t="n">
         <v>0.6625</v>
       </c>
       <c r="F228" t="n">
-        <v>1.3816</v>
+        <v>1.3821</v>
       </c>
       <c r="G228" t="n">
         <v>0.9902</v>
@@ -52170,19 +52170,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.7786</v>
+        <v>0.7788</v>
       </c>
       <c r="C229" t="n">
         <v>-1.989</v>
       </c>
       <c r="D229" t="n">
-        <v>1.4513</v>
+        <v>1.4519</v>
       </c>
       <c r="E229" t="n">
         <v>0.6105</v>
       </c>
       <c r="F229" t="n">
-        <v>1.4513</v>
+        <v>1.4519</v>
       </c>
       <c r="G229" t="n">
         <v>0.7983</v>
@@ -52210,13 +52210,13 @@
         <v>-1.991</v>
       </c>
       <c r="D230" t="n">
-        <v>1.1744</v>
+        <v>1.1747</v>
       </c>
       <c r="E230" t="n">
         <v>0.6785</v>
       </c>
       <c r="F230" t="n">
-        <v>1.1744</v>
+        <v>1.1747</v>
       </c>
       <c r="G230" t="n">
         <v>0.8498</v>
@@ -52238,19 +52238,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8433</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
       </c>
       <c r="D231" t="n">
-        <v>1.4903</v>
+        <v>1.4909</v>
       </c>
       <c r="E231" t="n">
         <v>0.6815</v>
       </c>
       <c r="F231" t="n">
-        <v>1.4903</v>
+        <v>1.4909</v>
       </c>
       <c r="G231" t="n">
         <v>0.8058999999999999</v>
@@ -52272,19 +52272,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7923</v>
+        <v>0.7924</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
       </c>
       <c r="D232" t="n">
-        <v>1.3836</v>
+        <v>1.3842</v>
       </c>
       <c r="E232" t="n">
         <v>0.6444</v>
       </c>
       <c r="F232" t="n">
-        <v>1.3836</v>
+        <v>1.3842</v>
       </c>
       <c r="G232" t="n">
         <v>0.6032999999999999</v>
@@ -52306,19 +52306,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.7921</v>
+        <v>0.7922</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
       </c>
       <c r="D233" t="n">
-        <v>1.1824</v>
+        <v>1.1828</v>
       </c>
       <c r="E233" t="n">
         <v>0.6945</v>
       </c>
       <c r="F233" t="n">
-        <v>1.1824</v>
+        <v>1.1828</v>
       </c>
       <c r="G233" t="n">
         <v>0.5891</v>
@@ -52340,19 +52340,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8867</v>
+        <v>0.8868</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
       </c>
       <c r="D234" t="n">
-        <v>1.2978</v>
+        <v>1.2983</v>
       </c>
       <c r="E234" t="n">
         <v>0.7839</v>
       </c>
       <c r="F234" t="n">
-        <v>1.2978</v>
+        <v>1.2983</v>
       </c>
       <c r="G234" t="n">
         <v>0.8854</v>
@@ -52361,7 +52361,7 @@
         <v>0.0287</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6426</v>
+        <v>1.6425</v>
       </c>
       <c r="J234" t="n">
         <v>0.579</v>
@@ -52374,19 +52374,19 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8202</v>
       </c>
       <c r="C235" t="n">
         <v>-1.935</v>
       </c>
       <c r="D235" t="n">
-        <v>1.3367</v>
+        <v>1.3372</v>
       </c>
       <c r="E235" t="n">
         <v>0.6909</v>
       </c>
       <c r="F235" t="n">
-        <v>1.3367</v>
+        <v>1.3372</v>
       </c>
       <c r="G235" t="n">
         <v>0.4561</v>
@@ -52408,19 +52408,19 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8531</v>
+        <v>0.8532</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
       </c>
       <c r="D236" t="n">
-        <v>1.3711</v>
+        <v>1.3716</v>
       </c>
       <c r="E236" t="n">
         <v>0.7236</v>
       </c>
       <c r="F236" t="n">
-        <v>1.3711</v>
+        <v>1.3716</v>
       </c>
       <c r="G236" t="n">
         <v>0.4962</v>
@@ -52442,19 +52442,19 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.8587</v>
+        <v>0.8588</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
       </c>
       <c r="D237" t="n">
-        <v>1.4207</v>
+        <v>1.4213</v>
       </c>
       <c r="E237" t="n">
         <v>0.7181999999999999</v>
       </c>
       <c r="F237" t="n">
-        <v>1.4207</v>
+        <v>1.4213</v>
       </c>
       <c r="G237" t="n">
         <v>0.6461</v>
@@ -52476,19 +52476,19 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7268</v>
+        <v>0.7269</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
       </c>
       <c r="D238" t="n">
-        <v>1.2146</v>
+        <v>1.2149</v>
       </c>
       <c r="E238" t="n">
         <v>0.6048</v>
       </c>
       <c r="F238" t="n">
-        <v>1.2146</v>
+        <v>1.2149</v>
       </c>
       <c r="G238" t="n">
         <v>0.231</v>
@@ -52510,19 +52510,19 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7518</v>
+        <v>0.7519</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
       </c>
       <c r="D239" t="n">
-        <v>1.1457</v>
+        <v>1.146</v>
       </c>
       <c r="E239" t="n">
         <v>0.6533</v>
       </c>
       <c r="F239" t="n">
-        <v>1.1457</v>
+        <v>1.146</v>
       </c>
       <c r="G239" t="n">
         <v>0.2812</v>
@@ -52544,19 +52544,19 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8131</v>
       </c>
       <c r="C240" t="n">
         <v>-1.795</v>
       </c>
       <c r="D240" t="n">
-        <v>1.2522</v>
+        <v>1.2526</v>
       </c>
       <c r="E240" t="n">
         <v>0.7032</v>
       </c>
       <c r="F240" t="n">
-        <v>1.2522</v>
+        <v>1.2526</v>
       </c>
       <c r="G240" t="n">
         <v>0.2989</v>
@@ -52578,19 +52578,19 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.736</v>
+        <v>0.7361</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
       </c>
       <c r="D241" t="n">
-        <v>1.293</v>
+        <v>1.2935</v>
       </c>
       <c r="E241" t="n">
         <v>0.5968</v>
       </c>
       <c r="F241" t="n">
-        <v>1.293</v>
+        <v>1.2935</v>
       </c>
       <c r="G241" t="n">
         <v>-0.1409</v>
@@ -52599,7 +52599,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7731</v>
+        <v>1.773</v>
       </c>
       <c r="J241" t="n">
         <v>0.7578</v>
@@ -52612,19 +52612,19 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.7978</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="C242" t="n">
         <v>-1.726</v>
       </c>
       <c r="D242" t="n">
-        <v>1.4351</v>
+        <v>1.4356</v>
       </c>
       <c r="E242" t="n">
         <v>0.6385</v>
       </c>
       <c r="F242" t="n">
-        <v>1.4351</v>
+        <v>1.4356</v>
       </c>
       <c r="G242" t="n">
         <v>-0.06419999999999999</v>
@@ -52646,19 +52646,19 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.7639</v>
+        <v>0.764</v>
       </c>
       <c r="C243" t="n">
         <v>-1.541</v>
       </c>
       <c r="D243" t="n">
-        <v>1.3061</v>
+        <v>1.3065</v>
       </c>
       <c r="E243" t="n">
         <v>0.6284</v>
       </c>
       <c r="F243" t="n">
-        <v>1.3061</v>
+        <v>1.3065</v>
       </c>
       <c r="G243" t="n">
         <v>-0.053</v>
@@ -52686,13 +52686,13 @@
         <v>-1.645</v>
       </c>
       <c r="D244" t="n">
-        <v>1.3528</v>
+        <v>1.3533</v>
       </c>
       <c r="E244" t="n">
         <v>0.4822</v>
       </c>
       <c r="F244" t="n">
-        <v>1.3528</v>
+        <v>1.3533</v>
       </c>
       <c r="G244" t="n">
         <v>-0.4456</v>
@@ -52714,19 +52714,19 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.7027</v>
+        <v>0.7028</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
       </c>
       <c r="D245" t="n">
-        <v>1.5766</v>
+        <v>1.5772</v>
       </c>
       <c r="E245" t="n">
         <v>0.4842</v>
       </c>
       <c r="F245" t="n">
-        <v>1.5766</v>
+        <v>1.5772</v>
       </c>
       <c r="G245" t="n">
         <v>-0.3835</v>
@@ -52748,19 +52748,19 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.7794</v>
+        <v>0.7795</v>
       </c>
       <c r="C246" t="n">
         <v>-1.645</v>
       </c>
       <c r="D246" t="n">
-        <v>1.5802</v>
+        <v>1.5808</v>
       </c>
       <c r="E246" t="n">
         <v>0.5792</v>
       </c>
       <c r="F246" t="n">
-        <v>1.5802</v>
+        <v>1.5808</v>
       </c>
       <c r="G246" t="n">
         <v>-0.2409</v>
@@ -52782,19 +52782,19 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.7035</v>
+        <v>0.7037</v>
       </c>
       <c r="C247" t="n">
         <v>-1.552</v>
       </c>
       <c r="D247" t="n">
-        <v>1.4545</v>
+        <v>1.4551</v>
       </c>
       <c r="E247" t="n">
         <v>0.5158</v>
       </c>
       <c r="F247" t="n">
-        <v>1.4545</v>
+        <v>1.4551</v>
       </c>
       <c r="G247" t="n">
         <v>-0.4055</v>
@@ -52816,19 +52816,19 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.6623</v>
+        <v>0.6624</v>
       </c>
       <c r="C248" t="n">
         <v>-1.551</v>
       </c>
       <c r="D248" t="n">
-        <v>1.3002</v>
+        <v>1.3006</v>
       </c>
       <c r="E248" t="n">
         <v>0.5029</v>
       </c>
       <c r="F248" t="n">
-        <v>1.3002</v>
+        <v>1.3006</v>
       </c>
       <c r="G248" t="n">
         <v>-0.6183999999999999</v>
@@ -52837,7 +52837,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8183</v>
+        <v>1.8182</v>
       </c>
       <c r="J248" t="n">
         <v>0.921</v>
@@ -52850,19 +52850,19 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
       </c>
       <c r="D249" t="n">
-        <v>1.1165</v>
+        <v>1.1168</v>
       </c>
       <c r="E249" t="n">
         <v>0.5658</v>
       </c>
       <c r="F249" t="n">
-        <v>1.1165</v>
+        <v>1.1168</v>
       </c>
       <c r="G249" t="n">
         <v>-0.4586</v>
@@ -52884,19 +52884,19 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6324</v>
+        <v>0.6325</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
       </c>
       <c r="D250" t="n">
-        <v>1.2158</v>
+        <v>1.2162</v>
       </c>
       <c r="E250" t="n">
         <v>0.4866</v>
       </c>
       <c r="F250" t="n">
-        <v>1.2158</v>
+        <v>1.2162</v>
       </c>
       <c r="G250" t="n">
         <v>-0.8758</v>
@@ -52918,19 +52918,19 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7071</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
       </c>
       <c r="D251" t="n">
-        <v>1.236</v>
+        <v>1.2364</v>
       </c>
       <c r="E251" t="n">
         <v>0.5749</v>
       </c>
       <c r="F251" t="n">
-        <v>1.236</v>
+        <v>1.2364</v>
       </c>
       <c r="G251" t="n">
         <v>-0.673</v>
@@ -52952,19 +52952,19 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7776</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
       </c>
       <c r="D252" t="n">
-        <v>1.2102</v>
+        <v>1.2106</v>
       </c>
       <c r="E252" t="n">
         <v>0.6695</v>
       </c>
       <c r="F252" t="n">
-        <v>1.2102</v>
+        <v>1.2106</v>
       </c>
       <c r="G252" t="n">
         <v>-0.4796</v>
@@ -52986,19 +52986,19 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4635</v>
+        <v>0.4634</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
       </c>
       <c r="D253" t="n">
-        <v>0.0331</v>
+        <v>0.0326</v>
       </c>
       <c r="E253" t="n">
         <v>0.5711000000000001</v>
       </c>
       <c r="F253" t="n">
-        <v>0.0331</v>
+        <v>0.0326</v>
       </c>
       <c r="G253" t="n">
         <v>-0.8964</v>
@@ -53026,13 +53026,13 @@
         <v>-1.316</v>
       </c>
       <c r="D254" t="n">
-        <v>0.6443</v>
+        <v>0.6442</v>
       </c>
       <c r="E254" t="n">
         <v>0.5981</v>
       </c>
       <c r="F254" t="n">
-        <v>0.6443</v>
+        <v>0.6442</v>
       </c>
       <c r="G254" t="n">
         <v>-0.924</v>
@@ -53054,19 +53054,19 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5752</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
       </c>
       <c r="D255" t="n">
-        <v>0.4423</v>
+        <v>0.4421</v>
       </c>
       <c r="E255" t="n">
         <v>0.6084000000000001</v>
       </c>
       <c r="F255" t="n">
-        <v>0.4423</v>
+        <v>0.4421</v>
       </c>
       <c r="G255" t="n">
         <v>-1.0807</v>
@@ -53094,13 +53094,13 @@
         <v>-1.516</v>
       </c>
       <c r="D256" t="n">
-        <v>0.4895</v>
+        <v>0.4893</v>
       </c>
       <c r="E256" t="n">
         <v>0.4648</v>
       </c>
       <c r="F256" t="n">
-        <v>0.4895</v>
+        <v>0.4893</v>
       </c>
       <c r="G256" t="n">
         <v>-1.5826</v>
@@ -53122,19 +53122,19 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4908</v>
+        <v>0.4907</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
       </c>
       <c r="D257" t="n">
-        <v>0.3214</v>
+        <v>0.321</v>
       </c>
       <c r="E257" t="n">
         <v>0.5332</v>
       </c>
       <c r="F257" t="n">
-        <v>0.3214</v>
+        <v>0.321</v>
       </c>
       <c r="G257" t="n">
         <v>-1.4828</v>
@@ -53156,19 +53156,19 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4967</v>
+        <v>0.4966</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
       </c>
       <c r="D258" t="n">
-        <v>0.2926</v>
+        <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5477</v>
+        <v>0.5476</v>
       </c>
       <c r="F258" t="n">
-        <v>0.2926</v>
+        <v>0.2923</v>
       </c>
       <c r="G258" t="n">
         <v>-1.5633</v>
@@ -53196,13 +53196,13 @@
         <v>-1.503</v>
       </c>
       <c r="D259" t="n">
-        <v>0.3237</v>
+        <v>0.3234</v>
       </c>
       <c r="E259" t="n">
         <v>0.5859</v>
       </c>
       <c r="F259" t="n">
-        <v>0.3237</v>
+        <v>0.3234</v>
       </c>
       <c r="G259" t="n">
         <v>-1.6661</v>
@@ -53224,19 +53224,19 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5819</v>
+        <v>0.5818</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
       </c>
       <c r="D260" t="n">
-        <v>0.41</v>
+        <v>0.4097</v>
       </c>
       <c r="E260" t="n">
         <v>0.6249</v>
       </c>
       <c r="F260" t="n">
-        <v>0.41</v>
+        <v>0.4097</v>
       </c>
       <c r="G260" t="n">
         <v>-1.5813</v>
@@ -53258,14 +53258,20 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.6173</v>
+        <v>0.5601</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
       </c>
+      <c r="D261" t="n">
+        <v>0.331</v>
+      </c>
       <c r="E261" t="n">
         <v>0.6173</v>
       </c>
+      <c r="F261" t="n">
+        <v>0.331</v>
+      </c>
       <c r="G261" t="n">
         <v>-1.5813</v>
       </c>
@@ -53286,13 +53292,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.6095</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.6095</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53301,7 +53307,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9579</v>
+        <v>2.9583</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>-0.778</v>
+        <v>-0.777</v>
       </c>
     </row>
     <row r="77">
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.557</v>
+        <v>1.558</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.288</v>
+        <v>2.29</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.962</v>
+        <v>2.963</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.037</v>
+        <v>4.038</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.143</v>
+        <v>-1.142</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.609</v>
+        <v>-0.608</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64708.995</v>
+        <v>64762.661</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44235,19 +44235,19 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.557</v>
+        <v>1.5585</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8429</v>
+        <v>1.8434</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2884</v>
+        <v>2.2896</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9619</v>
+        <v>2.9633</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0372</v>
+        <v>4.0376</v>
       </c>
       <c r="H262" t="n">
         <v>2.7</v>
@@ -44259,13 +44259,13 @@
         <v>2.6</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.143</v>
+        <v>-1.1415</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6086</v>
+        <v>-0.6079</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3619</v>
+        <v>0.3633</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>64708.995</v>
+        <v>64762.6613</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.5092</v>
+        <v>10.4998</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0752</v>
+        <v>1.0744</v>
       </c>
     </row>
   </sheetData>
@@ -46105,7 +46105,7 @@
         <v>-2.1632</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0929</v>
+        <v>-1.0928</v>
       </c>
       <c r="J50" t="n">
         <v>0.7332</v>
@@ -46637,7 +46637,7 @@
         <v>-0.2093</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2664</v>
+        <v>-1.2663</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2093</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9833</v>
       </c>
       <c r="C70" t="n">
         <v>0.3843</v>
@@ -47138,7 +47138,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6249</v>
+        <v>-0.6248</v>
       </c>
       <c r="C81" t="n">
         <v>-0.0248</v>
@@ -47329,7 +47329,7 @@
         <v>-0.5998</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.326</v>
+        <v>-1.3259</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1958</v>
@@ -47465,7 +47465,7 @@
         <v>-0.6727</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2784</v>
+        <v>-1.2783</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0461</v>
@@ -47669,7 +47669,7 @@
         <v>-0.4521</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2438</v>
+        <v>-1.2437</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7599</v>
@@ -47975,7 +47975,7 @@
         <v>-0.2907</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7499</v>
+        <v>-0.7498</v>
       </c>
       <c r="J105" t="n">
         <v>-0.2972</v>
@@ -48294,7 +48294,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3445</v>
+        <v>0.3446</v>
       </c>
       <c r="C115" t="n">
         <v>-1.072</v>
@@ -49561,7 +49561,7 @@
         <v>0.6333</v>
       </c>
       <c r="E152" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6315</v>
       </c>
       <c r="F152" t="n">
         <v>0.6333</v>
@@ -49573,7 +49573,7 @@
         <v>1.1951</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0089</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="J152" t="n">
         <v>0.5984</v>
@@ -49994,7 +49994,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7474</v>
+        <v>0.7473</v>
       </c>
       <c r="C165" t="n">
         <v>-0.603</v>
@@ -50151,7 +50151,7 @@
         <v>1.0748</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0165</v>
+        <v>0.0164</v>
       </c>
       <c r="J169" t="n">
         <v>1.3249</v>
@@ -50185,7 +50185,7 @@
         <v>1.0748</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0609</v>
+        <v>-0.061</v>
       </c>
       <c r="J170" t="n">
         <v>1.4058</v>
@@ -50525,7 +50525,7 @@
         <v>0.9367</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1671</v>
+        <v>-0.1672</v>
       </c>
       <c r="J180" t="n">
         <v>1.8124</v>
@@ -51375,7 +51375,7 @@
         <v>0.3341</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4153</v>
+        <v>0.4152</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4193</v>
@@ -51388,7 +51388,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3202</v>
+        <v>0.3201</v>
       </c>
       <c r="C206" t="n">
         <v>-0.8100000000000001</v>
@@ -51579,7 +51579,7 @@
         <v>0.253</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7186</v>
+        <v>0.7185</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1668</v>
@@ -51626,7 +51626,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.7025</v>
+        <v>0.7024</v>
       </c>
       <c r="C213" t="n">
         <v>-2.07</v>
@@ -51987,7 +51987,7 @@
         <v>0.0545</v>
       </c>
       <c r="I223" t="n">
-        <v>1.012</v>
+        <v>1.0119</v>
       </c>
       <c r="J223" t="n">
         <v>0.3149</v>
@@ -52021,7 +52021,7 @@
         <v>0.0545</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0401</v>
+        <v>1.04</v>
       </c>
       <c r="J224" t="n">
         <v>0.3625</v>
@@ -52191,7 +52191,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2138</v>
+        <v>1.2137</v>
       </c>
       <c r="J229" t="n">
         <v>0.4323</v>
@@ -52259,7 +52259,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4491</v>
+        <v>1.449</v>
       </c>
       <c r="J231" t="n">
         <v>0.4733</v>
@@ -52272,7 +52272,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7924</v>
+        <v>0.7923</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52327,7 +52327,7 @@
         <v>0.0287</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5835</v>
+        <v>1.5834</v>
       </c>
       <c r="J233" t="n">
         <v>0.5769</v>
@@ -52395,7 +52395,7 @@
         <v>0.0287</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7064</v>
+        <v>1.7063</v>
       </c>
       <c r="J235" t="n">
         <v>0.5726</v>
@@ -52429,7 +52429,7 @@
         <v>0.0287</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7397</v>
+        <v>1.7396</v>
       </c>
       <c r="J236" t="n">
         <v>0.6299</v>
@@ -52463,7 +52463,7 @@
         <v>0.0287</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5316</v>
+        <v>1.5315</v>
       </c>
       <c r="J237" t="n">
         <v>0.6664</v>
@@ -52476,7 +52476,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7269</v>
+        <v>0.7268</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
@@ -52531,7 +52531,7 @@
         <v>0.0542</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6485</v>
+        <v>1.6484</v>
       </c>
       <c r="J239" t="n">
         <v>0.6294999999999999</v>
@@ -52782,7 +52782,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.7037</v>
+        <v>0.7036</v>
       </c>
       <c r="C247" t="n">
         <v>-1.552</v>
@@ -52871,7 +52871,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8912</v>
+        <v>1.8911</v>
       </c>
       <c r="J249" t="n">
         <v>0.9399</v>
@@ -52905,7 +52905,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9762</v>
+        <v>1.9761</v>
       </c>
       <c r="J250" t="n">
         <v>0.9868</v>
@@ -52927,7 +52927,7 @@
         <v>1.2364</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5749</v>
+        <v>0.5748</v>
       </c>
       <c r="F251" t="n">
         <v>1.2364</v>
@@ -52973,7 +52973,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2472</v>
+        <v>2.2471</v>
       </c>
       <c r="J252" t="n">
         <v>1.0513</v>
@@ -52995,7 +52995,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53097,7 +53097,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4648</v>
+        <v>0.4647</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53109,7 +53109,7 @@
         <v>-0.172</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4838</v>
+        <v>2.4837</v>
       </c>
       <c r="J256" t="n">
         <v>1.1299</v>
@@ -53177,7 +53177,7 @@
         <v>-0.172</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7565</v>
+        <v>2.7564</v>
       </c>
       <c r="J258" t="n">
         <v>1.1695</v>
@@ -53190,7 +53190,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5334</v>
+        <v>0.5333</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53199,7 +53199,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5859</v>
+        <v>0.5858</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53211,7 +53211,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9458</v>
+        <v>2.9457</v>
       </c>
       <c r="J259" t="n">
         <v>1.2103</v>
@@ -53245,7 +53245,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9916</v>
+        <v>2.9915</v>
       </c>
       <c r="J260" t="n">
         <v>1.2358</v>
@@ -53279,7 +53279,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9897</v>
+        <v>2.9896</v>
       </c>
       <c r="J261" t="n">
         <v>1.2076</v>
@@ -53292,13 +53292,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6095</v>
+        <v>0.6097</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6095</v>
+        <v>0.6097</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9583</v>
+        <v>2.9593</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.558</v>
+        <v>1.563</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.843</v>
+        <v>1.848</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.29</v>
+        <v>2.297</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.963</v>
+        <v>2.971</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.038</v>
+        <v>4.043</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.142</v>
+        <v>-1.137</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.608</v>
+        <v>-0.602</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.363</v>
+        <v>0.371</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64762.661</v>
+        <v>64862.757</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -44235,19 +44235,19 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.5585</v>
+        <v>1.5631</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8434</v>
+        <v>1.8479</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2896</v>
+        <v>2.2969</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9633</v>
+        <v>2.9706</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0376</v>
+        <v>4.0428</v>
       </c>
       <c r="H262" t="n">
         <v>2.7</v>
@@ -44259,13 +44259,13 @@
         <v>2.6</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.1415</v>
+        <v>-1.1369</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6079</v>
+        <v>-0.6024</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3633</v>
+        <v>0.3706</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>64762.6613</v>
+        <v>64862.7575</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.4998</v>
+        <v>10.4513</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0744</v>
+        <v>1.0722</v>
       </c>
     </row>
   </sheetData>
@@ -44520,7 +44520,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4602</v>
+        <v>-0.4601</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2002</v>
@@ -44597,7 +44597,7 @@
         <v>0.2692</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6066</v>
+        <v>-0.6065</v>
       </c>
       <c r="F6" t="n">
         <v>0.2692</v>
@@ -44779,7 +44779,7 @@
         <v>0.1628</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2992</v>
+        <v>-0.2991</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2795</v>
@@ -44949,7 +44949,7 @@
         <v>0.4878</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1556</v>
+        <v>-0.1555</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0065</v>
@@ -45153,7 +45153,7 @@
         <v>0.2276</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1029</v>
+        <v>-0.1028</v>
       </c>
       <c r="J22" t="n">
         <v>-0.6839</v>
@@ -45323,7 +45323,7 @@
         <v>0.3183</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0526</v>
+        <v>0.0527</v>
       </c>
       <c r="J27" t="n">
         <v>-0.5154</v>
@@ -45527,7 +45527,7 @@
         <v>0.3179</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0475</v>
+        <v>-0.0474</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1919</v>
@@ -45923,7 +45923,7 @@
         <v>1.0383</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5243</v>
+        <v>-0.5242</v>
       </c>
       <c r="F45" t="n">
         <v>1.0383</v>
@@ -46309,7 +46309,7 @@
         <v>-2.8207</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0417</v>
+        <v>-1.0416</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2702</v>
@@ -46331,7 +46331,7 @@
         <v>-0.895</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2996</v>
+        <v>-1.2995</v>
       </c>
       <c r="F57" t="n">
         <v>-0.895</v>
@@ -46343,7 +46343,7 @@
         <v>-2.8207</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0208</v>
+        <v>-1.0207</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3938</v>
@@ -46513,7 +46513,7 @@
         <v>-2.1899</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0585</v>
+        <v>-1.0584</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2651</v>
@@ -46649,7 +46649,7 @@
         <v>-1.8257</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0547</v>
+        <v>-1.0546</v>
       </c>
       <c r="J66" t="n">
         <v>-1.917</v>
@@ -46705,7 +46705,7 @@
         <v>-0.2742</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2198</v>
+        <v>-1.2197</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2742</v>
@@ -46853,7 +46853,7 @@
         <v>-1.0927</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2199</v>
+        <v>-1.2198</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8476</v>
@@ -47002,7 +47002,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7402</v>
+        <v>-0.7401</v>
       </c>
       <c r="C77" t="n">
         <v>0.107</v>
@@ -47227,7 +47227,7 @@
         <v>-0.6175</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3361</v>
+        <v>-1.336</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3367</v>
@@ -47261,7 +47261,7 @@
         <v>-0.6175</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.311</v>
+        <v>-1.3109</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2939</v>
@@ -47295,7 +47295,7 @@
         <v>-0.5998</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3249</v>
+        <v>-1.3248</v>
       </c>
       <c r="J85" t="n">
         <v>-1.204</v>
@@ -47363,7 +47363,7 @@
         <v>-0.5998</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2837</v>
+        <v>-1.2836</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1149</v>
@@ -47533,7 +47533,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.3009</v>
+        <v>-1.3008</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9318</v>
@@ -47555,7 +47555,7 @@
         <v>0.1757</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6214</v>
+        <v>-0.6213</v>
       </c>
       <c r="F93" t="n">
         <v>0.1757</v>
@@ -47567,7 +47567,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2838</v>
+        <v>-1.2837</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8832</v>
@@ -47805,7 +47805,7 @@
         <v>-0.4698</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9129</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4283</v>
@@ -48519,7 +48519,7 @@
         <v>0.3793</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0772</v>
+        <v>-0.0771</v>
       </c>
       <c r="J121" t="n">
         <v>-0.1356</v>
@@ -49722,7 +49722,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6942</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="C157" t="n">
         <v>-0.527</v>
@@ -50355,7 +50355,7 @@
         <v>0.9648</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1332</v>
+        <v>-0.1333</v>
       </c>
       <c r="J175" t="n">
         <v>1.6095</v>
@@ -50559,7 +50559,7 @@
         <v>0.8405</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1831</v>
+        <v>-0.1832</v>
       </c>
       <c r="J181" t="n">
         <v>1.8971</v>
@@ -50717,7 +50717,7 @@
         <v>0.3984</v>
       </c>
       <c r="E186" t="n">
-        <v>0.7654</v>
+        <v>0.7653</v>
       </c>
       <c r="F186" t="n">
         <v>0.3984</v>
@@ -50865,7 +50865,7 @@
         <v>-0.0253</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1453</v>
+        <v>-0.1454</v>
       </c>
       <c r="J190" t="n">
         <v>1.4298</v>
@@ -50899,7 +50899,7 @@
         <v>-0.0253</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.122</v>
+        <v>-0.1221</v>
       </c>
       <c r="J191" t="n">
         <v>1.1911</v>
@@ -51069,7 +51069,7 @@
         <v>0.2023</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1832</v>
+        <v>0.1831</v>
       </c>
       <c r="J196" t="n">
         <v>0.06320000000000001</v>
@@ -51239,7 +51239,7 @@
         <v>0.2926</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2791</v>
+        <v>0.279</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5885</v>
@@ -51307,7 +51307,7 @@
         <v>0.3596</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3888</v>
+        <v>0.3887</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5014</v>
@@ -51443,7 +51443,7 @@
         <v>0.3341</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4197</v>
+        <v>0.4196</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3088</v>
@@ -51490,7 +51490,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5603</v>
+        <v>0.5602</v>
       </c>
       <c r="C209" t="n">
         <v>-1.483</v>
@@ -51545,7 +51545,7 @@
         <v>0.1786</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6319</v>
+        <v>0.6318</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2497</v>
@@ -51715,7 +51715,7 @@
         <v>0.1175</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9556</v>
+        <v>0.9555</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0412</v>
@@ -51771,7 +51771,7 @@
         <v>1.5631</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3949</v>
+        <v>0.3948</v>
       </c>
       <c r="F217" t="n">
         <v>1.5631</v>
@@ -51783,7 +51783,7 @@
         <v>0.0131</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7804</v>
+        <v>0.7803</v>
       </c>
       <c r="J217" t="n">
         <v>0.039</v>
@@ -51839,7 +51839,7 @@
         <v>1.6773</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4678</v>
+        <v>0.4677</v>
       </c>
       <c r="F219" t="n">
         <v>1.6773</v>
@@ -52000,7 +52000,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8149</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
@@ -52055,7 +52055,7 @@
         <v>0.0545</v>
       </c>
       <c r="I225" t="n">
-        <v>1.1096</v>
+        <v>1.1095</v>
       </c>
       <c r="J225" t="n">
         <v>0.3074</v>
@@ -52089,7 +52089,7 @@
         <v>-0.0499</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1912</v>
+        <v>1.1911</v>
       </c>
       <c r="J226" t="n">
         <v>0.3581</v>
@@ -52145,7 +52145,7 @@
         <v>1.3821</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6625</v>
+        <v>0.6624</v>
       </c>
       <c r="F228" t="n">
         <v>1.3821</v>
@@ -52157,7 +52157,7 @@
         <v>-0.0499</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2903</v>
+        <v>1.2902</v>
       </c>
       <c r="J228" t="n">
         <v>0.4192</v>
@@ -52225,7 +52225,7 @@
         <v>-0.0025</v>
       </c>
       <c r="I230" t="n">
-        <v>1.3268</v>
+        <v>1.3267</v>
       </c>
       <c r="J230" t="n">
         <v>0.5399</v>
@@ -52247,7 +52247,7 @@
         <v>1.4909</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6815</v>
+        <v>0.6814</v>
       </c>
       <c r="F231" t="n">
         <v>1.4909</v>
@@ -52497,7 +52497,7 @@
         <v>0.0542</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4968</v>
+        <v>1.4967</v>
       </c>
       <c r="J238" t="n">
         <v>0.6374</v>
@@ -52565,7 +52565,7 @@
         <v>0.0542</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7357</v>
+        <v>1.7356</v>
       </c>
       <c r="J240" t="n">
         <v>0.7241</v>
@@ -52621,7 +52621,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.6385</v>
+        <v>0.6384</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52633,7 +52633,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8327</v>
+        <v>1.8326</v>
       </c>
       <c r="J242" t="n">
         <v>0.7882</v>
@@ -52667,7 +52667,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7559</v>
+        <v>1.7558</v>
       </c>
       <c r="J243" t="n">
         <v>0.8135</v>
@@ -52701,7 +52701,7 @@
         <v>-0.115</v>
       </c>
       <c r="I244" t="n">
-        <v>1.7229</v>
+        <v>1.7228</v>
       </c>
       <c r="J244" t="n">
         <v>0.7667</v>
@@ -52769,7 +52769,7 @@
         <v>-0.115</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6934</v>
+        <v>1.6933</v>
       </c>
       <c r="J246" t="n">
         <v>0.9795</v>
@@ -52803,7 +52803,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7218</v>
+        <v>1.7217</v>
       </c>
       <c r="J247" t="n">
         <v>0.8564000000000001</v>
@@ -52825,7 +52825,7 @@
         <v>1.3006</v>
       </c>
       <c r="E248" t="n">
-        <v>0.5029</v>
+        <v>0.5028</v>
       </c>
       <c r="F248" t="n">
         <v>1.3006</v>
@@ -52893,7 +52893,7 @@
         <v>1.2162</v>
       </c>
       <c r="E250" t="n">
-        <v>0.4866</v>
+        <v>0.4865</v>
       </c>
       <c r="F250" t="n">
         <v>1.2162</v>
@@ -52918,7 +52918,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.7071</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -52939,7 +52939,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I251" t="n">
-        <v>2.1381</v>
+        <v>2.138</v>
       </c>
       <c r="J251" t="n">
         <v>0.9752999999999999</v>
@@ -52973,7 +52973,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2471</v>
+        <v>2.247</v>
       </c>
       <c r="J252" t="n">
         <v>1.0513</v>
@@ -52986,7 +52986,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4634</v>
+        <v>0.4633</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53007,7 +53007,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3023</v>
+        <v>2.3022</v>
       </c>
       <c r="J253" t="n">
         <v>0.9856</v>
@@ -53041,7 +53041,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I254" t="n">
-        <v>2.395</v>
+        <v>2.3949</v>
       </c>
       <c r="J254" t="n">
         <v>1.0285</v>
@@ -53075,7 +53075,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4617</v>
+        <v>2.4616</v>
       </c>
       <c r="J255" t="n">
         <v>1.1598</v>
@@ -53088,7 +53088,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4697</v>
+        <v>0.4696</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53109,7 +53109,7 @@
         <v>-0.172</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4837</v>
+        <v>2.4836</v>
       </c>
       <c r="J256" t="n">
         <v>1.1299</v>
@@ -53131,7 +53131,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5332</v>
+        <v>0.5331</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53143,7 +53143,7 @@
         <v>-0.172</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6069</v>
+        <v>2.6068</v>
       </c>
       <c r="J257" t="n">
         <v>1.1806</v>
@@ -53156,7 +53156,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4966</v>
+        <v>0.4965</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53177,7 +53177,7 @@
         <v>-0.172</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7564</v>
+        <v>2.7563</v>
       </c>
       <c r="J258" t="n">
         <v>1.1695</v>
@@ -53211,7 +53211,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9457</v>
+        <v>2.9456</v>
       </c>
       <c r="J259" t="n">
         <v>1.2103</v>
@@ -53233,7 +53233,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6249</v>
+        <v>0.6248</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53245,7 +53245,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9915</v>
+        <v>2.9914</v>
       </c>
       <c r="J260" t="n">
         <v>1.2358</v>
@@ -53258,7 +53258,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5601</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53279,7 +53279,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9896</v>
+        <v>2.9895</v>
       </c>
       <c r="J261" t="n">
         <v>1.2076</v>
@@ -53292,13 +53292,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6097</v>
+        <v>0.6102</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6097</v>
+        <v>0.6102</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9593</v>
+        <v>2.961</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3596,7 +3596,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.563</v>
+        <v>1.576</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.848</v>
+        <v>1.862</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.297</v>
+        <v>2.313</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.971</v>
+        <v>2.983</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.043</v>
+        <v>4.052</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.137</v>
+        <v>-1.124</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.602</v>
+        <v>-0.588</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.371</v>
+        <v>0.383</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.65</v>
+        <v>-0.66</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64862.757</v>
+        <v>64922.455</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44235,19 +44235,19 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.5631</v>
+        <v>1.5757</v>
       </c>
       <c r="D262" t="n">
-        <v>1.8479</v>
+        <v>1.8616</v>
       </c>
       <c r="E262" t="n">
-        <v>2.2969</v>
+        <v>2.3128</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9706</v>
+        <v>2.9831</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0428</v>
+        <v>4.0515</v>
       </c>
       <c r="H262" t="n">
         <v>2.7</v>
@@ -44259,13 +44259,13 @@
         <v>2.6</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.1369</v>
+        <v>-1.1243</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.6024</v>
+        <v>-0.588</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3706</v>
+        <v>0.3831</v>
       </c>
       <c r="N262" t="n">
         <v>-1.723</v>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>64862.7575</v>
+        <v>64922.4553</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44373,10 +44373,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.4513</v>
+        <v>10.3774</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0722</v>
+        <v>1.0685</v>
       </c>
     </row>
   </sheetData>
@@ -44813,7 +44813,7 @@
         <v>0.1628</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2153</v>
+        <v>-0.2152</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2191</v>
@@ -45663,7 +45663,7 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2386</v>
+        <v>-0.2385</v>
       </c>
       <c r="J37" t="n">
         <v>0.0274</v>
@@ -46152,7 +46152,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0641</v>
+        <v>-1.064</v>
       </c>
       <c r="C52" t="n">
         <v>0.2794</v>
@@ -46207,7 +46207,7 @@
         <v>-3.3944</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9896</v>
+        <v>-0.9895</v>
       </c>
       <c r="J53" t="n">
         <v>0.1297</v>
@@ -46220,7 +46220,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.148</v>
+        <v>-1.1479</v>
       </c>
       <c r="C54" t="n">
         <v>0.2814</v>
@@ -47057,7 +47057,7 @@
         <v>-0.7026</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2422</v>
+        <v>-1.2421</v>
       </c>
       <c r="J78" t="n">
         <v>-1.5723</v>
@@ -47193,7 +47193,7 @@
         <v>-0.6175</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3254</v>
+        <v>-1.3253</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3495</v>
@@ -47657,7 +47657,7 @@
         <v>0.2764</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.5569</v>
       </c>
       <c r="F96" t="n">
         <v>0.2764</v>
@@ -47954,7 +47954,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-0.0562</v>
+        <v>-0.0561</v>
       </c>
       <c r="C105" t="n">
         <v>-0.7124</v>
@@ -48247,7 +48247,7 @@
         <v>0.0854</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5346</v>
+        <v>-0.5345</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2701</v>
@@ -48757,7 +48757,7 @@
         <v>0.7669</v>
       </c>
       <c r="I128" t="n">
-        <v>0.132</v>
+        <v>0.1319</v>
       </c>
       <c r="J128" t="n">
         <v>-0.1134</v>
@@ -49029,7 +49029,7 @@
         <v>0.952</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0721</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>-0.09470000000000001</v>
@@ -49675,7 +49675,7 @@
         <v>1.1222</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0624</v>
+        <v>0.0623</v>
       </c>
       <c r="J155" t="n">
         <v>0.7189</v>
@@ -49926,7 +49926,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.7336</v>
+        <v>0.7335</v>
       </c>
       <c r="C163" t="n">
         <v>-0.615</v>
@@ -50083,7 +50083,7 @@
         <v>1.1085</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0839</v>
+        <v>0.0838</v>
       </c>
       <c r="J167" t="n">
         <v>1.2492</v>
@@ -50661,7 +50661,7 @@
         <v>0.581</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3299</v>
+        <v>-0.33</v>
       </c>
       <c r="J184" t="n">
         <v>1.9625</v>
@@ -50819,7 +50819,7 @@
         <v>0.2496</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4462</v>
+        <v>0.4461</v>
       </c>
       <c r="F189" t="n">
         <v>0.2496</v>
@@ -50955,7 +50955,7 @@
         <v>0.1261</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3283</v>
+        <v>0.3282</v>
       </c>
       <c r="F193" t="n">
         <v>0.1261</v>
@@ -50967,7 +50967,7 @@
         <v>-0.0002</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.023</v>
+        <v>-0.0231</v>
       </c>
       <c r="J193" t="n">
         <v>0.7811</v>
@@ -51001,7 +51001,7 @@
         <v>-0.0002</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0157</v>
+        <v>0.0156</v>
       </c>
       <c r="J194" t="n">
         <v>0.5315</v>
@@ -51171,7 +51171,7 @@
         <v>0.2926</v>
       </c>
       <c r="I199" t="n">
-        <v>0.266</v>
+        <v>0.2659</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6283</v>
@@ -51341,7 +51341,7 @@
         <v>0.3596</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4233</v>
+        <v>0.4232</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4109</v>
@@ -51511,7 +51511,7 @@
         <v>0.1786</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6049</v>
+        <v>0.6048</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2486</v>
@@ -51635,7 +51635,7 @@
         <v>1.5668</v>
       </c>
       <c r="E213" t="n">
-        <v>0.4864</v>
+        <v>0.4863</v>
       </c>
       <c r="F213" t="n">
         <v>1.5668</v>
@@ -51647,7 +51647,7 @@
         <v>0.253</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7942</v>
+        <v>0.7941</v>
       </c>
       <c r="J213" t="n">
         <v>-0.07140000000000001</v>
@@ -51749,7 +51749,7 @@
         <v>0.1175</v>
       </c>
       <c r="I216" t="n">
-        <v>0.9123</v>
+        <v>0.9122</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0005</v>
@@ -52170,7 +52170,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.7788</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="C229" t="n">
         <v>-1.989</v>
@@ -52293,7 +52293,7 @@
         <v>0.0287</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5129</v>
+        <v>1.5128</v>
       </c>
       <c r="J232" t="n">
         <v>0.4327</v>
@@ -52361,7 +52361,7 @@
         <v>0.0287</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6425</v>
+        <v>1.6424</v>
       </c>
       <c r="J234" t="n">
         <v>0.579</v>
@@ -52429,7 +52429,7 @@
         <v>0.0287</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7396</v>
+        <v>1.7395</v>
       </c>
       <c r="J236" t="n">
         <v>0.6299</v>
@@ -52510,7 +52510,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7519</v>
+        <v>0.7518</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52599,7 +52599,7 @@
         <v>-0.0028</v>
       </c>
       <c r="I241" t="n">
-        <v>1.773</v>
+        <v>1.7729</v>
       </c>
       <c r="J241" t="n">
         <v>0.7578</v>
@@ -52735,7 +52735,7 @@
         <v>-0.115</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5915</v>
+        <v>1.5914</v>
       </c>
       <c r="J245" t="n">
         <v>0.8439</v>
@@ -52837,7 +52837,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I248" t="n">
-        <v>1.8182</v>
+        <v>1.8181</v>
       </c>
       <c r="J248" t="n">
         <v>0.921</v>
@@ -52859,7 +52859,7 @@
         <v>1.1168</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5658</v>
+        <v>0.5657</v>
       </c>
       <c r="F249" t="n">
         <v>1.1168</v>
@@ -52905,7 +52905,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9761</v>
+        <v>1.976</v>
       </c>
       <c r="J250" t="n">
         <v>0.9868</v>
@@ -52939,7 +52939,7 @@
         <v>-0.1409</v>
       </c>
       <c r="I251" t="n">
-        <v>2.138</v>
+        <v>2.1379</v>
       </c>
       <c r="J251" t="n">
         <v>0.9752999999999999</v>
@@ -53007,7 +53007,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I253" t="n">
-        <v>2.3022</v>
+        <v>2.3021</v>
       </c>
       <c r="J253" t="n">
         <v>0.9856</v>
@@ -53029,7 +53029,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5981</v>
+        <v>0.598</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53075,7 +53075,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4616</v>
+        <v>2.4615</v>
       </c>
       <c r="J255" t="n">
         <v>1.1598</v>
@@ -53143,7 +53143,7 @@
         <v>-0.172</v>
       </c>
       <c r="I257" t="n">
-        <v>2.6068</v>
+        <v>2.6067</v>
       </c>
       <c r="J257" t="n">
         <v>1.1806</v>
@@ -53177,7 +53177,7 @@
         <v>-0.172</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7563</v>
+        <v>2.7562</v>
       </c>
       <c r="J258" t="n">
         <v>1.1695</v>
@@ -53211,7 +53211,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I259" t="n">
-        <v>2.9456</v>
+        <v>2.9455</v>
       </c>
       <c r="J259" t="n">
         <v>1.2103</v>
@@ -53279,7 +53279,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9895</v>
+        <v>2.9894</v>
       </c>
       <c r="J261" t="n">
         <v>1.2076</v>
@@ -53292,13 +53292,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6102</v>
+        <v>0.6105</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6102</v>
+        <v>0.6105</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.961</v>
+        <v>2.9621</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.61</v>
+        <v>0.611</v>
       </c>
     </row>
   </sheetData>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>64922.455</v>
+        <v>64953.501</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z262" t="n">
-        <v>64922.4553</v>
+        <v>64953.5006</v>
       </c>
       <c r="AA262" t="n">
         <v>158.8476</v>
@@ -44575,7 +44575,7 @@
         <v>-0.0185</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5415</v>
+        <v>-0.5414</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5318</v>
@@ -46037,7 +46037,7 @@
         <v>-0.9858</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9305</v>
+        <v>-0.9304</v>
       </c>
       <c r="J48" t="n">
         <v>0.7558</v>
@@ -46050,7 +46050,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8232</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="C49" t="n">
         <v>-0.2307</v>
@@ -46139,7 +46139,7 @@
         <v>-2.1632</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.098</v>
+        <v>-1.0979</v>
       </c>
       <c r="J51" t="n">
         <v>0.5424</v>
@@ -46785,7 +46785,7 @@
         <v>-1.0927</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2023</v>
+        <v>-1.2022</v>
       </c>
       <c r="J70" t="n">
         <v>-1.986</v>
@@ -47070,7 +47070,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7261</v>
+        <v>-0.726</v>
       </c>
       <c r="C79" t="n">
         <v>-0.0368</v>
@@ -47431,7 +47431,7 @@
         <v>-0.6727</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2294</v>
+        <v>-1.2293</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0466</v>
@@ -47737,7 +47737,7 @@
         <v>-0.5034999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0596</v>
+        <v>-1.0595</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5264</v>
@@ -47771,7 +47771,7 @@
         <v>-0.5034999999999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9651</v>
+        <v>-0.965</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5256</v>
@@ -50491,7 +50491,7 @@
         <v>0.9367</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1902</v>
+        <v>-0.1903</v>
       </c>
       <c r="J179" t="n">
         <v>1.7188</v>
@@ -50593,7 +50593,7 @@
         <v>0.8405</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2011</v>
+        <v>-0.2012</v>
       </c>
       <c r="J182" t="n">
         <v>1.9628</v>
@@ -50887,7 +50887,7 @@
         <v>0.082</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3594</v>
+        <v>0.3593</v>
       </c>
       <c r="F191" t="n">
         <v>0.082</v>
@@ -51409,7 +51409,7 @@
         <v>0.3341</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4133</v>
+        <v>0.4132</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4053</v>
@@ -51477,7 +51477,7 @@
         <v>0.1786</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4687</v>
+        <v>0.4686</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2303</v>
@@ -51660,7 +51660,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.7239</v>
+        <v>0.7238</v>
       </c>
       <c r="C214" t="n">
         <v>-2.284</v>
@@ -52111,7 +52111,7 @@
         <v>1.5267</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5707</v>
+        <v>0.5706</v>
       </c>
       <c r="F227" t="n">
         <v>1.5267</v>
@@ -52340,7 +52340,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8868</v>
+        <v>0.8867</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52395,7 +52395,7 @@
         <v>0.0287</v>
       </c>
       <c r="I235" t="n">
-        <v>1.7063</v>
+        <v>1.7062</v>
       </c>
       <c r="J235" t="n">
         <v>0.5726</v>
@@ -52451,7 +52451,7 @@
         <v>1.4213</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7181</v>
       </c>
       <c r="F237" t="n">
         <v>1.4213</v>
@@ -52463,7 +52463,7 @@
         <v>0.0287</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5315</v>
+        <v>1.5314</v>
       </c>
       <c r="J237" t="n">
         <v>0.6664</v>
@@ -52531,7 +52531,7 @@
         <v>0.0542</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6484</v>
+        <v>1.6483</v>
       </c>
       <c r="J239" t="n">
         <v>0.6294999999999999</v>
@@ -52871,7 +52871,7 @@
         <v>-0.1094</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8911</v>
+        <v>1.891</v>
       </c>
       <c r="J249" t="n">
         <v>0.9399</v>
@@ -53041,7 +53041,7 @@
         <v>-0.1072</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3949</v>
+        <v>2.3948</v>
       </c>
       <c r="J254" t="n">
         <v>1.0285</v>
@@ -53245,7 +53245,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9914</v>
+        <v>2.9913</v>
       </c>
       <c r="J260" t="n">
         <v>1.2358</v>
@@ -53292,13 +53292,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6105</v>
+        <v>0.6106</v>
       </c>
       <c r="C262" t="n">
         <v>-1.367</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6105</v>
+        <v>0.6106</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5813</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1465</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9621</v>
+        <v>2.9626</v>
       </c>
       <c r="J262" t="n">
         <v>1.2076</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>+0.61</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-0.431</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="7">
@@ -808,7 +808,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-1.37pp</t>
+          <t>-1.27pp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-0.376</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="10">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>-0.295</v>
+        <v>-0.294</v>
       </c>
     </row>
     <row r="14">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.60 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 0.98%. The real policy rate is about -1.72%, roughly 1.37pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.61 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 0.98%. The real policy rate is about -1.62%, roughly 1.27pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>-0.327</v>
+        <v>-0.326</v>
       </c>
     </row>
     <row r="27">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>-0.384</v>
+        <v>-0.383</v>
       </c>
     </row>
     <row r="33">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>-0.383</v>
+        <v>-0.382</v>
       </c>
     </row>
     <row r="35">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>-0.297</v>
+        <v>-0.296</v>
       </c>
     </row>
     <row r="37">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>-0.277</v>
+        <v>-0.276</v>
       </c>
     </row>
     <row r="40">
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>-1.145</v>
+        <v>-1.144</v>
       </c>
     </row>
     <row r="56">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>-1.138</v>
+        <v>-1.137</v>
       </c>
     </row>
     <row r="61">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="112">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0.127</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="113">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>0.402</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="124">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="134">
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="138">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>0.534</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="188">
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="199">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="241">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>0.627</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="251">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="252">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="J252" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="253">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="254">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="258">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
     </row>
     <row r="261">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.552</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="262">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.601</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="263">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.601</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -3602,11 +3602,11 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.582</v>
+        <v>1.668</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3628,11 +3628,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.868</v>
+        <v>1.939</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3654,11 +3654,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.319</v>
+        <v>2.407</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3680,11 +3680,11 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.989</v>
+        <v>3.092</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3706,11 +3706,11 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.056</v>
+        <v>4.122</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3732,11 +3732,11 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
@@ -3784,11 +3784,11 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -3814,19 +3814,19 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-1.118</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>0.28</v>
+      <c r="E13" s="12" t="n">
+        <v>0.06</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Mildly accommodative</t>
+          <t>Broadly neutral</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.582</v>
+        <v>-0.505</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.389</v>
+        <v>0.592</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.66</v>
+        <v>-0.86</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>-1.723</v>
+        <v>-1.623</v>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
@@ -4068,11 +4068,11 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-0.57</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-0.87</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>65048.249</v>
+        <v>68956.72</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.61</v>
+        <v>3.91</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -4236,11 +4236,11 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>158.848</v>
+        <v>156.417</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -44245,40 +44245,40 @@
         <v>0.977</v>
       </c>
       <c r="C262" t="n">
-        <v>1.5822</v>
+        <v>1.5875</v>
       </c>
       <c r="D262" t="n">
-        <v>1.868</v>
+        <v>1.8724</v>
       </c>
       <c r="E262" t="n">
-        <v>2.3191</v>
+        <v>2.3233</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9886</v>
+        <v>2.9922</v>
       </c>
       <c r="G262" t="n">
-        <v>4.0557</v>
+        <v>4.0579</v>
       </c>
       <c r="H262" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I262" t="n">
         <v>2.6</v>
       </c>
       <c r="J262" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K262" t="n">
-        <v>-1.1178</v>
+        <v>-1.0125</v>
       </c>
       <c r="L262" t="n">
-        <v>-0.5816</v>
+        <v>-0.5773</v>
       </c>
       <c r="M262" t="n">
-        <v>0.3886</v>
+        <v>0.4922</v>
       </c>
       <c r="N262" t="n">
-        <v>-1.723</v>
+        <v>-1.623</v>
       </c>
       <c r="O262" t="n">
         <v>-0.3883</v>
@@ -44299,13 +44299,13 @@
         <v>0.2908</v>
       </c>
       <c r="U262" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V262" t="n">
         <v>12</v>
       </c>
       <c r="W262" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X262" t="n">
         <v>8</v>
@@ -44317,7 +44317,7 @@
         <v>65048.2489</v>
       </c>
       <c r="AA262" t="n">
-        <v>158.8476</v>
+        <v>156.4171</v>
       </c>
       <c r="AB262" t="n">
         <v>5.8</v>
@@ -44383,10 +44383,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.3483</v>
+        <v>10.3303</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0671</v>
+        <v>1.0657</v>
       </c>
     </row>
     <row r="263">
@@ -44399,40 +44399,40 @@
         <v>0.977</v>
       </c>
       <c r="C263" t="n">
-        <v>1.5822</v>
+        <v>1.668</v>
       </c>
       <c r="D263" t="n">
-        <v>1.868</v>
+        <v>1.939</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3191</v>
+        <v>2.407</v>
       </c>
       <c r="F263" t="n">
-        <v>2.9886</v>
+        <v>3.092</v>
       </c>
       <c r="G263" t="n">
-        <v>4.0557</v>
+        <v>4.122</v>
       </c>
       <c r="H263" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I263" t="n">
         <v>2.6</v>
       </c>
       <c r="J263" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-1.1178</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5816</v>
+        <v>-0.505</v>
       </c>
       <c r="M263" t="n">
-        <v>0.3886</v>
+        <v>0.592</v>
       </c>
       <c r="N263" t="n">
-        <v>-1.723</v>
+        <v>-1.623</v>
       </c>
       <c r="O263" t="n">
         <v>-0.3883</v>
@@ -44453,13 +44453,13 @@
         <v>0.2908</v>
       </c>
       <c r="U263" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V263" t="n">
         <v>12</v>
       </c>
       <c r="W263" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X263" t="n">
         <v>8</v>
@@ -44468,10 +44468,10 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>65048.2489</v>
+        <v>68956.72</v>
       </c>
       <c r="AA263" t="n">
-        <v>158.8476</v>
+        <v>156.4171</v>
       </c>
       <c r="AB263" t="n">
         <v>5.8</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.3483</v>
+        <v>9.877700000000001</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0671</v>
+        <v>1.03</v>
       </c>
     </row>
   </sheetData>
@@ -44628,13 +44628,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5752</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="D2" t="n">
         <v>0.2564</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8524</v>
+        <v>-0.8522</v>
       </c>
       <c r="F2" t="n">
         <v>0.2564</v>
@@ -44643,7 +44643,7 @@
         <v>-0.3626</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6321</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5626</v>
@@ -44656,13 +44656,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5231</v>
+        <v>-0.5229</v>
       </c>
       <c r="D3" t="n">
         <v>0.1068</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.733</v>
+        <v>-0.7328</v>
       </c>
       <c r="F3" t="n">
         <v>0.1068</v>
@@ -44671,7 +44671,7 @@
         <v>-0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5906</v>
+        <v>-0.59</v>
       </c>
       <c r="J3" t="n">
         <v>-1.5477</v>
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4593</v>
+        <v>-0.4592</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2002</v>
@@ -44693,7 +44693,7 @@
         <v>0.1583</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6137</v>
+        <v>-0.6136</v>
       </c>
       <c r="F4" t="n">
         <v>0.1583</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5664</v>
+        <v>-0.5658</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44718,7 +44718,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4292</v>
+        <v>-0.429</v>
       </c>
       <c r="C5" t="n">
         <v>-0.2012</v>
@@ -44727,7 +44727,7 @@
         <v>0.2203</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5915</v>
+        <v>-0.5914</v>
       </c>
       <c r="F5" t="n">
         <v>0.2203</v>
@@ -44739,7 +44739,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5431</v>
+        <v>-0.5425</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5329</v>
@@ -44752,7 +44752,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4305</v>
+        <v>-0.4304</v>
       </c>
       <c r="C6" t="n">
         <v>-0.2012</v>
@@ -44761,7 +44761,7 @@
         <v>0.2692</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6055</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>0.2692</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5341</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44786,7 +44786,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3819</v>
+        <v>-0.3817</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2098</v>
@@ -44795,7 +44795,7 @@
         <v>0.1458</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5138</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>0.1458</v>
@@ -44804,10 +44804,10 @@
         <v>-0.348</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4993</v>
+        <v>-0.4986</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44820,7 +44820,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.394</v>
+        <v>-0.3939</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2098</v>
@@ -44829,7 +44829,7 @@
         <v>0.1279</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5245</v>
+        <v>-0.5243</v>
       </c>
       <c r="F8" t="n">
         <v>0.1279</v>
@@ -44838,10 +44838,10 @@
         <v>-0.3807</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4182</v>
+        <v>-0.4174</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -44854,7 +44854,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3756</v>
+        <v>-0.3754</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2098</v>
@@ -44863,7 +44863,7 @@
         <v>0.1045</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4956</v>
+        <v>-0.4954</v>
       </c>
       <c r="F9" t="n">
         <v>0.1045</v>
@@ -44872,10 +44872,10 @@
         <v>-0.3297</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1513</v>
+        <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4163</v>
+        <v>-0.4156</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44888,7 +44888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3539</v>
+        <v>-0.3538</v>
       </c>
       <c r="C10" t="n">
         <v>-0.4074</v>
@@ -44897,7 +44897,7 @@
         <v>0.0919</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4654</v>
+        <v>-0.4653</v>
       </c>
       <c r="F10" t="n">
         <v>0.0919</v>
@@ -44909,7 +44909,7 @@
         <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3909</v>
+        <v>-0.3902</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2593</v>
@@ -44922,7 +44922,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3693</v>
+        <v>-0.3692</v>
       </c>
       <c r="C11" t="n">
         <v>-0.4074</v>
@@ -44931,7 +44931,7 @@
         <v>0.1034</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4875</v>
+        <v>-0.4873</v>
       </c>
       <c r="F11" t="n">
         <v>0.1034</v>
@@ -44943,7 +44943,7 @@
         <v>0.1635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.304</v>
+        <v>-0.3032</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2811</v>
@@ -44956,7 +44956,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.3168</v>
+        <v>-0.3167</v>
       </c>
       <c r="C12" t="n">
         <v>-0.4074</v>
@@ -44965,7 +44965,7 @@
         <v>0.1005</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4211</v>
+        <v>-0.4209</v>
       </c>
       <c r="F12" t="n">
         <v>0.1005</v>
@@ -44977,7 +44977,7 @@
         <v>0.1635</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2211</v>
+        <v>-0.2203</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2209</v>
@@ -44990,7 +44990,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.2946</v>
+        <v>-0.2944</v>
       </c>
       <c r="C13" t="n">
         <v>-0.4636</v>
@@ -44999,7 +44999,7 @@
         <v>0.1003</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3933</v>
+        <v>-0.3931</v>
       </c>
       <c r="F13" t="n">
         <v>0.1003</v>
@@ -45011,7 +45011,7 @@
         <v>0.3251</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1815</v>
+        <v>-0.1809</v>
       </c>
       <c r="J13" t="n">
         <v>-1.1549</v>
@@ -45024,7 +45024,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.3169</v>
+        <v>-0.3168</v>
       </c>
       <c r="C14" t="n">
         <v>-0.4636</v>
@@ -45033,7 +45033,7 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4202</v>
+        <v>-0.42</v>
       </c>
       <c r="F14" t="n">
         <v>0.09619999999999999</v>
@@ -45045,7 +45045,7 @@
         <v>0.3251</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2206</v>
+        <v>-0.2201</v>
       </c>
       <c r="J14" t="n">
         <v>-1.0677</v>
@@ -45058,7 +45058,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2901</v>
+        <v>-0.29</v>
       </c>
       <c r="C15" t="n">
         <v>-0.4636</v>
@@ -45067,7 +45067,7 @@
         <v>0.1053</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3889</v>
+        <v>-0.3888</v>
       </c>
       <c r="F15" t="n">
         <v>0.1053</v>
@@ -45079,7 +45079,7 @@
         <v>0.3251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.175</v>
+        <v>-0.1744</v>
       </c>
       <c r="J15" t="n">
         <v>-1.0238</v>
@@ -45092,7 +45092,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.2311</v>
+        <v>-0.231</v>
       </c>
       <c r="C16" t="n">
         <v>-0.5116000000000001</v>
@@ -45101,7 +45101,7 @@
         <v>0.0897</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3113</v>
+        <v>-0.3112</v>
       </c>
       <c r="F16" t="n">
         <v>0.0897</v>
@@ -45113,7 +45113,7 @@
         <v>0.4889</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1628</v>
+        <v>-0.1622</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0083</v>
@@ -45126,7 +45126,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.2624</v>
+        <v>-0.2623</v>
       </c>
       <c r="C17" t="n">
         <v>-0.5116000000000001</v>
@@ -45135,7 +45135,7 @@
         <v>-0.0547</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3143</v>
+        <v>-0.3142</v>
       </c>
       <c r="F17" t="n">
         <v>-0.0547</v>
@@ -45147,7 +45147,7 @@
         <v>0.4889</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1424</v>
+        <v>-0.1419</v>
       </c>
       <c r="J17" t="n">
         <v>-0.9249000000000001</v>
@@ -45160,7 +45160,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.2824</v>
+        <v>-0.2823</v>
       </c>
       <c r="C18" t="n">
         <v>-0.4936</v>
@@ -45169,7 +45169,7 @@
         <v>-0.0315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3451</v>
+        <v>-0.345</v>
       </c>
       <c r="F18" t="n">
         <v>-0.0315</v>
@@ -45181,7 +45181,7 @@
         <v>0.4889</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2342</v>
+        <v>-0.2338</v>
       </c>
       <c r="J18" t="n">
         <v>-0.8802</v>
@@ -45194,7 +45194,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3047</v>
       </c>
       <c r="C19" t="n">
         <v>-0.534</v>
@@ -45203,7 +45203,7 @@
         <v>0.0354</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3899</v>
+        <v>-0.3897</v>
       </c>
       <c r="F19" t="n">
         <v>0.0354</v>
@@ -45215,7 +45215,7 @@
         <v>0.4155</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2011</v>
+        <v>-0.2005</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8472</v>
@@ -45228,7 +45228,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.329</v>
+        <v>-0.3289</v>
       </c>
       <c r="C20" t="n">
         <v>-0.415</v>
@@ -45237,7 +45237,7 @@
         <v>0.013</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4145</v>
+        <v>-0.4143</v>
       </c>
       <c r="F20" t="n">
         <v>0.013</v>
@@ -45249,7 +45249,7 @@
         <v>0.4155</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.16</v>
+        <v>-0.1594</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8268</v>
@@ -45262,7 +45262,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.2913</v>
+        <v>-0.2912</v>
       </c>
       <c r="C21" t="n">
         <v>-0.32</v>
@@ -45271,7 +45271,7 @@
         <v>0.1084</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3913</v>
+        <v>-0.3911</v>
       </c>
       <c r="F21" t="n">
         <v>0.1084</v>
@@ -45283,7 +45283,7 @@
         <v>0.4155</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1452</v>
+        <v>-0.1446</v>
       </c>
       <c r="J21" t="n">
         <v>-0.8549</v>
@@ -45296,7 +45296,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.3088</v>
+        <v>-0.3087</v>
       </c>
       <c r="C22" t="n">
         <v>-0.4462</v>
@@ -45305,7 +45305,7 @@
         <v>0.1088</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4132</v>
+        <v>-0.4131</v>
       </c>
       <c r="F22" t="n">
         <v>0.1088</v>
@@ -45314,10 +45314,10 @@
         <v>-1.0842</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.111</v>
+        <v>-0.1104</v>
       </c>
       <c r="J22" t="n">
         <v>-0.6861</v>
@@ -45330,7 +45330,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3647</v>
+        <v>-0.3646</v>
       </c>
       <c r="C23" t="n">
         <v>-0.4532</v>
@@ -45339,7 +45339,7 @@
         <v>0.0237</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4618</v>
+        <v>-0.4617</v>
       </c>
       <c r="F23" t="n">
         <v>0.0237</v>
@@ -45348,10 +45348,10 @@
         <v>-1.3515</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0567</v>
+        <v>-0.0561</v>
       </c>
       <c r="J23" t="n">
         <v>-0.6675</v>
@@ -45364,7 +45364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3506</v>
+        <v>-0.3505</v>
       </c>
       <c r="C24" t="n">
         <v>-0.4502</v>
@@ -45373,7 +45373,7 @@
         <v>0.0522</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4513</v>
+        <v>-0.4512</v>
       </c>
       <c r="F24" t="n">
         <v>0.0522</v>
@@ -45382,10 +45382,10 @@
         <v>-1.2706</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J24" t="n">
         <v>-0.6834</v>
@@ -45398,7 +45398,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.328</v>
+        <v>-0.3279</v>
       </c>
       <c r="C25" t="n">
         <v>-0.4581</v>
@@ -45407,7 +45407,7 @@
         <v>0.0978</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4345</v>
+        <v>-0.4343</v>
       </c>
       <c r="F25" t="n">
         <v>0.0978</v>
@@ -45419,7 +45419,7 @@
         <v>0.3191</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0514</v>
+        <v>-0.0509</v>
       </c>
       <c r="J25" t="n">
         <v>-0.6254</v>
@@ -45432,7 +45432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3265</v>
+        <v>-0.3264</v>
       </c>
       <c r="C26" t="n">
         <v>-0.4461</v>
@@ -45441,7 +45441,7 @@
         <v>-0.0392</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3984</v>
+        <v>-0.3982</v>
       </c>
       <c r="F26" t="n">
         <v>-0.0392</v>
@@ -45453,7 +45453,7 @@
         <v>0.3191</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0223</v>
+        <v>0.0228</v>
       </c>
       <c r="J26" t="n">
         <v>-0.5208</v>
@@ -45466,7 +45466,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3364</v>
+        <v>-0.3363</v>
       </c>
       <c r="C27" t="n">
         <v>-0.3561</v>
@@ -45475,7 +45475,7 @@
         <v>-0.078</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.401</v>
+        <v>-0.4009</v>
       </c>
       <c r="F27" t="n">
         <v>-0.078</v>
@@ -45487,7 +45487,7 @@
         <v>0.3191</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0422</v>
+        <v>0.0427</v>
       </c>
       <c r="J27" t="n">
         <v>-0.5181</v>
@@ -45500,7 +45500,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3842</v>
+        <v>-0.3841</v>
       </c>
       <c r="C28" t="n">
         <v>-0.1935</v>
@@ -45509,7 +45509,7 @@
         <v>-0.1722</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4372</v>
+        <v>-0.4371</v>
       </c>
       <c r="F28" t="n">
         <v>-0.1722</v>
@@ -45518,10 +45518,10 @@
         <v>-1.4983</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0148</v>
+        <v>-0.0143</v>
       </c>
       <c r="J28" t="n">
         <v>-0.4641</v>
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3827</v>
+        <v>-0.3826</v>
       </c>
       <c r="C29" t="n">
         <v>-0.1915</v>
@@ -45543,7 +45543,7 @@
         <v>-0.0907</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4557</v>
+        <v>-0.4556</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0907</v>
@@ -45552,10 +45552,10 @@
         <v>-1.7413</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0408</v>
+        <v>0.0413</v>
       </c>
       <c r="J29" t="n">
         <v>-0.3507</v>
@@ -45568,7 +45568,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3884</v>
+        <v>-0.3883</v>
       </c>
       <c r="C30" t="n">
         <v>-0.1815</v>
@@ -45577,7 +45577,7 @@
         <v>-0.1171</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4563</v>
+        <v>-0.4561</v>
       </c>
       <c r="F30" t="n">
         <v>-0.1171</v>
@@ -45586,10 +45586,10 @@
         <v>-1.6821</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2283</v>
+        <v>0.2284</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0735</v>
+        <v>0.074</v>
       </c>
       <c r="J30" t="n">
         <v>-0.4449</v>
@@ -45602,7 +45602,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3568</v>
+        <v>-0.3567</v>
       </c>
       <c r="C31" t="n">
         <v>-0.3423</v>
@@ -45611,7 +45611,7 @@
         <v>-0.1824</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4004</v>
+        <v>-0.4003</v>
       </c>
       <c r="F31" t="n">
         <v>-0.1824</v>
@@ -45620,10 +45620,10 @@
         <v>-1.7109</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3187</v>
+        <v>0.3188</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1243</v>
+        <v>0.1249</v>
       </c>
       <c r="J31" t="n">
         <v>-0.3338</v>
@@ -45636,7 +45636,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3835</v>
+        <v>-0.3834</v>
       </c>
       <c r="C32" t="n">
         <v>-0.3533</v>
@@ -45645,7 +45645,7 @@
         <v>-0.175</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4357</v>
+        <v>-0.4355</v>
       </c>
       <c r="F32" t="n">
         <v>-0.175</v>
@@ -45654,10 +45654,10 @@
         <v>-1.9384</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3187</v>
+        <v>0.3188</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0693</v>
+        <v>0.0698</v>
       </c>
       <c r="J32" t="n">
         <v>-0.1923</v>
@@ -45670,7 +45670,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3629</v>
+        <v>-0.3628</v>
       </c>
       <c r="C33" t="n">
         <v>-0.3673</v>
@@ -45679,7 +45679,7 @@
         <v>-0.1099</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4261</v>
+        <v>-0.426</v>
       </c>
       <c r="F33" t="n">
         <v>-0.1099</v>
@@ -45688,10 +45688,10 @@
         <v>-1.7716</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3187</v>
+        <v>0.3188</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0566</v>
+        <v>-0.0561</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1949</v>
@@ -45704,7 +45704,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3826</v>
+        <v>-0.3825</v>
       </c>
       <c r="C34" t="n">
         <v>-0.4155</v>
@@ -45713,7 +45713,7 @@
         <v>-0.09859999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4536</v>
+        <v>-0.4535</v>
       </c>
       <c r="F34" t="n">
         <v>-0.09859999999999999</v>
@@ -45722,10 +45722,10 @@
         <v>-1.7575</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1178</v>
+        <v>-0.1173</v>
       </c>
       <c r="J34" t="n">
         <v>-0.1277</v>
@@ -45738,7 +45738,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3888</v>
+        <v>-0.3887</v>
       </c>
       <c r="C35" t="n">
         <v>-0.4195</v>
@@ -45747,7 +45747,7 @@
         <v>-0.0027</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4854</v>
+        <v>-0.4852</v>
       </c>
       <c r="F35" t="n">
         <v>-0.0027</v>
@@ -45756,10 +45756,10 @@
         <v>-1.9436</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1115</v>
+        <v>-0.1111</v>
       </c>
       <c r="J35" t="n">
         <v>-0.075</v>
@@ -45772,7 +45772,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2966</v>
+        <v>-0.2965</v>
       </c>
       <c r="C36" t="n">
         <v>-0.4255</v>
@@ -45781,7 +45781,7 @@
         <v>0.1653</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4121</v>
+        <v>-0.4119</v>
       </c>
       <c r="F36" t="n">
         <v>0.1653</v>
@@ -45790,10 +45790,10 @@
         <v>-1.6423</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1886</v>
+        <v>0.1887</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2358</v>
+        <v>-0.2353</v>
       </c>
       <c r="J36" t="n">
         <v>0.0412</v>
@@ -45806,7 +45806,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.285</v>
+        <v>-0.2849</v>
       </c>
       <c r="C37" t="n">
         <v>-0.4583</v>
@@ -45815,7 +45815,7 @@
         <v>0.4868</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4779</v>
+        <v>-0.4778</v>
       </c>
       <c r="F37" t="n">
         <v>0.4868</v>
@@ -45827,7 +45827,7 @@
         <v>0.0667</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2451</v>
+        <v>-0.2446</v>
       </c>
       <c r="J37" t="n">
         <v>0.0238</v>
@@ -45840,7 +45840,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.2643</v>
+        <v>-0.2642</v>
       </c>
       <c r="C38" t="n">
         <v>-0.4533</v>
@@ -45849,7 +45849,7 @@
         <v>0.4008</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.4306</v>
+        <v>-0.4305</v>
       </c>
       <c r="F38" t="n">
         <v>0.4008</v>
@@ -45861,7 +45861,7 @@
         <v>0.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3821</v>
+        <v>-0.3815</v>
       </c>
       <c r="J38" t="n">
         <v>0.1937</v>
@@ -45874,7 +45874,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.2765</v>
+        <v>-0.2764</v>
       </c>
       <c r="C39" t="n">
         <v>-0.4513</v>
@@ -45883,7 +45883,7 @@
         <v>0.4916</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.4686</v>
+        <v>-0.4684</v>
       </c>
       <c r="F39" t="n">
         <v>0.4916</v>
@@ -45895,7 +45895,7 @@
         <v>0.0667</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4184</v>
+        <v>-0.4179</v>
       </c>
       <c r="J39" t="n">
         <v>0.1293</v>
@@ -45908,7 +45908,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3454</v>
+        <v>-0.3453</v>
       </c>
       <c r="C40" t="n">
         <v>-0.3972</v>
@@ -45917,7 +45917,7 @@
         <v>0.6104000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5843</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="F40" t="n">
         <v>0.6104000000000001</v>
@@ -45926,10 +45926,10 @@
         <v>-1.7344</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.3119</v>
+        <v>-0.312</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5682</v>
+        <v>-0.5678</v>
       </c>
       <c r="J40" t="n">
         <v>0.2773</v>
@@ -45951,7 +45951,7 @@
         <v>0.4132</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5606</v>
+        <v>-0.5605</v>
       </c>
       <c r="F41" t="n">
         <v>0.4132</v>
@@ -45960,10 +45960,10 @@
         <v>-1.6924</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3119</v>
+        <v>-0.312</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.555</v>
+        <v>-0.5546</v>
       </c>
       <c r="J41" t="n">
         <v>0.3169</v>
@@ -45985,7 +45985,7 @@
         <v>0.5652</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5155</v>
+        <v>-0.5154</v>
       </c>
       <c r="F42" t="n">
         <v>0.5652</v>
@@ -45994,10 +45994,10 @@
         <v>-1.6122</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3119</v>
+        <v>-0.312</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5531</v>
+        <v>-0.5527</v>
       </c>
       <c r="J42" t="n">
         <v>0.4153</v>
@@ -46010,7 +46010,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3256</v>
+        <v>-0.3255</v>
       </c>
       <c r="C43" t="n">
         <v>-0.5</v>
@@ -46019,7 +46019,7 @@
         <v>0.7407</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.5921</v>
       </c>
       <c r="F43" t="n">
         <v>0.7407</v>
@@ -46031,7 +46031,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5234</v>
+        <v>-0.523</v>
       </c>
       <c r="J43" t="n">
         <v>0.4481</v>
@@ -46044,7 +46044,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.238</v>
+        <v>-0.2379</v>
       </c>
       <c r="C44" t="n">
         <v>-0.506</v>
@@ -46053,7 +46053,7 @@
         <v>1.0016</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.5478</v>
       </c>
       <c r="F44" t="n">
         <v>1.0016</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5697</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46078,7 +46078,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.2102</v>
+        <v>-0.2101</v>
       </c>
       <c r="C45" t="n">
         <v>-0.505</v>
@@ -46087,7 +46087,7 @@
         <v>1.0383</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5224</v>
+        <v>-0.5222</v>
       </c>
       <c r="F45" t="n">
         <v>1.0383</v>
@@ -46099,7 +46099,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5687</v>
+        <v>-0.5681</v>
       </c>
       <c r="J45" t="n">
         <v>0.613</v>
@@ -46112,7 +46112,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.3811</v>
+        <v>-0.381</v>
       </c>
       <c r="C46" t="n">
         <v>-0.6071</v>
@@ -46121,7 +46121,7 @@
         <v>0.9778</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.7209</v>
+        <v>-0.7207</v>
       </c>
       <c r="F46" t="n">
         <v>0.9778</v>
@@ -46130,10 +46130,10 @@
         <v>-1.8259</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.9865</v>
+        <v>-0.9866</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6515</v>
+        <v>-0.6509</v>
       </c>
       <c r="J46" t="n">
         <v>0.5804</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4055</v>
+        <v>-0.4053</v>
       </c>
       <c r="C47" t="n">
         <v>-0.6151</v>
@@ -46155,7 +46155,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.7052</v>
+        <v>-0.705</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -46164,10 +46164,10 @@
         <v>-1.7419</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.9865</v>
+        <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8344</v>
+        <v>-0.8337</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46180,7 +46180,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4322</v>
+        <v>-0.4321</v>
       </c>
       <c r="C48" t="n">
         <v>-0.8011</v>
@@ -46189,7 +46189,7 @@
         <v>0.4542</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6539</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="F48" t="n">
         <v>0.4542</v>
@@ -46198,10 +46198,10 @@
         <v>-1.4528</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.9865</v>
+        <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9268</v>
+        <v>-0.9262</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46223,7 +46223,7 @@
         <v>-0.0883</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0044</v>
+        <v>-1.0043</v>
       </c>
       <c r="F49" t="n">
         <v>-0.0883</v>
@@ -46232,10 +46232,10 @@
         <v>-1.6067</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.1653</v>
+        <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0512</v>
+        <v>-1.0507</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46248,7 +46248,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.7464</v>
       </c>
       <c r="C50" t="n">
         <v>-0.3217</v>
@@ -46257,7 +46257,7 @@
         <v>0.1309</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.9658</v>
+        <v>-0.9657</v>
       </c>
       <c r="F50" t="n">
         <v>0.1309</v>
@@ -46266,10 +46266,10 @@
         <v>-1.3388</v>
       </c>
       <c r="H50" t="n">
-        <v>-2.1653</v>
+        <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0875</v>
+        <v>-1.087</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46282,7 +46282,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7746</v>
       </c>
       <c r="C51" t="n">
         <v>-0.3307</v>
@@ -46291,7 +46291,7 @@
         <v>0.1167</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9976</v>
+        <v>-0.9974</v>
       </c>
       <c r="F51" t="n">
         <v>0.1167</v>
@@ -46300,10 +46300,10 @@
         <v>-1.2704</v>
       </c>
       <c r="H51" t="n">
-        <v>-2.1653</v>
+        <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.092</v>
+        <v>-1.0914</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46325,7 +46325,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.3452</v>
+        <v>-1.3451</v>
       </c>
       <c r="F52" t="n">
         <v>0.06900000000000001</v>
@@ -46334,10 +46334,10 @@
         <v>-1.3636</v>
       </c>
       <c r="H52" t="n">
-        <v>-3.3977</v>
+        <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0097</v>
+        <v>-1.009</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46359,7 +46359,7 @@
         <v>0.061</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.3365</v>
+        <v>-1.3364</v>
       </c>
       <c r="F53" t="n">
         <v>0.061</v>
@@ -46368,10 +46368,10 @@
         <v>-1.0891</v>
       </c>
       <c r="H53" t="n">
-        <v>-3.3977</v>
+        <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9846</v>
+        <v>-0.9839</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.1467</v>
+        <v>-1.1466</v>
       </c>
       <c r="C54" t="n">
         <v>0.2814</v>
@@ -46393,7 +46393,7 @@
         <v>-0.331</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.3506</v>
+        <v>-1.3505</v>
       </c>
       <c r="F54" t="n">
         <v>-0.331</v>
@@ -46402,10 +46402,10 @@
         <v>-0.9853</v>
       </c>
       <c r="H54" t="n">
-        <v>-3.3977</v>
+        <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0103</v>
+        <v>-1.0098</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46427,7 +46427,7 @@
         <v>-0.5726</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2875</v>
+        <v>-1.2874</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5726</v>
@@ -46436,10 +46436,10 @@
         <v>-1.1684</v>
       </c>
       <c r="H55" t="n">
-        <v>-2.8234</v>
+        <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9828</v>
+        <v>-0.9822</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46461,7 +46461,7 @@
         <v>-0.8169999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.2736</v>
+        <v>-1.2735</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8169999999999999</v>
@@ -46470,10 +46470,10 @@
         <v>-0.9601</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.8234</v>
+        <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0366</v>
+        <v>-1.0362</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46495,7 +46495,7 @@
         <v>-0.895</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2978</v>
+        <v>-1.2977</v>
       </c>
       <c r="F57" t="n">
         <v>-0.895</v>
@@ -46504,10 +46504,10 @@
         <v>-0.9540999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.8234</v>
+        <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0161</v>
+        <v>-1.0157</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46529,7 +46529,7 @@
         <v>-0.8349</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.2702</v>
+        <v>-1.2701</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8349</v>
@@ -46538,10 +46538,10 @@
         <v>-0.9547</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.3758</v>
+        <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0751</v>
+        <v>-1.0748</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1662</v>
+        <v>-1.1661</v>
       </c>
       <c r="C59" t="n">
         <v>0.7284</v>
@@ -46563,7 +46563,7 @@
         <v>-0.8138</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.2543</v>
+        <v>-1.2542</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8138</v>
@@ -46572,10 +46572,10 @@
         <v>-0.7307</v>
       </c>
       <c r="H59" t="n">
-        <v>-2.3758</v>
+        <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0753</v>
+        <v>-1.075</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46597,7 +46597,7 @@
         <v>-0.5429</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.2862</v>
+        <v>-1.2861</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5429</v>
@@ -46606,10 +46606,10 @@
         <v>-0.6816</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.3758</v>
+        <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1066</v>
+        <v>-1.1063</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46622,7 +46622,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.1031</v>
+        <v>-1.103</v>
       </c>
       <c r="C61" t="n">
         <v>0.5718</v>
@@ -46631,7 +46631,7 @@
         <v>-0.3888</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.2817</v>
+        <v>-1.2816</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3888</v>
@@ -46640,10 +46640,10 @@
         <v>-0.7097</v>
       </c>
       <c r="H61" t="n">
-        <v>-2.1921</v>
+        <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0804</v>
+        <v>-1.0801</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46674,10 +46674,10 @@
         <v>-0.5488</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.1921</v>
+        <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0538</v>
+        <v>-1.0535</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46690,7 +46690,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1074</v>
+        <v>-1.1073</v>
       </c>
       <c r="C63" t="n">
         <v>0.5718</v>
@@ -46708,10 +46708,10 @@
         <v>-0.5744</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.1921</v>
+        <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0905</v>
+        <v>-1.0902</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.0999</v>
+        <v>-1.0998</v>
       </c>
       <c r="C64" t="n">
         <v>0.5042</v>
@@ -46733,7 +46733,7 @@
         <v>-0.2631</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3091</v>
+        <v>-1.309</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2631</v>
@@ -46742,10 +46742,10 @@
         <v>-0.6361</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.8274</v>
+        <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0759</v>
+        <v>-1.0756</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46767,7 +46767,7 @@
         <v>-0.3032</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.2295</v>
+        <v>-1.2294</v>
       </c>
       <c r="F65" t="n">
         <v>-0.3032</v>
@@ -46776,10 +46776,10 @@
         <v>-0.2958</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.8274</v>
+        <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0177</v>
+        <v>-1.0174</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46792,7 +46792,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0533</v>
+        <v>-1.0532</v>
       </c>
       <c r="C66" t="n">
         <v>0.4982</v>
@@ -46801,7 +46801,7 @@
         <v>-0.2093</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2643</v>
+        <v>-1.2642</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2093</v>
@@ -46810,10 +46810,10 @@
         <v>-0.2612</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.8274</v>
+        <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0499</v>
+        <v>-1.0495</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46835,7 +46835,7 @@
         <v>-0.1883</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.241</v>
+        <v>-1.2409</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1883</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0826</v>
+        <v>-1.0822</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46860,7 +46860,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0286</v>
+        <v>-1.0285</v>
       </c>
       <c r="C68" t="n">
         <v>0.453</v>
@@ -46869,7 +46869,7 @@
         <v>-0.2742</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2172</v>
+        <v>-1.2171</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2742</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1493</v>
+        <v>-1.149</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46903,7 +46903,7 @@
         <v>-0.2627</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2114</v>
+        <v>-1.2113</v>
       </c>
       <c r="F69" t="n">
         <v>-0.2627</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.182</v>
+        <v>-1.1817</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46937,7 +46937,7 @@
         <v>-0.2939</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1531</v>
+        <v>-1.153</v>
       </c>
       <c r="F70" t="n">
         <v>-0.2939</v>
@@ -46946,10 +46946,10 @@
         <v>-0.3348</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0937</v>
+        <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1961</v>
+        <v>-1.1959</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46971,7 +46971,7 @@
         <v>-0.111</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0947</v>
+        <v>-1.0946</v>
       </c>
       <c r="F71" t="n">
         <v>-0.111</v>
@@ -46980,10 +46980,10 @@
         <v>-0.1346</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.0937</v>
+        <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2205</v>
+        <v>-1.2204</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47005,7 +47005,7 @@
         <v>-0.151</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0968</v>
+        <v>-1.0967</v>
       </c>
       <c r="F72" t="n">
         <v>-0.151</v>
@@ -47014,10 +47014,10 @@
         <v>-0.23</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0937</v>
+        <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2137</v>
+        <v>-1.2136</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1919</v>
+        <v>-1.1918</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47064,7 +47064,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8376</v>
+        <v>-0.8375</v>
       </c>
       <c r="C74" t="n">
         <v>0.299</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1882</v>
+        <v>-1.1881</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47166,7 +47166,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7382</v>
+        <v>-0.7381</v>
       </c>
       <c r="C77" t="n">
         <v>0.107</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.197</v>
+        <v>-1.1969</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47252,7 +47252,7 @@
         <v>-0.1981</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.7734</v>
+        <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
         <v>-1.2426</v>
@@ -47286,7 +47286,7 @@
         <v>-0.0208</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.7734</v>
+        <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
         <v>-1.2557</v>
@@ -47320,10 +47320,10 @@
         <v>-0.009900000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.7734</v>
+        <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3021</v>
+        <v>-1.302</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6203</v>
+        <v>-0.6202</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0603</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3039</v>
+        <v>-1.3038</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47456,10 +47456,10 @@
         <v>-0.0066</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.6</v>
+        <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3175</v>
+        <v>-1.3174</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47481,7 +47481,7 @@
         <v>0.2359</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.796</v>
       </c>
       <c r="F86" t="n">
         <v>0.2359</v>
@@ -47490,7 +47490,7 @@
         <v>-0.0658</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.6</v>
+        <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
         <v>-1.3187</v>
@@ -47524,10 +47524,10 @@
         <v>0.17</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.6</v>
+        <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.277</v>
+        <v>-1.2769</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47558,7 +47558,7 @@
         <v>0.0403</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.673</v>
+        <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
         <v>-1.216</v>
@@ -47592,7 +47592,7 @@
         <v>-0.1356</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.673</v>
+        <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
         <v>-1.2232</v>
@@ -47626,10 +47626,10 @@
         <v>0.1537</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.673</v>
+        <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2715</v>
+        <v>-1.2714</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47651,7 +47651,7 @@
         <v>0.1753</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6446</v>
+        <v>-0.6445</v>
       </c>
       <c r="F91" t="n">
         <v>0.1753</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2753</v>
+        <v>-1.2752</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2938</v>
+        <v>-1.2937</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47762,10 +47762,10 @@
         <v>0.1401</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.4521</v>
+        <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2993</v>
+        <v>-1.2992</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47796,10 +47796,10 @@
         <v>0.0367</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.4521</v>
+        <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2865</v>
+        <v>-1.2864</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47830,10 +47830,10 @@
         <v>0.2315</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.4521</v>
+        <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2373</v>
+        <v>-1.2372</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47864,10 +47864,10 @@
         <v>0.0827</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.5036</v>
+        <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1812</v>
+        <v>-1.1811</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47880,7 +47880,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3783</v>
+        <v>-0.3782</v>
       </c>
       <c r="C98" t="n">
         <v>-0.6211</v>
@@ -47898,10 +47898,10 @@
         <v>0.0604</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.5036</v>
+        <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0552</v>
+        <v>-1.055</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3006</v>
+        <v>-0.3005</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
@@ -47932,10 +47932,10 @@
         <v>0.3344</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.5036</v>
+        <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9618</v>
+        <v>-0.9615</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -47948,7 +47948,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.281</v>
+        <v>-0.2809</v>
       </c>
       <c r="C100" t="n">
         <v>-0.6868</v>
@@ -47966,10 +47966,10 @@
         <v>0.3172</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.4699</v>
+        <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9103</v>
+        <v>-0.91</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -47982,7 +47982,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.3328</v>
+        <v>-0.3327</v>
       </c>
       <c r="C101" t="n">
         <v>-0.6928</v>
@@ -47991,7 +47991,7 @@
         <v>0.1061</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.4425</v>
+        <v>-0.4424</v>
       </c>
       <c r="F101" t="n">
         <v>0.1061</v>
@@ -48000,10 +48000,10 @@
         <v>0.0568</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.4699</v>
+        <v>-0.47</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8369</v>
+        <v>-0.8367</v>
       </c>
       <c r="J101" t="n">
         <v>-0.5199</v>
@@ -48034,10 +48034,10 @@
         <v>0.3651</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.4699</v>
+        <v>-0.47</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7392</v>
+        <v>-0.739</v>
       </c>
       <c r="J102" t="n">
         <v>-0.3549</v>
@@ -48050,7 +48050,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.1475</v>
+        <v>-0.1474</v>
       </c>
       <c r="C103" t="n">
         <v>-0.7114</v>
@@ -48059,7 +48059,7 @@
         <v>0.3906</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.282</v>
+        <v>-0.2819</v>
       </c>
       <c r="F103" t="n">
         <v>0.3906</v>
@@ -48068,10 +48068,10 @@
         <v>0.3936</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.2905</v>
+        <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.804</v>
+        <v>-0.8037</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48093,7 +48093,7 @@
         <v>0.5312</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.2786</v>
+        <v>-0.2785</v>
       </c>
       <c r="F104" t="n">
         <v>0.5312</v>
@@ -48102,10 +48102,10 @@
         <v>0.2106</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.2905</v>
+        <v>-0.2906</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7302</v>
+        <v>-0.73</v>
       </c>
       <c r="J104" t="n">
         <v>-0.3041</v>
@@ -48136,10 +48136,10 @@
         <v>0.4707</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.2905</v>
+        <v>-0.2906</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7498</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="J105" t="n">
         <v>-0.3022</v>
@@ -48152,7 +48152,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.0732</v>
+        <v>-0.0731</v>
       </c>
       <c r="C106" t="n">
         <v>-0.8269</v>
@@ -48170,10 +48170,10 @@
         <v>0.2823</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.1604</v>
+        <v>-0.1605</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.699</v>
+        <v>-0.6988</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3368</v>
@@ -48195,7 +48195,7 @@
         <v>0.6533</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.2563</v>
+        <v>-0.2562</v>
       </c>
       <c r="F107" t="n">
         <v>0.6533</v>
@@ -48204,10 +48204,10 @@
         <v>0.1964</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.1604</v>
+        <v>-0.1605</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.713</v>
+        <v>-0.7129</v>
       </c>
       <c r="J107" t="n">
         <v>-0.348</v>
@@ -48238,10 +48238,10 @@
         <v>0.4342</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.1604</v>
+        <v>-0.1605</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6425</v>
       </c>
       <c r="J108" t="n">
         <v>-0.3957</v>
@@ -48272,10 +48272,10 @@
         <v>0.3113</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.0185</v>
+        <v>-0.0186</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5739</v>
+        <v>-0.5736</v>
       </c>
       <c r="J109" t="n">
         <v>-0.3653</v>
@@ -48288,7 +48288,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.057</v>
+        <v>0.0571</v>
       </c>
       <c r="C110" t="n">
         <v>-0.8542999999999999</v>
@@ -48297,7 +48297,7 @@
         <v>0.8839</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1497</v>
+        <v>-0.1496</v>
       </c>
       <c r="F110" t="n">
         <v>0.8839</v>
@@ -48306,10 +48306,10 @@
         <v>0.2409</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.0185</v>
+        <v>-0.0186</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5584</v>
+        <v>-0.5581</v>
       </c>
       <c r="J110" t="n">
         <v>-0.2626</v>
@@ -48331,7 +48331,7 @@
         <v>0.8897</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.0969</v>
+        <v>-0.0968</v>
       </c>
       <c r="F111" t="n">
         <v>0.8897</v>
@@ -48340,10 +48340,10 @@
         <v>0.5133</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.0185</v>
+        <v>-0.0186</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5824</v>
+        <v>-0.5821</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2998</v>
@@ -48365,7 +48365,7 @@
         <v>0.8887</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="F112" t="n">
         <v>0.8887</v>
@@ -48374,10 +48374,10 @@
         <v>0.4536</v>
       </c>
       <c r="H112" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5582</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2325</v>
@@ -48408,10 +48408,10 @@
         <v>0.2628</v>
       </c>
       <c r="H113" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5375</v>
+        <v>-0.5372</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2751</v>
@@ -48442,10 +48442,10 @@
         <v>0.6371</v>
       </c>
       <c r="H114" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5452</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J114" t="n">
         <v>-0.1624</v>
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3435</v>
+        <v>0.3436</v>
       </c>
       <c r="C115" t="n">
         <v>-1.072</v>
@@ -48467,7 +48467,7 @@
         <v>1.7505</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0081</v>
       </c>
       <c r="F115" t="n">
         <v>1.7505</v>
@@ -48479,7 +48479,7 @@
         <v>0.3854</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5135</v>
+        <v>-0.5133</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2898</v>
@@ -48501,7 +48501,7 @@
         <v>1.7569</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="F116" t="n">
         <v>1.7569</v>
@@ -48513,7 +48513,7 @@
         <v>0.3854</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4866</v>
+        <v>-0.4864</v>
       </c>
       <c r="J116" t="n">
         <v>-0.2774</v>
@@ -48547,7 +48547,7 @@
         <v>0.3854</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4524</v>
+        <v>-0.4522</v>
       </c>
       <c r="J117" t="n">
         <v>-0.2606</v>
@@ -48581,7 +48581,7 @@
         <v>0.3858</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3591</v>
+        <v>-0.3588</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1556</v>
@@ -48594,7 +48594,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4029</v>
+        <v>0.403</v>
       </c>
       <c r="C119" t="n">
         <v>-1.1</v>
@@ -48603,7 +48603,7 @@
         <v>1.5836</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1077</v>
+        <v>0.1078</v>
       </c>
       <c r="F119" t="n">
         <v>1.5836</v>
@@ -48615,7 +48615,7 @@
         <v>0.3858</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3516</v>
+        <v>-0.3512</v>
       </c>
       <c r="J119" t="n">
         <v>-0.1251</v>
@@ -48628,7 +48628,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.3946</v>
+        <v>0.3947</v>
       </c>
       <c r="C120" t="n">
         <v>-1.094</v>
@@ -48637,7 +48637,7 @@
         <v>1.4582</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1287</v>
+        <v>0.1289</v>
       </c>
       <c r="F120" t="n">
         <v>1.4582</v>
@@ -48649,7 +48649,7 @@
         <v>0.3858</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1654</v>
+        <v>-0.165</v>
       </c>
       <c r="J120" t="n">
         <v>-0.1869</v>
@@ -48662,7 +48662,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2052</v>
+        <v>0.2053</v>
       </c>
       <c r="C121" t="n">
         <v>-1</v>
@@ -48671,7 +48671,7 @@
         <v>0.3528</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1683</v>
+        <v>0.1684</v>
       </c>
       <c r="F121" t="n">
         <v>0.3528</v>
@@ -48680,10 +48680,10 @@
         <v>0.5189</v>
       </c>
       <c r="H121" t="n">
-        <v>0.3803</v>
+        <v>0.3802</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.0856</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>-0.1406</v>
@@ -48696,7 +48696,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4066</v>
+        <v>0.4067</v>
       </c>
       <c r="C122" t="n">
         <v>-0.994</v>
@@ -48705,7 +48705,7 @@
         <v>1.355</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1695</v>
+        <v>0.1696</v>
       </c>
       <c r="F122" t="n">
         <v>1.355</v>
@@ -48714,10 +48714,10 @@
         <v>0.5226</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3803</v>
+        <v>0.3802</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0922</v>
+        <v>-0.0917</v>
       </c>
       <c r="J122" t="n">
         <v>-0.1326</v>
@@ -48739,7 +48739,7 @@
         <v>1.2439</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1921</v>
+        <v>0.1922</v>
       </c>
       <c r="F123" t="n">
         <v>1.2439</v>
@@ -48748,10 +48748,10 @@
         <v>0.6441</v>
       </c>
       <c r="H123" t="n">
-        <v>0.3803</v>
+        <v>0.3802</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0615</v>
+        <v>-0.061</v>
       </c>
       <c r="J123" t="n">
         <v>-0.1944</v>
@@ -48764,7 +48764,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4995</v>
+        <v>0.4996</v>
       </c>
       <c r="C124" t="n">
         <v>-0.9419999999999999</v>
@@ -48773,7 +48773,7 @@
         <v>1.2804</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3043</v>
+        <v>0.3044</v>
       </c>
       <c r="F124" t="n">
         <v>1.2804</v>
@@ -48785,7 +48785,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0014</v>
+        <v>-0.001</v>
       </c>
       <c r="J124" t="n">
         <v>-0.1048</v>
@@ -48798,7 +48798,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.3513</v>
+        <v>0.3514</v>
       </c>
       <c r="C125" t="n">
         <v>-0.951</v>
@@ -48807,7 +48807,7 @@
         <v>0.5219</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3087</v>
+        <v>0.3088</v>
       </c>
       <c r="F125" t="n">
         <v>0.5219</v>
@@ -48819,7 +48819,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>0.002</v>
+        <v>0.0023</v>
       </c>
       <c r="J125" t="n">
         <v>-0.095</v>
@@ -48832,7 +48832,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3351</v>
+        <v>0.3352</v>
       </c>
       <c r="C126" t="n">
         <v>-0.9429999999999999</v>
@@ -48841,7 +48841,7 @@
         <v>0.4295</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3115</v>
+        <v>0.3116</v>
       </c>
       <c r="F126" t="n">
         <v>0.4295</v>
@@ -48853,7 +48853,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0597</v>
+        <v>0.0601</v>
       </c>
       <c r="J126" t="n">
         <v>-0.2019</v>
@@ -48866,7 +48866,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.3342</v>
+        <v>0.3343</v>
       </c>
       <c r="C127" t="n">
         <v>-0.9389999999999999</v>
@@ -48875,7 +48875,7 @@
         <v>0.3784</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3232</v>
+        <v>0.3233</v>
       </c>
       <c r="F127" t="n">
         <v>0.3784</v>
@@ -48887,7 +48887,7 @@
         <v>0.7683</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1115</v>
+        <v>0.1119</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0956</v>
@@ -48900,7 +48900,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.3239</v>
+        <v>0.324</v>
       </c>
       <c r="C128" t="n">
         <v>-0.9370000000000001</v>
@@ -48909,7 +48909,7 @@
         <v>0.2942</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3313</v>
+        <v>0.3314</v>
       </c>
       <c r="F128" t="n">
         <v>0.2942</v>
@@ -48921,7 +48921,7 @@
         <v>0.7683</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1203</v>
+        <v>0.1207</v>
       </c>
       <c r="J128" t="n">
         <v>-0.1184</v>
@@ -48943,7 +48943,7 @@
         <v>0.2549</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3953</v>
+        <v>0.3954</v>
       </c>
       <c r="F129" t="n">
         <v>0.2549</v>
@@ -48955,7 +48955,7 @@
         <v>0.7683</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1075</v>
+        <v>0.108</v>
       </c>
       <c r="J129" t="n">
         <v>-0.045</v>
@@ -48968,7 +48968,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.3341</v>
+        <v>0.3342</v>
       </c>
       <c r="C130" t="n">
         <v>-0.786</v>
@@ -48977,7 +48977,7 @@
         <v>0.2579</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3532</v>
+        <v>0.3533</v>
       </c>
       <c r="F130" t="n">
         <v>0.2579</v>
@@ -48989,7 +48989,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0356</v>
+        <v>0.0361</v>
       </c>
       <c r="J130" t="n">
         <v>-0.0596</v>
@@ -49002,7 +49002,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.3264</v>
+        <v>0.3265</v>
       </c>
       <c r="C131" t="n">
         <v>-0.783</v>
@@ -49011,7 +49011,7 @@
         <v>0.2217</v>
       </c>
       <c r="E131" t="n">
-        <v>0.3525</v>
+        <v>0.3527</v>
       </c>
       <c r="F131" t="n">
         <v>0.2217</v>
@@ -49023,7 +49023,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>0.036</v>
+        <v>0.0365</v>
       </c>
       <c r="J131" t="n">
         <v>-0.1274</v>
@@ -49036,7 +49036,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.3398</v>
+        <v>0.3399</v>
       </c>
       <c r="C132" t="n">
         <v>-0.781</v>
@@ -49045,7 +49045,7 @@
         <v>0.3558</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3358</v>
+        <v>0.3359</v>
       </c>
       <c r="F132" t="n">
         <v>0.3558</v>
@@ -49057,7 +49057,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1024</v>
+        <v>0.1029</v>
       </c>
       <c r="J132" t="n">
         <v>-0.1091</v>
@@ -49070,7 +49070,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.3635</v>
+        <v>0.3636</v>
       </c>
       <c r="C133" t="n">
         <v>-0.62</v>
@@ -49079,7 +49079,7 @@
         <v>0.3665</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3627</v>
+        <v>0.3628</v>
       </c>
       <c r="F133" t="n">
         <v>0.3665</v>
@@ -49091,7 +49091,7 @@
         <v>0.7917</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0717</v>
+        <v>0.0722</v>
       </c>
       <c r="J133" t="n">
         <v>0.0138</v>
@@ -49104,7 +49104,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3679</v>
+        <v>0.368</v>
       </c>
       <c r="C134" t="n">
         <v>-0.621</v>
@@ -49113,7 +49113,7 @@
         <v>0.3861</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3633</v>
+        <v>0.3634</v>
       </c>
       <c r="F134" t="n">
         <v>0.3861</v>
@@ -49125,7 +49125,7 @@
         <v>0.7917</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0047</v>
+        <v>-0.0042</v>
       </c>
       <c r="J134" t="n">
         <v>-0.0891</v>
@@ -49138,7 +49138,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3914</v>
+        <v>0.3915</v>
       </c>
       <c r="C135" t="n">
         <v>-0.662</v>
@@ -49147,7 +49147,7 @@
         <v>0.4546</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3756</v>
+        <v>0.3757</v>
       </c>
       <c r="F135" t="n">
         <v>0.4546</v>
@@ -49159,7 +49159,7 @@
         <v>0.7917</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0725</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J135" t="n">
         <v>0.022</v>
@@ -49172,7 +49172,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.3994</v>
+        <v>0.3995</v>
       </c>
       <c r="C136" t="n">
         <v>-0.503</v>
@@ -49181,7 +49181,7 @@
         <v>0.3201</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4192</v>
+        <v>0.4193</v>
       </c>
       <c r="F136" t="n">
         <v>0.3201</v>
@@ -49193,7 +49193,7 @@
         <v>0.9537</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0815</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J136" t="n">
         <v>-0.0994</v>
@@ -49215,7 +49215,7 @@
         <v>0.2948</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3906</v>
+        <v>0.3907</v>
       </c>
       <c r="F137" t="n">
         <v>0.2948</v>
@@ -49227,7 +49227,7 @@
         <v>0.9537</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1477</v>
+        <v>-0.1474</v>
       </c>
       <c r="J137" t="n">
         <v>-0.074</v>
@@ -49240,7 +49240,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4102</v>
+        <v>0.4103</v>
       </c>
       <c r="C138" t="n">
         <v>-0.5590000000000001</v>
@@ -49249,7 +49249,7 @@
         <v>0.3077</v>
       </c>
       <c r="E138" t="n">
-        <v>0.4358</v>
+        <v>0.4359</v>
       </c>
       <c r="F138" t="n">
         <v>0.3077</v>
@@ -49261,7 +49261,7 @@
         <v>0.9537</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1529</v>
+        <v>-0.1526</v>
       </c>
       <c r="J138" t="n">
         <v>0.0357</v>
@@ -49283,7 +49283,7 @@
         <v>0.325</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4176</v>
+        <v>0.4177</v>
       </c>
       <c r="F139" t="n">
         <v>0.325</v>
@@ -49295,7 +49295,7 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2165</v>
+        <v>-0.2163</v>
       </c>
       <c r="J139" t="n">
         <v>-0.0402</v>
@@ -49308,7 +49308,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4155</v>
+        <v>0.4156</v>
       </c>
       <c r="C140" t="n">
         <v>-0.409</v>
@@ -49317,7 +49317,7 @@
         <v>0.3006</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4442</v>
+        <v>0.4443</v>
       </c>
       <c r="F140" t="n">
         <v>0.3006</v>
@@ -49329,7 +49329,7 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2279</v>
+        <v>-0.2277</v>
       </c>
       <c r="J140" t="n">
         <v>0.1018</v>
@@ -49342,7 +49342,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3987</v>
+        <v>0.3988</v>
       </c>
       <c r="C141" t="n">
         <v>-0.409</v>
@@ -49351,7 +49351,7 @@
         <v>0.2423</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4378</v>
+        <v>0.4379</v>
       </c>
       <c r="F141" t="n">
         <v>0.2423</v>
@@ -49363,7 +49363,7 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2685</v>
+        <v>-0.2684</v>
       </c>
       <c r="J141" t="n">
         <v>0.1044</v>
@@ -49376,7 +49376,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4019</v>
+        <v>0.402</v>
       </c>
       <c r="C142" t="n">
         <v>-0.362</v>
@@ -49394,10 +49394,10 @@
         <v>0.8161</v>
       </c>
       <c r="H142" t="n">
-        <v>1.1149</v>
+        <v>1.115</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2602</v>
+        <v>-0.2601</v>
       </c>
       <c r="J142" t="n">
         <v>0.0814</v>
@@ -49419,7 +49419,7 @@
         <v>0.3533</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4515</v>
+        <v>0.4516</v>
       </c>
       <c r="F143" t="n">
         <v>0.3533</v>
@@ -49428,10 +49428,10 @@
         <v>0.7829</v>
       </c>
       <c r="H143" t="n">
-        <v>1.1149</v>
+        <v>1.115</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2181</v>
+        <v>-0.218</v>
       </c>
       <c r="J143" t="n">
         <v>0.1265</v>
@@ -49444,7 +49444,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4849</v>
+        <v>0.485</v>
       </c>
       <c r="C144" t="n">
         <v>-0.359</v>
@@ -49453,7 +49453,7 @@
         <v>0.333</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5229</v>
+        <v>0.523</v>
       </c>
       <c r="F144" t="n">
         <v>0.333</v>
@@ -49462,10 +49462,10 @@
         <v>0.8552</v>
       </c>
       <c r="H144" t="n">
-        <v>1.1149</v>
+        <v>1.115</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1308</v>
+        <v>-0.1306</v>
       </c>
       <c r="J144" t="n">
         <v>0.2525</v>
@@ -49487,7 +49487,7 @@
         <v>0.633</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5737</v>
+        <v>0.5738</v>
       </c>
       <c r="F145" t="n">
         <v>0.633</v>
@@ -49496,10 +49496,10 @@
         <v>0.8317</v>
       </c>
       <c r="H145" t="n">
-        <v>1.1067</v>
+        <v>1.1068</v>
       </c>
       <c r="I145" t="n">
-        <v>0.0227</v>
+        <v>0.023</v>
       </c>
       <c r="J145" t="n">
         <v>0.3337</v>
@@ -49512,7 +49512,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5381</v>
+        <v>0.5382</v>
       </c>
       <c r="C146" t="n">
         <v>-0.439</v>
@@ -49521,7 +49521,7 @@
         <v>0.5052</v>
       </c>
       <c r="E146" t="n">
-        <v>0.5463</v>
+        <v>0.5464</v>
       </c>
       <c r="F146" t="n">
         <v>0.5052</v>
@@ -49530,10 +49530,10 @@
         <v>0.7673</v>
       </c>
       <c r="H146" t="n">
-        <v>1.1067</v>
+        <v>1.1068</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0196</v>
+        <v>0.0199</v>
       </c>
       <c r="J146" t="n">
         <v>0.2917</v>
@@ -49555,7 +49555,7 @@
         <v>0.5475</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5981</v>
+        <v>0.5982</v>
       </c>
       <c r="F147" t="n">
         <v>0.5475</v>
@@ -49564,10 +49564,10 @@
         <v>0.9033</v>
       </c>
       <c r="H147" t="n">
-        <v>1.1067</v>
+        <v>1.1068</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0095</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="J147" t="n">
         <v>0.3918</v>
@@ -49580,7 +49580,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5789</v>
+        <v>0.579</v>
       </c>
       <c r="C148" t="n">
         <v>-0.456</v>
@@ -49589,7 +49589,7 @@
         <v>0.6008</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5734</v>
+        <v>0.5735</v>
       </c>
       <c r="F148" t="n">
         <v>0.6008</v>
@@ -49598,10 +49598,10 @@
         <v>0.7959000000000001</v>
       </c>
       <c r="H148" t="n">
-        <v>1.0752</v>
+        <v>1.0753</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0041</v>
+        <v>-0.0039</v>
       </c>
       <c r="J148" t="n">
         <v>0.4268</v>
@@ -49614,7 +49614,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5621</v>
       </c>
       <c r="C149" t="n">
         <v>-0.468</v>
@@ -49623,7 +49623,7 @@
         <v>0.585</v>
       </c>
       <c r="E149" t="n">
-        <v>0.5563</v>
+        <v>0.5564</v>
       </c>
       <c r="F149" t="n">
         <v>0.585</v>
@@ -49632,10 +49632,10 @@
         <v>0.7794</v>
       </c>
       <c r="H149" t="n">
-        <v>1.0752</v>
+        <v>1.0753</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0626</v>
       </c>
       <c r="J149" t="n">
         <v>0.4334</v>
@@ -49648,7 +49648,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.6243</v>
+        <v>0.6244</v>
       </c>
       <c r="C150" t="n">
         <v>-0.467</v>
@@ -49657,7 +49657,7 @@
         <v>0.6139</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6269</v>
+        <v>0.627</v>
       </c>
       <c r="F150" t="n">
         <v>0.6139</v>
@@ -49666,10 +49666,10 @@
         <v>0.9236</v>
       </c>
       <c r="H150" t="n">
-        <v>1.0752</v>
+        <v>1.0753</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0075</v>
+        <v>-0.0074</v>
       </c>
       <c r="J150" t="n">
         <v>0.5164</v>
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.6247</v>
+        <v>0.6248</v>
       </c>
       <c r="C151" t="n">
         <v>-0.547</v>
@@ -49700,7 +49700,7 @@
         <v>0.7832</v>
       </c>
       <c r="H151" t="n">
-        <v>1.1971</v>
+        <v>1.1972</v>
       </c>
       <c r="I151" t="n">
         <v>-0.0125</v>
@@ -49716,7 +49716,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.6288</v>
+        <v>0.6289</v>
       </c>
       <c r="C152" t="n">
         <v>-0.545</v>
@@ -49725,7 +49725,7 @@
         <v>0.6333</v>
       </c>
       <c r="E152" t="n">
-        <v>0.6277</v>
+        <v>0.6278</v>
       </c>
       <c r="F152" t="n">
         <v>0.6333</v>
@@ -49734,10 +49734,10 @@
         <v>0.7234</v>
       </c>
       <c r="H152" t="n">
-        <v>1.1971</v>
+        <v>1.1972</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0024</v>
+        <v>-0.0023</v>
       </c>
       <c r="J152" t="n">
         <v>0.5928</v>
@@ -49759,7 +49759,7 @@
         <v>0.734</v>
       </c>
       <c r="E153" t="n">
-        <v>0.6546</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="F153" t="n">
         <v>0.734</v>
@@ -49768,7 +49768,7 @@
         <v>0.8375</v>
       </c>
       <c r="H153" t="n">
-        <v>1.1971</v>
+        <v>1.1972</v>
       </c>
       <c r="I153" t="n">
         <v>-0.044</v>
@@ -49793,7 +49793,7 @@
         <v>0.7359</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6207</v>
+        <v>0.6208</v>
       </c>
       <c r="F154" t="n">
         <v>0.7359</v>
@@ -49802,10 +49802,10 @@
         <v>0.7796</v>
       </c>
       <c r="H154" t="n">
-        <v>1.1241</v>
+        <v>1.1242</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.012</v>
+        <v>-0.0119</v>
       </c>
       <c r="J154" t="n">
         <v>0.5913</v>
@@ -49836,7 +49836,7 @@
         <v>0.6351</v>
       </c>
       <c r="H155" t="n">
-        <v>1.1241</v>
+        <v>1.1242</v>
       </c>
       <c r="I155" t="n">
         <v>0.0501</v>
@@ -49870,10 +49870,10 @@
         <v>0.6133999999999999</v>
       </c>
       <c r="H156" t="n">
-        <v>1.1241</v>
+        <v>1.1242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0663</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J156" t="n">
         <v>0.6836</v>
@@ -49904,10 +49904,10 @@
         <v>0.6995</v>
       </c>
       <c r="H157" t="n">
-        <v>1.1578</v>
+        <v>1.1579</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0688</v>
+        <v>0.0687</v>
       </c>
       <c r="J157" t="n">
         <v>0.7487</v>
@@ -49920,7 +49920,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7192</v>
       </c>
       <c r="C158" t="n">
         <v>-0.525</v>
@@ -49938,10 +49938,10 @@
         <v>0.7191</v>
       </c>
       <c r="H158" t="n">
-        <v>1.1578</v>
+        <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.064</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -49954,7 +49954,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7313</v>
       </c>
       <c r="C159" t="n">
         <v>-0.527</v>
@@ -49972,10 +49972,10 @@
         <v>0.8097</v>
       </c>
       <c r="H159" t="n">
-        <v>1.1578</v>
+        <v>1.1579</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.017</v>
+        <v>-0.0172</v>
       </c>
       <c r="J159" t="n">
         <v>0.837</v>
@@ -49988,7 +49988,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.7214</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="C160" t="n">
         <v>-0.5669999999999999</v>
@@ -50006,10 +50006,10 @@
         <v>0.7652</v>
       </c>
       <c r="H160" t="n">
-        <v>1.1756</v>
+        <v>1.1757</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0409</v>
+        <v>-0.0411</v>
       </c>
       <c r="J160" t="n">
         <v>0.9242</v>
@@ -50022,7 +50022,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.724</v>
+        <v>0.7239</v>
       </c>
       <c r="C161" t="n">
         <v>-0.5679999999999999</v>
@@ -50031,7 +50031,7 @@
         <v>0.7343</v>
       </c>
       <c r="E161" t="n">
-        <v>0.7214</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="F161" t="n">
         <v>0.7343</v>
@@ -50040,10 +50040,10 @@
         <v>0.6953</v>
       </c>
       <c r="H161" t="n">
-        <v>1.1756</v>
+        <v>1.1757</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0104</v>
+        <v>-0.0106</v>
       </c>
       <c r="J161" t="n">
         <v>1.0249</v>
@@ -50074,10 +50074,10 @@
         <v>0.7768</v>
       </c>
       <c r="H162" t="n">
-        <v>1.1756</v>
+        <v>1.1757</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0267</v>
+        <v>0.0265</v>
       </c>
       <c r="J162" t="n">
         <v>1.0036</v>
@@ -50108,10 +50108,10 @@
         <v>0.5895</v>
       </c>
       <c r="H163" t="n">
-        <v>1.1752</v>
+        <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0474</v>
+        <v>0.0472</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50142,10 +50142,10 @@
         <v>0.6227</v>
       </c>
       <c r="H164" t="n">
-        <v>1.1752</v>
+        <v>1.1753</v>
       </c>
       <c r="I164" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0704</v>
       </c>
       <c r="J164" t="n">
         <v>1.1755</v>
@@ -50176,10 +50176,10 @@
         <v>0.5366</v>
       </c>
       <c r="H165" t="n">
-        <v>1.1752</v>
+        <v>1.1753</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0614</v>
+        <v>0.0612</v>
       </c>
       <c r="J165" t="n">
         <v>1.141</v>
@@ -50210,10 +50210,10 @@
         <v>0.6329</v>
       </c>
       <c r="H166" t="n">
-        <v>1.1103</v>
+        <v>1.1104</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1027</v>
+        <v>0.1026</v>
       </c>
       <c r="J166" t="n">
         <v>1.2041</v>
@@ -50244,10 +50244,10 @@
         <v>0.508</v>
       </c>
       <c r="H167" t="n">
-        <v>1.1103</v>
+        <v>1.1104</v>
       </c>
       <c r="I167" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0709</v>
       </c>
       <c r="J167" t="n">
         <v>1.2431</v>
@@ -50278,7 +50278,7 @@
         <v>0.663</v>
       </c>
       <c r="H168" t="n">
-        <v>1.1103</v>
+        <v>1.1104</v>
       </c>
       <c r="I168" t="n">
         <v>0.06320000000000001</v>
@@ -50312,7 +50312,7 @@
         <v>0.5461</v>
       </c>
       <c r="H169" t="n">
-        <v>1.0766</v>
+        <v>1.0767</v>
       </c>
       <c r="I169" t="n">
         <v>0.0049</v>
@@ -50346,7 +50346,7 @@
         <v>0.6744</v>
       </c>
       <c r="H170" t="n">
-        <v>1.0766</v>
+        <v>1.0767</v>
       </c>
       <c r="I170" t="n">
         <v>-0.0717</v>
@@ -50371,7 +50371,7 @@
         <v>0.7524999999999999</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7826</v>
+        <v>0.7827</v>
       </c>
       <c r="F171" t="n">
         <v>0.7524999999999999</v>
@@ -50380,7 +50380,7 @@
         <v>0.663</v>
       </c>
       <c r="H171" t="n">
-        <v>1.0766</v>
+        <v>1.0767</v>
       </c>
       <c r="I171" t="n">
         <v>-0.0503</v>
@@ -50485,7 +50485,7 @@
         <v>1.0374</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1044</v>
+        <v>-0.1045</v>
       </c>
       <c r="J174" t="n">
         <v>1.5397</v>
@@ -50519,7 +50519,7 @@
         <v>0.9665</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1429</v>
+        <v>-0.143</v>
       </c>
       <c r="J175" t="n">
         <v>1.6029</v>
@@ -50553,7 +50553,7 @@
         <v>0.9665</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1614</v>
+        <v>-0.1616</v>
       </c>
       <c r="J176" t="n">
         <v>1.6097</v>
@@ -50587,7 +50587,7 @@
         <v>0.9665</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2184</v>
+        <v>-0.2185</v>
       </c>
       <c r="J177" t="n">
         <v>1.7354</v>
@@ -50618,10 +50618,10 @@
         <v>0.5442</v>
       </c>
       <c r="H178" t="n">
-        <v>0.9384</v>
+        <v>0.9385</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2035</v>
+        <v>-0.2036</v>
       </c>
       <c r="J178" t="n">
         <v>1.719</v>
@@ -50643,7 +50643,7 @@
         <v>0.6654</v>
       </c>
       <c r="E179" t="n">
-        <v>0.7317</v>
+        <v>0.7316</v>
       </c>
       <c r="F179" t="n">
         <v>0.6654</v>
@@ -50652,10 +50652,10 @@
         <v>0.4754</v>
       </c>
       <c r="H179" t="n">
-        <v>0.9384</v>
+        <v>0.9385</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1991</v>
+        <v>-0.1993</v>
       </c>
       <c r="J179" t="n">
         <v>1.712</v>
@@ -50677,7 +50677,7 @@
         <v>0.6761</v>
       </c>
       <c r="E180" t="n">
-        <v>0.802</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="F180" t="n">
         <v>0.6761</v>
@@ -50686,10 +50686,10 @@
         <v>0.6405999999999999</v>
       </c>
       <c r="H180" t="n">
-        <v>0.9384</v>
+        <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1764</v>
+        <v>-0.1767</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -50711,7 +50711,7 @@
         <v>0.5617</v>
       </c>
       <c r="E181" t="n">
-        <v>0.7412</v>
+        <v>0.7411</v>
       </c>
       <c r="F181" t="n">
         <v>0.5617</v>
@@ -50720,10 +50720,10 @@
         <v>0.425</v>
       </c>
       <c r="H181" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1921</v>
+        <v>-0.1924</v>
       </c>
       <c r="J181" t="n">
         <v>1.8899</v>
@@ -50745,7 +50745,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="E182" t="n">
-        <v>0.7927</v>
+        <v>0.7926</v>
       </c>
       <c r="F182" t="n">
         <v>0.7828000000000001</v>
@@ -50754,10 +50754,10 @@
         <v>0.5829</v>
       </c>
       <c r="H182" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2098</v>
+        <v>-0.2101</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50779,7 +50779,7 @@
         <v>0.7167</v>
       </c>
       <c r="E183" t="n">
-        <v>0.7725</v>
+        <v>0.7724</v>
       </c>
       <c r="F183" t="n">
         <v>0.7167</v>
@@ -50788,10 +50788,10 @@
         <v>0.4962</v>
       </c>
       <c r="H183" t="n">
-        <v>0.842</v>
+        <v>0.8421</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2173</v>
+        <v>-0.2176</v>
       </c>
       <c r="J183" t="n">
         <v>1.969</v>
@@ -50813,7 +50813,7 @@
         <v>0.718</v>
       </c>
       <c r="E184" t="n">
-        <v>0.6671</v>
+        <v>0.667</v>
       </c>
       <c r="F184" t="n">
         <v>0.718</v>
@@ -50822,10 +50822,10 @@
         <v>0.4666</v>
       </c>
       <c r="H184" t="n">
-        <v>0.5823</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.3361</v>
+        <v>-0.336</v>
       </c>
       <c r="J184" t="n">
         <v>1.9554</v>
@@ -50856,10 +50856,10 @@
         <v>0.6519</v>
       </c>
       <c r="H185" t="n">
-        <v>0.5823</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3061</v>
+        <v>-0.306</v>
       </c>
       <c r="J185" t="n">
         <v>2.0331</v>
@@ -50872,7 +50872,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="C186" t="n">
         <v>-0.055</v>
@@ -50890,10 +50890,10 @@
         <v>0.7091</v>
       </c>
       <c r="H186" t="n">
-        <v>0.5823</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2792</v>
+        <v>-0.2793</v>
       </c>
       <c r="J186" t="n">
         <v>2.0342</v>
@@ -50906,7 +50906,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5335</v>
+        <v>0.5334</v>
       </c>
       <c r="C187" t="n">
         <v>0.119</v>
@@ -50915,7 +50915,7 @@
         <v>0.3922</v>
       </c>
       <c r="E187" t="n">
-        <v>0.5688</v>
+        <v>0.5687</v>
       </c>
       <c r="F187" t="n">
         <v>0.3922</v>
@@ -50924,10 +50924,10 @@
         <v>0.457</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.1326</v>
+        <v>-0.1328</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2084</v>
+        <v>-0.2087</v>
       </c>
       <c r="J187" t="n">
         <v>2.1594</v>
@@ -50940,7 +50940,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.4833</v>
+        <v>0.4832</v>
       </c>
       <c r="C188" t="n">
         <v>0.139</v>
@@ -50949,7 +50949,7 @@
         <v>0.4356</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4952</v>
+        <v>0.4951</v>
       </c>
       <c r="F188" t="n">
         <v>0.4356</v>
@@ -50958,10 +50958,10 @@
         <v>0.39</v>
       </c>
       <c r="H188" t="n">
-        <v>-0.1326</v>
+        <v>-0.1328</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1991</v>
+        <v>-0.1993</v>
       </c>
       <c r="J188" t="n">
         <v>1.9226</v>
@@ -50974,7 +50974,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0.4038</v>
+        <v>0.4037</v>
       </c>
       <c r="C189" t="n">
         <v>0.132</v>
@@ -50983,7 +50983,7 @@
         <v>0.2496</v>
       </c>
       <c r="E189" t="n">
-        <v>0.4424</v>
+        <v>0.4422</v>
       </c>
       <c r="F189" t="n">
         <v>0.2496</v>
@@ -50992,10 +50992,10 @@
         <v>0.4402</v>
       </c>
       <c r="H189" t="n">
-        <v>-0.1326</v>
+        <v>-0.1328</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1832</v>
+        <v>-0.1836</v>
       </c>
       <c r="J189" t="n">
         <v>1.6451</v>
@@ -51008,7 +51008,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.3703</v>
+        <v>0.3702</v>
       </c>
       <c r="C190" t="n">
         <v>0.067</v>
@@ -51017,7 +51017,7 @@
         <v>0.257</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3986</v>
+        <v>0.3984</v>
       </c>
       <c r="F190" t="n">
         <v>0.257</v>
@@ -51026,10 +51026,10 @@
         <v>0.3506</v>
       </c>
       <c r="H190" t="n">
-        <v>-0.0244</v>
+        <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1555</v>
+        <v>-0.1559</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51042,7 +51042,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.3009</v>
+        <v>0.3008</v>
       </c>
       <c r="C191" t="n">
         <v>0.101</v>
@@ -51051,7 +51051,7 @@
         <v>0.082</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3557</v>
+        <v>0.3555</v>
       </c>
       <c r="F191" t="n">
         <v>0.082</v>
@@ -51060,10 +51060,10 @@
         <v>0.3947</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.0244</v>
+        <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1327</v>
+        <v>-0.1331</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51076,7 +51076,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3443</v>
+        <v>0.3442</v>
       </c>
       <c r="C192" t="n">
         <v>0.089</v>
@@ -51085,7 +51085,7 @@
         <v>-0.0004</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4305</v>
+        <v>0.4303</v>
       </c>
       <c r="F192" t="n">
         <v>-0.0004</v>
@@ -51094,10 +51094,10 @@
         <v>0.8058</v>
       </c>
       <c r="H192" t="n">
-        <v>-0.0244</v>
+        <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51110,7 +51110,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2844</v>
+        <v>0.2842</v>
       </c>
       <c r="C193" t="n">
         <v>0.08400000000000001</v>
@@ -51119,7 +51119,7 @@
         <v>0.1261</v>
       </c>
       <c r="E193" t="n">
-        <v>0.324</v>
+        <v>0.3237</v>
       </c>
       <c r="F193" t="n">
         <v>0.1261</v>
@@ -51128,10 +51128,10 @@
         <v>0.5552</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.036</v>
+        <v>-0.0367</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51144,7 +51144,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2823</v>
+        <v>0.2821</v>
       </c>
       <c r="C194" t="n">
         <v>0.093</v>
@@ -51153,7 +51153,7 @@
         <v>0.1208</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3227</v>
+        <v>0.3224</v>
       </c>
       <c r="F194" t="n">
         <v>0.1208</v>
@@ -51162,10 +51162,10 @@
         <v>0.7616000000000001</v>
       </c>
       <c r="H194" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0019</v>
+        <v>0.001</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51178,7 +51178,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.2239</v>
+        <v>0.2236</v>
       </c>
       <c r="C195" t="n">
         <v>0.094</v>
@@ -51187,7 +51187,7 @@
         <v>0.1947</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2312</v>
+        <v>0.2309</v>
       </c>
       <c r="F195" t="n">
         <v>0.1947</v>
@@ -51196,10 +51196,10 @@
         <v>0.6114000000000001</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0871</v>
+        <v>0.0862</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51212,7 +51212,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2599</v>
+        <v>0.2597</v>
       </c>
       <c r="C196" t="n">
         <v>-0.08500000000000001</v>
@@ -51221,7 +51221,7 @@
         <v>0.2423</v>
       </c>
       <c r="E196" t="n">
-        <v>0.2643</v>
+        <v>0.2641</v>
       </c>
       <c r="F196" t="n">
         <v>0.2423</v>
@@ -51230,10 +51230,10 @@
         <v>0.6279</v>
       </c>
       <c r="H196" t="n">
-        <v>0.2034</v>
+        <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1672</v>
+        <v>0.1664</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2009</v>
+        <v>0.2007</v>
       </c>
       <c r="C197" t="n">
         <v>-0.08</v>
@@ -51255,7 +51255,7 @@
         <v>0.0726</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2329</v>
+        <v>0.2327</v>
       </c>
       <c r="F197" t="n">
         <v>0.0726</v>
@@ -51264,10 +51264,10 @@
         <v>0.7429</v>
       </c>
       <c r="H197" t="n">
-        <v>0.2034</v>
+        <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.196</v>
+        <v>0.1952</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51280,7 +51280,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.2116</v>
+        <v>0.2114</v>
       </c>
       <c r="C198" t="n">
         <v>-0.08500000000000001</v>
@@ -51289,7 +51289,7 @@
         <v>0.1598</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2245</v>
+        <v>0.2243</v>
       </c>
       <c r="F198" t="n">
         <v>0.1598</v>
@@ -51298,10 +51298,10 @@
         <v>0.9523</v>
       </c>
       <c r="H198" t="n">
-        <v>0.2034</v>
+        <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1985</v>
+        <v>0.1978</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51314,7 +51314,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1628</v>
+        <v>0.1627</v>
       </c>
       <c r="C199" t="n">
         <v>-0.283</v>
@@ -51323,7 +51323,7 @@
         <v>0.2044</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1524</v>
+        <v>0.1522</v>
       </c>
       <c r="F199" t="n">
         <v>0.2044</v>
@@ -51332,10 +51332,10 @@
         <v>0.6987</v>
       </c>
       <c r="H199" t="n">
-        <v>0.2937</v>
+        <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2488</v>
+        <v>0.2481</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51348,7 +51348,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.2069</v>
+        <v>0.2067</v>
       </c>
       <c r="C200" t="n">
         <v>-0.29</v>
@@ -51357,7 +51357,7 @@
         <v>0.3391</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1738</v>
+        <v>0.1737</v>
       </c>
       <c r="F200" t="n">
         <v>0.3391</v>
@@ -51366,10 +51366,10 @@
         <v>0.7856</v>
       </c>
       <c r="H200" t="n">
-        <v>0.2937</v>
+        <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2534</v>
+        <v>0.2528</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51382,7 +51382,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.2411</v>
+        <v>0.2409</v>
       </c>
       <c r="C201" t="n">
         <v>-0.288</v>
@@ -51391,7 +51391,7 @@
         <v>0.4287</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1942</v>
+        <v>0.194</v>
       </c>
       <c r="F201" t="n">
         <v>0.4287</v>
@@ -51400,10 +51400,10 @@
         <v>0.8129999999999999</v>
       </c>
       <c r="H201" t="n">
-        <v>0.2937</v>
+        <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2618</v>
+        <v>0.2612</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51416,7 +51416,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2619</v>
+        <v>0.2617</v>
       </c>
       <c r="C202" t="n">
         <v>-0.388</v>
@@ -51425,7 +51425,7 @@
         <v>0.4629</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2117</v>
+        <v>0.2114</v>
       </c>
       <c r="F202" t="n">
         <v>0.4629</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3465</v>
+        <v>0.3457</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51450,7 +51450,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.2974</v>
+        <v>0.2973</v>
       </c>
       <c r="C203" t="n">
         <v>-0.393</v>
@@ -51459,7 +51459,7 @@
         <v>0.5</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2468</v>
+        <v>0.2466</v>
       </c>
       <c r="F203" t="n">
         <v>0.5</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.37</v>
+        <v>0.3694</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51484,7 +51484,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3711</v>
+        <v>0.3709</v>
       </c>
       <c r="C204" t="n">
         <v>-0.406</v>
@@ -51493,7 +51493,7 @@
         <v>0.6372</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3045</v>
+        <v>0.3044</v>
       </c>
       <c r="F204" t="n">
         <v>0.6372</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.404</v>
+        <v>0.4034</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51518,7 +51518,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5709</v>
+        <v>0.5708</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8159999999999999</v>
@@ -51527,7 +51527,7 @@
         <v>1.7571</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2743</v>
+        <v>0.2742</v>
       </c>
       <c r="F205" t="n">
         <v>1.7571</v>
@@ -51536,10 +51536,10 @@
         <v>0.789</v>
       </c>
       <c r="H205" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3962</v>
+        <v>0.3956</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51552,7 +51552,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3159</v>
+        <v>0.3158</v>
       </c>
       <c r="C206" t="n">
         <v>-0.8100000000000001</v>
@@ -51561,7 +51561,7 @@
         <v>0.5259</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2634</v>
+        <v>0.2632</v>
       </c>
       <c r="F206" t="n">
         <v>0.5259</v>
@@ -51570,10 +51570,10 @@
         <v>0.7331</v>
       </c>
       <c r="H206" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3945</v>
+        <v>0.394</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51586,7 +51586,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.4065</v>
+        <v>0.4064</v>
       </c>
       <c r="C207" t="n">
         <v>-0.8080000000000001</v>
@@ -51595,7 +51595,7 @@
         <v>0.643</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3473</v>
+        <v>0.3472</v>
       </c>
       <c r="F207" t="n">
         <v>0.643</v>
@@ -51604,10 +51604,10 @@
         <v>0.966</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3352</v>
+        <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4009</v>
+        <v>0.4005</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51620,7 +51620,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3835</v>
+        <v>0.3834</v>
       </c>
       <c r="C208" t="n">
         <v>-1.479</v>
@@ -51629,7 +51629,7 @@
         <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2983</v>
+        <v>0.2982</v>
       </c>
       <c r="F208" t="n">
         <v>0.7243000000000001</v>
@@ -51638,10 +51638,10 @@
         <v>0.7981</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1796</v>
+        <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4497</v>
+        <v>0.4495</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51672,10 +51672,10 @@
         <v>0.968</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1796</v>
+        <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5848</v>
+        <v>0.5847</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51706,7 +51706,7 @@
         <v>1.0136</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1796</v>
+        <v>0.1795</v>
       </c>
       <c r="I210" t="n">
         <v>0.6118</v>
@@ -51731,7 +51731,7 @@
         <v>1.3419</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3937</v>
+        <v>0.3938</v>
       </c>
       <c r="F211" t="n">
         <v>1.3419</v>
@@ -51740,10 +51740,10 @@
         <v>0.7941</v>
       </c>
       <c r="H211" t="n">
-        <v>0.254</v>
+        <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6978</v>
+        <v>0.6979</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51756,7 +51756,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6496</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="C212" t="n">
         <v>-2.064</v>
@@ -51774,10 +51774,10 @@
         <v>0.9591</v>
       </c>
       <c r="H212" t="n">
-        <v>0.254</v>
+        <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.759</v>
+        <v>0.7592</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51808,10 +51808,10 @@
         <v>0.9696</v>
       </c>
       <c r="H213" t="n">
-        <v>0.254</v>
+        <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51833,7 +51833,7 @@
         <v>1.7325</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4653</v>
+        <v>0.4654</v>
       </c>
       <c r="F214" t="n">
         <v>1.7325</v>
@@ -51842,10 +51842,10 @@
         <v>0.8562</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1184</v>
+        <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8842</v>
+        <v>0.8845</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51867,7 +51867,7 @@
         <v>1.8962</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4849</v>
+        <v>0.485</v>
       </c>
       <c r="F215" t="n">
         <v>1.8962</v>
@@ -51876,10 +51876,10 @@
         <v>0.9344</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1184</v>
+        <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9328</v>
+        <v>0.9333</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51892,7 +51892,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8047</v>
+        <v>0.8048</v>
       </c>
       <c r="C216" t="n">
         <v>-2.302</v>
@@ -51910,10 +51910,10 @@
         <v>1.0459</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1184</v>
+        <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8894</v>
+        <v>0.8897</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51944,10 +51944,10 @@
         <v>0.7484</v>
       </c>
       <c r="H217" t="n">
-        <v>0.0138</v>
+        <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7588</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -51978,10 +51978,10 @@
         <v>0.793</v>
       </c>
       <c r="H218" t="n">
-        <v>0.0138</v>
+        <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6891</v>
+        <v>0.6892</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52012,10 +52012,10 @@
         <v>0.914</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0138</v>
+        <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7409</v>
+        <v>0.741</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52046,10 +52046,10 @@
         <v>0.8149</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.0488</v>
+        <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7628</v>
+        <v>0.7629</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52071,7 +52071,7 @@
         <v>1.8118</v>
       </c>
       <c r="E221" t="n">
-        <v>0.4312</v>
+        <v>0.4311</v>
       </c>
       <c r="F221" t="n">
         <v>1.8118</v>
@@ -52080,7 +52080,7 @@
         <v>0.8280999999999999</v>
       </c>
       <c r="H221" t="n">
-        <v>-0.0488</v>
+        <v>-0.049</v>
       </c>
       <c r="I221" t="n">
         <v>0.7766999999999999</v>
@@ -52105,7 +52105,7 @@
         <v>1.7254</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5077</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="F222" t="n">
         <v>1.7254</v>
@@ -52114,7 +52114,7 @@
         <v>1.0106</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.0488</v>
+        <v>-0.049</v>
       </c>
       <c r="I222" t="n">
         <v>0.8745000000000001</v>
@@ -52130,7 +52130,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.7905</v>
+        <v>0.7904</v>
       </c>
       <c r="C223" t="n">
         <v>-2.155</v>
@@ -52139,7 +52139,7 @@
         <v>1.7757</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5442</v>
+        <v>0.5441</v>
       </c>
       <c r="F223" t="n">
         <v>1.7757</v>
@@ -52148,10 +52148,10 @@
         <v>0.8255</v>
       </c>
       <c r="H223" t="n">
-        <v>0.0553</v>
+        <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9866</v>
+        <v>0.9865</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6979</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5868</v>
+        <v>0.5867</v>
       </c>
       <c r="F224" t="n">
         <v>1.6979</v>
@@ -52182,10 +52182,10 @@
         <v>0.9207</v>
       </c>
       <c r="H224" t="n">
-        <v>0.0553</v>
+        <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0142</v>
+        <v>1.014</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52216,7 +52216,7 @@
         <v>0.9365</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0553</v>
+        <v>0.0552</v>
       </c>
       <c r="I225" t="n">
         <v>1.0832</v>
@@ -52232,7 +52232,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.7025</v>
+        <v>0.7024</v>
       </c>
       <c r="C226" t="n">
         <v>-2.088</v>
@@ -52241,7 +52241,7 @@
         <v>1.478</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5085</v>
       </c>
       <c r="F226" t="n">
         <v>1.478</v>
@@ -52250,10 +52250,10 @@
         <v>0.5671</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.0492</v>
+        <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1638</v>
+        <v>1.1639</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52284,10 +52284,10 @@
         <v>0.7927999999999999</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.0492</v>
+        <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2033</v>
+        <v>1.2036</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52318,10 +52318,10 @@
         <v>0.9908</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.0492</v>
+        <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2615</v>
+        <v>1.2616</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52352,10 +52352,10 @@
         <v>0.7995</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1853</v>
+        <v>1.1852</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52368,7 +52368,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.771</v>
+        <v>0.7709</v>
       </c>
       <c r="C230" t="n">
         <v>-1.991</v>
@@ -52377,7 +52377,7 @@
         <v>1.1747</v>
       </c>
       <c r="E230" t="n">
-        <v>0.67</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="F230" t="n">
         <v>1.1747</v>
@@ -52386,10 +52386,10 @@
         <v>0.8512</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2965</v>
+        <v>1.2963</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8361</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
@@ -52411,7 +52411,7 @@
         <v>1.4909</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6725</v>
+        <v>0.6724</v>
       </c>
       <c r="F231" t="n">
         <v>1.4909</v>
@@ -52420,10 +52420,10 @@
         <v>0.8074</v>
       </c>
       <c r="H231" t="n">
-        <v>-0.0018</v>
+        <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4169</v>
+        <v>1.4166</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52436,7 +52436,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7852</v>
+        <v>0.785</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52445,7 +52445,7 @@
         <v>1.3842</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6354</v>
+        <v>0.6353</v>
       </c>
       <c r="F232" t="n">
         <v>1.3842</v>
@@ -52454,10 +52454,10 @@
         <v>0.6059</v>
       </c>
       <c r="H232" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4795</v>
+        <v>1.479</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52470,7 +52470,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.7851</v>
+        <v>0.785</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6856</v>
+        <v>0.6855</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52488,10 +52488,10 @@
         <v>0.5925</v>
       </c>
       <c r="H233" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5496</v>
+        <v>1.5493</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8793</v>
+        <v>0.8792</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52513,7 +52513,7 @@
         <v>1.2983</v>
       </c>
       <c r="E234" t="n">
-        <v>0.7746</v>
+        <v>0.7745</v>
       </c>
       <c r="F234" t="n">
         <v>1.2983</v>
@@ -52522,10 +52522,10 @@
         <v>0.8879</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.608</v>
+        <v>1.6078</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52538,7 +52538,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8132</v>
+        <v>0.8131</v>
       </c>
       <c r="C235" t="n">
         <v>-1.935</v>
@@ -52547,7 +52547,7 @@
         <v>1.3372</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6822</v>
+        <v>0.6821</v>
       </c>
       <c r="F235" t="n">
         <v>1.3372</v>
@@ -52556,10 +52556,10 @@
         <v>0.4615</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.671</v>
+        <v>1.6709</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8461</v>
+        <v>0.846</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
@@ -52581,7 +52581,7 @@
         <v>1.3716</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7147</v>
+        <v>0.7146</v>
       </c>
       <c r="F236" t="n">
         <v>1.3716</v>
@@ -52590,10 +52590,10 @@
         <v>0.502</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7036</v>
+        <v>1.7032</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.852</v>
+        <v>0.8519</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
@@ -52615,7 +52615,7 @@
         <v>1.4213</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7097</v>
+        <v>0.7095</v>
       </c>
       <c r="F237" t="n">
         <v>1.4213</v>
@@ -52624,10 +52624,10 @@
         <v>0.6513</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0293</v>
+        <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4976</v>
+        <v>1.4973</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52640,7 +52640,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7207</v>
+        <v>0.7206</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
@@ -52649,7 +52649,7 @@
         <v>1.2149</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5971</v>
+        <v>0.597</v>
       </c>
       <c r="F238" t="n">
         <v>1.2149</v>
@@ -52658,10 +52658,10 @@
         <v>0.2396</v>
       </c>
       <c r="H238" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4629</v>
+        <v>1.4624</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52674,7 +52674,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7454</v>
+        <v>0.7453</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6453</v>
+        <v>0.6451</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52692,10 +52692,10 @@
         <v>0.29</v>
       </c>
       <c r="H239" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6129</v>
+        <v>1.6124</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52717,7 +52717,7 @@
         <v>1.2526</v>
       </c>
       <c r="E240" t="n">
-        <v>0.695</v>
+        <v>0.6949</v>
       </c>
       <c r="F240" t="n">
         <v>1.2526</v>
@@ -52726,10 +52726,10 @@
         <v>0.3082</v>
       </c>
       <c r="H240" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6992</v>
+        <v>1.6989</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.73</v>
+        <v>0.7299</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
@@ -52751,7 +52751,7 @@
         <v>1.2935</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5891</v>
+        <v>0.589</v>
       </c>
       <c r="F241" t="n">
         <v>1.2935</v>
@@ -52760,10 +52760,10 @@
         <v>-0.1287</v>
       </c>
       <c r="H241" t="n">
-        <v>-0.0022</v>
+        <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7359</v>
+        <v>1.7355</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52785,7 +52785,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.6308</v>
+        <v>0.6307</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52794,10 +52794,10 @@
         <v>-0.0516</v>
       </c>
       <c r="H242" t="n">
-        <v>-0.0022</v>
+        <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.795</v>
+        <v>1.7947</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52810,7 +52810,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.758</v>
+        <v>0.7579</v>
       </c>
       <c r="C243" t="n">
         <v>-1.541</v>
@@ -52819,7 +52819,7 @@
         <v>1.3065</v>
       </c>
       <c r="E243" t="n">
-        <v>0.6209</v>
+        <v>0.6207</v>
       </c>
       <c r="F243" t="n">
         <v>1.3065</v>
@@ -52828,10 +52828,10 @@
         <v>-0.0404</v>
       </c>
       <c r="H243" t="n">
-        <v>-0.0022</v>
+        <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7187</v>
+        <v>1.7184</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6509</v>
+        <v>0.6508</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52853,7 +52853,7 @@
         <v>1.3533</v>
       </c>
       <c r="E244" t="n">
-        <v>0.4754</v>
+        <v>0.4752</v>
       </c>
       <c r="F244" t="n">
         <v>1.3533</v>
@@ -52862,10 +52862,10 @@
         <v>-0.4305</v>
       </c>
       <c r="H244" t="n">
-        <v>-0.1145</v>
+        <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6861</v>
+        <v>1.6858</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52878,7 +52878,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.6977</v>
+        <v>0.6976</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
@@ -52887,7 +52887,7 @@
         <v>1.5772</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4778</v>
+        <v>0.4777</v>
       </c>
       <c r="F245" t="n">
         <v>1.5772</v>
@@ -52896,10 +52896,10 @@
         <v>-0.3682</v>
       </c>
       <c r="H245" t="n">
-        <v>-0.1145</v>
+        <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5565</v>
+        <v>1.5563</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52912,7 +52912,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.7739</v>
+        <v>0.7738</v>
       </c>
       <c r="C246" t="n">
         <v>-1.645</v>
@@ -52921,7 +52921,7 @@
         <v>1.5808</v>
       </c>
       <c r="E246" t="n">
-        <v>0.5722</v>
+        <v>0.572</v>
       </c>
       <c r="F246" t="n">
         <v>1.5808</v>
@@ -52930,10 +52930,10 @@
         <v>-0.226</v>
       </c>
       <c r="H246" t="n">
-        <v>-0.1145</v>
+        <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6564</v>
+        <v>1.6559</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52946,7 +52946,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="C247" t="n">
         <v>-1.552</v>
@@ -52955,7 +52955,7 @@
         <v>1.4551</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5088</v>
+        <v>0.5087</v>
       </c>
       <c r="F247" t="n">
         <v>1.4551</v>
@@ -52964,10 +52964,10 @@
         <v>-0.3896</v>
       </c>
       <c r="H247" t="n">
-        <v>-0.1089</v>
+        <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6841</v>
+        <v>1.6836</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52980,7 +52980,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6567</v>
       </c>
       <c r="C248" t="n">
         <v>-1.551</v>
@@ -52989,7 +52989,7 @@
         <v>1.3006</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4959</v>
+        <v>0.4957</v>
       </c>
       <c r="F248" t="n">
         <v>1.3006</v>
@@ -52998,10 +52998,10 @@
         <v>-0.6012</v>
       </c>
       <c r="H248" t="n">
-        <v>-0.1089</v>
+        <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7791</v>
+        <v>1.7785</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53014,7 +53014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6697</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
@@ -53023,7 +53023,7 @@
         <v>1.1168</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5582</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F249" t="n">
         <v>1.1168</v>
@@ -53032,10 +53032,10 @@
         <v>-0.4419</v>
       </c>
       <c r="H249" t="n">
-        <v>-0.1089</v>
+        <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8506</v>
+        <v>1.8498</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6266</v>
+        <v>0.6264</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53057,7 +53057,7 @@
         <v>1.2162</v>
       </c>
       <c r="E250" t="n">
-        <v>0.4793</v>
+        <v>0.479</v>
       </c>
       <c r="F250" t="n">
         <v>1.2162</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.934</v>
+        <v>1.933</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53082,7 +53082,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7005</v>
+        <v>0.7003</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53091,7 +53091,7 @@
         <v>1.2364</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5666</v>
+        <v>0.5663</v>
       </c>
       <c r="F251" t="n">
         <v>1.2364</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0932</v>
+        <v>2.092</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7704</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2106</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6607</v>
+        <v>0.6604</v>
       </c>
       <c r="F252" t="n">
         <v>1.2106</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2008</v>
+        <v>2.1995</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53150,7 +53150,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4567</v>
+        <v>0.4564</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53159,7 +53159,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5627</v>
+        <v>0.5624</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53168,10 +53168,10 @@
         <v>-0.8758</v>
       </c>
       <c r="H253" t="n">
-        <v>-0.1067</v>
+        <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2551</v>
+        <v>2.2539</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5893</v>
+        <v>0.589</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53202,10 +53202,10 @@
         <v>-0.9031</v>
       </c>
       <c r="H254" t="n">
-        <v>-0.1067</v>
+        <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.346</v>
+        <v>2.3446</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5681</v>
+        <v>0.5677</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.5996</v>
+        <v>0.5991</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53236,10 +53236,10 @@
         <v>-1.0579</v>
       </c>
       <c r="H255" t="n">
-        <v>-0.1067</v>
+        <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4109</v>
+        <v>2.4091</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4633</v>
+        <v>0.463</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4568</v>
+        <v>0.4564</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53270,10 +53270,10 @@
         <v>-1.5568</v>
       </c>
       <c r="H256" t="n">
-        <v>-0.1716</v>
+        <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4334</v>
+        <v>2.432</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4838</v>
+        <v>0.4835</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5246</v>
+        <v>0.5241</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53304,10 +53304,10 @@
         <v>-1.4572</v>
       </c>
       <c r="H257" t="n">
-        <v>-0.1716</v>
+        <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5541</v>
+        <v>2.5524</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4892</v>
+        <v>0.4887</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5384</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53338,10 +53338,10 @@
         <v>-1.5369</v>
       </c>
       <c r="H258" t="n">
-        <v>-0.1716</v>
+        <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7003</v>
+        <v>2.6981</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5255</v>
+        <v>0.5249</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.576</v>
+        <v>0.5753</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53372,10 +53372,10 @@
         <v>-1.6383</v>
       </c>
       <c r="H259" t="n">
-        <v>-0.146</v>
+        <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8861</v>
+        <v>2.8835</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5738</v>
+        <v>0.5733</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6148</v>
+        <v>0.6142</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53406,10 +53406,10 @@
         <v>-1.5539</v>
       </c>
       <c r="H260" t="n">
-        <v>-0.146</v>
+        <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9316</v>
+        <v>2.9292</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5514</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.6072</v>
+        <v>0.6065</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53440,10 +53440,10 @@
         <v>-1.5539</v>
       </c>
       <c r="H261" t="n">
-        <v>-0.146</v>
+        <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9291</v>
+        <v>2.9267</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,22 +53456,22 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.6011</v>
+        <v>0.5923</v>
       </c>
       <c r="C262" t="n">
-        <v>-1.367</v>
+        <v>-1.267</v>
       </c>
       <c r="E262" t="n">
-        <v>0.6011</v>
+        <v>0.5923</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5539</v>
       </c>
       <c r="H262" t="n">
-        <v>-0.146</v>
+        <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.9048</v>
+        <v>2.8642</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,22 +53484,22 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.6011</v>
+        <v>0.6102</v>
       </c>
       <c r="C263" t="n">
-        <v>-1.367</v>
+        <v>-1.267</v>
       </c>
       <c r="E263" t="n">
-        <v>0.6011</v>
+        <v>0.6102</v>
       </c>
       <c r="G263" t="n">
         <v>-1.5539</v>
       </c>
       <c r="H263" t="n">
-        <v>-0.146</v>
+        <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9048</v>
+        <v>2.9355</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>-0.382</v>
+        <v>-0.383</v>
       </c>
     </row>
     <row r="35">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="112">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="258">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.61</v>
+        <v>0.609</v>
       </c>
     </row>
   </sheetData>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68956.72</v>
+        <v>68633.09</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>68956.72</v>
+        <v>68633.09</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44634,7 +44634,7 @@
         <v>0.2564</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8522</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.2564</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5658</v>
+        <v>-0.5659</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5341</v>
+        <v>-0.5342</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4986</v>
+        <v>-0.4987</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4175</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -44943,7 +44943,7 @@
         <v>0.1635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3032</v>
+        <v>-0.3033</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2811</v>
@@ -44965,7 +44965,7 @@
         <v>0.1005</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4209</v>
+        <v>-0.421</v>
       </c>
       <c r="F12" t="n">
         <v>0.1005</v>
@@ -45215,7 +45215,7 @@
         <v>0.4155</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2005</v>
+        <v>-0.2006</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8472</v>
@@ -45283,7 +45283,7 @@
         <v>0.4155</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1446</v>
+        <v>-0.1447</v>
       </c>
       <c r="J21" t="n">
         <v>-0.8549</v>
@@ -45793,7 +45793,7 @@
         <v>0.1887</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2353</v>
+        <v>-0.2354</v>
       </c>
       <c r="J36" t="n">
         <v>0.0412</v>
@@ -45861,7 +45861,7 @@
         <v>0.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3815</v>
+        <v>-0.3816</v>
       </c>
       <c r="J38" t="n">
         <v>0.1937</v>
@@ -45929,7 +45929,7 @@
         <v>-0.312</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5678</v>
+        <v>-0.5679</v>
       </c>
       <c r="J40" t="n">
         <v>0.2773</v>
@@ -46010,7 +46010,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3255</v>
+        <v>-0.3256</v>
       </c>
       <c r="C43" t="n">
         <v>-0.5</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5692</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8337</v>
+        <v>-0.8338</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0507</v>
+        <v>-1.0508</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46257,7 +46257,7 @@
         <v>0.1309</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.9657</v>
+        <v>-0.9658</v>
       </c>
       <c r="F50" t="n">
         <v>0.1309</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.087</v>
+        <v>-1.0871</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0914</v>
+        <v>-1.0915</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.009</v>
+        <v>-1.0091</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46359,7 +46359,7 @@
         <v>0.061</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.3364</v>
+        <v>-1.3365</v>
       </c>
       <c r="F53" t="n">
         <v>0.061</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9839</v>
+        <v>-0.984</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46393,7 +46393,7 @@
         <v>-0.331</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.3505</v>
+        <v>-1.3506</v>
       </c>
       <c r="F54" t="n">
         <v>-0.331</v>
@@ -46427,7 +46427,7 @@
         <v>-0.5726</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.2874</v>
+        <v>-1.2875</v>
       </c>
       <c r="F55" t="n">
         <v>-0.5726</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9822</v>
+        <v>-0.9823</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46529,7 +46529,7 @@
         <v>-0.8349</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.2701</v>
+        <v>-1.2702</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8349</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0748</v>
+        <v>-1.0749</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.075</v>
+        <v>-1.0751</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46622,7 +46622,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-1.103</v>
+        <v>-1.1031</v>
       </c>
       <c r="C61" t="n">
         <v>0.5718</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0801</v>
+        <v>-1.0802</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0535</v>
+        <v>-1.0536</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0902</v>
+        <v>-1.0903</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0756</v>
+        <v>-1.0757</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0174</v>
+        <v>-1.0175</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0495</v>
+        <v>-1.0496</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0822</v>
+        <v>-1.0823</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.149</v>
+        <v>-1.1491</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46903,7 +46903,7 @@
         <v>-0.2627</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2113</v>
+        <v>-1.2114</v>
       </c>
       <c r="F69" t="n">
         <v>-0.2627</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1817</v>
+        <v>-1.1818</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46971,7 +46971,7 @@
         <v>-0.111</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0946</v>
+        <v>-1.0947</v>
       </c>
       <c r="F71" t="n">
         <v>-0.111</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2204</v>
+        <v>-1.2205</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2136</v>
+        <v>-1.2137</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47064,7 +47064,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8375</v>
+        <v>-0.8376</v>
       </c>
       <c r="C74" t="n">
         <v>0.299</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1881</v>
+        <v>-1.1882</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1991</v>
+        <v>-1.1992</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2557</v>
+        <v>-1.2558</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.302</v>
+        <v>-1.3021</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3287</v>
+        <v>-1.3288</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6202</v>
+        <v>-0.6203</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0603</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3038</v>
+        <v>-1.3039</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3174</v>
+        <v>-1.3175</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2769</v>
+        <v>-1.277</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47549,7 +47549,7 @@
         <v>0.3312</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.7325</v>
       </c>
       <c r="F88" t="n">
         <v>0.3312</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2714</v>
+        <v>-1.2715</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47651,7 +47651,7 @@
         <v>0.1753</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6445</v>
+        <v>-0.6446</v>
       </c>
       <c r="F91" t="n">
         <v>0.1753</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2992</v>
+        <v>-1.2993</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2864</v>
+        <v>-1.2865</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2372</v>
+        <v>-1.2373</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47880,7 +47880,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.3782</v>
+        <v>-0.3783</v>
       </c>
       <c r="C98" t="n">
         <v>-0.6211</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.055</v>
+        <v>-1.0551</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3005</v>
+        <v>-0.3006</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9615</v>
+        <v>-0.9616</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.91</v>
+        <v>-0.9101</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -47991,7 +47991,7 @@
         <v>0.1061</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.4424</v>
+        <v>-0.4425</v>
       </c>
       <c r="F101" t="n">
         <v>0.1061</v>
@@ -48071,7 +48071,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8037</v>
+        <v>-0.8038</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48139,7 +48139,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7496</v>
       </c>
       <c r="J105" t="n">
         <v>-0.3022</v>
@@ -48152,7 +48152,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-0.0731</v>
+        <v>-0.0732</v>
       </c>
       <c r="C106" t="n">
         <v>-0.8269</v>
@@ -48275,7 +48275,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5736</v>
+        <v>-0.5737</v>
       </c>
       <c r="J109" t="n">
         <v>-0.3653</v>
@@ -48365,7 +48365,7 @@
         <v>0.8887</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="F112" t="n">
         <v>0.8887</v>
@@ -48467,7 +48467,7 @@
         <v>1.7505</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.0081</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="F115" t="n">
         <v>1.7505</v>
@@ -48637,7 +48637,7 @@
         <v>1.4582</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1289</v>
+        <v>0.1288</v>
       </c>
       <c r="F120" t="n">
         <v>1.4582</v>
@@ -48717,7 +48717,7 @@
         <v>0.3802</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0917</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>-0.1326</v>
@@ -48887,7 +48887,7 @@
         <v>0.7683</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1119</v>
+        <v>0.112</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0956</v>
@@ -49045,7 +49045,7 @@
         <v>0.3558</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3359</v>
+        <v>0.336</v>
       </c>
       <c r="F132" t="n">
         <v>0.3558</v>
@@ -49669,7 +49669,7 @@
         <v>1.0753</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0074</v>
+        <v>-0.0073</v>
       </c>
       <c r="J150" t="n">
         <v>0.5164</v>
@@ -49818,7 +49818,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.6599</v>
+        <v>0.66</v>
       </c>
       <c r="C155" t="n">
         <v>-0.408</v>
@@ -49873,7 +49873,7 @@
         <v>1.1242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="J156" t="n">
         <v>0.6836</v>
@@ -49941,7 +49941,7 @@
         <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -49954,7 +49954,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.7313</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="C159" t="n">
         <v>-0.527</v>
@@ -50043,7 +50043,7 @@
         <v>1.1757</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0106</v>
+        <v>-0.0105</v>
       </c>
       <c r="J161" t="n">
         <v>1.0249</v>
@@ -50077,7 +50077,7 @@
         <v>1.1757</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0265</v>
+        <v>0.0266</v>
       </c>
       <c r="J162" t="n">
         <v>1.0036</v>
@@ -50124,7 +50124,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.7632</v>
+        <v>0.7633</v>
       </c>
       <c r="C164" t="n">
         <v>-0.614</v>
@@ -50145,7 +50145,7 @@
         <v>1.1753</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0704</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>1.1755</v>
@@ -50179,7 +50179,7 @@
         <v>1.1753</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0612</v>
+        <v>0.0613</v>
       </c>
       <c r="J165" t="n">
         <v>1.141</v>
@@ -50553,7 +50553,7 @@
         <v>0.9665</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1616</v>
+        <v>-0.1615</v>
       </c>
       <c r="J176" t="n">
         <v>1.6097</v>
@@ -50643,7 +50643,7 @@
         <v>0.6654</v>
       </c>
       <c r="E179" t="n">
-        <v>0.7316</v>
+        <v>0.7317</v>
       </c>
       <c r="F179" t="n">
         <v>0.6654</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2101</v>
+        <v>-0.21</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50791,7 +50791,7 @@
         <v>0.8421</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2176</v>
+        <v>-0.2175</v>
       </c>
       <c r="J183" t="n">
         <v>1.969</v>
@@ -50872,7 +50872,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.6889</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="C186" t="n">
         <v>-0.055</v>
@@ -50893,7 +50893,7 @@
         <v>0.5822000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2793</v>
+        <v>-0.2792</v>
       </c>
       <c r="J186" t="n">
         <v>2.0342</v>
@@ -50927,7 +50927,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2087</v>
+        <v>-0.2086</v>
       </c>
       <c r="J187" t="n">
         <v>2.1594</v>
@@ -50995,7 +50995,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1836</v>
+        <v>-0.1835</v>
       </c>
       <c r="J189" t="n">
         <v>1.6451</v>
@@ -51017,7 +51017,7 @@
         <v>0.257</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3984</v>
+        <v>0.3985</v>
       </c>
       <c r="F190" t="n">
         <v>0.257</v>
@@ -51029,7 +51029,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1559</v>
+        <v>-0.1558</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51063,7 +51063,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1331</v>
+        <v>-0.133</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0367</v>
+        <v>-0.0366</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51178,7 +51178,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.2236</v>
+        <v>0.2237</v>
       </c>
       <c r="C195" t="n">
         <v>0.094</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0862</v>
+        <v>0.0863</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1978</v>
+        <v>0.1979</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2481</v>
+        <v>0.2482</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51348,7 +51348,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.2067</v>
+        <v>0.2068</v>
       </c>
       <c r="C200" t="n">
         <v>-0.29</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51416,7 +51416,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2617</v>
+        <v>0.2618</v>
       </c>
       <c r="C202" t="n">
         <v>-0.388</v>
@@ -51425,7 +51425,7 @@
         <v>0.4629</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2114</v>
+        <v>0.2115</v>
       </c>
       <c r="F202" t="n">
         <v>0.4629</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3457</v>
+        <v>0.3458</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3694</v>
+        <v>0.3695</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3956</v>
+        <v>0.3957</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51561,7 +51561,7 @@
         <v>0.5259</v>
       </c>
       <c r="E206" t="n">
-        <v>0.2632</v>
+        <v>0.2633</v>
       </c>
       <c r="F206" t="n">
         <v>0.5259</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.394</v>
+        <v>0.3941</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4005</v>
+        <v>0.4006</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5847</v>
+        <v>0.5848</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6979</v>
+        <v>0.698</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7592</v>
+        <v>0.7593</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51799,7 +51799,7 @@
         <v>1.5668</v>
       </c>
       <c r="E213" t="n">
-        <v>0.4799</v>
+        <v>0.48</v>
       </c>
       <c r="F213" t="n">
         <v>1.5668</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7722</v>
+        <v>0.7723</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8845</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51858,7 +51858,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.7672</v>
+        <v>0.7673</v>
       </c>
       <c r="C215" t="n">
         <v>-2.285</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9333</v>
+        <v>0.9334</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51901,7 +51901,7 @@
         <v>1.9752</v>
       </c>
       <c r="E216" t="n">
-        <v>0.5121</v>
+        <v>0.5122</v>
       </c>
       <c r="F216" t="n">
         <v>1.9752</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8897</v>
+        <v>0.8898</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51935,7 +51935,7 @@
         <v>1.5631</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3887</v>
+        <v>0.3888</v>
       </c>
       <c r="F217" t="n">
         <v>1.5631</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.741</v>
+        <v>0.7411</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7629</v>
+        <v>0.763</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52071,7 +52071,7 @@
         <v>1.8118</v>
       </c>
       <c r="E221" t="n">
-        <v>0.4311</v>
+        <v>0.4312</v>
       </c>
       <c r="F221" t="n">
         <v>1.8118</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7768</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8746</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52130,7 +52130,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.7904</v>
+        <v>0.7905</v>
       </c>
       <c r="C223" t="n">
         <v>-2.155</v>
@@ -52139,7 +52139,7 @@
         <v>1.7757</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5441</v>
+        <v>0.5442</v>
       </c>
       <c r="F223" t="n">
         <v>1.7757</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9865</v>
+        <v>0.9866</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6979</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5867</v>
+        <v>0.5868</v>
       </c>
       <c r="F224" t="n">
         <v>1.6979</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.014</v>
+        <v>1.0141</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0832</v>
+        <v>1.0833</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52241,7 +52241,7 @@
         <v>1.478</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5085</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F226" t="n">
         <v>1.478</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1639</v>
+        <v>1.164</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2036</v>
+        <v>1.2037</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2616</v>
+        <v>1.2617</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1852</v>
+        <v>1.1853</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52377,7 +52377,7 @@
         <v>1.1747</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="F230" t="n">
         <v>1.1747</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2963</v>
+        <v>1.2964</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52411,7 +52411,7 @@
         <v>1.4909</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6724</v>
+        <v>0.6725</v>
       </c>
       <c r="F231" t="n">
         <v>1.4909</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4166</v>
+        <v>1.4168</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52436,7 +52436,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.785</v>
+        <v>0.7851</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.479</v>
+        <v>1.4791</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6855</v>
+        <v>0.6856</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5493</v>
+        <v>1.5495</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8792</v>
+        <v>0.8793</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6078</v>
+        <v>1.608</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6709</v>
+        <v>1.671</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7032</v>
+        <v>1.7034</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52615,7 +52615,7 @@
         <v>1.4213</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7095</v>
+        <v>0.7096</v>
       </c>
       <c r="F237" t="n">
         <v>1.4213</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4973</v>
+        <v>1.4974</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4624</v>
+        <v>1.4625</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6451</v>
+        <v>0.6452</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6124</v>
+        <v>1.6126</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52717,7 +52717,7 @@
         <v>1.2526</v>
       </c>
       <c r="E240" t="n">
-        <v>0.6949</v>
+        <v>0.695</v>
       </c>
       <c r="F240" t="n">
         <v>1.2526</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6989</v>
+        <v>1.6991</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7355</v>
+        <v>1.7357</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7947</v>
+        <v>1.7948</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52819,7 +52819,7 @@
         <v>1.3065</v>
       </c>
       <c r="E243" t="n">
-        <v>0.6207</v>
+        <v>0.6208</v>
       </c>
       <c r="F243" t="n">
         <v>1.3065</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7184</v>
+        <v>1.7185</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6508</v>
+        <v>0.6509</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52853,7 +52853,7 @@
         <v>1.3533</v>
       </c>
       <c r="E244" t="n">
-        <v>0.4752</v>
+        <v>0.4753</v>
       </c>
       <c r="F244" t="n">
         <v>1.3533</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6858</v>
+        <v>1.6859</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5563</v>
+        <v>1.5565</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52921,7 +52921,7 @@
         <v>1.5808</v>
       </c>
       <c r="E246" t="n">
-        <v>0.572</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="F246" t="n">
         <v>1.5808</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6559</v>
+        <v>1.6561</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6836</v>
+        <v>1.6837</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7785</v>
+        <v>1.7787</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53014,7 +53014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6697</v>
+        <v>0.6698</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8498</v>
+        <v>1.85</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6264</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53057,7 +53057,7 @@
         <v>1.2162</v>
       </c>
       <c r="E250" t="n">
-        <v>0.479</v>
+        <v>0.4791</v>
       </c>
       <c r="F250" t="n">
         <v>1.2162</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.933</v>
+        <v>1.9332</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.092</v>
+        <v>2.0922</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7704</v>
+        <v>0.7705</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1995</v>
+        <v>2.1998</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53150,7 +53150,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4564</v>
+        <v>0.4565</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2539</v>
+        <v>2.2541</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6</v>
+        <v>0.6001</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3446</v>
+        <v>2.3448</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5677</v>
+        <v>0.5678</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.5991</v>
+        <v>0.5992</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4091</v>
+        <v>2.4094</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4564</v>
+        <v>0.4565</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.432</v>
+        <v>2.4322</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5241</v>
+        <v>0.5242</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5524</v>
+        <v>2.5527</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4887</v>
+        <v>0.4888</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5379</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6981</v>
+        <v>2.6984</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5249</v>
+        <v>0.525</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5753</v>
+        <v>0.5754</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8835</v>
+        <v>2.8839</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5733</v>
+        <v>0.5734</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6142</v>
+        <v>0.6143</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9292</v>
+        <v>2.9295</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5514</v>
+        <v>0.5515</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.6065</v>
+        <v>0.6066</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9267</v>
+        <v>2.927</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5923</v>
+        <v>0.5924</v>
       </c>
       <c r="C262" t="n">
         <v>-1.267</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5923</v>
+        <v>0.5924</v>
       </c>
       <c r="G262" t="n">
         <v>-1.5539</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8642</v>
+        <v>2.8645</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.6102</v>
+        <v>0.6088</v>
       </c>
       <c r="C263" t="n">
         <v>-1.267</v>
       </c>
       <c r="E263" t="n">
-        <v>0.6102</v>
+        <v>0.6088</v>
       </c>
       <c r="G263" t="n">
         <v>-1.5539</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9355</v>
+        <v>2.93</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.182</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="57">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>0.571</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="206">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="228">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.569</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="256">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.485</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="258">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.586</v>
+        <v>0.588</v>
       </c>
     </row>
   </sheetData>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69071.01300000001</v>
+        <v>69474.255</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69071.01330000001</v>
+        <v>69474.255</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44693,7 +44693,7 @@
         <v>0.1583</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6127</v>
+        <v>-0.6126</v>
       </c>
       <c r="F4" t="n">
         <v>0.1583</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5658</v>
+        <v>-0.5657</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5341</v>
+        <v>-0.534</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4986</v>
+        <v>-0.4985</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4156</v>
+        <v>-0.4155</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44909,7 +44909,7 @@
         <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3902</v>
+        <v>-0.3901</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2593</v>
@@ -45169,7 +45169,7 @@
         <v>-0.0315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3442</v>
+        <v>-0.3441</v>
       </c>
       <c r="F18" t="n">
         <v>-0.0315</v>
@@ -45203,7 +45203,7 @@
         <v>0.0354</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3888</v>
+        <v>-0.3887</v>
       </c>
       <c r="F19" t="n">
         <v>0.0354</v>
@@ -45249,7 +45249,7 @@
         <v>0.4155</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1594</v>
+        <v>-0.1593</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8268</v>
@@ -45317,7 +45317,7 @@
         <v>0.2284</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1104</v>
+        <v>-0.1103</v>
       </c>
       <c r="J22" t="n">
         <v>-0.6861</v>
@@ -45543,7 +45543,7 @@
         <v>-0.0907</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4542</v>
+        <v>-0.4541</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0907</v>
@@ -45759,7 +45759,7 @@
         <v>0.1887</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1111</v>
+        <v>-0.111</v>
       </c>
       <c r="J35" t="n">
         <v>-0.075</v>
@@ -45827,7 +45827,7 @@
         <v>0.0667</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2446</v>
+        <v>-0.2445</v>
       </c>
       <c r="J37" t="n">
         <v>0.0238</v>
@@ -45895,7 +45895,7 @@
         <v>0.0667</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4179</v>
+        <v>-0.4178</v>
       </c>
       <c r="J39" t="n">
         <v>0.1293</v>
@@ -45963,7 +45963,7 @@
         <v>-0.312</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5546</v>
+        <v>-0.5545</v>
       </c>
       <c r="J41" t="n">
         <v>0.3169</v>
@@ -45997,7 +45997,7 @@
         <v>-0.312</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5527</v>
+        <v>-0.5526</v>
       </c>
       <c r="J42" t="n">
         <v>0.4153</v>
@@ -46031,7 +46031,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.523</v>
+        <v>-0.5229</v>
       </c>
       <c r="J43" t="n">
         <v>0.4481</v>
@@ -46044,7 +46044,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.237</v>
+        <v>-0.2369</v>
       </c>
       <c r="C44" t="n">
         <v>-0.506</v>
@@ -46087,7 +46087,7 @@
         <v>1.0383</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.5211</v>
+        <v>-0.521</v>
       </c>
       <c r="F45" t="n">
         <v>1.0383</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8337</v>
+        <v>-0.8336</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0507</v>
+        <v>-1.0506</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46257,7 +46257,7 @@
         <v>0.1309</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.9649</v>
+        <v>-0.9648</v>
       </c>
       <c r="F50" t="n">
         <v>0.1309</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.087</v>
+        <v>-1.0869</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0914</v>
+        <v>-1.0913</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.009</v>
+        <v>-1.0089</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9839</v>
+        <v>-0.9838</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0098</v>
+        <v>-1.0097</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9822</v>
+        <v>-0.9821</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0157</v>
+        <v>-1.0156</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0748</v>
+        <v>-1.0747</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46563,7 +46563,7 @@
         <v>-0.8138</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.2536</v>
+        <v>-1.2535</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8138</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.075</v>
+        <v>-1.0749</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0535</v>
+        <v>-1.0534</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0902</v>
+        <v>-1.0901</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.0992</v>
+        <v>-1.0991</v>
       </c>
       <c r="C64" t="n">
         <v>0.5042</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0756</v>
+        <v>-1.0755</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46792,7 +46792,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0529</v>
+        <v>-1.0528</v>
       </c>
       <c r="C66" t="n">
         <v>0.4982</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0495</v>
+        <v>-1.0494</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46826,7 +46826,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0299</v>
+        <v>-1.0298</v>
       </c>
       <c r="C67" t="n">
         <v>0.454</v>
@@ -46835,7 +46835,7 @@
         <v>-0.1883</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2403</v>
+        <v>-1.2402</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1883</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0822</v>
+        <v>-1.0821</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46869,7 +46869,7 @@
         <v>-0.2742</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2166</v>
+        <v>-1.2165</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2742</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.149</v>
+        <v>-1.1489</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1817</v>
+        <v>-1.1816</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1959</v>
+        <v>-1.1958</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2204</v>
+        <v>-1.2203</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47005,7 +47005,7 @@
         <v>-0.151</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0962</v>
+        <v>-1.0961</v>
       </c>
       <c r="F72" t="n">
         <v>-0.151</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2136</v>
+        <v>-1.2135</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1918</v>
+        <v>-1.1917</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47073,7 +47073,7 @@
         <v>-0.1694</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0042</v>
+        <v>-1.0041</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1694</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1881</v>
+        <v>-1.188</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1991</v>
+        <v>-1.199</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47132,7 +47132,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7752</v>
+        <v>-0.7751</v>
       </c>
       <c r="C76" t="n">
         <v>0.13</v>
@@ -47141,7 +47141,7 @@
         <v>-0.0872</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9472</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0872</v>
@@ -47166,7 +47166,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7377</v>
+        <v>-0.7376</v>
       </c>
       <c r="C77" t="n">
         <v>0.107</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2426</v>
+        <v>-1.2425</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2557</v>
+        <v>-1.2556</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47311,7 +47311,7 @@
         <v>0.3194</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.8583</v>
+        <v>-0.8582</v>
       </c>
       <c r="F81" t="n">
         <v>0.3194</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.302</v>
+        <v>-1.3019</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47370,7 +47370,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6946</v>
+        <v>-0.6945</v>
       </c>
       <c r="C83" t="n">
         <v>-0.0563</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3287</v>
+        <v>-1.3286</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3038</v>
+        <v>-1.3037</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47438,7 +47438,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5881</v>
       </c>
       <c r="C85" t="n">
         <v>-0.1757</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3174</v>
+        <v>-1.3173</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47481,7 +47481,7 @@
         <v>0.2359</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7955</v>
+        <v>-0.7954</v>
       </c>
       <c r="F86" t="n">
         <v>0.2359</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3187</v>
+        <v>-1.3186</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2769</v>
+        <v>-1.2768</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2714</v>
+        <v>-1.2713</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2751</v>
+        <v>-1.275</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47676,7 +47676,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.5226</v>
       </c>
       <c r="C92" t="n">
         <v>-0.3907</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2992</v>
+        <v>-1.2991</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2864</v>
+        <v>-1.2863</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47812,7 +47812,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.389</v>
+        <v>-0.3889</v>
       </c>
       <c r="C96" t="n">
         <v>-0.4517</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2372</v>
+        <v>-1.2371</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1811</v>
+        <v>-1.181</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.055</v>
+        <v>-1.0549</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3005</v>
+        <v>-0.3004</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9615</v>
+        <v>-0.9614</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -48003,7 +48003,7 @@
         <v>-0.47</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8367</v>
+        <v>-0.8366</v>
       </c>
       <c r="J101" t="n">
         <v>-0.5199</v>
@@ -48037,7 +48037,7 @@
         <v>-0.47</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.739</v>
+        <v>-0.7389</v>
       </c>
       <c r="J102" t="n">
         <v>-0.3549</v>
@@ -48059,7 +48059,7 @@
         <v>0.3906</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2818</v>
+        <v>-0.2817</v>
       </c>
       <c r="F103" t="n">
         <v>0.3906</v>
@@ -48173,7 +48173,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6988</v>
+        <v>-0.6987</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3368</v>
@@ -48207,7 +48207,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7129</v>
+        <v>-0.7128</v>
       </c>
       <c r="J107" t="n">
         <v>-0.348</v>
@@ -48241,7 +48241,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6425</v>
+        <v>-0.6424</v>
       </c>
       <c r="J108" t="n">
         <v>-0.3957</v>
@@ -48263,7 +48263,7 @@
         <v>1.5008</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.1614</v>
+        <v>-0.1613</v>
       </c>
       <c r="F109" t="n">
         <v>1.5008</v>
@@ -48377,7 +48377,7 @@
         <v>0.0859</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5579</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2325</v>
@@ -48513,7 +48513,7 @@
         <v>0.3854</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4864</v>
+        <v>-0.4863</v>
       </c>
       <c r="J116" t="n">
         <v>-0.2774</v>
@@ -48581,7 +48581,7 @@
         <v>0.3858</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3588</v>
+        <v>-0.3587</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1556</v>
@@ -48875,7 +48875,7 @@
         <v>0.3784</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3235</v>
+        <v>0.3234</v>
       </c>
       <c r="F127" t="n">
         <v>0.3784</v>
@@ -48921,7 +48921,7 @@
         <v>0.7683</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1207</v>
+        <v>0.1206</v>
       </c>
       <c r="J128" t="n">
         <v>-0.1184</v>
@@ -49057,7 +49057,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1029</v>
+        <v>0.1028</v>
       </c>
       <c r="J132" t="n">
         <v>-0.1091</v>
@@ -49079,7 +49079,7 @@
         <v>0.3665</v>
       </c>
       <c r="E133" t="n">
-        <v>0.363</v>
+        <v>0.3629</v>
       </c>
       <c r="F133" t="n">
         <v>0.3665</v>
@@ -49295,7 +49295,7 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2163</v>
+        <v>-0.2162</v>
       </c>
       <c r="J139" t="n">
         <v>-0.0402</v>
@@ -49410,7 +49410,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4318</v>
+        <v>0.4319</v>
       </c>
       <c r="C143" t="n">
         <v>-0.347</v>
@@ -49533,7 +49533,7 @@
         <v>1.1068</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0199</v>
+        <v>0.0198</v>
       </c>
       <c r="J146" t="n">
         <v>0.2917</v>
@@ -49555,7 +49555,7 @@
         <v>0.5475</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5979</v>
+        <v>0.5978</v>
       </c>
       <c r="F147" t="n">
         <v>0.5475</v>
@@ -49601,7 +49601,7 @@
         <v>1.0753</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0039</v>
+        <v>-0.004</v>
       </c>
       <c r="J148" t="n">
         <v>0.4268</v>
@@ -49737,7 +49737,7 @@
         <v>1.1972</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0023</v>
+        <v>-0.0024</v>
       </c>
       <c r="J152" t="n">
         <v>0.5928</v>
@@ -49852,7 +49852,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6647</v>
       </c>
       <c r="C156" t="n">
         <v>-0.419</v>
@@ -49963,7 +49963,7 @@
         <v>0.8693</v>
       </c>
       <c r="E159" t="n">
-        <v>0.6965</v>
+        <v>0.6964</v>
       </c>
       <c r="F159" t="n">
         <v>0.8693</v>
@@ -50009,7 +50009,7 @@
         <v>1.1757</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0411</v>
+        <v>-0.0412</v>
       </c>
       <c r="J160" t="n">
         <v>0.9242</v>
@@ -50031,7 +50031,7 @@
         <v>0.7343</v>
       </c>
       <c r="E161" t="n">
-        <v>0.7211</v>
+        <v>0.721</v>
       </c>
       <c r="F161" t="n">
         <v>0.7343</v>
@@ -50111,7 +50111,7 @@
         <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0472</v>
+        <v>0.0471</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50158,7 +50158,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7439</v>
+        <v>0.7438</v>
       </c>
       <c r="C165" t="n">
         <v>-0.603</v>
@@ -50281,7 +50281,7 @@
         <v>1.1104</v>
       </c>
       <c r="I168" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0631</v>
       </c>
       <c r="J168" t="n">
         <v>1.2437</v>
@@ -50362,7 +50362,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.7764</v>
+        <v>0.7763</v>
       </c>
       <c r="C171" t="n">
         <v>-0.518</v>
@@ -50383,7 +50383,7 @@
         <v>1.0767</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0503</v>
+        <v>-0.0504</v>
       </c>
       <c r="J171" t="n">
         <v>1.4412</v>
@@ -50417,7 +50417,7 @@
         <v>1.0374</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0578</v>
+        <v>-0.0579</v>
       </c>
       <c r="J172" t="n">
         <v>1.4574</v>
@@ -50451,7 +50451,7 @@
         <v>1.0374</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.056</v>
+        <v>-0.0561</v>
       </c>
       <c r="J173" t="n">
         <v>1.448</v>
@@ -50485,7 +50485,7 @@
         <v>1.0374</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1045</v>
+        <v>-0.1046</v>
       </c>
       <c r="J174" t="n">
         <v>1.5397</v>
@@ -50621,7 +50621,7 @@
         <v>0.9385</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2036</v>
+        <v>-0.2037</v>
       </c>
       <c r="J178" t="n">
         <v>1.719</v>
@@ -50736,7 +50736,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.7904</v>
+        <v>0.7903</v>
       </c>
       <c r="C182" t="n">
         <v>-0.301</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2101</v>
+        <v>-0.2102</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50940,7 +50940,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.4831</v>
+        <v>0.483</v>
       </c>
       <c r="C188" t="n">
         <v>0.139</v>
@@ -50961,7 +50961,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1993</v>
+        <v>-0.1994</v>
       </c>
       <c r="J188" t="n">
         <v>1.9226</v>
@@ -51051,7 +51051,7 @@
         <v>0.082</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3554</v>
+        <v>0.3553</v>
       </c>
       <c r="F191" t="n">
         <v>0.082</v>
@@ -51097,7 +51097,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0784</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51110,7 +51110,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.284</v>
+        <v>0.2839</v>
       </c>
       <c r="C193" t="n">
         <v>0.08400000000000001</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0367</v>
+        <v>-0.0368</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0862</v>
+        <v>0.0861</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51212,7 +51212,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2595</v>
+        <v>0.2594</v>
       </c>
       <c r="C196" t="n">
         <v>-0.08500000000000001</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1663</v>
+        <v>0.1662</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2004</v>
+        <v>0.2003</v>
       </c>
       <c r="C197" t="n">
         <v>-0.08</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1951</v>
+        <v>0.195</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51289,7 +51289,7 @@
         <v>0.1598</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2237</v>
+        <v>0.2236</v>
       </c>
       <c r="F198" t="n">
         <v>0.1598</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1978</v>
+        <v>0.1977</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51323,7 +51323,7 @@
         <v>0.2044</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1519</v>
+        <v>0.1518</v>
       </c>
       <c r="F199" t="n">
         <v>0.2044</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2481</v>
+        <v>0.248</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2527</v>
+        <v>0.2526</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2612</v>
+        <v>0.2611</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3456</v>
+        <v>0.3455</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3694</v>
+        <v>0.3693</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4033</v>
+        <v>0.4032</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3956</v>
+        <v>0.3955</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51552,7 +51552,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3156</v>
+        <v>0.3155</v>
       </c>
       <c r="C206" t="n">
         <v>-0.8100000000000001</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.394</v>
+        <v>0.3939</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51586,7 +51586,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.406</v>
+        <v>0.4059</v>
       </c>
       <c r="C207" t="n">
         <v>-0.8080000000000001</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4005</v>
+        <v>0.4004</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51620,7 +51620,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3832</v>
+        <v>0.3831</v>
       </c>
       <c r="C208" t="n">
         <v>-1.479</v>
@@ -51629,7 +51629,7 @@
         <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2979</v>
+        <v>0.2978</v>
       </c>
       <c r="F208" t="n">
         <v>0.7243000000000001</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5847</v>
+        <v>0.5846</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6118</v>
+        <v>0.6117</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6979</v>
+        <v>0.6978</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7592</v>
+        <v>0.7591</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51790,7 +51790,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.697</v>
+        <v>0.6969</v>
       </c>
       <c r="C213" t="n">
         <v>-2.07</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7722</v>
+        <v>0.7721</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8845</v>
+        <v>0.8844</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51858,7 +51858,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.767</v>
+        <v>0.7669</v>
       </c>
       <c r="C215" t="n">
         <v>-2.285</v>
@@ -51867,7 +51867,7 @@
         <v>1.8962</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4847</v>
+        <v>0.4846</v>
       </c>
       <c r="F215" t="n">
         <v>1.8962</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9333</v>
+        <v>0.9332</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51901,7 +51901,7 @@
         <v>1.9752</v>
       </c>
       <c r="E216" t="n">
-        <v>0.5117</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="F216" t="n">
         <v>1.9752</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8897</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51935,7 +51935,7 @@
         <v>1.5631</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3886</v>
+        <v>0.3885</v>
       </c>
       <c r="F217" t="n">
         <v>1.5631</v>
@@ -51969,7 +51969,7 @@
         <v>2.1416</v>
       </c>
       <c r="E218" t="n">
-        <v>0.373</v>
+        <v>0.3729</v>
       </c>
       <c r="F218" t="n">
         <v>2.1416</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6892</v>
+        <v>0.6891</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.741</v>
+        <v>0.7409</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7629</v>
+        <v>0.7628</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7766</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52105,7 +52105,7 @@
         <v>1.7254</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5072</v>
+        <v>0.5071</v>
       </c>
       <c r="F222" t="n">
         <v>1.7254</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8744</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52139,7 +52139,7 @@
         <v>1.7757</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5438</v>
       </c>
       <c r="F223" t="n">
         <v>1.7757</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9863</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6979</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5864</v>
+        <v>0.5863</v>
       </c>
       <c r="F224" t="n">
         <v>1.6979</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.014</v>
+        <v>1.0138</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52207,7 +52207,7 @@
         <v>1.6715</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5938</v>
+        <v>0.5937</v>
       </c>
       <c r="F225" t="n">
         <v>1.6715</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0832</v>
+        <v>1.083</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52232,7 +52232,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.7025</v>
+        <v>0.7024</v>
       </c>
       <c r="C226" t="n">
         <v>-2.088</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1638</v>
+        <v>1.1637</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2035</v>
+        <v>1.2034</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2615</v>
+        <v>1.2614</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1852</v>
+        <v>1.1851</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52377,7 +52377,7 @@
         <v>1.1747</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6697</v>
+        <v>0.6696</v>
       </c>
       <c r="F230" t="n">
         <v>1.1747</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2962</v>
+        <v>1.2961</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4166</v>
+        <v>1.4164</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4789</v>
+        <v>1.4787</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52470,7 +52470,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.785</v>
+        <v>0.7849</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5493</v>
+        <v>1.5491</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8789</v>
+        <v>0.8788</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6078</v>
+        <v>1.6076</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6708</v>
+        <v>1.6706</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52581,7 +52581,7 @@
         <v>1.3716</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7145</v>
+        <v>0.7144</v>
       </c>
       <c r="F236" t="n">
         <v>1.3716</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7032</v>
+        <v>1.703</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4972</v>
+        <v>1.497</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52649,7 +52649,7 @@
         <v>1.2149</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5972</v>
+        <v>0.5971</v>
       </c>
       <c r="F238" t="n">
         <v>1.2149</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4623</v>
+        <v>1.4622</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52674,7 +52674,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7454</v>
+        <v>0.7453</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6124</v>
+        <v>1.6122</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52708,7 +52708,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8065</v>
+        <v>0.8064</v>
       </c>
       <c r="C240" t="n">
         <v>-1.795</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6989</v>
+        <v>1.6987</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7302</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7355</v>
+        <v>1.7353</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7946</v>
+        <v>1.7944</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7183</v>
+        <v>1.7181</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6514</v>
+        <v>0.6513</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6857</v>
+        <v>1.6856</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52878,7 +52878,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
@@ -52887,7 +52887,7 @@
         <v>1.5772</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4783</v>
+        <v>0.4782</v>
       </c>
       <c r="F245" t="n">
         <v>1.5772</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5563</v>
+        <v>1.5562</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6559</v>
+        <v>1.6557</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52955,7 +52955,7 @@
         <v>1.4551</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5093</v>
+        <v>0.5092</v>
       </c>
       <c r="F247" t="n">
         <v>1.4551</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6835</v>
+        <v>1.6834</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52989,7 +52989,7 @@
         <v>1.3006</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4964</v>
+        <v>0.4963</v>
       </c>
       <c r="F248" t="n">
         <v>1.3006</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7785</v>
+        <v>1.7783</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53023,7 +53023,7 @@
         <v>1.1168</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5585</v>
+        <v>0.5584</v>
       </c>
       <c r="F249" t="n">
         <v>1.1168</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8498</v>
+        <v>1.8496</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6272</v>
+        <v>0.6271</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.933</v>
+        <v>1.9327</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0919</v>
+        <v>2.0916</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7708</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2106</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6609</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="F252" t="n">
         <v>1.2106</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1995</v>
+        <v>2.1992</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5633</v>
+        <v>0.5632</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2538</v>
+        <v>2.2535</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6007</v>
+        <v>0.6006</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5898</v>
+        <v>0.5897</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3445</v>
+        <v>2.3442</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.409</v>
+        <v>2.4087</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.458</v>
+        <v>0.4579</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4319</v>
+        <v>2.4316</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4846</v>
+        <v>0.4845</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5254</v>
+        <v>0.5253</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5523</v>
+        <v>2.552</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4898</v>
+        <v>0.4897</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5392</v>
+        <v>0.5391</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.698</v>
+        <v>2.6976</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5261</v>
+        <v>0.526</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5768</v>
+        <v>0.5767</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8834</v>
+        <v>2.8829</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5744</v>
+        <v>0.5743</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6156</v>
+        <v>0.6155</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9291</v>
+        <v>2.9286</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5316</v>
+        <v>0.5315</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5818</v>
+        <v>0.5816</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9265</v>
+        <v>2.9261</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5675</v>
+        <v>0.5674</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5675</v>
+        <v>0.5674</v>
       </c>
       <c r="G262" t="n">
         <v>-1.6529</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8641</v>
+        <v>2.8636</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5859</v>
+        <v>0.5876</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5859</v>
+        <v>0.5876</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9375</v>
+        <v>2.9444</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.532</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="262">
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.652</v>
+        <v>1.655</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.922</v>
+        <v>1.93</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.398</v>
+        <v>2.41</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.091</v>
+        <v>3.098</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.145</v>
+        <v>4.15</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.948</v>
+        <v>-0.945</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.519</v>
+        <v>-0.51</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.591</v>
+        <v>0.598</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.86</v>
+        <v>-0.87</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69474.255</v>
+        <v>69586.546</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.652</v>
+        <v>1.6546</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9223</v>
+        <v>1.9296</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3977</v>
+        <v>2.4096</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0913</v>
+        <v>3.0976</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1453</v>
+        <v>4.1504</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.948</v>
+        <v>-0.9454</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5192</v>
+        <v>-0.5104</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5913</v>
+        <v>0.5976</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69474.255</v>
+        <v>69586.546</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>9.8789</v>
+        <v>9.8695</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.054</v>
+        <v>1.0528</v>
       </c>
     </row>
   </sheetData>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4173</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -44977,7 +44977,7 @@
         <v>0.1635</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2203</v>
+        <v>-0.2202</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2209</v>
@@ -45815,7 +45815,7 @@
         <v>0.4868</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4765</v>
+        <v>-0.4764</v>
       </c>
       <c r="F37" t="n">
         <v>0.4868</v>
@@ -46010,7 +46010,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3245</v>
+        <v>-0.3244</v>
       </c>
       <c r="C43" t="n">
         <v>-0.5</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9261</v>
+        <v>-0.926</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46359,7 +46359,7 @@
         <v>0.061</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.3357</v>
+        <v>-1.3356</v>
       </c>
       <c r="F53" t="n">
         <v>0.061</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0361</v>
+        <v>-1.036</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1062</v>
+        <v>-1.1061</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0801</v>
+        <v>-1.08</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46699,7 +46699,7 @@
         <v>-0.2142</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.3299</v>
+        <v>-1.3298</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2142</v>
@@ -46733,7 +46733,7 @@
         <v>-0.2631</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3082</v>
+        <v>-1.3081</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2631</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0174</v>
+        <v>-1.0173</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2167</v>
+        <v>-1.2166</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1968</v>
+        <v>-1.1967</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2357</v>
+        <v>-1.2356</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3181</v>
+        <v>-1.318</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3186</v>
+        <v>-1.3185</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47549,7 +47549,7 @@
         <v>0.3312</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.7321</v>
+        <v>-0.732</v>
       </c>
       <c r="F88" t="n">
         <v>0.3312</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2159</v>
+        <v>-1.2158</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2231</v>
+        <v>-1.223</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2936</v>
+        <v>-1.2935</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2769</v>
+        <v>-1.2768</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.91</v>
+        <v>-0.9099</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -48105,7 +48105,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.73</v>
+        <v>-0.7299</v>
       </c>
       <c r="J104" t="n">
         <v>-0.3041</v>
@@ -48411,7 +48411,7 @@
         <v>0.0859</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5372</v>
+        <v>-0.5371</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2751</v>
@@ -49240,7 +49240,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.41</v>
+        <v>0.4101</v>
       </c>
       <c r="C138" t="n">
         <v>-0.5590000000000001</v>
@@ -49907,7 +49907,7 @@
         <v>1.1579</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0687</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="J157" t="n">
         <v>0.7487</v>
@@ -50247,7 +50247,7 @@
         <v>1.1104</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0709</v>
+        <v>0.0708</v>
       </c>
       <c r="J167" t="n">
         <v>1.2431</v>
@@ -50315,7 +50315,7 @@
         <v>1.0767</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="J169" t="n">
         <v>1.3187</v>
@@ -50689,7 +50689,7 @@
         <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1767</v>
+        <v>-0.1768</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -50872,7 +50872,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.6885</v>
+        <v>0.6884</v>
       </c>
       <c r="C186" t="n">
         <v>-0.055</v>
@@ -51314,7 +51314,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1624</v>
+        <v>0.1623</v>
       </c>
       <c r="C199" t="n">
         <v>-0.283</v>
@@ -51484,7 +51484,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3706</v>
+        <v>0.3705</v>
       </c>
       <c r="C204" t="n">
         <v>-0.406</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4494</v>
+        <v>0.4493</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7721</v>
+        <v>0.772</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7587</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8744</v>
+        <v>0.8743</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9863</v>
+        <v>0.9862</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52164,7 +52164,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8087</v>
+        <v>0.8086</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
@@ -52241,7 +52241,7 @@
         <v>1.478</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5085</v>
       </c>
       <c r="F226" t="n">
         <v>1.478</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1637</v>
+        <v>1.1636</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52300,7 +52300,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.7994</v>
+        <v>0.7993</v>
       </c>
       <c r="C228" t="n">
         <v>-2.049</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1851</v>
+        <v>1.185</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52368,7 +52368,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7706</v>
       </c>
       <c r="C230" t="n">
         <v>-1.991</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2961</v>
+        <v>1.296</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8359</v>
+        <v>0.8358</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4164</v>
+        <v>1.4163</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6855</v>
+        <v>0.6854</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5491</v>
+        <v>1.549</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6076</v>
+        <v>1.6075</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8459</v>
+        <v>0.8458</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.703</v>
+        <v>1.7029</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4622</v>
+        <v>1.4621</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6452</v>
+        <v>0.6451</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6122</v>
+        <v>1.6121</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7353</v>
+        <v>1.7352</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52785,7 +52785,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.631</v>
+        <v>0.6309</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6856</v>
+        <v>1.6855</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5562</v>
+        <v>1.5561</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6834</v>
+        <v>1.6833</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7783</v>
+        <v>1.7782</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8496</v>
+        <v>1.8495</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0916</v>
+        <v>2.0915</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1992</v>
+        <v>2.1991</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2535</v>
+        <v>2.2534</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3442</v>
+        <v>2.3441</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5685</v>
+        <v>0.5684</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6001</v>
+        <v>0.6</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4087</v>
+        <v>2.4086</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4642</v>
+        <v>0.4641</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4579</v>
+        <v>0.4578</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4316</v>
+        <v>2.4315</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.552</v>
+        <v>2.5519</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6976</v>
+        <v>2.6974</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8829</v>
+        <v>2.8828</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6155</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9286</v>
+        <v>2.9285</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9261</v>
+        <v>2.926</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8636</v>
+        <v>2.8635</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5876</v>
+        <v>0.5881</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5876</v>
+        <v>0.5881</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9444</v>
+        <v>2.9463</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>0.531</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="262">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.93</v>
+        <v>1.931</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.098</v>
+        <v>3.096</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.15</v>
+        <v>4.148</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.51</v>
+        <v>-0.509</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.598</v>
+        <v>0.596</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69586.546</v>
+        <v>69495.807</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44350,7 +44350,7 @@
         <v>1.7282</v>
       </c>
       <c r="AL262" t="n">
-        <v>-8.243600000000001</v>
+        <v>-10.1694</v>
       </c>
       <c r="AM262" t="n">
         <v>63.5506</v>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6546</v>
+        <v>1.655</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9296</v>
+        <v>1.9307</v>
       </c>
       <c r="E263" t="n">
-        <v>2.4096</v>
+        <v>2.4103</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0976</v>
+        <v>3.0962</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1504</v>
+        <v>4.148</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9454</v>
+        <v>-0.945</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5104</v>
+        <v>-0.5094</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5976</v>
+        <v>0.5962</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69586.546</v>
+        <v>69495.8067</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44504,7 +44504,7 @@
         <v>1.7282</v>
       </c>
       <c r="AL263" t="n">
-        <v>-8.243600000000001</v>
+        <v>-10.1694</v>
       </c>
       <c r="AM263" t="n">
         <v>63.5506</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>9.8695</v>
+        <v>9.8714</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0528</v>
+        <v>1.0518</v>
       </c>
     </row>
   </sheetData>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4173</v>
+        <v>-0.4174</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -46010,7 +46010,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.3244</v>
+        <v>-0.3245</v>
       </c>
       <c r="C43" t="n">
         <v>-0.5</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.926</v>
+        <v>-0.9261</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46359,7 +46359,7 @@
         <v>0.061</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.3356</v>
+        <v>-1.3357</v>
       </c>
       <c r="F53" t="n">
         <v>0.061</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.036</v>
+        <v>-1.0361</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1061</v>
+        <v>-1.1062</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46699,7 +46699,7 @@
         <v>-0.2142</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.3298</v>
+        <v>-1.3299</v>
       </c>
       <c r="F63" t="n">
         <v>-0.2142</v>
@@ -46733,7 +46733,7 @@
         <v>-0.2631</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3081</v>
+        <v>-1.3082</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2631</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2166</v>
+        <v>-1.2167</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1967</v>
+        <v>-1.1968</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2356</v>
+        <v>-1.2357</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.318</v>
+        <v>-1.3181</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3185</v>
+        <v>-1.3186</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47549,7 +47549,7 @@
         <v>0.3312</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.732</v>
+        <v>-0.7321</v>
       </c>
       <c r="F88" t="n">
         <v>0.3312</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2158</v>
+        <v>-1.2159</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.223</v>
+        <v>-1.2231</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2935</v>
+        <v>-1.2936</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9099</v>
+        <v>-0.91</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -48105,7 +48105,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.7299</v>
+        <v>-0.73</v>
       </c>
       <c r="J104" t="n">
         <v>-0.3041</v>
@@ -49240,7 +49240,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4101</v>
+        <v>0.41</v>
       </c>
       <c r="C138" t="n">
         <v>-0.5590000000000001</v>
@@ -49907,7 +49907,7 @@
         <v>1.1579</v>
       </c>
       <c r="I157" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0687</v>
       </c>
       <c r="J157" t="n">
         <v>0.7487</v>
@@ -50247,7 +50247,7 @@
         <v>1.1104</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0708</v>
+        <v>0.0709</v>
       </c>
       <c r="J167" t="n">
         <v>1.2431</v>
@@ -50315,7 +50315,7 @@
         <v>1.0767</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0048</v>
+        <v>0.0049</v>
       </c>
       <c r="J169" t="n">
         <v>1.3187</v>
@@ -51314,7 +51314,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.1623</v>
+        <v>0.1624</v>
       </c>
       <c r="C199" t="n">
         <v>-0.283</v>
@@ -51484,7 +51484,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3705</v>
+        <v>0.3706</v>
       </c>
       <c r="C204" t="n">
         <v>-0.406</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4493</v>
+        <v>0.4494</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.772</v>
+        <v>0.7721</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7587</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8743</v>
+        <v>0.8744</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9862</v>
+        <v>0.9863</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52164,7 +52164,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8086</v>
+        <v>0.8087</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
@@ -52241,7 +52241,7 @@
         <v>1.478</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5085</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="F226" t="n">
         <v>1.478</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1636</v>
+        <v>1.1637</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52300,7 +52300,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.7993</v>
+        <v>0.7994</v>
       </c>
       <c r="C228" t="n">
         <v>-2.049</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.185</v>
+        <v>1.1851</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52368,7 +52368,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.7706</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="C230" t="n">
         <v>-1.991</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.296</v>
+        <v>1.2961</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8358</v>
+        <v>0.8359</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4163</v>
+        <v>1.4164</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6854</v>
+        <v>0.6855</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.549</v>
+        <v>1.5491</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6075</v>
+        <v>1.6076</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8458</v>
+        <v>0.8459</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7029</v>
+        <v>1.703</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6451</v>
+        <v>0.6452</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6121</v>
+        <v>1.6122</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7352</v>
+        <v>1.7353</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6833</v>
+        <v>1.6834</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7782</v>
+        <v>1.7783</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0915</v>
+        <v>2.0916</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1991</v>
+        <v>2.1992</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2534</v>
+        <v>2.2535</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5684</v>
+        <v>0.5685</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6</v>
+        <v>0.6001</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4641</v>
+        <v>0.4642</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4578</v>
+        <v>0.4579</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4315</v>
+        <v>2.4316</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6974</v>
+        <v>2.6975</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8828</v>
+        <v>2.8829</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6155</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9285</v>
+        <v>2.9286</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.926</v>
+        <v>2.9261</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8635</v>
+        <v>2.8636</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5881</v>
+        <v>0.5877</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5881</v>
+        <v>0.5877</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9463</v>
+        <v>2.9448</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.588</v>
+        <v>0.587</v>
       </c>
     </row>
   </sheetData>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69495.807</v>
+        <v>69429.394</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69495.8067</v>
+        <v>69429.3943</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44977,7 +44977,7 @@
         <v>0.1635</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2202</v>
+        <v>-0.2203</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2209</v>
@@ -45815,7 +45815,7 @@
         <v>0.4868</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4764</v>
+        <v>-0.4765</v>
       </c>
       <c r="F37" t="n">
         <v>0.4868</v>
@@ -45895,7 +45895,7 @@
         <v>0.0667</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4178</v>
+        <v>-0.4179</v>
       </c>
       <c r="J39" t="n">
         <v>0.1293</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9821</v>
+        <v>-0.9822</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.08</v>
+        <v>-1.0801</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46724,7 +46724,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-1.0991</v>
+        <v>-1.0992</v>
       </c>
       <c r="C64" t="n">
         <v>0.5042</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0755</v>
+        <v>-1.0756</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0173</v>
+        <v>-1.0174</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1816</v>
+        <v>-1.1817</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.188</v>
+        <v>-1.1881</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47370,7 +47370,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.6945</v>
+        <v>-0.6946</v>
       </c>
       <c r="C83" t="n">
         <v>-0.0563</v>
@@ -47481,7 +47481,7 @@
         <v>0.2359</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.7954</v>
+        <v>-0.7955</v>
       </c>
       <c r="F86" t="n">
         <v>0.2359</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2768</v>
+        <v>-1.2769</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.275</v>
+        <v>-1.2751</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2768</v>
+        <v>-1.2769</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -48411,7 +48411,7 @@
         <v>0.0859</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5371</v>
+        <v>-0.5372</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2751</v>
@@ -49057,7 +49057,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1028</v>
+        <v>0.1029</v>
       </c>
       <c r="J132" t="n">
         <v>-0.1091</v>
@@ -49555,7 +49555,7 @@
         <v>0.5475</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5978</v>
+        <v>0.5979</v>
       </c>
       <c r="F147" t="n">
         <v>0.5475</v>
@@ -49601,7 +49601,7 @@
         <v>1.0753</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.004</v>
+        <v>-0.0039</v>
       </c>
       <c r="J148" t="n">
         <v>0.4268</v>
@@ -50485,7 +50485,7 @@
         <v>1.0374</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1046</v>
+        <v>-0.1045</v>
       </c>
       <c r="J174" t="n">
         <v>1.5397</v>
@@ -50689,7 +50689,7 @@
         <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1768</v>
+        <v>-0.1767</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2102</v>
+        <v>-0.2101</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50872,7 +50872,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.6884</v>
+        <v>0.6885</v>
       </c>
       <c r="C186" t="n">
         <v>-0.055</v>
@@ -50940,7 +50940,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.483</v>
+        <v>0.4831</v>
       </c>
       <c r="C188" t="n">
         <v>0.139</v>
@@ -51323,7 +51323,7 @@
         <v>0.2044</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1518</v>
+        <v>0.1519</v>
       </c>
       <c r="F199" t="n">
         <v>0.2044</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2526</v>
+        <v>0.2527</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4032</v>
+        <v>0.4033</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51935,7 +51935,7 @@
         <v>1.5631</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3885</v>
+        <v>0.3886</v>
       </c>
       <c r="F217" t="n">
         <v>1.5631</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0138</v>
+        <v>1.0139</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4787</v>
+        <v>1.4788</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.497</v>
+        <v>1.4971</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4621</v>
+        <v>1.4622</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52708,7 +52708,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8064</v>
+        <v>0.8065</v>
       </c>
       <c r="C240" t="n">
         <v>-1.795</v>
@@ -52785,7 +52785,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.6309</v>
+        <v>0.631</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7944</v>
+        <v>1.7945</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7181</v>
+        <v>1.7182</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6513</v>
+        <v>0.6514</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6855</v>
+        <v>1.6856</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5561</v>
+        <v>1.5562</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8495</v>
+        <v>1.8496</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9327</v>
+        <v>1.9328</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3441</v>
+        <v>2.3442</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4086</v>
+        <v>2.4087</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5253</v>
+        <v>0.5254</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5519</v>
+        <v>2.552</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6975</v>
+        <v>2.6976</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8829</v>
+        <v>2.883</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9286</v>
+        <v>2.9287</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5816</v>
+        <v>0.5817</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9261</v>
+        <v>2.9262</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8636</v>
+        <v>2.8637</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5877</v>
+        <v>0.5874</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5877</v>
+        <v>0.5874</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9448</v>
+        <v>2.9436</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.655</v>
+        <v>1.654</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.931</v>
+        <v>1.928</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.41</v>
+        <v>2.404</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.096</v>
+        <v>3.086</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.148</v>
+        <v>4.139</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.945</v>
+        <v>-0.946</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.509</v>
+        <v>-0.513</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.596</v>
+        <v>0.586</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.86</v>
+        <v>-0.85</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.655</v>
+        <v>1.6539</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9307</v>
+        <v>1.9279</v>
       </c>
       <c r="E263" t="n">
-        <v>2.4103</v>
+        <v>2.404</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0962</v>
+        <v>3.0863</v>
       </c>
       <c r="G263" t="n">
-        <v>4.148</v>
+        <v>4.139</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.945</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5094</v>
+        <v>-0.5134</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5962</v>
+        <v>0.5863</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>9.8714</v>
+        <v>9.8886</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0518</v>
+        <v>1.0527</v>
       </c>
     </row>
   </sheetData>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>-1.181</v>
+        <v>-1.182</v>
       </c>
     </row>
     <row r="57">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="206">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="228">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="J255" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="256">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="258">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.587</v>
+        <v>0.586</v>
       </c>
     </row>
   </sheetData>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.404</v>
+        <v>2.4</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.086</v>
+        <v>3.078</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.139</v>
+        <v>4.13</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.513</v>
+        <v>-0.515</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.586</v>
+        <v>0.578</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69429.394</v>
+        <v>69058.61900000001</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6539</v>
+        <v>1.6542</v>
       </c>
       <c r="D263" t="n">
         <v>1.9279</v>
       </c>
       <c r="E263" t="n">
-        <v>2.404</v>
+        <v>2.3999</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0863</v>
+        <v>3.0779</v>
       </c>
       <c r="G263" t="n">
-        <v>4.139</v>
+        <v>4.1296</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9458</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5134</v>
+        <v>-0.5148</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5863</v>
+        <v>0.5779</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69429.3943</v>
+        <v>69058.6189</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>9.8886</v>
+        <v>9.9091</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0527</v>
+        <v>1.0517</v>
       </c>
     </row>
   </sheetData>
@@ -44693,7 +44693,7 @@
         <v>0.1583</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6126</v>
+        <v>-0.6127</v>
       </c>
       <c r="F4" t="n">
         <v>0.1583</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5657</v>
+        <v>-0.5658</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.534</v>
+        <v>-0.5341</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4985</v>
+        <v>-0.4986</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4155</v>
+        <v>-0.4156</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44909,7 +44909,7 @@
         <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3901</v>
+        <v>-0.3902</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2593</v>
@@ -45169,7 +45169,7 @@
         <v>-0.0315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3441</v>
+        <v>-0.3442</v>
       </c>
       <c r="F18" t="n">
         <v>-0.0315</v>
@@ -45203,7 +45203,7 @@
         <v>0.0354</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3887</v>
+        <v>-0.3888</v>
       </c>
       <c r="F19" t="n">
         <v>0.0354</v>
@@ -45249,7 +45249,7 @@
         <v>0.4155</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1593</v>
+        <v>-0.1594</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8268</v>
@@ -45317,7 +45317,7 @@
         <v>0.2284</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1103</v>
+        <v>-0.1104</v>
       </c>
       <c r="J22" t="n">
         <v>-0.6861</v>
@@ -45543,7 +45543,7 @@
         <v>-0.0907</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4541</v>
+        <v>-0.4542</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0907</v>
@@ -45759,7 +45759,7 @@
         <v>0.1887</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.111</v>
+        <v>-0.1111</v>
       </c>
       <c r="J35" t="n">
         <v>-0.075</v>
@@ -45827,7 +45827,7 @@
         <v>0.0667</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2445</v>
+        <v>-0.2446</v>
       </c>
       <c r="J37" t="n">
         <v>0.0238</v>
@@ -45963,7 +45963,7 @@
         <v>-0.312</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5545</v>
+        <v>-0.5546</v>
       </c>
       <c r="J41" t="n">
         <v>0.3169</v>
@@ -45997,7 +45997,7 @@
         <v>-0.312</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5526</v>
+        <v>-0.5527</v>
       </c>
       <c r="J42" t="n">
         <v>0.4153</v>
@@ -46031,7 +46031,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5229</v>
+        <v>-0.523</v>
       </c>
       <c r="J43" t="n">
         <v>0.4481</v>
@@ -46044,7 +46044,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.2369</v>
+        <v>-0.237</v>
       </c>
       <c r="C44" t="n">
         <v>-0.506</v>
@@ -46087,7 +46087,7 @@
         <v>1.0383</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.521</v>
+        <v>-0.5211</v>
       </c>
       <c r="F45" t="n">
         <v>1.0383</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8336</v>
+        <v>-0.8337</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0506</v>
+        <v>-1.0507</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46257,7 +46257,7 @@
         <v>0.1309</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.9648</v>
+        <v>-0.9649</v>
       </c>
       <c r="F50" t="n">
         <v>0.1309</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0869</v>
+        <v>-1.087</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0913</v>
+        <v>-1.0914</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0089</v>
+        <v>-1.009</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9838</v>
+        <v>-0.9839</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0097</v>
+        <v>-1.0098</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0361</v>
+        <v>-1.0362</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0156</v>
+        <v>-1.0157</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0747</v>
+        <v>-1.0748</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46563,7 +46563,7 @@
         <v>-0.8138</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.2535</v>
+        <v>-1.2536</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8138</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0749</v>
+        <v>-1.075</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0534</v>
+        <v>-1.0535</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0901</v>
+        <v>-1.0902</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46792,7 +46792,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0528</v>
+        <v>-1.0529</v>
       </c>
       <c r="C66" t="n">
         <v>0.4982</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0494</v>
+        <v>-1.0495</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46826,7 +46826,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.0298</v>
+        <v>-1.0299</v>
       </c>
       <c r="C67" t="n">
         <v>0.454</v>
@@ -46835,7 +46835,7 @@
         <v>-0.1883</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2402</v>
+        <v>-1.2403</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1883</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0821</v>
+        <v>-1.0822</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46869,7 +46869,7 @@
         <v>-0.2742</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2165</v>
+        <v>-1.2166</v>
       </c>
       <c r="F68" t="n">
         <v>-0.2742</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1489</v>
+        <v>-1.149</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1958</v>
+        <v>-1.1959</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2203</v>
+        <v>-1.2204</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47005,7 +47005,7 @@
         <v>-0.151</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0961</v>
+        <v>-1.0962</v>
       </c>
       <c r="F72" t="n">
         <v>-0.151</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2135</v>
+        <v>-1.2136</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1917</v>
+        <v>-1.1918</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47073,7 +47073,7 @@
         <v>-0.1694</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0041</v>
+        <v>-1.0042</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1694</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.199</v>
+        <v>-1.1991</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47132,7 +47132,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7751</v>
+        <v>-0.7752</v>
       </c>
       <c r="C76" t="n">
         <v>0.13</v>
@@ -47141,7 +47141,7 @@
         <v>-0.0872</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9472</v>
       </c>
       <c r="F76" t="n">
         <v>-0.0872</v>
@@ -47166,7 +47166,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.7376</v>
+        <v>-0.7377</v>
       </c>
       <c r="C77" t="n">
         <v>0.107</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2425</v>
+        <v>-1.2426</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2556</v>
+        <v>-1.2557</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47311,7 +47311,7 @@
         <v>0.3194</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.8582</v>
+        <v>-0.8583</v>
       </c>
       <c r="F81" t="n">
         <v>0.3194</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3019</v>
+        <v>-1.302</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3286</v>
+        <v>-1.3287</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3037</v>
+        <v>-1.3038</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47438,7 +47438,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.5881</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="C85" t="n">
         <v>-0.1757</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3173</v>
+        <v>-1.3174</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3186</v>
+        <v>-1.3187</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2713</v>
+        <v>-1.2714</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47676,7 +47676,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.5226</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="C92" t="n">
         <v>-0.3907</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2991</v>
+        <v>-1.2992</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2863</v>
+        <v>-1.2864</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47812,7 +47812,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3889</v>
+        <v>-0.389</v>
       </c>
       <c r="C96" t="n">
         <v>-0.4517</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2371</v>
+        <v>-1.2372</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.181</v>
+        <v>-1.1811</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0549</v>
+        <v>-1.055</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3004</v>
+        <v>-0.3005</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9614</v>
+        <v>-0.9615</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -48003,7 +48003,7 @@
         <v>-0.47</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8366</v>
+        <v>-0.8367</v>
       </c>
       <c r="J101" t="n">
         <v>-0.5199</v>
@@ -48037,7 +48037,7 @@
         <v>-0.47</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7389</v>
+        <v>-0.739</v>
       </c>
       <c r="J102" t="n">
         <v>-0.3549</v>
@@ -48059,7 +48059,7 @@
         <v>0.3906</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2817</v>
+        <v>-0.2818</v>
       </c>
       <c r="F103" t="n">
         <v>0.3906</v>
@@ -48173,7 +48173,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6987</v>
+        <v>-0.6988</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3368</v>
@@ -48207,7 +48207,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7128</v>
+        <v>-0.7129</v>
       </c>
       <c r="J107" t="n">
         <v>-0.348</v>
@@ -48241,7 +48241,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6424</v>
+        <v>-0.6425</v>
       </c>
       <c r="J108" t="n">
         <v>-0.3957</v>
@@ -48263,7 +48263,7 @@
         <v>1.5008</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.1613</v>
+        <v>-0.1614</v>
       </c>
       <c r="F109" t="n">
         <v>1.5008</v>
@@ -48377,7 +48377,7 @@
         <v>0.0859</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5579</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2325</v>
@@ -48513,7 +48513,7 @@
         <v>0.3854</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4863</v>
+        <v>-0.4864</v>
       </c>
       <c r="J116" t="n">
         <v>-0.2774</v>
@@ -48581,7 +48581,7 @@
         <v>0.3858</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3587</v>
+        <v>-0.3588</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1556</v>
@@ -48875,7 +48875,7 @@
         <v>0.3784</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3234</v>
+        <v>0.3235</v>
       </c>
       <c r="F127" t="n">
         <v>0.3784</v>
@@ -48921,7 +48921,7 @@
         <v>0.7683</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1206</v>
+        <v>0.1207</v>
       </c>
       <c r="J128" t="n">
         <v>-0.1184</v>
@@ -49079,7 +49079,7 @@
         <v>0.3665</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3629</v>
+        <v>0.363</v>
       </c>
       <c r="F133" t="n">
         <v>0.3665</v>
@@ -49227,7 +49227,7 @@
         <v>0.9537</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1473</v>
+        <v>-0.1474</v>
       </c>
       <c r="J137" t="n">
         <v>-0.074</v>
@@ -49295,7 +49295,7 @@
         <v>1.06</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2162</v>
+        <v>-0.2163</v>
       </c>
       <c r="J139" t="n">
         <v>-0.0402</v>
@@ -49410,7 +49410,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4319</v>
+        <v>0.4318</v>
       </c>
       <c r="C143" t="n">
         <v>-0.347</v>
@@ -49533,7 +49533,7 @@
         <v>1.1068</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0198</v>
+        <v>0.0199</v>
       </c>
       <c r="J146" t="n">
         <v>0.2917</v>
@@ -49737,7 +49737,7 @@
         <v>1.1972</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0024</v>
+        <v>-0.0023</v>
       </c>
       <c r="J152" t="n">
         <v>0.5928</v>
@@ -49852,7 +49852,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.6647</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="C156" t="n">
         <v>-0.419</v>
@@ -49963,7 +49963,7 @@
         <v>0.8693</v>
       </c>
       <c r="E159" t="n">
-        <v>0.6964</v>
+        <v>0.6965</v>
       </c>
       <c r="F159" t="n">
         <v>0.8693</v>
@@ -50009,7 +50009,7 @@
         <v>1.1757</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0412</v>
+        <v>-0.0411</v>
       </c>
       <c r="J160" t="n">
         <v>0.9242</v>
@@ -50031,7 +50031,7 @@
         <v>0.7343</v>
       </c>
       <c r="E161" t="n">
-        <v>0.721</v>
+        <v>0.7211</v>
       </c>
       <c r="F161" t="n">
         <v>0.7343</v>
@@ -50111,7 +50111,7 @@
         <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0471</v>
+        <v>0.0472</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50158,7 +50158,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.7438</v>
+        <v>0.7439</v>
       </c>
       <c r="C165" t="n">
         <v>-0.603</v>
@@ -50281,7 +50281,7 @@
         <v>1.1104</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0631</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>1.2437</v>
@@ -50362,7 +50362,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.7763</v>
+        <v>0.7764</v>
       </c>
       <c r="C171" t="n">
         <v>-0.518</v>
@@ -50383,7 +50383,7 @@
         <v>1.0767</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0504</v>
+        <v>-0.0503</v>
       </c>
       <c r="J171" t="n">
         <v>1.4412</v>
@@ -50417,7 +50417,7 @@
         <v>1.0374</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0579</v>
+        <v>-0.0578</v>
       </c>
       <c r="J172" t="n">
         <v>1.4574</v>
@@ -50451,7 +50451,7 @@
         <v>1.0374</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0561</v>
+        <v>-0.056</v>
       </c>
       <c r="J173" t="n">
         <v>1.448</v>
@@ -50621,7 +50621,7 @@
         <v>0.9385</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2037</v>
+        <v>-0.2036</v>
       </c>
       <c r="J178" t="n">
         <v>1.719</v>
@@ -50736,7 +50736,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.7903</v>
+        <v>0.7904</v>
       </c>
       <c r="C182" t="n">
         <v>-0.301</v>
@@ -50915,7 +50915,7 @@
         <v>0.3922</v>
       </c>
       <c r="E187" t="n">
-        <v>0.5684</v>
+        <v>0.5685</v>
       </c>
       <c r="F187" t="n">
         <v>0.3922</v>
@@ -50961,7 +50961,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1994</v>
+        <v>-0.1993</v>
       </c>
       <c r="J188" t="n">
         <v>1.9226</v>
@@ -51051,7 +51051,7 @@
         <v>0.082</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3553</v>
+        <v>0.3554</v>
       </c>
       <c r="F191" t="n">
         <v>0.082</v>
@@ -51097,7 +51097,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0784</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51110,7 +51110,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2839</v>
+        <v>0.284</v>
       </c>
       <c r="C193" t="n">
         <v>0.08400000000000001</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0368</v>
+        <v>-0.0367</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0861</v>
+        <v>0.0862</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51212,7 +51212,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2594</v>
+        <v>0.2595</v>
       </c>
       <c r="C196" t="n">
         <v>-0.08500000000000001</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1662</v>
+        <v>0.1663</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2003</v>
+        <v>0.2004</v>
       </c>
       <c r="C197" t="n">
         <v>-0.08</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.195</v>
+        <v>0.1951</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51289,7 +51289,7 @@
         <v>0.1598</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2236</v>
+        <v>0.2237</v>
       </c>
       <c r="F198" t="n">
         <v>0.1598</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1977</v>
+        <v>0.1978</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.248</v>
+        <v>0.2481</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2611</v>
+        <v>0.2612</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3455</v>
+        <v>0.3456</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3693</v>
+        <v>0.3694</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3955</v>
+        <v>0.3956</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51552,7 +51552,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.3155</v>
+        <v>0.3156</v>
       </c>
       <c r="C206" t="n">
         <v>-0.8100000000000001</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3939</v>
+        <v>0.394</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51586,7 +51586,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.4059</v>
+        <v>0.406</v>
       </c>
       <c r="C207" t="n">
         <v>-0.8080000000000001</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4004</v>
+        <v>0.4005</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51620,7 +51620,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.3831</v>
+        <v>0.3832</v>
       </c>
       <c r="C208" t="n">
         <v>-1.479</v>
@@ -51629,7 +51629,7 @@
         <v>0.7243000000000001</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2978</v>
+        <v>0.2979</v>
       </c>
       <c r="F208" t="n">
         <v>0.7243000000000001</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5846</v>
+        <v>0.5847</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6117</v>
+        <v>0.6118</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6978</v>
+        <v>0.6979</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7591</v>
+        <v>0.7592</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51790,7 +51790,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.6969</v>
+        <v>0.697</v>
       </c>
       <c r="C213" t="n">
         <v>-2.07</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8844</v>
+        <v>0.8845</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51858,7 +51858,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.7669</v>
+        <v>0.767</v>
       </c>
       <c r="C215" t="n">
         <v>-2.285</v>
@@ -51867,7 +51867,7 @@
         <v>1.8962</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4846</v>
+        <v>0.4847</v>
       </c>
       <c r="F215" t="n">
         <v>1.8962</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9332</v>
+        <v>0.9333</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51901,7 +51901,7 @@
         <v>1.9752</v>
       </c>
       <c r="E216" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.5117</v>
       </c>
       <c r="F216" t="n">
         <v>1.9752</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8897</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51969,7 +51969,7 @@
         <v>2.1416</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3729</v>
+        <v>0.373</v>
       </c>
       <c r="F218" t="n">
         <v>2.1416</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6891</v>
+        <v>0.6892</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7409</v>
+        <v>0.741</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7628</v>
+        <v>0.7629</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7766</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52105,7 +52105,7 @@
         <v>1.7254</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5071</v>
+        <v>0.5072</v>
       </c>
       <c r="F222" t="n">
         <v>1.7254</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8744</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52139,7 +52139,7 @@
         <v>1.7757</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5438</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="F223" t="n">
         <v>1.7757</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9863</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6979</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5863</v>
+        <v>0.5864</v>
       </c>
       <c r="F224" t="n">
         <v>1.6979</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0139</v>
+        <v>1.014</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52207,7 +52207,7 @@
         <v>1.6715</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5937</v>
+        <v>0.5938</v>
       </c>
       <c r="F225" t="n">
         <v>1.6715</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.083</v>
+        <v>1.0832</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52232,7 +52232,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.7024</v>
+        <v>0.7025</v>
       </c>
       <c r="C226" t="n">
         <v>-2.088</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1637</v>
+        <v>1.1638</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2034</v>
+        <v>1.2035</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2614</v>
+        <v>1.2615</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1851</v>
+        <v>1.1852</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52377,7 +52377,7 @@
         <v>1.1747</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6696</v>
+        <v>0.6697</v>
       </c>
       <c r="F230" t="n">
         <v>1.1747</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2961</v>
+        <v>1.2962</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4164</v>
+        <v>1.4166</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4788</v>
+        <v>1.4789</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52470,7 +52470,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.7849</v>
+        <v>0.785</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5491</v>
+        <v>1.5493</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8788</v>
+        <v>0.8789</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6076</v>
+        <v>1.6078</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6706</v>
+        <v>1.6708</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52581,7 +52581,7 @@
         <v>1.3716</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7144</v>
+        <v>0.7145</v>
       </c>
       <c r="F236" t="n">
         <v>1.3716</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.703</v>
+        <v>1.7032</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.8516</v>
+        <v>0.8517</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4971</v>
+        <v>1.4972</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52649,7 +52649,7 @@
         <v>1.2149</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5971</v>
+        <v>0.5972</v>
       </c>
       <c r="F238" t="n">
         <v>1.2149</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4622</v>
+        <v>1.4623</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52674,7 +52674,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7453</v>
+        <v>0.7454</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6122</v>
+        <v>1.6124</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6987</v>
+        <v>1.6989</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.7302</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
@@ -52751,7 +52751,7 @@
         <v>1.2935</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5894</v>
+        <v>0.5895</v>
       </c>
       <c r="F241" t="n">
         <v>1.2935</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7353</v>
+        <v>1.7355</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7945</v>
+        <v>1.7946</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7182</v>
+        <v>1.7183</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6856</v>
+        <v>1.6857</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52878,7 +52878,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.698</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
@@ -52887,7 +52887,7 @@
         <v>1.5772</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4782</v>
+        <v>0.4783</v>
       </c>
       <c r="F245" t="n">
         <v>1.5772</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5562</v>
+        <v>1.5563</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6557</v>
+        <v>1.6559</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52955,7 +52955,7 @@
         <v>1.4551</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5092</v>
+        <v>0.5093</v>
       </c>
       <c r="F247" t="n">
         <v>1.4551</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6834</v>
+        <v>1.6836</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52989,7 +52989,7 @@
         <v>1.3006</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4963</v>
+        <v>0.4964</v>
       </c>
       <c r="F248" t="n">
         <v>1.3006</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7783</v>
+        <v>1.7785</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53023,7 +53023,7 @@
         <v>1.1168</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5584</v>
+        <v>0.5585</v>
       </c>
       <c r="F249" t="n">
         <v>1.1168</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8496</v>
+        <v>1.8498</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6271</v>
+        <v>0.6272</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9328</v>
+        <v>1.933</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0916</v>
+        <v>2.0919</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7708</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2106</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6609</v>
       </c>
       <c r="F252" t="n">
         <v>1.2106</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1992</v>
+        <v>2.1995</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5632</v>
+        <v>0.5633</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2535</v>
+        <v>2.2538</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6006</v>
+        <v>0.6007</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5897</v>
+        <v>0.5898</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3442</v>
+        <v>2.3445</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4087</v>
+        <v>2.409</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4579</v>
+        <v>0.458</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4316</v>
+        <v>2.4319</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4845</v>
+        <v>0.4846</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.552</v>
+        <v>2.5523</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4897</v>
+        <v>0.4898</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5391</v>
+        <v>0.5392</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6976</v>
+        <v>2.698</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.526</v>
+        <v>0.5261</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5767</v>
+        <v>0.5768</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.883</v>
+        <v>2.8834</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5743</v>
+        <v>0.5744</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6155</v>
+        <v>0.6156</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9287</v>
+        <v>2.9291</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5315</v>
+        <v>0.5316</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5817</v>
+        <v>0.5818</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9262</v>
+        <v>2.9266</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5674</v>
+        <v>0.5675</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5674</v>
+        <v>0.5675</v>
       </c>
       <c r="G262" t="n">
         <v>-1.6529</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8637</v>
+        <v>2.8641</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5874</v>
+        <v>0.5858</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5874</v>
+        <v>0.5858</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9436</v>
+        <v>2.9373</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.59</t>
+          <t>+0.58</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.59 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.04%. The real policy rate is about -1.56%, roughly 1.20pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.58 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.04%. The real policy rate is about -1.56%, roughly 1.20pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>-0.86</v>
+        <v>-0.861</v>
       </c>
     </row>
     <row r="74">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>-0.592</v>
+        <v>-0.593</v>
       </c>
     </row>
     <row r="83">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="114">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>0.261</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="203">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>0.623</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="218">
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="261">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.586</v>
+        <v>0.584</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.654</v>
+        <v>1.655</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.4</v>
+        <v>2.398</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.078</v>
+        <v>3.071</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.13</v>
+        <v>4.123</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.946</v>
+        <v>-0.945</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.578</v>
+        <v>0.571</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>69058.61900000001</v>
+        <v>68595.352</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>2.3233</v>
       </c>
       <c r="F262" t="n">
-        <v>2.9922</v>
+        <v>3.05</v>
       </c>
       <c r="G262" t="n">
         <v>4.0579</v>
@@ -44275,7 +44275,7 @@
         <v>-0.5773</v>
       </c>
       <c r="M262" t="n">
-        <v>0.4922</v>
+        <v>0.55</v>
       </c>
       <c r="N262" t="n">
         <v>-1.557</v>
@@ -44383,10 +44383,10 @@
         <v>20.552</v>
       </c>
       <c r="AW262" t="n">
-        <v>10.3303</v>
+        <v>10.1724</v>
       </c>
       <c r="AX262" t="n">
-        <v>1.0657</v>
+        <v>1.0079</v>
       </c>
     </row>
     <row r="263">
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6542</v>
+        <v>1.6549</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9279</v>
+        <v>1.928</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3999</v>
+        <v>2.3976</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0779</v>
+        <v>3.0709</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1296</v>
+        <v>4.1232</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9458</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5148</v>
+        <v>-0.5155</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5779</v>
+        <v>0.5709</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>69058.6189</v>
+        <v>68595.352</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>9.9091</v>
+        <v>10.0809</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0517</v>
+        <v>1.0523</v>
       </c>
     </row>
   </sheetData>
@@ -44643,7 +44643,7 @@
         <v>-0.358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6315</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5626</v>
@@ -44656,7 +44656,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5221</v>
+        <v>-0.5222</v>
       </c>
       <c r="D3" t="n">
         <v>0.1068</v>
@@ -44671,7 +44671,7 @@
         <v>-0.0577</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5899</v>
+        <v>-0.59</v>
       </c>
       <c r="J3" t="n">
         <v>-1.5477</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5658</v>
+        <v>-0.5659</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44727,7 +44727,7 @@
         <v>0.2203</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5904</v>
+        <v>-0.5905</v>
       </c>
       <c r="F5" t="n">
         <v>0.2203</v>
@@ -44739,7 +44739,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5424</v>
+        <v>-0.5425</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5329</v>
@@ -44761,7 +44761,7 @@
         <v>0.2692</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.6044</v>
       </c>
       <c r="F6" t="n">
         <v>0.2692</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5341</v>
+        <v>-0.5342</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4986</v>
+        <v>-0.4987</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4175</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -44897,7 +44897,7 @@
         <v>0.0919</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4644</v>
+        <v>-0.4645</v>
       </c>
       <c r="F10" t="n">
         <v>0.0919</v>
@@ -44931,7 +44931,7 @@
         <v>0.1034</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4864</v>
+        <v>-0.4865</v>
       </c>
       <c r="F11" t="n">
         <v>0.1034</v>
@@ -44943,7 +44943,7 @@
         <v>0.1635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3032</v>
+        <v>-0.3033</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2811</v>
@@ -45045,7 +45045,7 @@
         <v>0.3251</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.22</v>
+        <v>-0.2201</v>
       </c>
       <c r="J14" t="n">
         <v>-1.0677</v>
@@ -45113,7 +45113,7 @@
         <v>0.4889</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1622</v>
+        <v>-0.1623</v>
       </c>
       <c r="J16" t="n">
         <v>-1.0083</v>
@@ -45215,7 +45215,7 @@
         <v>0.4155</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2005</v>
+        <v>-0.2006</v>
       </c>
       <c r="J19" t="n">
         <v>-0.8472</v>
@@ -45228,7 +45228,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3279</v>
+        <v>-0.328</v>
       </c>
       <c r="C20" t="n">
         <v>-0.415</v>
@@ -45283,7 +45283,7 @@
         <v>0.4155</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1446</v>
+        <v>-0.1447</v>
       </c>
       <c r="J21" t="n">
         <v>-0.8549</v>
@@ -45670,7 +45670,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3616</v>
+        <v>-0.3617</v>
       </c>
       <c r="C33" t="n">
         <v>-0.3673</v>
@@ -45793,7 +45793,7 @@
         <v>0.1887</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2353</v>
+        <v>-0.2354</v>
       </c>
       <c r="J36" t="n">
         <v>0.0412</v>
@@ -45861,7 +45861,7 @@
         <v>0.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3815</v>
+        <v>-0.3816</v>
       </c>
       <c r="J38" t="n">
         <v>0.1937</v>
@@ -45929,7 +45929,7 @@
         <v>-0.312</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5678</v>
+        <v>-0.5679</v>
       </c>
       <c r="J40" t="n">
         <v>0.2773</v>
@@ -45942,7 +45942,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.3647</v>
+        <v>-0.3648</v>
       </c>
       <c r="C41" t="n">
         <v>-0.4022</v>
@@ -46019,7 +46019,7 @@
         <v>0.7407</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5907</v>
+        <v>-0.5908</v>
       </c>
       <c r="F43" t="n">
         <v>0.7407</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5692</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46099,7 +46099,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5681</v>
       </c>
       <c r="J45" t="n">
         <v>0.613</v>
@@ -46133,7 +46133,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6508</v>
+        <v>-0.6509</v>
       </c>
       <c r="J46" t="n">
         <v>0.5804</v>
@@ -46155,7 +46155,7 @@
         <v>0.7934</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.7037</v>
+        <v>-0.7038</v>
       </c>
       <c r="F47" t="n">
         <v>0.7934</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8337</v>
+        <v>-0.8338</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9261</v>
+        <v>-0.9262</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46214,7 +46214,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8202</v>
       </c>
       <c r="C49" t="n">
         <v>-0.2307</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0507</v>
+        <v>-1.0508</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.087</v>
+        <v>-1.0871</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46291,7 +46291,7 @@
         <v>0.1167</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.9966</v>
       </c>
       <c r="F51" t="n">
         <v>0.1167</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0914</v>
+        <v>-1.0915</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46316,7 +46316,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0614</v>
+        <v>-1.0615</v>
       </c>
       <c r="C52" t="n">
         <v>0.2794</v>
@@ -46325,7 +46325,7 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.344</v>
+        <v>-1.3441</v>
       </c>
       <c r="F52" t="n">
         <v>0.06900000000000001</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.009</v>
+        <v>-1.0091</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46350,7 +46350,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-1.0563</v>
+        <v>-1.0564</v>
       </c>
       <c r="C53" t="n">
         <v>0.2834</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9839</v>
+        <v>-0.984</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46393,7 +46393,7 @@
         <v>-0.331</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.3498</v>
+        <v>-1.3499</v>
       </c>
       <c r="F54" t="n">
         <v>-0.331</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0098</v>
+        <v>-1.0099</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9822</v>
+        <v>-0.9823</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46461,7 +46461,7 @@
         <v>-0.8169999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.2726</v>
+        <v>-1.2727</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8169999999999999</v>
@@ -46495,7 +46495,7 @@
         <v>-0.895</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2968</v>
+        <v>-1.2969</v>
       </c>
       <c r="F57" t="n">
         <v>-0.895</v>
@@ -46529,7 +46529,7 @@
         <v>-0.8349</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.2692</v>
+        <v>-1.2693</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8349</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0748</v>
+        <v>-1.0749</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.075</v>
+        <v>-1.0751</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1062</v>
+        <v>-1.1063</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0801</v>
+        <v>-1.0802</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0535</v>
+        <v>-1.0536</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46690,7 +46690,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-1.1067</v>
+        <v>-1.1068</v>
       </c>
       <c r="C63" t="n">
         <v>0.5718</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0902</v>
+        <v>-1.0903</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0756</v>
+        <v>-1.0757</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0174</v>
+        <v>-1.0175</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46801,7 +46801,7 @@
         <v>-0.2093</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2637</v>
+        <v>-1.2638</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2093</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0495</v>
+        <v>-1.0496</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0822</v>
+        <v>-1.0823</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.149</v>
+        <v>-1.1491</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46903,7 +46903,7 @@
         <v>-0.2627</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2107</v>
+        <v>-1.2108</v>
       </c>
       <c r="F69" t="n">
         <v>-0.2627</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1817</v>
+        <v>-1.1818</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1959</v>
+        <v>-1.196</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2204</v>
+        <v>-1.2205</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2136</v>
+        <v>-1.2137</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47039,7 +47039,7 @@
         <v>-0.1183</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.046</v>
+        <v>-1.0461</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1183</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1918</v>
+        <v>-1.1919</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1881</v>
+        <v>-1.1882</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1991</v>
+        <v>-1.1992</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2167</v>
+        <v>-1.2168</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1968</v>
+        <v>-1.1969</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47200,7 +47200,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.6908</v>
+        <v>-0.6909</v>
       </c>
       <c r="C78" t="n">
         <v>0.114</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2357</v>
+        <v>-1.2358</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2557</v>
+        <v>-1.2558</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.302</v>
+        <v>-1.3021</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3181</v>
+        <v>-1.3182</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3287</v>
+        <v>-1.3288</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6199</v>
+        <v>-0.62</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0603</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3038</v>
+        <v>-1.3039</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47447,7 +47447,7 @@
         <v>0.1889</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.7824</v>
+        <v>-0.7825</v>
       </c>
       <c r="F85" t="n">
         <v>0.1889</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3174</v>
+        <v>-1.3175</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3187</v>
+        <v>-1.3188</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47506,7 +47506,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5079</v>
+        <v>-0.508</v>
       </c>
       <c r="C87" t="n">
         <v>-0.1687</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2769</v>
+        <v>-1.277</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2159</v>
+        <v>-1.216</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47574,7 +47574,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.5484</v>
+        <v>-0.5485</v>
       </c>
       <c r="C89" t="n">
         <v>-0.2707</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2231</v>
+        <v>-1.2232</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5254</v>
+        <v>-0.5255</v>
       </c>
       <c r="C90" t="n">
         <v>-0.2617</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2714</v>
+        <v>-1.2715</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2751</v>
+        <v>-1.2752</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2936</v>
+        <v>-1.2937</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2769</v>
+        <v>-1.277</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47744,7 +47744,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4359</v>
+        <v>-0.436</v>
       </c>
       <c r="C94" t="n">
         <v>-0.4527</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2992</v>
+        <v>-1.2993</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47787,7 +47787,7 @@
         <v>0.2712</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.5929</v>
+        <v>-0.593</v>
       </c>
       <c r="F95" t="n">
         <v>0.2712</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2864</v>
+        <v>-1.2865</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2372</v>
+        <v>-1.2373</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.055</v>
+        <v>-1.0551</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9615</v>
+        <v>-0.9616</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.91</v>
+        <v>-0.9101</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -48071,7 +48071,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8037</v>
+        <v>-0.8038</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48139,7 +48139,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7496</v>
       </c>
       <c r="J105" t="n">
         <v>-0.3022</v>
@@ -48275,7 +48275,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5736</v>
+        <v>-0.5737</v>
       </c>
       <c r="J109" t="n">
         <v>-0.3653</v>
@@ -48365,7 +48365,7 @@
         <v>0.8887</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.0626</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="F112" t="n">
         <v>0.8887</v>
@@ -48560,7 +48560,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3901</v>
+        <v>0.39</v>
       </c>
       <c r="C118" t="n">
         <v>-1.093</v>
@@ -48717,7 +48717,7 @@
         <v>0.3802</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.0917</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J122" t="n">
         <v>-0.1326</v>
@@ -48841,7 +48841,7 @@
         <v>0.4295</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3115</v>
+        <v>0.3116</v>
       </c>
       <c r="F126" t="n">
         <v>0.4295</v>
@@ -48887,7 +48887,7 @@
         <v>0.7683</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1119</v>
+        <v>0.112</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0956</v>
@@ -48955,7 +48955,7 @@
         <v>0.7683</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1079</v>
+        <v>0.108</v>
       </c>
       <c r="J129" t="n">
         <v>-0.045</v>
@@ -49215,7 +49215,7 @@
         <v>0.2948</v>
       </c>
       <c r="E137" t="n">
-        <v>0.3906</v>
+        <v>0.3905</v>
       </c>
       <c r="F137" t="n">
         <v>0.2948</v>
@@ -49376,7 +49376,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4019</v>
+        <v>0.4018</v>
       </c>
       <c r="C142" t="n">
         <v>-0.362</v>
@@ -49478,7 +49478,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5854</v>
+        <v>0.5855</v>
       </c>
       <c r="C145" t="n">
         <v>-0.438</v>
@@ -49669,7 +49669,7 @@
         <v>1.0753</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0074</v>
+        <v>-0.0073</v>
       </c>
       <c r="J150" t="n">
         <v>0.5164</v>
@@ -49784,7 +49784,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6437</v>
       </c>
       <c r="C154" t="n">
         <v>-0.429</v>
@@ -49873,7 +49873,7 @@
         <v>1.1242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="J156" t="n">
         <v>0.6836</v>
@@ -49941,7 +49941,7 @@
         <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0638</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -49975,7 +49975,7 @@
         <v>1.1579</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0172</v>
+        <v>-0.0171</v>
       </c>
       <c r="J159" t="n">
         <v>0.837</v>
@@ -50043,7 +50043,7 @@
         <v>1.1757</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0106</v>
+        <v>-0.0105</v>
       </c>
       <c r="J161" t="n">
         <v>1.0249</v>
@@ -50056,7 +50056,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.743</v>
+        <v>0.7431</v>
       </c>
       <c r="C162" t="n">
         <v>-0.5659999999999999</v>
@@ -50077,7 +50077,7 @@
         <v>1.1757</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0265</v>
+        <v>0.0266</v>
       </c>
       <c r="J162" t="n">
         <v>1.0036</v>
@@ -50145,7 +50145,7 @@
         <v>1.1753</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0704</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="J164" t="n">
         <v>1.1755</v>
@@ -50167,7 +50167,7 @@
         <v>0.8058999999999999</v>
       </c>
       <c r="E165" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.7284</v>
       </c>
       <c r="F165" t="n">
         <v>0.8058999999999999</v>
@@ -50179,7 +50179,7 @@
         <v>1.1753</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0612</v>
+        <v>0.0613</v>
       </c>
       <c r="J165" t="n">
         <v>1.141</v>
@@ -50192,7 +50192,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.7704</v>
+        <v>0.7705</v>
       </c>
       <c r="C166" t="n">
         <v>-0.472</v>
@@ -50213,7 +50213,7 @@
         <v>1.1104</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1025</v>
+        <v>0.1026</v>
       </c>
       <c r="J166" t="n">
         <v>1.2041</v>
@@ -50235,7 +50235,7 @@
         <v>0.8496</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7329</v>
+        <v>0.733</v>
       </c>
       <c r="F167" t="n">
         <v>0.8496</v>
@@ -50519,7 +50519,7 @@
         <v>0.9665</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1431</v>
+        <v>-0.143</v>
       </c>
       <c r="J175" t="n">
         <v>1.6029</v>
@@ -50553,7 +50553,7 @@
         <v>0.9665</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1616</v>
+        <v>-0.1615</v>
       </c>
       <c r="J176" t="n">
         <v>1.6097</v>
@@ -50689,7 +50689,7 @@
         <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1767</v>
+        <v>-0.1766</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -50723,7 +50723,7 @@
         <v>0.8421</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1925</v>
+        <v>-0.1924</v>
       </c>
       <c r="J181" t="n">
         <v>1.8899</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2101</v>
+        <v>-0.21</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50791,7 +50791,7 @@
         <v>0.8421</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2176</v>
+        <v>-0.2175</v>
       </c>
       <c r="J183" t="n">
         <v>1.969</v>
@@ -50893,7 +50893,7 @@
         <v>0.5822000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2793</v>
+        <v>-0.2792</v>
       </c>
       <c r="J186" t="n">
         <v>2.0342</v>
@@ -50927,7 +50927,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2087</v>
+        <v>-0.2086</v>
       </c>
       <c r="J187" t="n">
         <v>2.1594</v>
@@ -50995,7 +50995,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1836</v>
+        <v>-0.1835</v>
       </c>
       <c r="J189" t="n">
         <v>1.6451</v>
@@ -51017,7 +51017,7 @@
         <v>0.257</v>
       </c>
       <c r="E190" t="n">
-        <v>0.3983</v>
+        <v>0.3984</v>
       </c>
       <c r="F190" t="n">
         <v>0.257</v>
@@ -51029,7 +51029,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1559</v>
+        <v>-0.1558</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51063,7 +51063,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1331</v>
+        <v>-0.133</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51085,7 +51085,7 @@
         <v>-0.0004</v>
       </c>
       <c r="E192" t="n">
-        <v>0.4297</v>
+        <v>0.4298</v>
       </c>
       <c r="F192" t="n">
         <v>-0.0004</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0367</v>
+        <v>-0.0366</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.001</v>
+        <v>0.0011</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51187,7 +51187,7 @@
         <v>0.1947</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2305</v>
+        <v>0.2306</v>
       </c>
       <c r="F195" t="n">
         <v>0.1947</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0862</v>
+        <v>0.0863</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51221,7 +51221,7 @@
         <v>0.2423</v>
       </c>
       <c r="E196" t="n">
-        <v>0.2637</v>
+        <v>0.2638</v>
       </c>
       <c r="F196" t="n">
         <v>0.2423</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1663</v>
+        <v>0.1665</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1951</v>
+        <v>0.1953</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1978</v>
+        <v>0.1979</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2481</v>
+        <v>0.2482</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2527</v>
+        <v>0.2528</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51391,7 +51391,7 @@
         <v>0.4287</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1935</v>
+        <v>0.1936</v>
       </c>
       <c r="F201" t="n">
         <v>0.4287</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2612</v>
+        <v>0.2613</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51425,7 +51425,7 @@
         <v>0.4629</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2111</v>
+        <v>0.2112</v>
       </c>
       <c r="F202" t="n">
         <v>0.4629</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3456</v>
+        <v>0.3458</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51459,7 +51459,7 @@
         <v>0.5</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2462</v>
+        <v>0.2463</v>
       </c>
       <c r="F203" t="n">
         <v>0.5</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3694</v>
+        <v>0.3695</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4033</v>
+        <v>0.4035</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51527,7 +51527,7 @@
         <v>1.7571</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2738</v>
+        <v>0.2739</v>
       </c>
       <c r="F205" t="n">
         <v>1.7571</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3956</v>
+        <v>0.3957</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.394</v>
+        <v>0.3941</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4005</v>
+        <v>0.4006</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4494</v>
+        <v>0.4495</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5847</v>
+        <v>0.5848</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51697,7 +51697,7 @@
         <v>1.2956</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3872</v>
+        <v>0.3873</v>
       </c>
       <c r="F210" t="n">
         <v>1.2956</v>
@@ -51731,7 +51731,7 @@
         <v>1.3419</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3935</v>
+        <v>0.3936</v>
       </c>
       <c r="F211" t="n">
         <v>1.3419</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6979</v>
+        <v>0.698</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51756,7 +51756,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.6493</v>
+        <v>0.6494</v>
       </c>
       <c r="C212" t="n">
         <v>-2.064</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7592</v>
+        <v>0.7593</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7722</v>
+        <v>0.7723</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8845</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9333</v>
+        <v>0.9334</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8897</v>
+        <v>0.8898</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7587</v>
+        <v>0.7588</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6892</v>
+        <v>0.6893</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.741</v>
+        <v>0.7411</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7629</v>
+        <v>0.763</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7768</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8746</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52130,7 +52130,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.7902</v>
+        <v>0.7903</v>
       </c>
       <c r="C223" t="n">
         <v>-2.155</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9866</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.014</v>
+        <v>1.0141</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52198,7 +52198,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.8093</v>
+        <v>0.8094</v>
       </c>
       <c r="C225" t="n">
         <v>-2.152</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0832</v>
+        <v>1.0833</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1638</v>
+        <v>1.164</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52275,7 +52275,7 @@
         <v>1.5267</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5627</v>
+        <v>0.5628</v>
       </c>
       <c r="F227" t="n">
         <v>1.5267</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2035</v>
+        <v>1.2037</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2615</v>
+        <v>1.2617</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52343,7 +52343,7 @@
         <v>1.4519</v>
       </c>
       <c r="E229" t="n">
-        <v>0.6021</v>
+        <v>0.6022</v>
       </c>
       <c r="F229" t="n">
         <v>1.4519</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1852</v>
+        <v>1.1854</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2962</v>
+        <v>1.2964</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52411,7 +52411,7 @@
         <v>1.4909</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6721</v>
+        <v>0.6722</v>
       </c>
       <c r="F231" t="n">
         <v>1.4909</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4166</v>
+        <v>1.4168</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52436,7 +52436,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.785</v>
+        <v>0.7851</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52445,7 +52445,7 @@
         <v>1.3842</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6352</v>
+        <v>0.6353</v>
       </c>
       <c r="F232" t="n">
         <v>1.3842</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4789</v>
+        <v>1.4792</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6855</v>
+        <v>0.6856</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5493</v>
+        <v>1.5495</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52513,7 +52513,7 @@
         <v>1.2983</v>
       </c>
       <c r="E234" t="n">
-        <v>0.774</v>
+        <v>0.7741</v>
       </c>
       <c r="F234" t="n">
         <v>1.2983</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6078</v>
+        <v>1.608</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52538,7 +52538,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8131</v>
+        <v>0.8132</v>
       </c>
       <c r="C235" t="n">
         <v>-1.935</v>
@@ -52547,7 +52547,7 @@
         <v>1.3372</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6821</v>
+        <v>0.6822</v>
       </c>
       <c r="F235" t="n">
         <v>1.3372</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6708</v>
+        <v>1.671</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7032</v>
+        <v>1.7034</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52615,7 +52615,7 @@
         <v>1.4213</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7093</v>
       </c>
       <c r="F237" t="n">
         <v>1.4213</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4972</v>
+        <v>1.4974</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52640,7 +52640,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7207</v>
+        <v>0.7208</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4623</v>
+        <v>1.4625</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6452</v>
+        <v>0.6453</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6124</v>
+        <v>1.6126</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52717,7 +52717,7 @@
         <v>1.2526</v>
       </c>
       <c r="E240" t="n">
-        <v>0.6949</v>
+        <v>0.695</v>
       </c>
       <c r="F240" t="n">
         <v>1.2526</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6989</v>
+        <v>1.6991</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7355</v>
+        <v>1.7357</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52776,7 +52776,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.7919</v>
+        <v>0.792</v>
       </c>
       <c r="C242" t="n">
         <v>-1.726</v>
@@ -52785,7 +52785,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.631</v>
+        <v>0.6311</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7946</v>
+        <v>1.7949</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52810,7 +52810,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.7581</v>
+        <v>0.7582</v>
       </c>
       <c r="C243" t="n">
         <v>-1.541</v>
@@ -52819,7 +52819,7 @@
         <v>1.3065</v>
       </c>
       <c r="E243" t="n">
-        <v>0.621</v>
+        <v>0.6211</v>
       </c>
       <c r="F243" t="n">
         <v>1.3065</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7183</v>
+        <v>1.7185</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52853,7 +52853,7 @@
         <v>1.3533</v>
       </c>
       <c r="E244" t="n">
-        <v>0.4759</v>
+        <v>0.476</v>
       </c>
       <c r="F244" t="n">
         <v>1.3533</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6857</v>
+        <v>1.6859</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5563</v>
+        <v>1.5565</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52921,7 +52921,7 @@
         <v>1.5808</v>
       </c>
       <c r="E246" t="n">
-        <v>0.5724</v>
+        <v>0.5725</v>
       </c>
       <c r="F246" t="n">
         <v>1.5808</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6559</v>
+        <v>1.6561</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52946,7 +52946,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.6984</v>
+        <v>0.6985</v>
       </c>
       <c r="C247" t="n">
         <v>-1.552</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6836</v>
+        <v>1.6838</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52980,7 +52980,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.6572</v>
+        <v>0.6573</v>
       </c>
       <c r="C248" t="n">
         <v>-1.551</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7785</v>
+        <v>1.7787</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53014,7 +53014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6701</v>
+        <v>0.6702</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8498</v>
+        <v>1.85</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53057,7 +53057,7 @@
         <v>1.2162</v>
       </c>
       <c r="E250" t="n">
-        <v>0.4799</v>
+        <v>0.48</v>
       </c>
       <c r="F250" t="n">
         <v>1.2162</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.933</v>
+        <v>1.9333</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53082,7 +53082,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7008</v>
+        <v>0.7009</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53091,7 +53091,7 @@
         <v>1.2364</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5669</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F251" t="n">
         <v>1.2364</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0919</v>
+        <v>2.0922</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7708</v>
+        <v>0.7709</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1995</v>
+        <v>2.1998</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53150,7 +53150,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4571</v>
+        <v>0.4572</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2538</v>
+        <v>2.2541</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6007</v>
+        <v>0.6008</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5898</v>
+        <v>0.5899</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3445</v>
+        <v>2.3448</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5685</v>
+        <v>0.5686</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6001</v>
+        <v>0.6002</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.409</v>
+        <v>2.4094</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4642</v>
+        <v>0.4643</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4319</v>
+        <v>2.4323</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5254</v>
+        <v>0.5255</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5523</v>
+        <v>2.5527</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4898</v>
+        <v>0.4899</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5392</v>
+        <v>0.5393</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.698</v>
+        <v>2.6984</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5261</v>
+        <v>0.5262</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5768</v>
+        <v>0.5769</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8834</v>
+        <v>2.8839</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5744</v>
+        <v>0.5745</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6156</v>
+        <v>0.6157</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9291</v>
+        <v>2.9296</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5316</v>
+        <v>0.5317</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5818</v>
+        <v>0.5819</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9266</v>
+        <v>2.9271</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5675</v>
+        <v>0.5677</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5675</v>
+        <v>0.5677</v>
       </c>
       <c r="G262" t="n">
         <v>-1.6529</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8641</v>
+        <v>2.8646</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5858</v>
+        <v>0.5839</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5858</v>
+        <v>0.5839</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9373</v>
+        <v>2.9293</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>-1.216</v>
+        <v>-1.217</v>
       </c>
     </row>
     <row r="58">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="190">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>0.702</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="227">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.584</v>
+        <v>0.583</v>
       </c>
     </row>
   </sheetData>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.928</v>
+        <v>1.926</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.398</v>
+        <v>2.391</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.071</v>
+        <v>3.059</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.123</v>
+        <v>4.113</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.515</v>
+        <v>-0.519</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.571</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.84</v>
+        <v>-0.83</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68595.352</v>
+        <v>68297.98299999999</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6549</v>
+        <v>1.6546</v>
       </c>
       <c r="D263" t="n">
-        <v>1.928</v>
+        <v>1.9265</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3976</v>
+        <v>2.3909</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0709</v>
+        <v>3.0586</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1232</v>
+        <v>4.1133</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.9454</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5155</v>
+        <v>-0.5187</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5709</v>
+        <v>0.5586</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>68595.352</v>
+        <v>68297.98269999999</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.0809</v>
+        <v>10.1847</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0523</v>
+        <v>1.0547</v>
       </c>
     </row>
   </sheetData>
@@ -44643,7 +44643,7 @@
         <v>-0.358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.6317</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5626</v>
@@ -44671,7 +44671,7 @@
         <v>-0.0577</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.59</v>
+        <v>-0.5901</v>
       </c>
       <c r="J3" t="n">
         <v>-1.5477</v>
@@ -44739,7 +44739,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5425</v>
+        <v>-0.5426</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5329</v>
@@ -44752,7 +44752,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4296</v>
+        <v>-0.4297</v>
       </c>
       <c r="C6" t="n">
         <v>-0.2012</v>
@@ -44820,7 +44820,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3931</v>
+        <v>-0.3932</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2098</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4156</v>
+        <v>-0.4157</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44909,7 +44909,7 @@
         <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3902</v>
+        <v>-0.3903</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2593</v>
@@ -44977,7 +44977,7 @@
         <v>0.1635</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2203</v>
+        <v>-0.2204</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2209</v>
@@ -45895,7 +45895,7 @@
         <v>0.0667</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4179</v>
+        <v>-0.418</v>
       </c>
       <c r="J39" t="n">
         <v>0.1293</v>
@@ -45908,7 +45908,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3442</v>
+        <v>-0.3443</v>
       </c>
       <c r="C40" t="n">
         <v>-0.3972</v>
@@ -45951,7 +45951,7 @@
         <v>0.4132</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.5592</v>
+        <v>-0.5593</v>
       </c>
       <c r="F41" t="n">
         <v>0.4132</v>
@@ -45963,7 +45963,7 @@
         <v>-0.312</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5546</v>
+        <v>-0.5547</v>
       </c>
       <c r="J41" t="n">
         <v>0.3169</v>
@@ -45976,7 +45976,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.2983</v>
+        <v>-0.2984</v>
       </c>
       <c r="C42" t="n">
         <v>-0.4032</v>
@@ -46121,7 +46121,7 @@
         <v>0.9778</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.7194</v>
       </c>
       <c r="F46" t="n">
         <v>0.9778</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8338</v>
+        <v>-0.8339</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46180,7 +46180,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4313</v>
+        <v>-0.4314</v>
       </c>
       <c r="C48" t="n">
         <v>-0.8011</v>
@@ -46189,7 +46189,7 @@
         <v>0.4542</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.6528</v>
       </c>
       <c r="F48" t="n">
         <v>0.4542</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9262</v>
+        <v>-0.9263</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0508</v>
+        <v>-1.0509</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0871</v>
+        <v>-1.0872</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0915</v>
+        <v>-1.0916</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0091</v>
+        <v>-1.0092</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.984</v>
+        <v>-0.9841</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9823</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0362</v>
+        <v>-1.0363</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0157</v>
+        <v>-1.0158</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46588,7 +46588,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1369</v>
+        <v>-1.137</v>
       </c>
       <c r="C60" t="n">
         <v>0.7274</v>
@@ -46597,7 +46597,7 @@
         <v>-0.5429</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.2854</v>
+        <v>-1.2855</v>
       </c>
       <c r="F60" t="n">
         <v>-0.5429</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1063</v>
+        <v>-1.1064</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0802</v>
+        <v>-1.0803</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46894,7 +46894,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0211</v>
+        <v>-1.0212</v>
       </c>
       <c r="C69" t="n">
         <v>0.454</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1818</v>
+        <v>-1.1819</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46971,7 +46971,7 @@
         <v>-0.111</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0942</v>
+        <v>-1.0943</v>
       </c>
       <c r="F71" t="n">
         <v>-0.111</v>
@@ -46996,7 +46996,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9071</v>
+        <v>-0.9072</v>
       </c>
       <c r="C72" t="n">
         <v>0.3843</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2168</v>
+        <v>-1.2169</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1969</v>
+        <v>-1.197</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2358</v>
+        <v>-1.2359</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47243,7 +47243,7 @@
         <v>0.1224</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9351</v>
+        <v>-0.9352</v>
       </c>
       <c r="F79" t="n">
         <v>0.1224</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2426</v>
+        <v>-1.2427</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47302,7 +47302,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.6227</v>
+        <v>-0.6228</v>
       </c>
       <c r="C81" t="n">
         <v>-0.0248</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3021</v>
+        <v>-1.3022</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47345,7 +47345,7 @@
         <v>0.3257</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.822</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="F82" t="n">
         <v>0.3257</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3182</v>
+        <v>-1.3183</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47379,7 +47379,7 @@
         <v>0.1813</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.9135</v>
+        <v>-0.9136</v>
       </c>
       <c r="F83" t="n">
         <v>0.1813</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3039</v>
+        <v>-1.304</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3175</v>
+        <v>-1.3176</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.277</v>
+        <v>-1.2771</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.216</v>
+        <v>-1.2161</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47583,7 +47583,7 @@
         <v>0.3374</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.7699</v>
+        <v>-0.77</v>
       </c>
       <c r="F89" t="n">
         <v>0.3374</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2232</v>
+        <v>-1.2233</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2715</v>
+        <v>-1.2716</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47642,7 +47642,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4802</v>
+        <v>-0.4803</v>
       </c>
       <c r="C91" t="n">
         <v>-0.3987</v>
@@ -47651,7 +47651,7 @@
         <v>0.1753</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6441</v>
+        <v>-0.6442</v>
       </c>
       <c r="F91" t="n">
         <v>0.1753</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2752</v>
+        <v>-1.2753</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2937</v>
+        <v>-1.2938</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47710,7 +47710,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4602</v>
+        <v>-0.4603</v>
       </c>
       <c r="C93" t="n">
         <v>-0.3887</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.277</v>
+        <v>-1.2771</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2993</v>
+        <v>-1.2994</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2865</v>
+        <v>-1.2866</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47855,7 +47855,7 @@
         <v>0.5886</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.5809</v>
+        <v>-0.581</v>
       </c>
       <c r="F97" t="n">
         <v>0.5886</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1811</v>
+        <v>-1.1812</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47991,7 +47991,7 @@
         <v>0.1061</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.4419</v>
+        <v>-0.442</v>
       </c>
       <c r="F101" t="n">
         <v>0.1061</v>
@@ -48105,7 +48105,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.73</v>
+        <v>-0.7301</v>
       </c>
       <c r="J104" t="n">
         <v>-0.3041</v>
@@ -48309,7 +48309,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5581</v>
+        <v>-0.5582</v>
       </c>
       <c r="J110" t="n">
         <v>-0.2626</v>
@@ -48343,7 +48343,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5821</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="J111" t="n">
         <v>-0.2998</v>
@@ -48411,7 +48411,7 @@
         <v>0.0859</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5372</v>
+        <v>-0.5373</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2751</v>
@@ -48445,7 +48445,7 @@
         <v>0.0859</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.545</v>
       </c>
       <c r="J114" t="n">
         <v>-0.1624</v>
@@ -48615,7 +48615,7 @@
         <v>0.3858</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3512</v>
+        <v>-0.3513</v>
       </c>
       <c r="J119" t="n">
         <v>-0.1251</v>
@@ -48683,7 +48683,7 @@
         <v>0.3802</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0851</v>
       </c>
       <c r="J121" t="n">
         <v>-0.1406</v>
@@ -49125,7 +49125,7 @@
         <v>0.7917</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0042</v>
+        <v>-0.0043</v>
       </c>
       <c r="J134" t="n">
         <v>-0.0891</v>
@@ -49261,7 +49261,7 @@
         <v>0.9537</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1526</v>
+        <v>-0.1527</v>
       </c>
       <c r="J138" t="n">
         <v>0.0357</v>
@@ -49329,7 +49329,7 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2277</v>
+        <v>-0.2278</v>
       </c>
       <c r="J140" t="n">
         <v>0.1018</v>
@@ -49657,7 +49657,7 @@
         <v>0.6139</v>
       </c>
       <c r="E150" t="n">
-        <v>0.6266</v>
+        <v>0.6267</v>
       </c>
       <c r="F150" t="n">
         <v>0.6139</v>
@@ -49827,7 +49827,7 @@
         <v>0.777</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6306</v>
       </c>
       <c r="F155" t="n">
         <v>0.777</v>
@@ -49907,7 +49907,7 @@
         <v>1.1579</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0687</v>
+        <v>0.0688</v>
       </c>
       <c r="J157" t="n">
         <v>0.7487</v>
@@ -49929,7 +49929,7 @@
         <v>0.773</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7055</v>
+        <v>0.7056</v>
       </c>
       <c r="F158" t="n">
         <v>0.773</v>
@@ -50247,7 +50247,7 @@
         <v>1.1104</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0709</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J167" t="n">
         <v>1.2431</v>
@@ -50587,7 +50587,7 @@
         <v>0.9665</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2185</v>
+        <v>-0.2184</v>
       </c>
       <c r="J177" t="n">
         <v>1.7354</v>
@@ -50655,7 +50655,7 @@
         <v>0.9385</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1993</v>
+        <v>-0.1992</v>
       </c>
       <c r="J179" t="n">
         <v>1.712</v>
@@ -50745,7 +50745,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="E182" t="n">
-        <v>0.7922</v>
+        <v>0.7923</v>
       </c>
       <c r="F182" t="n">
         <v>0.7828000000000001</v>
@@ -51097,7 +51097,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0011</v>
+        <v>0.0012</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0863</v>
+        <v>0.0864</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1979</v>
+        <v>0.198</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2482</v>
+        <v>0.2483</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2528</v>
+        <v>0.2529</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3695</v>
+        <v>0.3696</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51493,7 +51493,7 @@
         <v>0.6372</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3039</v>
+        <v>0.304</v>
       </c>
       <c r="F204" t="n">
         <v>0.6372</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3957</v>
+        <v>0.3958</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3941</v>
+        <v>0.3942</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4006</v>
+        <v>0.4007</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4495</v>
+        <v>0.4496</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51654,7 +51654,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5552</v>
+        <v>0.5553</v>
       </c>
       <c r="C209" t="n">
         <v>-1.483</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6118</v>
+        <v>0.6119</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51722,7 +51722,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5833</v>
       </c>
       <c r="C211" t="n">
         <v>-2.09</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7593</v>
+        <v>0.7594</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8847</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9334</v>
+        <v>0.9335</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8898</v>
+        <v>0.8899</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7588</v>
+        <v>0.7589</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -52028,7 +52028,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6891</v>
       </c>
       <c r="C220" t="n">
         <v>-2.405</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7768</v>
+        <v>0.7769</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8746</v>
+        <v>0.8747</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9866</v>
+        <v>0.9867</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0141</v>
+        <v>1.0142</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0833</v>
+        <v>1.0834</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52241,7 +52241,7 @@
         <v>1.478</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5087</v>
       </c>
       <c r="F226" t="n">
         <v>1.478</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.164</v>
+        <v>1.1641</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7556</v>
       </c>
       <c r="C227" t="n">
         <v>-2.054</v>
@@ -52309,7 +52309,7 @@
         <v>1.3821</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6538</v>
       </c>
       <c r="F228" t="n">
         <v>1.3821</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2617</v>
+        <v>1.2618</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1854</v>
+        <v>1.1855</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52377,7 +52377,7 @@
         <v>1.1747</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6697</v>
+        <v>0.6698</v>
       </c>
       <c r="F230" t="n">
         <v>1.1747</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2964</v>
+        <v>1.2965</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8359</v>
+        <v>0.836</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4168</v>
+        <v>1.4169</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4792</v>
+        <v>1.4793</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5495</v>
+        <v>1.5496</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8789</v>
+        <v>0.879</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.608</v>
+        <v>1.6081</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.671</v>
+        <v>1.6712</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8459</v>
+        <v>0.846</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7034</v>
+        <v>1.7036</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4974</v>
+        <v>1.4975</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4625</v>
+        <v>1.4627</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6126</v>
+        <v>1.6127</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52708,7 +52708,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8065</v>
+        <v>0.8066</v>
       </c>
       <c r="C240" t="n">
         <v>-1.795</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6991</v>
+        <v>1.6992</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7357</v>
+        <v>1.7359</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7949</v>
+        <v>1.795</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7185</v>
+        <v>1.7187</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6859</v>
+        <v>1.6861</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5565</v>
+        <v>1.5566</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52912,7 +52912,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.7741</v>
+        <v>0.7742</v>
       </c>
       <c r="C246" t="n">
         <v>-1.645</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6561</v>
+        <v>1.6562</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6838</v>
+        <v>1.6839</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52989,7 +52989,7 @@
         <v>1.3006</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4964</v>
+        <v>0.4965</v>
       </c>
       <c r="F248" t="n">
         <v>1.3006</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7787</v>
+        <v>1.7789</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53023,7 +53023,7 @@
         <v>1.1168</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5585</v>
+        <v>0.5586</v>
       </c>
       <c r="F249" t="n">
         <v>1.1168</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.85</v>
+        <v>1.8502</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6272</v>
+        <v>0.6273</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9333</v>
+        <v>1.9334</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53091,7 +53091,7 @@
         <v>1.2364</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5671</v>
       </c>
       <c r="F251" t="n">
         <v>1.2364</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0922</v>
+        <v>2.0924</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53125,7 +53125,7 @@
         <v>1.2106</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6609</v>
+        <v>0.661</v>
       </c>
       <c r="F252" t="n">
         <v>1.2106</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.1998</v>
+        <v>2.2</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5633</v>
+        <v>0.5634</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2541</v>
+        <v>2.2544</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5899</v>
+        <v>0.59</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3448</v>
+        <v>2.3451</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5686</v>
+        <v>0.5687</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6002</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4094</v>
+        <v>2.4097</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.458</v>
+        <v>0.4581</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4323</v>
+        <v>2.4325</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4846</v>
+        <v>0.4847</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5255</v>
+        <v>0.5256</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5527</v>
+        <v>2.553</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4899</v>
+        <v>0.49</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5393</v>
+        <v>0.5394</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6984</v>
+        <v>2.6987</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5262</v>
+        <v>0.5263</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5769</v>
+        <v>0.577</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8839</v>
+        <v>2.8842</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5745</v>
+        <v>0.5746</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6157</v>
+        <v>0.6158</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9296</v>
+        <v>2.9299</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5317</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5819</v>
+        <v>0.582</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9271</v>
+        <v>2.9274</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8646</v>
+        <v>2.8649</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5839</v>
+        <v>0.5826</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5839</v>
+        <v>0.5826</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9293</v>
+        <v>2.9242</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-0.458</v>
+        <v>-0.459</v>
       </c>
     </row>
     <row r="5">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-0.368</v>
+        <v>-0.369</v>
       </c>
     </row>
     <row r="12">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>-0.387</v>
+        <v>-0.388</v>
       </c>
     </row>
     <row r="36">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="197">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="J247" t="n">
-        <v>0.698</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="248">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.583</v>
+        <v>0.581</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.655</v>
+        <v>1.654</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.391</v>
+        <v>2.386</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.059</v>
+        <v>3.049</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.113</v>
+        <v>4.107</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.945</v>
+        <v>-0.946</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.519</v>
+        <v>-0.521</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.549</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.83</v>
+        <v>-0.82</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68297.98299999999</v>
+        <v>68016.209</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6546</v>
+        <v>1.6541</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9265</v>
+        <v>1.9257</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3909</v>
+        <v>2.3858</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0586</v>
+        <v>3.0495</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1133</v>
+        <v>4.1066</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9454</v>
+        <v>-0.9459</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5187</v>
+        <v>-0.5209</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5586</v>
+        <v>0.5495</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>68297.98269999999</v>
+        <v>68016.2092</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.1847</v>
+        <v>10.2686</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0547</v>
+        <v>1.0572</v>
       </c>
     </row>
   </sheetData>
@@ -44628,7 +44628,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5739</v>
+        <v>-0.574</v>
       </c>
       <c r="D2" t="n">
         <v>0.2564</v>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5659</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5342</v>
+        <v>-0.5343</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4987</v>
+        <v>-0.4988</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4175</v>
+        <v>-0.4176</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -45079,7 +45079,7 @@
         <v>0.3251</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1744</v>
+        <v>-0.1745</v>
       </c>
       <c r="J15" t="n">
         <v>-1.0238</v>
@@ -45181,7 +45181,7 @@
         <v>0.4889</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2338</v>
+        <v>-0.2339</v>
       </c>
       <c r="J18" t="n">
         <v>-0.8802</v>
@@ -45883,7 +45883,7 @@
         <v>0.4916</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.4672</v>
+        <v>-0.4673</v>
       </c>
       <c r="F39" t="n">
         <v>0.4916</v>
@@ -45929,7 +45929,7 @@
         <v>-0.312</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5679</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0.2773</v>
@@ -45997,7 +45997,7 @@
         <v>-0.312</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5527</v>
+        <v>-0.5528</v>
       </c>
       <c r="J42" t="n">
         <v>0.4153</v>
@@ -46031,7 +46031,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.523</v>
+        <v>-0.5231</v>
       </c>
       <c r="J43" t="n">
         <v>0.4481</v>
@@ -46099,7 +46099,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5681</v>
+        <v>-0.5682</v>
       </c>
       <c r="J45" t="n">
         <v>0.613</v>
@@ -46133,7 +46133,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6509</v>
+        <v>-0.651</v>
       </c>
       <c r="J46" t="n">
         <v>0.5804</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4043</v>
+        <v>-0.4044</v>
       </c>
       <c r="C47" t="n">
         <v>-0.6151</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9263</v>
+        <v>-0.9264</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46223,7 +46223,7 @@
         <v>-0.0883</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0031</v>
+        <v>-1.0032</v>
       </c>
       <c r="F49" t="n">
         <v>-0.0883</v>
@@ -46248,7 +46248,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7457</v>
+        <v>-0.7458</v>
       </c>
       <c r="C50" t="n">
         <v>-0.3217</v>
@@ -46282,7 +46282,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7739</v>
+        <v>-0.774</v>
       </c>
       <c r="C51" t="n">
         <v>-0.3307</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0099</v>
+        <v>-1.01</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46452,7 +46452,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.1815</v>
+        <v>-1.1816</v>
       </c>
       <c r="C56" t="n">
         <v>0.9229000000000001</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0749</v>
+        <v>-1.075</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0751</v>
+        <v>-1.0752</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46631,7 +46631,7 @@
         <v>-0.3888</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.2808</v>
+        <v>-1.2809</v>
       </c>
       <c r="F61" t="n">
         <v>-0.3888</v>
@@ -46665,7 +46665,7 @@
         <v>-0.2609</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.265</v>
+        <v>-1.2651</v>
       </c>
       <c r="F62" t="n">
         <v>-0.2609</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0536</v>
+        <v>-1.0537</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0903</v>
+        <v>-1.0904</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0757</v>
+        <v>-1.0758</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46758,7 +46758,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.0438</v>
+        <v>-1.0439</v>
       </c>
       <c r="C65" t="n">
         <v>0.5002</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0175</v>
+        <v>-1.0176</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0496</v>
+        <v>-1.0497</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0823</v>
+        <v>-1.0824</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1491</v>
+        <v>-1.1492</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.196</v>
+        <v>-1.1961</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2205</v>
+        <v>-1.2206</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2137</v>
+        <v>-1.2138</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1919</v>
+        <v>-1.192</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1882</v>
+        <v>-1.1883</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1992</v>
+        <v>-1.1993</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47209,7 +47209,7 @@
         <v>0.113</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.8918</v>
+        <v>-0.8919</v>
       </c>
       <c r="F78" t="n">
         <v>0.113</v>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7236</v>
+        <v>-0.7237</v>
       </c>
       <c r="C79" t="n">
         <v>-0.0368</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2427</v>
+        <v>-1.2428</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47277,7 +47277,7 @@
         <v>0.263</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.8992</v>
+        <v>-0.8993</v>
       </c>
       <c r="F80" t="n">
         <v>0.263</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2558</v>
+        <v>-1.2559</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3183</v>
+        <v>-1.3184</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3288</v>
+        <v>-1.3289</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3188</v>
+        <v>-1.3189</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47515,7 +47515,7 @@
         <v>0.2847</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7062</v>
       </c>
       <c r="F87" t="n">
         <v>0.2847</v>
@@ -47540,7 +47540,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.5194</v>
+        <v>-0.5195</v>
       </c>
       <c r="C88" t="n">
         <v>-0.2617</v>
@@ -47617,7 +47617,7 @@
         <v>0.2124</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.7099</v>
+        <v>-0.71</v>
       </c>
       <c r="F90" t="n">
         <v>0.2124</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2753</v>
+        <v>-1.2754</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2938</v>
+        <v>-1.2939</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47719,7 +47719,7 @@
         <v>0.1757</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6192</v>
+        <v>-0.6193</v>
       </c>
       <c r="F93" t="n">
         <v>0.1757</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2771</v>
+        <v>-1.2772</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47778,7 +47778,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.4201</v>
+        <v>-0.4202</v>
       </c>
       <c r="C95" t="n">
         <v>-0.4527</v>
@@ -47821,7 +47821,7 @@
         <v>0.2764</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.5553</v>
+        <v>-0.5554</v>
       </c>
       <c r="F96" t="n">
         <v>0.2764</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2373</v>
+        <v>-1.2374</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.347</v>
+        <v>-0.3471</v>
       </c>
       <c r="C97" t="n">
         <v>-0.6221</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1812</v>
+        <v>-1.1813</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47889,7 +47889,7 @@
         <v>0.1382</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.5069</v>
+        <v>-0.507</v>
       </c>
       <c r="F98" t="n">
         <v>0.1382</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0551</v>
+        <v>-1.0552</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9101</v>
+        <v>-0.9102</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -48003,7 +48003,7 @@
         <v>-0.47</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8367</v>
+        <v>-0.8368</v>
       </c>
       <c r="J101" t="n">
         <v>-0.5199</v>
@@ -48093,7 +48093,7 @@
         <v>0.5312</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.2781</v>
+        <v>-0.2782</v>
       </c>
       <c r="F104" t="n">
         <v>0.5312</v>
@@ -48207,7 +48207,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7129</v>
+        <v>-0.713</v>
       </c>
       <c r="J107" t="n">
         <v>-0.348</v>
@@ -48377,7 +48377,7 @@
         <v>0.0859</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5581</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2325</v>
@@ -48424,7 +48424,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3525</v>
+        <v>0.3524</v>
       </c>
       <c r="C114" t="n">
         <v>-1.041</v>
@@ -48479,7 +48479,7 @@
         <v>0.3854</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5133</v>
+        <v>-0.5134</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2898</v>
@@ -48547,7 +48547,7 @@
         <v>0.3854</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4522</v>
+        <v>-0.4523</v>
       </c>
       <c r="J117" t="n">
         <v>-0.2606</v>
@@ -49363,7 +49363,7 @@
         <v>1.06</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2684</v>
+        <v>-0.2685</v>
       </c>
       <c r="J141" t="n">
         <v>0.1044</v>
@@ -49703,7 +49703,7 @@
         <v>1.1972</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.0125</v>
+        <v>-0.0124</v>
       </c>
       <c r="J151" t="n">
         <v>0.5609</v>
@@ -49771,7 +49771,7 @@
         <v>1.1972</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.044</v>
+        <v>-0.0439</v>
       </c>
       <c r="J153" t="n">
         <v>0.628</v>
@@ -49839,7 +49839,7 @@
         <v>1.1242</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0501</v>
+        <v>0.0502</v>
       </c>
       <c r="J155" t="n">
         <v>0.7134</v>
@@ -49920,7 +49920,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.719</v>
+        <v>0.7191</v>
       </c>
       <c r="C158" t="n">
         <v>-0.525</v>
@@ -50111,7 +50111,7 @@
         <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0472</v>
+        <v>0.0473</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50201,7 +50201,7 @@
         <v>0.8033</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7622</v>
+        <v>0.7623</v>
       </c>
       <c r="F166" t="n">
         <v>0.8033</v>
@@ -50213,7 +50213,7 @@
         <v>1.1104</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1026</v>
+        <v>0.1027</v>
       </c>
       <c r="J166" t="n">
         <v>1.2041</v>
@@ -50281,7 +50281,7 @@
         <v>1.1104</v>
       </c>
       <c r="I168" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="J168" t="n">
         <v>1.2437</v>
@@ -50349,7 +50349,7 @@
         <v>1.0767</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0717</v>
+        <v>-0.0716</v>
       </c>
       <c r="J170" t="n">
         <v>1.3994</v>
@@ -50600,7 +50600,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.7352</v>
+        <v>0.7353</v>
       </c>
       <c r="C178" t="n">
         <v>-0.383</v>
@@ -50723,7 +50723,7 @@
         <v>0.8421</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1924</v>
+        <v>-0.1923</v>
       </c>
       <c r="J181" t="n">
         <v>1.8899</v>
@@ -50949,7 +50949,7 @@
         <v>0.4356</v>
       </c>
       <c r="E188" t="n">
-        <v>0.4949</v>
+        <v>0.495</v>
       </c>
       <c r="F188" t="n">
         <v>0.4356</v>
@@ -50961,7 +50961,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1993</v>
+        <v>-0.1992</v>
       </c>
       <c r="J188" t="n">
         <v>1.9226</v>
@@ -51119,7 +51119,7 @@
         <v>0.1261</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3234</v>
+        <v>0.3235</v>
       </c>
       <c r="F193" t="n">
         <v>0.1261</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0366</v>
+        <v>-0.0365</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51153,7 +51153,7 @@
         <v>0.1208</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3219</v>
+        <v>0.322</v>
       </c>
       <c r="F194" t="n">
         <v>0.1208</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0864</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1665</v>
+        <v>0.1666</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51255,7 +51255,7 @@
         <v>0.0726</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2323</v>
+        <v>0.2324</v>
       </c>
       <c r="F197" t="n">
         <v>0.0726</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1953</v>
+        <v>0.1954</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51357,7 +51357,7 @@
         <v>0.3391</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1732</v>
+        <v>0.1733</v>
       </c>
       <c r="F200" t="n">
         <v>0.3391</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2529</v>
+        <v>0.253</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2613</v>
+        <v>0.2614</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3458</v>
+        <v>0.3459</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3696</v>
+        <v>0.3697</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4035</v>
+        <v>0.4036</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5848</v>
+        <v>0.5849</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6119</v>
+        <v>0.612</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.698</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51765,7 +51765,7 @@
         <v>1.4363</v>
       </c>
       <c r="E212" t="n">
-        <v>0.4526</v>
+        <v>0.4527</v>
       </c>
       <c r="F212" t="n">
         <v>1.4363</v>
@@ -51799,7 +51799,7 @@
         <v>1.5668</v>
       </c>
       <c r="E213" t="n">
-        <v>0.4795</v>
+        <v>0.4796</v>
       </c>
       <c r="F213" t="n">
         <v>1.5668</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7723</v>
+        <v>0.7724</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51833,7 +51833,7 @@
         <v>1.7325</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4651</v>
+        <v>0.4652</v>
       </c>
       <c r="F214" t="n">
         <v>1.7325</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7589</v>
+        <v>0.759</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6893</v>
+        <v>0.6894</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52003,7 +52003,7 @@
         <v>1.6773</v>
       </c>
       <c r="E219" t="n">
-        <v>0.461</v>
+        <v>0.4611</v>
       </c>
       <c r="F219" t="n">
         <v>1.6773</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7411</v>
+        <v>0.7412</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.763</v>
+        <v>0.7631</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52096,7 +52096,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.7508</v>
+        <v>0.7509</v>
       </c>
       <c r="C222" t="n">
         <v>-2.439</v>
@@ -52139,7 +52139,7 @@
         <v>1.7757</v>
       </c>
       <c r="E223" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="F223" t="n">
         <v>1.7757</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9867</v>
+        <v>0.9868</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6979</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5864</v>
+        <v>0.5865</v>
       </c>
       <c r="F224" t="n">
         <v>1.6979</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0142</v>
+        <v>1.0143</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52207,7 +52207,7 @@
         <v>1.6715</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5938</v>
+        <v>0.5939</v>
       </c>
       <c r="F225" t="n">
         <v>1.6715</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0834</v>
+        <v>1.0835</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1641</v>
+        <v>1.1642</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2037</v>
+        <v>1.2038</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52300,7 +52300,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.7994</v>
+        <v>0.7995</v>
       </c>
       <c r="C228" t="n">
         <v>-2.049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2618</v>
+        <v>1.2619</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52334,7 +52334,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="C229" t="n">
         <v>-1.989</v>
@@ -52368,7 +52368,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.7708</v>
       </c>
       <c r="C230" t="n">
         <v>-1.991</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2965</v>
+        <v>1.2966</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52411,7 +52411,7 @@
         <v>1.4909</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6722</v>
+        <v>0.6723</v>
       </c>
       <c r="F231" t="n">
         <v>1.4909</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4169</v>
+        <v>1.417</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52445,7 +52445,7 @@
         <v>1.3842</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6353</v>
+        <v>0.6354</v>
       </c>
       <c r="F232" t="n">
         <v>1.3842</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4793</v>
+        <v>1.4794</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52470,7 +52470,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.785</v>
+        <v>0.7851</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5496</v>
+        <v>1.5498</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6081</v>
+        <v>1.6082</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6712</v>
+        <v>1.6713</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52581,7 +52581,7 @@
         <v>1.3716</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7145</v>
+        <v>0.7146</v>
       </c>
       <c r="F236" t="n">
         <v>1.3716</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7036</v>
+        <v>1.7037</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52615,7 +52615,7 @@
         <v>1.4213</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7093</v>
+        <v>0.7094</v>
       </c>
       <c r="F237" t="n">
         <v>1.4213</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4975</v>
+        <v>1.4976</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52649,7 +52649,7 @@
         <v>1.2149</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5972</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="F238" t="n">
         <v>1.2149</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4627</v>
+        <v>1.4628</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52674,7 +52674,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7454</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6127</v>
+        <v>1.6129</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52717,7 +52717,7 @@
         <v>1.2526</v>
       </c>
       <c r="E240" t="n">
-        <v>0.695</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="F240" t="n">
         <v>1.2526</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6992</v>
+        <v>1.6994</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7304</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
@@ -52751,7 +52751,7 @@
         <v>1.2935</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5895</v>
+        <v>0.5896</v>
       </c>
       <c r="F241" t="n">
         <v>1.2935</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7359</v>
+        <v>1.736</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.795</v>
+        <v>1.7951</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7187</v>
+        <v>1.7188</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6514</v>
+        <v>0.6515</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6861</v>
+        <v>1.6862</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52887,7 +52887,7 @@
         <v>1.5772</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4783</v>
+        <v>0.4784</v>
       </c>
       <c r="F245" t="n">
         <v>1.5772</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5566</v>
+        <v>1.5567</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6562</v>
+        <v>1.6564</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52955,7 +52955,7 @@
         <v>1.4551</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5093</v>
+        <v>0.5094</v>
       </c>
       <c r="F247" t="n">
         <v>1.4551</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6839</v>
+        <v>1.684</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7789</v>
+        <v>1.779</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8502</v>
+        <v>1.8503</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53057,7 +53057,7 @@
         <v>1.2162</v>
       </c>
       <c r="E250" t="n">
-        <v>0.48</v>
+        <v>0.4801</v>
       </c>
       <c r="F250" t="n">
         <v>1.2162</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9334</v>
+        <v>1.9336</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53082,7 +53082,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7009</v>
+        <v>0.701</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0924</v>
+        <v>2.0926</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2</v>
+        <v>2.2002</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53150,7 +53150,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4572</v>
+        <v>0.4573</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2544</v>
+        <v>2.2546</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6008</v>
+        <v>0.6009</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3451</v>
+        <v>2.3453</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53227,7 +53227,7 @@
         <v>0.4421</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6004</v>
       </c>
       <c r="F255" t="n">
         <v>0.4421</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4097</v>
+        <v>2.4099</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4643</v>
+        <v>0.4644</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4893</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4581</v>
+        <v>0.4582</v>
       </c>
       <c r="F256" t="n">
         <v>0.4893</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4325</v>
+        <v>2.4327</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53295,7 +53295,7 @@
         <v>0.321</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5256</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="F257" t="n">
         <v>0.321</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.553</v>
+        <v>2.5532</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6987</v>
+        <v>2.699</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5263</v>
+        <v>0.5264</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.577</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8842</v>
+        <v>2.8845</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53397,7 +53397,7 @@
         <v>0.4097</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6158</v>
+        <v>0.6159</v>
       </c>
       <c r="F260" t="n">
         <v>0.4097</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9299</v>
+        <v>2.9302</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9274</v>
+        <v>2.9277</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5677</v>
+        <v>0.5678</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5677</v>
+        <v>0.5678</v>
       </c>
       <c r="G262" t="n">
         <v>-1.6529</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8649</v>
+        <v>2.8652</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5826</v>
+        <v>0.5814</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5826</v>
+        <v>0.5814</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9242</v>
+        <v>2.9194</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.581</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.654</v>
+        <v>1.653</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.926</v>
+        <v>1.924</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.386</v>
+        <v>2.38</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.049</v>
+        <v>3.04</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.107</v>
+        <v>4.1</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.946</v>
+        <v>-0.947</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.521</v>
+        <v>-0.524</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.36</v>
+        <v>-0.35</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.549</v>
+        <v>0.54</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.82</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68016.209</v>
+        <v>67713.072</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6541</v>
+        <v>1.6531</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9257</v>
+        <v>1.9239</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3858</v>
+        <v>2.3798</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0495</v>
+        <v>3.0399</v>
       </c>
       <c r="G263" t="n">
-        <v>4.1066</v>
+        <v>4.1001</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9459</v>
+        <v>-0.9469</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5209</v>
+        <v>-0.5241</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5495</v>
+        <v>0.5399</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>68016.2092</v>
+        <v>67713.07150000001</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.2686</v>
+        <v>10.3619</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0572</v>
+        <v>1.0602</v>
       </c>
     </row>
   </sheetData>
@@ -44634,7 +44634,7 @@
         <v>0.2564</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8507</v>
+        <v>-0.8508</v>
       </c>
       <c r="F2" t="n">
         <v>0.2564</v>
@@ -44786,7 +44786,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.381</v>
+        <v>-0.3811</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2098</v>
@@ -44795,7 +44795,7 @@
         <v>0.1458</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5127</v>
+        <v>-0.5128</v>
       </c>
       <c r="F7" t="n">
         <v>0.1458</v>
@@ -44863,7 +44863,7 @@
         <v>0.1045</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4946</v>
+        <v>-0.4947</v>
       </c>
       <c r="F9" t="n">
         <v>0.1045</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4157</v>
+        <v>-0.4158</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44943,7 +44943,7 @@
         <v>0.1635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3033</v>
+        <v>-0.3034</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2811</v>
@@ -45011,7 +45011,7 @@
         <v>0.3251</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1809</v>
+        <v>-0.181</v>
       </c>
       <c r="J13" t="n">
         <v>-1.1549</v>
@@ -45101,7 +45101,7 @@
         <v>0.0897</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3104</v>
+        <v>-0.3105</v>
       </c>
       <c r="F16" t="n">
         <v>0.0897</v>
@@ -45555,7 +45555,7 @@
         <v>0.2284</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0413</v>
+        <v>0.0412</v>
       </c>
       <c r="J29" t="n">
         <v>-0.3507</v>
@@ -45691,7 +45691,7 @@
         <v>0.3188</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0561</v>
+        <v>-0.0562</v>
       </c>
       <c r="J33" t="n">
         <v>-0.1949</v>
@@ -45725,7 +45725,7 @@
         <v>0.1887</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1173</v>
+        <v>-0.1174</v>
       </c>
       <c r="J34" t="n">
         <v>-0.1277</v>
@@ -45861,7 +45861,7 @@
         <v>0.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3816</v>
+        <v>-0.3817</v>
       </c>
       <c r="J38" t="n">
         <v>0.1937</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5692</v>
+        <v>-0.5693</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46112,7 +46112,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.3799</v>
+        <v>-0.38</v>
       </c>
       <c r="C46" t="n">
         <v>-0.6071</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8339</v>
+        <v>-0.834</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0509</v>
+        <v>-1.051</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0872</v>
+        <v>-1.0873</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0916</v>
+        <v>-1.0917</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0092</v>
+        <v>-1.0093</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9841</v>
+        <v>-0.9842</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46418,7 +46418,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1.1437</v>
+        <v>-1.1438</v>
       </c>
       <c r="C55" t="n">
         <v>0.9249000000000001</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.9825</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0363</v>
+        <v>-1.0364</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0158</v>
+        <v>-1.0159</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1656</v>
+        <v>-1.1657</v>
       </c>
       <c r="C59" t="n">
         <v>0.7284</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1064</v>
+        <v>-1.1065</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0803</v>
+        <v>-1.0804</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0824</v>
+        <v>-1.0825</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1492</v>
+        <v>-1.1493</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1819</v>
+        <v>-1.182</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -47064,7 +47064,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8373</v>
       </c>
       <c r="C74" t="n">
         <v>0.299</v>
@@ -47107,7 +47107,7 @@
         <v>-0.1846</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.9811</v>
+        <v>-0.9812</v>
       </c>
       <c r="F75" t="n">
         <v>-0.1846</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2169</v>
+        <v>-1.217</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.197</v>
+        <v>-1.1971</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2359</v>
+        <v>-1.236</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3022</v>
+        <v>-1.3023</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3289</v>
+        <v>-1.329</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47413,7 +47413,7 @@
         <v>0.1343</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.8085</v>
+        <v>-0.8086</v>
       </c>
       <c r="F84" t="n">
         <v>0.1343</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.304</v>
+        <v>-1.3041</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3176</v>
+        <v>-1.3177</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47472,7 +47472,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.5893</v>
       </c>
       <c r="C86" t="n">
         <v>-0.1737</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2771</v>
+        <v>-1.2772</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2161</v>
+        <v>-1.2162</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2233</v>
+        <v>-1.2234</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2716</v>
+        <v>-1.2717</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47685,7 +47685,7 @@
         <v>0.1323</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.6864</v>
+        <v>-0.6865</v>
       </c>
       <c r="F92" t="n">
         <v>0.1323</v>
@@ -47753,7 +47753,7 @@
         <v>0.271</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.6127</v>
+        <v>-0.6128</v>
       </c>
       <c r="F94" t="n">
         <v>0.271</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2994</v>
+        <v>-1.2995</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2866</v>
+        <v>-1.2867</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2374</v>
+        <v>-1.2375</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9616</v>
+        <v>-0.9617</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -47982,7 +47982,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.3323</v>
+        <v>-0.3324</v>
       </c>
       <c r="C101" t="n">
         <v>-0.6928</v>
@@ -48037,7 +48037,7 @@
         <v>-0.47</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.739</v>
+        <v>-0.7391</v>
       </c>
       <c r="J102" t="n">
         <v>-0.3549</v>
@@ -48071,7 +48071,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8038</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48139,7 +48139,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7496</v>
+        <v>-0.7497</v>
       </c>
       <c r="J105" t="n">
         <v>-0.3022</v>
@@ -48173,7 +48173,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6988</v>
+        <v>-0.6989</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3368</v>
@@ -48241,7 +48241,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6425</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J108" t="n">
         <v>-0.3957</v>
@@ -48399,7 +48399,7 @@
         <v>1.6996</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.1155</v>
+        <v>-0.1156</v>
       </c>
       <c r="F113" t="n">
         <v>1.6996</v>
@@ -48832,7 +48832,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.3351</v>
+        <v>0.3352</v>
       </c>
       <c r="C126" t="n">
         <v>-0.9429999999999999</v>
@@ -48909,7 +48909,7 @@
         <v>0.2942</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3315</v>
+        <v>0.3316</v>
       </c>
       <c r="F128" t="n">
         <v>0.2942</v>
@@ -48977,7 +48977,7 @@
         <v>0.2579</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3534</v>
+        <v>0.3533</v>
       </c>
       <c r="F130" t="n">
         <v>0.2579</v>
@@ -49113,7 +49113,7 @@
         <v>0.3861</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3634</v>
+        <v>0.3633</v>
       </c>
       <c r="F134" t="n">
         <v>0.3861</v>
@@ -49397,7 +49397,7 @@
         <v>1.115</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.2601</v>
+        <v>-0.2602</v>
       </c>
       <c r="J142" t="n">
         <v>0.0814</v>
@@ -49431,7 +49431,7 @@
         <v>1.115</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.218</v>
+        <v>-0.2181</v>
       </c>
       <c r="J143" t="n">
         <v>0.1265</v>
@@ -49805,7 +49805,7 @@
         <v>1.1242</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0119</v>
+        <v>-0.0118</v>
       </c>
       <c r="J154" t="n">
         <v>0.5913</v>
@@ -49873,7 +49873,7 @@
         <v>1.1242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0663</v>
+        <v>0.0664</v>
       </c>
       <c r="J156" t="n">
         <v>0.6836</v>
@@ -49941,7 +49941,7 @@
         <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0638</v>
+        <v>0.0639</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -49997,7 +49997,7 @@
         <v>0.7828000000000001</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7056</v>
+        <v>0.7057</v>
       </c>
       <c r="F160" t="n">
         <v>0.7828000000000001</v>
@@ -50009,7 +50009,7 @@
         <v>1.1757</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0411</v>
+        <v>-0.041</v>
       </c>
       <c r="J160" t="n">
         <v>0.9242</v>
@@ -50179,7 +50179,7 @@
         <v>1.1753</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0613</v>
+        <v>0.0614</v>
       </c>
       <c r="J165" t="n">
         <v>1.141</v>
@@ -50315,7 +50315,7 @@
         <v>1.0767</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="J169" t="n">
         <v>1.3187</v>
@@ -50383,7 +50383,7 @@
         <v>1.0767</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0503</v>
+        <v>-0.0502</v>
       </c>
       <c r="J171" t="n">
         <v>1.4412</v>
@@ -50417,7 +50417,7 @@
         <v>1.0374</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0578</v>
+        <v>-0.0577</v>
       </c>
       <c r="J172" t="n">
         <v>1.4574</v>
@@ -50451,7 +50451,7 @@
         <v>1.0374</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.056</v>
+        <v>-0.0559</v>
       </c>
       <c r="J173" t="n">
         <v>1.448</v>
@@ -50485,7 +50485,7 @@
         <v>1.0374</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1045</v>
+        <v>-0.1044</v>
       </c>
       <c r="J174" t="n">
         <v>1.5397</v>
@@ -50621,7 +50621,7 @@
         <v>0.9385</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2036</v>
+        <v>-0.2035</v>
       </c>
       <c r="J178" t="n">
         <v>1.719</v>
@@ -50689,7 +50689,7 @@
         <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1766</v>
+        <v>-0.1765</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -50711,7 +50711,7 @@
         <v>0.5617</v>
       </c>
       <c r="E181" t="n">
-        <v>0.7409</v>
+        <v>0.741</v>
       </c>
       <c r="F181" t="n">
         <v>0.5617</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.21</v>
+        <v>-0.2099</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50791,7 +50791,7 @@
         <v>0.8421</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2175</v>
+        <v>-0.2174</v>
       </c>
       <c r="J183" t="n">
         <v>1.969</v>
@@ -50995,7 +50995,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1835</v>
+        <v>-0.1834</v>
       </c>
       <c r="J189" t="n">
         <v>1.6451</v>
@@ -51029,7 +51029,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1558</v>
+        <v>-0.1557</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51063,7 +51063,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.133</v>
+        <v>-0.1329</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51076,7 +51076,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3437</v>
+        <v>0.3438</v>
       </c>
       <c r="C192" t="n">
         <v>0.089</v>
@@ -51097,7 +51097,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0781</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1666</v>
+        <v>0.1667</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1954</v>
+        <v>0.1955</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51280,7 +51280,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.2109</v>
+        <v>0.211</v>
       </c>
       <c r="C198" t="n">
         <v>-0.08500000000000001</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.198</v>
+        <v>0.1981</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51323,7 +51323,7 @@
         <v>0.2044</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1519</v>
+        <v>0.152</v>
       </c>
       <c r="F199" t="n">
         <v>0.2044</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2483</v>
+        <v>0.2484</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2614</v>
+        <v>0.2615</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51416,7 +51416,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2615</v>
+        <v>0.2616</v>
       </c>
       <c r="C202" t="n">
         <v>-0.388</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3459</v>
+        <v>0.346</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4036</v>
+        <v>0.4037</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51518,7 +51518,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5705</v>
+        <v>0.5706</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8159999999999999</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3958</v>
+        <v>0.3959</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51561,7 +51561,7 @@
         <v>0.5259</v>
       </c>
       <c r="E206" t="n">
-        <v>0.263</v>
+        <v>0.2631</v>
       </c>
       <c r="F206" t="n">
         <v>0.5259</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3942</v>
+        <v>0.3943</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51595,7 +51595,7 @@
         <v>0.643</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3467</v>
+        <v>0.3468</v>
       </c>
       <c r="F207" t="n">
         <v>0.643</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4007</v>
+        <v>0.4008</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4496</v>
+        <v>0.4497</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51663,7 +51663,7 @@
         <v>1.2986</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3694</v>
+        <v>0.3695</v>
       </c>
       <c r="F209" t="n">
         <v>1.2986</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5849</v>
+        <v>0.585</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51688,7 +51688,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.5689</v>
+        <v>0.569</v>
       </c>
       <c r="C210" t="n">
         <v>-1.489</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7594</v>
+        <v>0.7595</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7724</v>
+        <v>0.7725</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8847</v>
+        <v>0.8848</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9335</v>
+        <v>0.9336</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8899</v>
+        <v>0.89</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7412</v>
+        <v>0.7413</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52037,7 +52037,7 @@
         <v>1.7408</v>
       </c>
       <c r="E220" t="n">
-        <v>0.4261</v>
+        <v>0.4262</v>
       </c>
       <c r="F220" t="n">
         <v>1.7408</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7631</v>
+        <v>0.7632</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52071,7 +52071,7 @@
         <v>1.8118</v>
       </c>
       <c r="E221" t="n">
-        <v>0.4309</v>
+        <v>0.431</v>
       </c>
       <c r="F221" t="n">
         <v>1.8118</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7769</v>
+        <v>0.777</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52105,7 +52105,7 @@
         <v>1.7254</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5072</v>
+        <v>0.5073</v>
       </c>
       <c r="F222" t="n">
         <v>1.7254</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8747</v>
+        <v>0.8748</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9868</v>
+        <v>0.9869</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52164,7 +52164,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8087</v>
+        <v>0.8088</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0143</v>
+        <v>1.0144</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0835</v>
+        <v>1.0836</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52232,7 +52232,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.7025</v>
+        <v>0.7026</v>
       </c>
       <c r="C226" t="n">
         <v>-2.088</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1642</v>
+        <v>1.1643</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2038</v>
+        <v>1.2039</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2619</v>
+        <v>1.262</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52343,7 +52343,7 @@
         <v>1.4519</v>
       </c>
       <c r="E229" t="n">
-        <v>0.6022</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="F229" t="n">
         <v>1.4519</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1855</v>
+        <v>1.1856</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2966</v>
+        <v>1.2968</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.417</v>
+        <v>1.4172</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52436,7 +52436,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7851</v>
+        <v>0.7852</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4794</v>
+        <v>1.4796</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52479,7 +52479,7 @@
         <v>1.1828</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6856</v>
+        <v>0.6857</v>
       </c>
       <c r="F233" t="n">
         <v>1.1828</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5498</v>
+        <v>1.5499</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52513,7 +52513,7 @@
         <v>1.2983</v>
       </c>
       <c r="E234" t="n">
-        <v>0.7741</v>
+        <v>0.7742</v>
       </c>
       <c r="F234" t="n">
         <v>1.2983</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6082</v>
+        <v>1.6084</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52538,7 +52538,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8132</v>
+        <v>0.8133</v>
       </c>
       <c r="C235" t="n">
         <v>-1.935</v>
@@ -52547,7 +52547,7 @@
         <v>1.3372</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6822</v>
+        <v>0.6823</v>
       </c>
       <c r="F235" t="n">
         <v>1.3372</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6713</v>
+        <v>1.6714</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7037</v>
+        <v>1.7039</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.8517</v>
+        <v>0.8518</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4976</v>
+        <v>1.4978</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4628</v>
+        <v>1.4629</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52683,7 +52683,7 @@
         <v>1.146</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6453</v>
+        <v>0.6454</v>
       </c>
       <c r="F239" t="n">
         <v>1.146</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6129</v>
+        <v>1.613</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6994</v>
+        <v>1.6995</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.736</v>
+        <v>1.7361</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52776,7 +52776,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.792</v>
+        <v>0.7921</v>
       </c>
       <c r="C242" t="n">
         <v>-1.726</v>
@@ -52785,7 +52785,7 @@
         <v>1.4356</v>
       </c>
       <c r="E242" t="n">
-        <v>0.6311</v>
+        <v>0.6312</v>
       </c>
       <c r="F242" t="n">
         <v>1.4356</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7951</v>
+        <v>1.7953</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52819,7 +52819,7 @@
         <v>1.3065</v>
       </c>
       <c r="E243" t="n">
-        <v>0.6211</v>
+        <v>0.6212</v>
       </c>
       <c r="F243" t="n">
         <v>1.3065</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7188</v>
+        <v>1.7189</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52853,7 +52853,7 @@
         <v>1.3533</v>
       </c>
       <c r="E244" t="n">
-        <v>0.476</v>
+        <v>0.4761</v>
       </c>
       <c r="F244" t="n">
         <v>1.3533</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6862</v>
+        <v>1.6863</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52878,7 +52878,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.6982</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5567</v>
+        <v>1.5568</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52921,7 +52921,7 @@
         <v>1.5808</v>
       </c>
       <c r="E246" t="n">
-        <v>0.5725</v>
+        <v>0.5726</v>
       </c>
       <c r="F246" t="n">
         <v>1.5808</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6564</v>
+        <v>1.6565</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.684</v>
+        <v>1.6842</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52980,7 +52980,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.6573</v>
+        <v>0.6574</v>
       </c>
       <c r="C248" t="n">
         <v>-1.551</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.779</v>
+        <v>1.7791</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53014,7 +53014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6702</v>
+        <v>0.6703</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8503</v>
+        <v>1.8505</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9336</v>
+        <v>1.9338</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53091,7 +53091,7 @@
         <v>1.2364</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5671</v>
+        <v>0.5672</v>
       </c>
       <c r="F251" t="n">
         <v>1.2364</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0926</v>
+        <v>2.0928</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7709</v>
+        <v>0.771</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2106</v>
       </c>
       <c r="E252" t="n">
-        <v>0.661</v>
+        <v>0.6611</v>
       </c>
       <c r="F252" t="n">
         <v>1.2106</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2002</v>
+        <v>2.2004</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0326</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5634</v>
+        <v>0.5635</v>
       </c>
       <c r="F253" t="n">
         <v>0.0326</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2546</v>
+        <v>2.2548</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53193,7 +53193,7 @@
         <v>0.6442</v>
       </c>
       <c r="E254" t="n">
-        <v>0.59</v>
+        <v>0.5901</v>
       </c>
       <c r="F254" t="n">
         <v>0.6442</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3453</v>
+        <v>2.3455</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5687</v>
+        <v>0.5688</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4099</v>
+        <v>2.4102</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4327</v>
+        <v>2.433</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4847</v>
+        <v>0.4848</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5532</v>
+        <v>2.5535</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.49</v>
+        <v>0.4901</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2923</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5394</v>
+        <v>0.5395</v>
       </c>
       <c r="F258" t="n">
         <v>0.2923</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.699</v>
+        <v>2.6993</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53363,7 +53363,7 @@
         <v>0.3234</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5772</v>
       </c>
       <c r="F259" t="n">
         <v>0.3234</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8845</v>
+        <v>2.8849</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5746</v>
+        <v>0.5747</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9302</v>
+        <v>2.9305</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5319</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.331</v>
       </c>
       <c r="E261" t="n">
-        <v>0.582</v>
+        <v>0.5821</v>
       </c>
       <c r="F261" t="n">
         <v>0.331</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9277</v>
+        <v>2.928</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,13 +53456,13 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5678</v>
+        <v>0.5679</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5678</v>
+        <v>0.5679</v>
       </c>
       <c r="G262" t="n">
         <v>-1.6529</v>
@@ -53471,7 +53471,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8652</v>
+        <v>2.8655</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53484,13 +53484,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5814</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5814</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53499,7 +53499,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9194</v>
+        <v>2.9142</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>0.649</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="213">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="242">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.578</v>
+        <v>0.577</v>
       </c>
     </row>
   </sheetData>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.37</v>
+        <v>2.366</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.024</v>
+        <v>3.016</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.084</v>
+        <v>4.075</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.529</v>
+        <v>-0.53</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.524</v>
+        <v>0.516</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>67186.601</v>
+        <v>66905.761</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6527</v>
+        <v>1.6532</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9221</v>
+        <v>1.9216</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3699</v>
+        <v>2.3655</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0235</v>
+        <v>3.0162</v>
       </c>
       <c r="G263" t="n">
-        <v>4.0838</v>
+        <v>4.075</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9473</v>
+        <v>-0.9468</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5286</v>
+        <v>-0.5304</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5235</v>
+        <v>0.5162</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>67186.6007</v>
+        <v>66905.76059999999</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.5361</v>
+        <v>10.6189</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0603</v>
+        <v>1.0588</v>
       </c>
     </row>
   </sheetData>
@@ -44643,7 +44643,7 @@
         <v>-0.358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6318</v>
+        <v>-0.6319</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5626</v>
@@ -44671,7 +44671,7 @@
         <v>-0.0577</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.5903</v>
       </c>
       <c r="J3" t="n">
         <v>-1.5477</v>
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.4586</v>
+        <v>-0.4587</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2002</v>
@@ -44739,7 +44739,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5427</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5329</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4158</v>
+        <v>-0.4159</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -44922,7 +44922,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3686</v>
+        <v>-0.3687</v>
       </c>
       <c r="C11" t="n">
         <v>-0.4074</v>
@@ -44965,7 +44965,7 @@
         <v>0.0998</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4202</v>
+        <v>-0.4203</v>
       </c>
       <c r="F12" t="n">
         <v>0.0998</v>
@@ -44977,7 +44977,7 @@
         <v>0.1635</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2204</v>
+        <v>-0.2205</v>
       </c>
       <c r="J12" t="n">
         <v>-1.2209</v>
@@ -45419,7 +45419,7 @@
         <v>0.3191</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0509</v>
+        <v>-0.051</v>
       </c>
       <c r="J25" t="n">
         <v>-0.6254</v>
@@ -45793,7 +45793,7 @@
         <v>0.1887</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2354</v>
+        <v>-0.2355</v>
       </c>
       <c r="J36" t="n">
         <v>0.0412</v>
@@ -45997,7 +45997,7 @@
         <v>-0.312</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5528</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0.4153</v>
@@ -46031,7 +46031,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5231</v>
+        <v>-0.5232</v>
       </c>
       <c r="J43" t="n">
         <v>0.4481</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5693</v>
+        <v>-0.5694</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8341</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9265</v>
+        <v>-0.9266</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0511</v>
+        <v>-1.0512</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0874</v>
+        <v>-1.0875</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0918</v>
+        <v>-1.0919</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46316,7 +46316,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0616</v>
+        <v>-1.0617</v>
       </c>
       <c r="C52" t="n">
         <v>0.2794</v>
@@ -46325,7 +46325,7 @@
         <v>0.0683</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.3441</v>
+        <v>-1.3442</v>
       </c>
       <c r="F52" t="n">
         <v>0.0683</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0094</v>
+        <v>-1.0095</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9843</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46393,7 +46393,7 @@
         <v>-0.3319</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.3499</v>
+        <v>-1.35</v>
       </c>
       <c r="F54" t="n">
         <v>-0.3319</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0101</v>
+        <v>-1.0102</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46452,7 +46452,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-1.1818</v>
+        <v>-1.1819</v>
       </c>
       <c r="C56" t="n">
         <v>0.9229000000000001</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0365</v>
+        <v>-1.0366</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0751</v>
+        <v>-1.0752</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46563,7 +46563,7 @@
         <v>-0.8151</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.2536</v>
+        <v>-1.2537</v>
       </c>
       <c r="F59" t="n">
         <v>-0.8151</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0753</v>
+        <v>-1.0754</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46656,7 +46656,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-1.0644</v>
+        <v>-1.0645</v>
       </c>
       <c r="C62" t="n">
         <v>0.5668</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0905</v>
+        <v>-1.0906</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46733,7 +46733,7 @@
         <v>-0.2641</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.3082</v>
+        <v>-1.3083</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2641</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.0759</v>
+        <v>-1.076</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0177</v>
+        <v>-1.0178</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0498</v>
+        <v>-1.0499</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46835,7 +46835,7 @@
         <v>-0.1891</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2403</v>
+        <v>-1.2404</v>
       </c>
       <c r="F67" t="n">
         <v>-0.1891</v>
@@ -46928,7 +46928,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9809</v>
+        <v>-0.981</v>
       </c>
       <c r="C70" t="n">
         <v>0.3843</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1962</v>
+        <v>-1.1963</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2207</v>
+        <v>-1.2208</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47005,7 +47005,7 @@
         <v>-0.1519</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0962</v>
+        <v>-1.0963</v>
       </c>
       <c r="F72" t="n">
         <v>-0.1519</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.2139</v>
+        <v>-1.214</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47073,7 +47073,7 @@
         <v>-0.1702</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0042</v>
+        <v>-1.0043</v>
       </c>
       <c r="F74" t="n">
         <v>-0.1702</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1884</v>
+        <v>-1.1885</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47141,7 +47141,7 @@
         <v>-0.08790000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9472</v>
+        <v>-0.9473</v>
       </c>
       <c r="F76" t="n">
         <v>-0.08790000000000001</v>
@@ -47200,7 +47200,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6911</v>
       </c>
       <c r="C78" t="n">
         <v>0.114</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.2429</v>
+        <v>-1.243</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47268,7 +47268,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.6669</v>
+        <v>-0.667</v>
       </c>
       <c r="C80" t="n">
         <v>-0.0328</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.256</v>
+        <v>-1.2561</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3185</v>
+        <v>-1.3186</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47404,7 +47404,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6201</v>
+        <v>-0.6202</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0603</v>
@@ -47438,7 +47438,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.5883</v>
+        <v>-0.5884</v>
       </c>
       <c r="C85" t="n">
         <v>-0.1757</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3178</v>
+        <v>-1.3179</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.319</v>
+        <v>-1.3191</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2773</v>
+        <v>-1.2774</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2755</v>
+        <v>-1.2756</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.294</v>
+        <v>-1.2941</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2773</v>
+        <v>-1.2774</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2996</v>
+        <v>-1.2997</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2868</v>
+        <v>-1.2869</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47812,7 +47812,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.3891</v>
+        <v>-0.3892</v>
       </c>
       <c r="C96" t="n">
         <v>-0.4517</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1814</v>
+        <v>-1.1815</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -48016,7 +48016,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-0.1905</v>
+        <v>-0.1906</v>
       </c>
       <c r="C102" t="n">
         <v>-0.6918</v>
@@ -48071,7 +48071,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.804</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48220,7 +48220,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.0052</v>
+        <v>0.0051</v>
       </c>
       <c r="C108" t="n">
         <v>-0.8259</v>
@@ -48275,7 +48275,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.5737</v>
+        <v>-0.5738</v>
       </c>
       <c r="J109" t="n">
         <v>-0.3653</v>
@@ -48411,7 +48411,7 @@
         <v>0.0859</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5373</v>
+        <v>-0.5374</v>
       </c>
       <c r="J113" t="n">
         <v>-0.2751</v>
@@ -48424,7 +48424,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3526</v>
+        <v>0.3525</v>
       </c>
       <c r="C114" t="n">
         <v>-1.041</v>
@@ -48581,7 +48581,7 @@
         <v>0.3858</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.3588</v>
+        <v>-0.3589</v>
       </c>
       <c r="J118" t="n">
         <v>-0.1556</v>
@@ -48615,7 +48615,7 @@
         <v>0.3858</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3513</v>
+        <v>-0.3514</v>
       </c>
       <c r="J119" t="n">
         <v>-0.1251</v>
@@ -48819,7 +48819,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0023</v>
+        <v>0.0024</v>
       </c>
       <c r="J125" t="n">
         <v>-0.095</v>
@@ -48853,7 +48853,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>0.0601</v>
+        <v>0.0602</v>
       </c>
       <c r="J126" t="n">
         <v>-0.2019</v>
@@ -48921,7 +48921,7 @@
         <v>0.7683</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1207</v>
+        <v>0.1208</v>
       </c>
       <c r="J128" t="n">
         <v>-0.1184</v>
@@ -49193,7 +49193,7 @@
         <v>0.9537</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J136" t="n">
         <v>-0.0994</v>
@@ -49737,7 +49737,7 @@
         <v>1.1972</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0023</v>
+        <v>-0.0022</v>
       </c>
       <c r="J152" t="n">
         <v>0.5928</v>
@@ -49895,7 +49895,7 @@
         <v>0.7795</v>
       </c>
       <c r="E157" t="n">
-        <v>0.6685</v>
+        <v>0.6686</v>
       </c>
       <c r="F157" t="n">
         <v>0.7795</v>
@@ -49920,7 +49920,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.719</v>
+        <v>0.7191</v>
       </c>
       <c r="C158" t="n">
         <v>-0.525</v>
@@ -49941,7 +49941,7 @@
         <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0639</v>
+        <v>0.064</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -49954,7 +49954,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.731</v>
+        <v>0.7311</v>
       </c>
       <c r="C159" t="n">
         <v>-0.527</v>
@@ -50111,7 +50111,7 @@
         <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0473</v>
+        <v>0.0474</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50213,7 +50213,7 @@
         <v>1.1104</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1027</v>
+        <v>0.1028</v>
       </c>
       <c r="J166" t="n">
         <v>1.2041</v>
@@ -50281,7 +50281,7 @@
         <v>1.1104</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0633</v>
+        <v>0.0634</v>
       </c>
       <c r="J168" t="n">
         <v>1.2437</v>
@@ -50362,7 +50362,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.7763</v>
+        <v>0.7764</v>
       </c>
       <c r="C171" t="n">
         <v>-0.518</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2099</v>
+        <v>-0.2098</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -50791,7 +50791,7 @@
         <v>0.8421</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.2174</v>
+        <v>-0.2173</v>
       </c>
       <c r="J183" t="n">
         <v>1.969</v>
@@ -50893,7 +50893,7 @@
         <v>0.5822000000000001</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2792</v>
+        <v>-0.2791</v>
       </c>
       <c r="J186" t="n">
         <v>2.0342</v>
@@ -50961,7 +50961,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1992</v>
+        <v>-0.1991</v>
       </c>
       <c r="J188" t="n">
         <v>1.9226</v>
@@ -50995,7 +50995,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1834</v>
+        <v>-0.1833</v>
       </c>
       <c r="J189" t="n">
         <v>1.6451</v>
@@ -51029,7 +51029,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1557</v>
+        <v>-0.1556</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51063,7 +51063,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1329</v>
+        <v>-0.1328</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0364</v>
+        <v>-0.0363</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51144,7 +51144,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2816</v>
+        <v>0.2817</v>
       </c>
       <c r="C194" t="n">
         <v>0.093</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51212,7 +51212,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.2594</v>
+        <v>0.2595</v>
       </c>
       <c r="C196" t="n">
         <v>-0.08500000000000001</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1668</v>
+        <v>0.1669</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1956</v>
+        <v>0.1957</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1982</v>
+        <v>0.1983</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2485</v>
+        <v>0.2486</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51391,7 +51391,7 @@
         <v>0.4284</v>
       </c>
       <c r="E201" t="n">
-        <v>0.1936</v>
+        <v>0.1937</v>
       </c>
       <c r="F201" t="n">
         <v>0.4284</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3461</v>
+        <v>0.3462</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51459,7 +51459,7 @@
         <v>0.4997</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2463</v>
+        <v>0.2464</v>
       </c>
       <c r="F203" t="n">
         <v>0.4997</v>
@@ -51493,7 +51493,7 @@
         <v>0.637</v>
       </c>
       <c r="E204" t="n">
-        <v>0.304</v>
+        <v>0.3041</v>
       </c>
       <c r="F204" t="n">
         <v>0.637</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4038</v>
+        <v>0.4039</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51527,7 +51527,7 @@
         <v>1.7577</v>
       </c>
       <c r="E205" t="n">
-        <v>0.2739</v>
+        <v>0.274</v>
       </c>
       <c r="F205" t="n">
         <v>1.7577</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.396</v>
+        <v>0.3961</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3944</v>
+        <v>0.3945</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51629,7 +51629,7 @@
         <v>0.7242</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2979</v>
+        <v>0.298</v>
       </c>
       <c r="F208" t="n">
         <v>0.7242</v>
@@ -51654,7 +51654,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.5553</v>
+        <v>0.5554</v>
       </c>
       <c r="C209" t="n">
         <v>-1.483</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6121</v>
+        <v>0.6122</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6982</v>
+        <v>0.6983</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8901</v>
+        <v>0.8902</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51926,7 +51926,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.6236</v>
+        <v>0.6237</v>
       </c>
       <c r="C217" t="n">
         <v>-2.379</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7591</v>
+        <v>0.7592</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6895</v>
+        <v>0.6896</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7771</v>
+        <v>0.7772</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.987</v>
+        <v>0.9871</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0146</v>
+        <v>1.0147</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52198,7 +52198,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.8095</v>
+        <v>0.8096</v>
       </c>
       <c r="C225" t="n">
         <v>-2.152</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0837</v>
+        <v>1.0838</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52241,7 +52241,7 @@
         <v>1.4783</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5087</v>
+        <v>0.5088</v>
       </c>
       <c r="F226" t="n">
         <v>1.4783</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1644</v>
+        <v>1.1645</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2041</v>
+        <v>1.2042</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52309,7 +52309,7 @@
         <v>1.3824</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6538</v>
+        <v>0.6539</v>
       </c>
       <c r="F228" t="n">
         <v>1.3824</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2621</v>
+        <v>1.2622</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1858</v>
+        <v>1.1859</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.297</v>
+        <v>1.2971</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.8361</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="C231" t="n">
         <v>-1.983</v>
@@ -52411,7 +52411,7 @@
         <v>1.4913</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6723</v>
+        <v>0.6724</v>
       </c>
       <c r="F231" t="n">
         <v>1.4913</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4174</v>
+        <v>1.4175</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4798</v>
+        <v>1.48</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52479,7 +52479,7 @@
         <v>1.183</v>
       </c>
       <c r="E233" t="n">
-        <v>0.6857</v>
+        <v>0.6858</v>
       </c>
       <c r="F233" t="n">
         <v>1.183</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5501</v>
+        <v>1.5503</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52513,7 +52513,7 @@
         <v>1.2985</v>
       </c>
       <c r="E234" t="n">
-        <v>0.7742</v>
+        <v>0.7743</v>
       </c>
       <c r="F234" t="n">
         <v>1.2985</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6086</v>
+        <v>1.6087</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52547,7 +52547,7 @@
         <v>1.3375</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6823</v>
+        <v>0.6824</v>
       </c>
       <c r="F235" t="n">
         <v>1.3375</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6717</v>
+        <v>1.6718</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.8461</v>
+        <v>0.8462</v>
       </c>
       <c r="C236" t="n">
         <v>-1.934</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7041</v>
+        <v>1.7042</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52615,7 +52615,7 @@
         <v>1.4216</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7094</v>
+        <v>0.7095</v>
       </c>
       <c r="F237" t="n">
         <v>1.4216</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.498</v>
+        <v>1.4981</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4631</v>
+        <v>1.4632</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6132</v>
+        <v>1.6134</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6997</v>
+        <v>1.6999</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7364</v>
+        <v>1.7365</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52785,7 +52785,7 @@
         <v>1.436</v>
       </c>
       <c r="E242" t="n">
-        <v>0.6312</v>
+        <v>0.6313</v>
       </c>
       <c r="F242" t="n">
         <v>1.436</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7955</v>
+        <v>1.7956</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52810,7 +52810,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.7583</v>
+        <v>0.7584</v>
       </c>
       <c r="C243" t="n">
         <v>-1.541</v>
@@ -52819,7 +52819,7 @@
         <v>1.3068</v>
       </c>
       <c r="E243" t="n">
-        <v>0.6212</v>
+        <v>0.6213</v>
       </c>
       <c r="F243" t="n">
         <v>1.3068</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7192</v>
+        <v>1.7193</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6865</v>
+        <v>1.6866</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52887,7 +52887,7 @@
         <v>1.5777</v>
       </c>
       <c r="E245" t="n">
-        <v>0.4784</v>
+        <v>0.4785</v>
       </c>
       <c r="F245" t="n">
         <v>1.5777</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.557</v>
+        <v>1.5571</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52912,7 +52912,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.7743</v>
+        <v>0.7744</v>
       </c>
       <c r="C246" t="n">
         <v>-1.645</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6567</v>
+        <v>1.6568</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6844</v>
+        <v>1.6845</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7794</v>
+        <v>1.7795</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8508</v>
+        <v>1.8509</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53048,7 +53048,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.6274</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="C250" t="n">
         <v>-1.567</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9341</v>
+        <v>1.9342</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53082,7 +53082,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7012</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0931</v>
+        <v>2.0933</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2008</v>
+        <v>2.201</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2551</v>
+        <v>2.2553</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.6009</v>
+        <v>0.601</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3459</v>
+        <v>2.3461</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53227,7 +53227,7 @@
         <v>0.4417</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6005</v>
+        <v>0.6006</v>
       </c>
       <c r="F255" t="n">
         <v>0.4417</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4106</v>
+        <v>2.4108</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4644</v>
+        <v>0.4645</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4889</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4583</v>
+        <v>0.4584</v>
       </c>
       <c r="F256" t="n">
         <v>0.4889</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4334</v>
+        <v>2.4336</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53295,7 +53295,7 @@
         <v>0.3205</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5258</v>
+        <v>0.5259</v>
       </c>
       <c r="F257" t="n">
         <v>0.3205</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5539</v>
+        <v>2.5542</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53329,7 +53329,7 @@
         <v>0.2918</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5396</v>
+        <v>0.5397</v>
       </c>
       <c r="F258" t="n">
         <v>0.2918</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.6998</v>
+        <v>2.7001</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5264</v>
+        <v>0.5265</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3229</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5773</v>
+        <v>0.5774</v>
       </c>
       <c r="F259" t="n">
         <v>0.3229</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8854</v>
+        <v>2.8858</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5747</v>
+        <v>0.5748</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4093</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6161</v>
+        <v>0.6162</v>
       </c>
       <c r="F260" t="n">
         <v>0.4093</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9311</v>
+        <v>2.9314</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.5319</v>
+        <v>0.532</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9285</v>
+        <v>2.9288</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53465,7 +53465,7 @@
         <v>0.4117</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5681</v>
       </c>
       <c r="F262" t="n">
         <v>0.4117</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.866</v>
+        <v>2.8663</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5778</v>
+        <v>0.5766</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5778</v>
+        <v>0.5766</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9051</v>
+        <v>2.9003</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>-0.431</v>
+        <v>-0.432</v>
       </c>
     </row>
     <row r="49">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="224">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>0.657</v>
+        <v>0.658</v>
       </c>
     </row>
     <row r="249">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="257">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>0.526</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="260">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.577</v>
+        <v>0.575</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.653</v>
+        <v>1.652</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.922</v>
+        <v>1.918</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.366</v>
+        <v>2.358</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.016</v>
+        <v>3.005</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.075</v>
+        <v>4.064</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.947</v>
+        <v>-0.948</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.53</v>
+        <v>-0.535</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.516</v>
+        <v>0.505</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66905.761</v>
+        <v>66628.342</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6532</v>
+        <v>1.6525</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9216</v>
+        <v>1.9185</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3655</v>
+        <v>2.3576</v>
       </c>
       <c r="F263" t="n">
-        <v>3.0162</v>
+        <v>3.005</v>
       </c>
       <c r="G263" t="n">
-        <v>4.075</v>
+        <v>4.0643</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9468</v>
+        <v>-0.9475</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5304</v>
+        <v>-0.5351</v>
       </c>
       <c r="M263" t="n">
-        <v>0.5162</v>
+        <v>0.505</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>66905.76059999999</v>
+        <v>66628.34239999999</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.6189</v>
+        <v>10.7519</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0588</v>
+        <v>1.0593</v>
       </c>
     </row>
   </sheetData>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5344</v>
+        <v>-0.5345</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44807,7 +44807,7 @@
         <v>0.1514</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4989</v>
+        <v>-0.499</v>
       </c>
       <c r="J7" t="n">
         <v>-1.3592</v>
@@ -44841,7 +44841,7 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4177</v>
+        <v>-0.4178</v>
       </c>
       <c r="J8" t="n">
         <v>-1.4505</v>
@@ -44888,7 +44888,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.3533</v>
+        <v>-0.3534</v>
       </c>
       <c r="C10" t="n">
         <v>-0.4074</v>
@@ -44909,7 +44909,7 @@
         <v>0.1635</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3904</v>
+        <v>-0.3905</v>
       </c>
       <c r="J10" t="n">
         <v>-1.2593</v>
@@ -44943,7 +44943,7 @@
         <v>0.1635</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3034</v>
+        <v>-0.3035</v>
       </c>
       <c r="J11" t="n">
         <v>-1.2811</v>
@@ -45045,7 +45045,7 @@
         <v>0.3251</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2201</v>
+        <v>-0.2202</v>
       </c>
       <c r="J14" t="n">
         <v>-1.0677</v>
@@ -45283,7 +45283,7 @@
         <v>0.4155</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1447</v>
+        <v>-0.1448</v>
       </c>
       <c r="J21" t="n">
         <v>-0.8549</v>
@@ -45861,7 +45861,7 @@
         <v>0.0667</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3817</v>
+        <v>-0.3818</v>
       </c>
       <c r="J38" t="n">
         <v>0.1937</v>
@@ -45917,7 +45917,7 @@
         <v>0.6101</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5829</v>
+        <v>-0.583</v>
       </c>
       <c r="F40" t="n">
         <v>0.6101</v>
@@ -46053,7 +46053,7 @@
         <v>1.0016</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5466</v>
+        <v>-0.5467</v>
       </c>
       <c r="F44" t="n">
         <v>1.0016</v>
@@ -46133,7 +46133,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6511</v>
+        <v>-0.6512</v>
       </c>
       <c r="J46" t="n">
         <v>0.5804</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9266</v>
+        <v>-0.9267</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0095</v>
+        <v>-1.0096</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-1.1463</v>
+        <v>-1.1464</v>
       </c>
       <c r="C54" t="n">
         <v>0.2814</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9826</v>
+        <v>-0.9827</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46461,7 +46461,7 @@
         <v>-0.8183</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.2727</v>
+        <v>-1.2728</v>
       </c>
       <c r="F56" t="n">
         <v>-0.8183</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.016</v>
+        <v>-1.0161</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46554,7 +46554,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-1.1659</v>
+        <v>-1.166</v>
       </c>
       <c r="C59" t="n">
         <v>0.7284</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1066</v>
+        <v>-1.1067</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46643,7 +46643,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0805</v>
+        <v>-1.0806</v>
       </c>
       <c r="J61" t="n">
         <v>-1.1445</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0538</v>
+        <v>-1.0539</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46801,7 +46801,7 @@
         <v>-0.2101</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.2638</v>
+        <v>-1.2639</v>
       </c>
       <c r="F66" t="n">
         <v>-0.2101</v>
@@ -46847,7 +46847,7 @@
         <v>-1.362</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.0826</v>
+        <v>-1.0827</v>
       </c>
       <c r="J67" t="n">
         <v>-2.1324</v>
@@ -46860,7 +46860,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.0283</v>
+        <v>-1.0284</v>
       </c>
       <c r="C68" t="n">
         <v>0.453</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1494</v>
+        <v>-1.1495</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46903,7 +46903,7 @@
         <v>-0.2636</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2108</v>
+        <v>-1.2109</v>
       </c>
       <c r="F69" t="n">
         <v>-0.2636</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1821</v>
+        <v>-1.1822</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1921</v>
+        <v>-1.1922</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47064,7 +47064,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8374</v>
+        <v>-0.8375</v>
       </c>
       <c r="C74" t="n">
         <v>0.299</v>
@@ -47098,7 +47098,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.822</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="C75" t="n">
         <v>0.307</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1994</v>
+        <v>-1.1995</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2171</v>
+        <v>-1.2172</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1972</v>
+        <v>-1.1973</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2361</v>
+        <v>-1.2362</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3024</v>
+        <v>-1.3025</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3291</v>
+        <v>-1.3292</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3042</v>
+        <v>-1.3043</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47447,7 +47447,7 @@
         <v>0.1884</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.7825</v>
+        <v>-0.7826</v>
       </c>
       <c r="F85" t="n">
         <v>0.1884</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3191</v>
+        <v>-1.3192</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2163</v>
+        <v>-1.2164</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2235</v>
+        <v>-1.2236</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.5256</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="C90" t="n">
         <v>-0.2617</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2718</v>
+        <v>-1.2719</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47787,7 +47787,7 @@
         <v>0.2707</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.593</v>
+        <v>-0.5931</v>
       </c>
       <c r="F95" t="n">
         <v>0.2707</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2376</v>
+        <v>-1.2377</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-0.3471</v>
+        <v>-0.3472</v>
       </c>
       <c r="C97" t="n">
         <v>-0.6221</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0553</v>
+        <v>-1.0554</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -47935,7 +47935,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.9618</v>
+        <v>-0.9619</v>
       </c>
       <c r="J99" t="n">
         <v>-0.5304</v>
@@ -47948,7 +47948,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.2809</v>
+        <v>-0.281</v>
       </c>
       <c r="C100" t="n">
         <v>-0.6868</v>
@@ -48139,7 +48139,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7497</v>
+        <v>-0.7498</v>
       </c>
       <c r="J105" t="n">
         <v>-0.3022</v>
@@ -48173,7 +48173,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6989</v>
+        <v>-0.699</v>
       </c>
       <c r="J106" t="n">
         <v>-0.3368</v>
@@ -48195,7 +48195,7 @@
         <v>0.6531</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.2558</v>
+        <v>-0.2559</v>
       </c>
       <c r="F107" t="n">
         <v>0.6531</v>
@@ -48207,7 +48207,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.713</v>
+        <v>-0.7131</v>
       </c>
       <c r="J107" t="n">
         <v>-0.348</v>
@@ -48309,7 +48309,7 @@
         <v>-0.0186</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.5582</v>
+        <v>-0.5583</v>
       </c>
       <c r="J110" t="n">
         <v>-0.2626</v>
@@ -48377,7 +48377,7 @@
         <v>0.0859</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.5581</v>
+        <v>-0.5582</v>
       </c>
       <c r="J112" t="n">
         <v>-0.2325</v>
@@ -48433,7 +48433,7 @@
         <v>1.7473</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="F114" t="n">
         <v>1.7473</v>
@@ -48467,7 +48467,7 @@
         <v>1.7511</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="F115" t="n">
         <v>1.7511</v>
@@ -48479,7 +48479,7 @@
         <v>0.3854</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5134</v>
+        <v>-0.5135</v>
       </c>
       <c r="J115" t="n">
         <v>-0.2898</v>
@@ -48535,7 +48535,7 @@
         <v>1.6666</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0761</v>
+        <v>0.076</v>
       </c>
       <c r="F117" t="n">
         <v>1.6666</v>
@@ -48785,7 +48785,7 @@
         <v>0.7112000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.001</v>
+        <v>-0.0009</v>
       </c>
       <c r="J124" t="n">
         <v>-0.1048</v>
@@ -48887,7 +48887,7 @@
         <v>0.7683</v>
       </c>
       <c r="I127" t="n">
-        <v>0.112</v>
+        <v>0.1121</v>
       </c>
       <c r="J127" t="n">
         <v>-0.0956</v>
@@ -49342,7 +49342,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3985</v>
+        <v>0.3984</v>
       </c>
       <c r="C141" t="n">
         <v>-0.409</v>
@@ -49839,7 +49839,7 @@
         <v>1.1242</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0502</v>
+        <v>0.0503</v>
       </c>
       <c r="J155" t="n">
         <v>0.7134</v>
@@ -49861,7 +49861,7 @@
         <v>0.8369</v>
       </c>
       <c r="E156" t="n">
-        <v>0.6217</v>
+        <v>0.6218</v>
       </c>
       <c r="F156" t="n">
         <v>0.8369</v>
@@ -49873,7 +49873,7 @@
         <v>1.1242</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0664</v>
+        <v>0.0665</v>
       </c>
       <c r="J156" t="n">
         <v>0.6836</v>
@@ -50077,7 +50077,7 @@
         <v>1.1757</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0267</v>
+        <v>0.0268</v>
       </c>
       <c r="J162" t="n">
         <v>1.0036</v>
@@ -50179,7 +50179,7 @@
         <v>1.1753</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0614</v>
+        <v>0.0615</v>
       </c>
       <c r="J165" t="n">
         <v>1.141</v>
@@ -50371,7 +50371,7 @@
         <v>0.7524</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7823</v>
+        <v>0.7824</v>
       </c>
       <c r="F171" t="n">
         <v>0.7524</v>
@@ -50451,7 +50451,7 @@
         <v>1.0374</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.0559</v>
+        <v>-0.0558</v>
       </c>
       <c r="J173" t="n">
         <v>1.448</v>
@@ -50621,7 +50621,7 @@
         <v>0.9385</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2035</v>
+        <v>-0.2034</v>
       </c>
       <c r="J178" t="n">
         <v>1.719</v>
@@ -50689,7 +50689,7 @@
         <v>0.9385</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1765</v>
+        <v>-0.1764</v>
       </c>
       <c r="J180" t="n">
         <v>1.8053</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0867</v>
+        <v>0.0868</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51246,7 +51246,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2003</v>
+        <v>0.2004</v>
       </c>
       <c r="C197" t="n">
         <v>-0.08</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2486</v>
+        <v>0.2487</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2532</v>
+        <v>0.2533</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2616</v>
+        <v>0.2617</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3462</v>
+        <v>0.3463</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3699</v>
+        <v>0.37</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51484,7 +51484,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.3706</v>
+        <v>0.3707</v>
       </c>
       <c r="C204" t="n">
         <v>-0.406</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3961</v>
+        <v>0.3962</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4009</v>
+        <v>0.401</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4498</v>
+        <v>0.4499</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5851</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51731,7 +51731,7 @@
         <v>1.3422</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3936</v>
+        <v>0.3937</v>
       </c>
       <c r="F211" t="n">
         <v>1.3422</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.7597</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51790,7 +51790,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.6972</v>
       </c>
       <c r="C213" t="n">
         <v>-2.07</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7726</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.8849</v>
+        <v>0.885</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9337</v>
+        <v>0.9338</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -51960,7 +51960,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.7269</v>
+        <v>0.727</v>
       </c>
       <c r="C218" t="n">
         <v>-2.333</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7415</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7633</v>
+        <v>0.7634</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.875</v>
+        <v>0.8751</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52139,7 +52139,7 @@
         <v>1.7763</v>
       </c>
       <c r="E223" t="n">
-        <v>0.544</v>
+        <v>0.5441</v>
       </c>
       <c r="F223" t="n">
         <v>1.7763</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9871</v>
+        <v>0.9872</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52173,7 +52173,7 @@
         <v>1.6984</v>
       </c>
       <c r="E224" t="n">
-        <v>0.5865</v>
+        <v>0.5866</v>
       </c>
       <c r="F224" t="n">
         <v>1.6984</v>
@@ -52207,7 +52207,7 @@
         <v>1.6721</v>
       </c>
       <c r="E225" t="n">
-        <v>0.5939</v>
+        <v>0.594</v>
       </c>
       <c r="F225" t="n">
         <v>1.6721</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0838</v>
+        <v>1.0839</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1645</v>
+        <v>1.1646</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2622</v>
+        <v>1.2623</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1859</v>
+        <v>1.186</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2971</v>
+        <v>1.2972</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4175</v>
+        <v>1.4176</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.48</v>
+        <v>1.4801</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5503</v>
+        <v>1.5504</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6087</v>
+        <v>1.6089</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6718</v>
+        <v>1.6719</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7042</v>
+        <v>1.7044</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4981</v>
+        <v>1.4982</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52640,7 +52640,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.7209</v>
+        <v>0.721</v>
       </c>
       <c r="C238" t="n">
         <v>-1.795</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4632</v>
+        <v>1.4634</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52683,7 +52683,7 @@
         <v>1.1461</v>
       </c>
       <c r="E239" t="n">
-        <v>0.6454</v>
+        <v>0.6455</v>
       </c>
       <c r="F239" t="n">
         <v>1.1461</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6134</v>
+        <v>1.6135</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.6999</v>
+        <v>1.7</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7365</v>
+        <v>1.7366</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7956</v>
+        <v>1.7958</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7193</v>
+        <v>1.7194</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52853,7 +52853,7 @@
         <v>1.3536</v>
       </c>
       <c r="E244" t="n">
-        <v>0.4761</v>
+        <v>0.4762</v>
       </c>
       <c r="F244" t="n">
         <v>1.3536</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6866</v>
+        <v>1.6868</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5571</v>
+        <v>1.5572</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52921,7 +52921,7 @@
         <v>1.5813</v>
       </c>
       <c r="E246" t="n">
-        <v>0.5726</v>
+        <v>0.5727</v>
       </c>
       <c r="F246" t="n">
         <v>1.5813</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6568</v>
+        <v>1.6569</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6845</v>
+        <v>1.6846</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -52989,7 +52989,7 @@
         <v>1.3009</v>
       </c>
       <c r="E248" t="n">
-        <v>0.4966</v>
+        <v>0.4967</v>
       </c>
       <c r="F248" t="n">
         <v>1.3009</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7795</v>
+        <v>1.7797</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53023,7 +53023,7 @@
         <v>1.1169</v>
       </c>
       <c r="E249" t="n">
-        <v>0.5587</v>
+        <v>0.5588</v>
       </c>
       <c r="F249" t="n">
         <v>1.1169</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8509</v>
+        <v>1.8511</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53057,7 +53057,7 @@
         <v>1.2163</v>
       </c>
       <c r="E250" t="n">
-        <v>0.4802</v>
+        <v>0.4803</v>
       </c>
       <c r="F250" t="n">
         <v>1.2163</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9342</v>
+        <v>1.9344</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0933</v>
+        <v>2.0935</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7711</v>
+        <v>0.7712</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2108</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6612</v>
+        <v>0.6613</v>
       </c>
       <c r="F252" t="n">
         <v>1.2108</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.201</v>
+        <v>2.2012</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0319</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5636</v>
+        <v>0.5637</v>
       </c>
       <c r="F253" t="n">
         <v>0.0319</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2553</v>
+        <v>2.2555</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53193,7 +53193,7 @@
         <v>0.6439</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5903</v>
       </c>
       <c r="F254" t="n">
         <v>0.6439</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3461</v>
+        <v>2.3463</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5688</v>
+        <v>0.5689</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4417</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6006</v>
+        <v>0.6007</v>
       </c>
       <c r="F255" t="n">
         <v>0.4417</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4108</v>
+        <v>2.4111</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4336</v>
+        <v>2.4338</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4848</v>
+        <v>0.4849</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53295,7 +53295,7 @@
         <v>0.3205</v>
       </c>
       <c r="E257" t="n">
-        <v>0.5259</v>
+        <v>0.526</v>
       </c>
       <c r="F257" t="n">
         <v>0.3205</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5542</v>
+        <v>2.5544</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4901</v>
+        <v>0.4902</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53329,7 +53329,7 @@
         <v>0.2918</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5397</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="F258" t="n">
         <v>0.2918</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7001</v>
+        <v>2.7003</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5265</v>
+        <v>0.5266</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53363,7 +53363,7 @@
         <v>0.3229</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5774</v>
+        <v>0.5775</v>
       </c>
       <c r="F259" t="n">
         <v>0.3229</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8858</v>
+        <v>2.8861</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9314</v>
+        <v>2.9317</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53431,7 +53431,7 @@
         <v>0.3305</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5823</v>
+        <v>0.5824</v>
       </c>
       <c r="F261" t="n">
         <v>0.3305</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9288</v>
+        <v>2.9291</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53456,7 +53456,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5369</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
@@ -53465,7 +53465,7 @@
         <v>0.4117</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5681</v>
+        <v>0.5682</v>
       </c>
       <c r="F262" t="n">
         <v>0.4117</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8663</v>
+        <v>2.8666</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5766</v>
+        <v>0.5754</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5766</v>
+        <v>0.5754</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.9003</v>
+        <v>2.8955</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>+0.58</t>
+          <t>+0.57</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B22" s="8" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>The composite Financial Conditions Index reads +0.58 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.04%. The real policy rate is about -1.56%, roughly 1.20pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
+          <t>The composite Financial Conditions Index reads +0.57 (accommodative relative to its 2005+ history), indicating that financial conditions remain accommodative even after the policy rate was raised to 1.04%. The real policy rate is about -1.56%, roughly 1.20pp below the midpoint natural-rate estimate (-0.36%), so on the natural-rate lens the stance is still accommodative; the six-model natural-rate band (-0.94% to +0.53%) means this read carries wide uncertainty. Horizon: the headline real-rate axis is now scored over its longest available history (ex-post, since 1974/1986), not the ZIRP/NIRP-dominated 2005+ window (kept as a reference). On that long baseline the real-rate stance is mildly accommodative; it reads broadly neutral versus 1990 and mildly restrictive only versus post-1995 baselines (see the horizon table). Other axes remain on 2005+ history.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>-0.332</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="102">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="J250" t="n">
-        <v>0.627</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="251">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.918</v>
+        <v>1.917</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.358</v>
+        <v>2.351</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.005</v>
+        <v>2.994</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.064</v>
+        <v>4.054</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.535</v>
+        <v>-0.539</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.505</v>
+        <v>0.494</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66628.342</v>
+        <v>66441.677</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6525</v>
+        <v>1.6523</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9185</v>
+        <v>1.9167</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3576</v>
+        <v>2.3507</v>
       </c>
       <c r="F263" t="n">
-        <v>3.005</v>
+        <v>2.9944</v>
       </c>
       <c r="G263" t="n">
-        <v>4.0643</v>
+        <v>4.0537</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9475</v>
+        <v>-0.9477</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5351</v>
+        <v>-0.5386</v>
       </c>
       <c r="M263" t="n">
-        <v>0.505</v>
+        <v>0.4944</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>66628.34239999999</v>
+        <v>66441.67720000001</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.7519</v>
+        <v>10.8851</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0593</v>
+        <v>1.0594</v>
       </c>
     </row>
   </sheetData>
@@ -44705,7 +44705,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5661</v>
+        <v>-0.5662</v>
       </c>
       <c r="J4" t="n">
         <v>-1.6144</v>
@@ -45738,7 +45738,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3876</v>
+        <v>-0.3877</v>
       </c>
       <c r="C35" t="n">
         <v>-0.4195</v>
@@ -45895,7 +45895,7 @@
         <v>0.0667</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4181</v>
+        <v>-0.4182</v>
       </c>
       <c r="J39" t="n">
         <v>0.1293</v>
@@ -45929,7 +45929,7 @@
         <v>-0.312</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5681</v>
+        <v>-0.5682</v>
       </c>
       <c r="J40" t="n">
         <v>0.2773</v>
@@ -45963,7 +45963,7 @@
         <v>-0.312</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5548</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0.3169</v>
@@ -46155,7 +46155,7 @@
         <v>0.7932</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.7038</v>
+        <v>-0.7039</v>
       </c>
       <c r="F47" t="n">
         <v>0.7932</v>
@@ -46235,7 +46235,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.0512</v>
+        <v>-1.0513</v>
       </c>
       <c r="J49" t="n">
         <v>0.8058</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.0919</v>
+        <v>-1.092</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46371,7 +46371,7 @@
         <v>-3.398</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.9845</v>
       </c>
       <c r="J53" t="n">
         <v>0.1253</v>
@@ -46405,7 +46405,7 @@
         <v>-3.398</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.0102</v>
+        <v>-1.0103</v>
       </c>
       <c r="J54" t="n">
         <v>-0.0091</v>
@@ -46495,7 +46495,7 @@
         <v>-0.8964</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.2969</v>
+        <v>-1.297</v>
       </c>
       <c r="F57" t="n">
         <v>-0.8964</v>
@@ -46529,7 +46529,7 @@
         <v>-0.8362000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.2693</v>
+        <v>-1.2694</v>
       </c>
       <c r="F58" t="n">
         <v>-0.8362000000000001</v>
@@ -46575,7 +46575,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.0754</v>
+        <v>-1.0755</v>
       </c>
       <c r="J59" t="n">
         <v>-0.8351</v>
@@ -46949,7 +46949,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1963</v>
+        <v>-1.1964</v>
       </c>
       <c r="J70" t="n">
         <v>-1.9877</v>
@@ -46983,7 +46983,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2208</v>
+        <v>-1.2209</v>
       </c>
       <c r="J71" t="n">
         <v>-1.9299</v>
@@ -47017,7 +47017,7 @@
         <v>-1.0936</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.214</v>
+        <v>-1.2141</v>
       </c>
       <c r="J72" t="n">
         <v>-1.8497</v>
@@ -47085,7 +47085,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1885</v>
+        <v>-1.1886</v>
       </c>
       <c r="J74" t="n">
         <v>-1.7532</v>
@@ -47289,7 +47289,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.2561</v>
+        <v>-1.2562</v>
       </c>
       <c r="J80" t="n">
         <v>-1.5483</v>
@@ -47345,7 +47345,7 @@
         <v>0.3252</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.8222</v>
       </c>
       <c r="F82" t="n">
         <v>0.3252</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3186</v>
+        <v>-1.3187</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47379,7 +47379,7 @@
         <v>0.1807</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.9136</v>
+        <v>-0.9137</v>
       </c>
       <c r="F83" t="n">
         <v>0.1807</v>
@@ -47459,7 +47459,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.3179</v>
+        <v>-1.318</v>
       </c>
       <c r="J85" t="n">
         <v>-1.2074</v>
@@ -47642,7 +47642,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-0.4804</v>
+        <v>-0.4805</v>
       </c>
       <c r="C91" t="n">
         <v>-0.3987</v>
@@ -47651,7 +47651,7 @@
         <v>0.1748</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.6442</v>
+        <v>-0.6443</v>
       </c>
       <c r="F91" t="n">
         <v>0.1748</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2756</v>
+        <v>-1.2757</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2941</v>
+        <v>-1.2942</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47731,7 +47731,7 @@
         <v>-0.421</v>
       </c>
       <c r="I93" t="n">
-        <v>-1.2774</v>
+        <v>-1.2775</v>
       </c>
       <c r="J93" t="n">
         <v>-0.8872</v>
@@ -47744,7 +47744,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-0.4361</v>
+        <v>-0.4362</v>
       </c>
       <c r="C94" t="n">
         <v>-0.4527</v>
@@ -47799,7 +47799,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.2869</v>
+        <v>-1.287</v>
       </c>
       <c r="J95" t="n">
         <v>-0.6718</v>
@@ -47969,7 +47969,7 @@
         <v>-0.47</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9103</v>
+        <v>-0.9104</v>
       </c>
       <c r="J100" t="n">
         <v>-0.4331</v>
@@ -48037,7 +48037,7 @@
         <v>-0.47</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.7391</v>
+        <v>-0.7392</v>
       </c>
       <c r="J102" t="n">
         <v>-0.3549</v>
@@ -48547,7 +48547,7 @@
         <v>0.3854</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.4523</v>
+        <v>-0.4524</v>
       </c>
       <c r="J117" t="n">
         <v>-0.2606</v>
@@ -49410,7 +49410,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4318</v>
+        <v>0.4317</v>
       </c>
       <c r="C143" t="n">
         <v>-0.347</v>
@@ -49907,7 +49907,7 @@
         <v>1.1579</v>
       </c>
       <c r="I157" t="n">
-        <v>0.0689</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J157" t="n">
         <v>0.7487</v>
@@ -50009,7 +50009,7 @@
         <v>1.1757</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.041</v>
+        <v>-0.0409</v>
       </c>
       <c r="J160" t="n">
         <v>0.9242</v>
@@ -50145,7 +50145,7 @@
         <v>1.1753</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0706</v>
+        <v>0.0707</v>
       </c>
       <c r="J164" t="n">
         <v>1.1755</v>
@@ -50247,7 +50247,7 @@
         <v>1.1104</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0711</v>
+        <v>0.0712</v>
       </c>
       <c r="J167" t="n">
         <v>1.2431</v>
@@ -50405,7 +50405,7 @@
         <v>0.7993</v>
       </c>
       <c r="E172" t="n">
-        <v>0.766</v>
+        <v>0.7661</v>
       </c>
       <c r="F172" t="n">
         <v>0.7993</v>
@@ -50417,7 +50417,7 @@
         <v>1.0374</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0577</v>
+        <v>-0.0576</v>
       </c>
       <c r="J172" t="n">
         <v>1.4574</v>
@@ -50485,7 +50485,7 @@
         <v>1.0374</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1044</v>
+        <v>-0.1043</v>
       </c>
       <c r="J174" t="n">
         <v>1.5397</v>
@@ -50587,7 +50587,7 @@
         <v>0.9665</v>
       </c>
       <c r="I177" t="n">
-        <v>-0.2184</v>
+        <v>-0.2183</v>
       </c>
       <c r="J177" t="n">
         <v>1.7354</v>
@@ -50723,7 +50723,7 @@
         <v>0.8421</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1922</v>
+        <v>-0.1921</v>
       </c>
       <c r="J181" t="n">
         <v>1.8899</v>
@@ -50779,7 +50779,7 @@
         <v>0.7165</v>
       </c>
       <c r="E183" t="n">
-        <v>0.7721</v>
+        <v>0.7722</v>
       </c>
       <c r="F183" t="n">
         <v>0.7165</v>
@@ -50927,7 +50927,7 @@
         <v>-0.1328</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.2085</v>
+        <v>-0.2084</v>
       </c>
       <c r="J187" t="n">
         <v>2.1594</v>
@@ -51076,7 +51076,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.3436</v>
+        <v>0.3437</v>
       </c>
       <c r="C192" t="n">
         <v>0.089</v>
@@ -51097,7 +51097,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.078</v>
+        <v>-0.0779</v>
       </c>
       <c r="J192" t="n">
         <v>1.0185</v>
@@ -51131,7 +51131,7 @@
         <v>0.0005</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.0363</v>
+        <v>-0.0362</v>
       </c>
       <c r="J193" t="n">
         <v>0.7759</v>
@@ -51199,7 +51199,7 @@
         <v>0.0005</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0868</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="J195" t="n">
         <v>0.2254</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1669</v>
+        <v>0.167</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1957</v>
+        <v>0.1958</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1983</v>
+        <v>0.1984</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51416,7 +51416,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.2615</v>
+        <v>0.2616</v>
       </c>
       <c r="C202" t="n">
         <v>-0.388</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4039</v>
+        <v>0.404</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51573,7 +51573,7 @@
         <v>0.3351</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3945</v>
+        <v>0.3946</v>
       </c>
       <c r="J206" t="n">
         <v>-0.4093</v>
@@ -51688,7 +51688,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.569</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="C210" t="n">
         <v>-1.489</v>
@@ -51697,7 +51697,7 @@
         <v>1.2959</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3873</v>
+        <v>0.3874</v>
       </c>
       <c r="F210" t="n">
         <v>1.2959</v>
@@ -51743,7 +51743,7 @@
         <v>0.2539</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6983</v>
+        <v>0.6984</v>
       </c>
       <c r="J211" t="n">
         <v>-0.1709</v>
@@ -51913,7 +51913,7 @@
         <v>0.1182</v>
       </c>
       <c r="I216" t="n">
-        <v>0.8902</v>
+        <v>0.8903</v>
       </c>
       <c r="J216" t="n">
         <v>-0.0052</v>
@@ -51947,7 +51947,7 @@
         <v>0.0137</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7592</v>
+        <v>0.7593</v>
       </c>
       <c r="J217" t="n">
         <v>0.0341</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7772</v>
+        <v>0.7773</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52096,7 +52096,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.751</v>
+        <v>0.7511</v>
       </c>
       <c r="C222" t="n">
         <v>-2.439</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8751</v>
+        <v>0.8752</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9872</v>
+        <v>0.9873</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52164,7 +52164,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.8089</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C224" t="n">
         <v>-2.135</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0147</v>
+        <v>1.0148</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.0839</v>
+        <v>1.084</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1646</v>
+        <v>1.1647</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52266,7 +52266,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.7557</v>
+        <v>0.7558</v>
       </c>
       <c r="C227" t="n">
         <v>-2.054</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2042</v>
+        <v>1.2043</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2623</v>
+        <v>1.2624</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52343,7 +52343,7 @@
         <v>1.4523</v>
       </c>
       <c r="E229" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6024</v>
       </c>
       <c r="F229" t="n">
         <v>1.4523</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.186</v>
+        <v>1.1861</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4176</v>
+        <v>1.4177</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52445,7 +52445,7 @@
         <v>1.3845</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6355</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="F232" t="n">
         <v>1.3845</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4801</v>
+        <v>1.4802</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5504</v>
+        <v>1.5505</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52504,7 +52504,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0.8791</v>
+        <v>0.8792</v>
       </c>
       <c r="C234" t="n">
         <v>-1.921</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.6719</v>
+        <v>1.672</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52581,7 +52581,7 @@
         <v>1.3719</v>
       </c>
       <c r="E236" t="n">
-        <v>0.7147</v>
+        <v>0.7148</v>
       </c>
       <c r="F236" t="n">
         <v>1.3719</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7044</v>
+        <v>1.7045</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4982</v>
+        <v>1.4983</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6135</v>
+        <v>1.6136</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52708,7 +52708,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.8067</v>
+        <v>0.8068</v>
       </c>
       <c r="C240" t="n">
         <v>-1.795</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7</v>
+        <v>1.7001</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52751,7 +52751,7 @@
         <v>1.2937</v>
       </c>
       <c r="E241" t="n">
-        <v>0.5897</v>
+        <v>0.5898</v>
       </c>
       <c r="F241" t="n">
         <v>1.2937</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7366</v>
+        <v>1.7367</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7958</v>
+        <v>1.7959</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7194</v>
+        <v>1.7195</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52844,7 +52844,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.6516</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="C244" t="n">
         <v>-1.645</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6569</v>
+        <v>1.657</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6846</v>
+        <v>1.6847</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7797</v>
+        <v>1.7798</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8511</v>
+        <v>1.8512</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9344</v>
+        <v>1.9345</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53091,7 +53091,7 @@
         <v>1.2366</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5673</v>
+        <v>0.5674</v>
       </c>
       <c r="F251" t="n">
         <v>1.2366</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0935</v>
+        <v>2.0936</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2012</v>
+        <v>2.2013</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53150,7 +53150,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.4573</v>
+        <v>0.4574</v>
       </c>
       <c r="C253" t="n">
         <v>-1.487</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2555</v>
+        <v>2.2556</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3463</v>
+        <v>2.3465</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4111</v>
+        <v>2.4112</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53252,7 +53252,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.4645</v>
+        <v>0.4646</v>
       </c>
       <c r="C256" t="n">
         <v>-1.516</v>
@@ -53261,7 +53261,7 @@
         <v>0.4889</v>
       </c>
       <c r="E256" t="n">
-        <v>0.4584</v>
+        <v>0.4585</v>
       </c>
       <c r="F256" t="n">
         <v>0.4889</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4338</v>
+        <v>2.434</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5544</v>
+        <v>2.5546</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7003</v>
+        <v>2.7005</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8861</v>
+        <v>2.8863</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53388,7 +53388,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.5748</v>
+        <v>0.5749</v>
       </c>
       <c r="C260" t="n">
         <v>-1.366</v>
@@ -53397,7 +53397,7 @@
         <v>0.4093</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6162</v>
+        <v>0.6163</v>
       </c>
       <c r="F260" t="n">
         <v>0.4093</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9317</v>
+        <v>2.9319</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53422,7 +53422,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.532</v>
+        <v>0.5321</v>
       </c>
       <c r="C261" t="n">
         <v>-1.367</v>
@@ -53431,7 +53431,7 @@
         <v>0.3305</v>
       </c>
       <c r="E261" t="n">
-        <v>0.5824</v>
+        <v>0.5825</v>
       </c>
       <c r="F261" t="n">
         <v>0.3305</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9291</v>
+        <v>2.9293</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8666</v>
+        <v>2.8668</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5754</v>
+        <v>0.5746</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5754</v>
+        <v>0.5746</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.8955</v>
+        <v>2.8923</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.575</v>
+        <v>0.574</v>
       </c>
     </row>
   </sheetData>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.652</v>
+        <v>1.653</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.917</v>
+        <v>1.915</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.351</v>
+        <v>2.342</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.994</v>
+        <v>2.979</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.054</v>
+        <v>4.039</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.948</v>
+        <v>-0.947</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.539</v>
+        <v>-0.543</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.494</v>
+        <v>0.479</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-0.77</v>
+        <v>-0.75</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66441.677</v>
+        <v>66310.757</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6523</v>
+        <v>1.6534</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9167</v>
+        <v>1.9151</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3507</v>
+        <v>2.3415</v>
       </c>
       <c r="F263" t="n">
-        <v>2.9944</v>
+        <v>2.9789</v>
       </c>
       <c r="G263" t="n">
-        <v>4.0537</v>
+        <v>4.0394</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9477</v>
+        <v>-0.9466</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5386</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="M263" t="n">
-        <v>0.4944</v>
+        <v>0.4789</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>66441.67720000001</v>
+        <v>66310.7568</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>10.8851</v>
+        <v>11.0888</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0594</v>
+        <v>1.0605</v>
       </c>
     </row>
   </sheetData>
@@ -44628,7 +44628,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5742</v>
       </c>
       <c r="D2" t="n">
         <v>0.2559</v>
@@ -44693,7 +44693,7 @@
         <v>0.1577</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6127</v>
+        <v>-0.6128</v>
       </c>
       <c r="F4" t="n">
         <v>0.1577</v>
@@ -45908,7 +45908,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.3443</v>
+        <v>-0.3444</v>
       </c>
       <c r="C40" t="n">
         <v>-0.3972</v>
@@ -46099,7 +46099,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5683</v>
+        <v>-0.5684</v>
       </c>
       <c r="J45" t="n">
         <v>0.613</v>
@@ -46167,7 +46167,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.8343</v>
       </c>
       <c r="J47" t="n">
         <v>0.7422</v>
@@ -46189,7 +46189,7 @@
         <v>0.4538</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6528</v>
+        <v>-0.6529</v>
       </c>
       <c r="F48" t="n">
         <v>0.4538</v>
@@ -46269,7 +46269,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.0875</v>
+        <v>-1.0876</v>
       </c>
       <c r="J50" t="n">
         <v>0.7282</v>
@@ -46282,7 +46282,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.7741</v>
+        <v>-0.7742</v>
       </c>
       <c r="C51" t="n">
         <v>-0.3307</v>
@@ -46473,7 +46473,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.0366</v>
+        <v>-1.0367</v>
       </c>
       <c r="J56" t="n">
         <v>-0.2741</v>
@@ -46541,7 +46541,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.0752</v>
+        <v>-1.0753</v>
       </c>
       <c r="J58" t="n">
         <v>-0.6751</v>
@@ -46597,7 +46597,7 @@
         <v>-0.544</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.2855</v>
+        <v>-1.2856</v>
       </c>
       <c r="F60" t="n">
         <v>-0.544</v>
@@ -46609,7 +46609,7 @@
         <v>-2.3759</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.1067</v>
+        <v>-1.1068</v>
       </c>
       <c r="J60" t="n">
         <v>-0.9807</v>
@@ -46711,7 +46711,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.0906</v>
+        <v>-1.0907</v>
       </c>
       <c r="J63" t="n">
         <v>-1.4655</v>
@@ -46745,7 +46745,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.076</v>
+        <v>-1.0761</v>
       </c>
       <c r="J64" t="n">
         <v>-1.6968</v>
@@ -46813,7 +46813,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.0499</v>
+        <v>-1.05</v>
       </c>
       <c r="J66" t="n">
         <v>-1.9186</v>
@@ -46915,7 +46915,7 @@
         <v>-1.362</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1822</v>
+        <v>-1.1823</v>
       </c>
       <c r="J69" t="n">
         <v>-1.9719</v>
@@ -46971,7 +46971,7 @@
         <v>-0.1118</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0943</v>
+        <v>-1.0944</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1118</v>
@@ -47039,7 +47039,7 @@
         <v>-0.1191</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0461</v>
+        <v>-1.0462</v>
       </c>
       <c r="F73" t="n">
         <v>-0.1191</v>
@@ -47187,7 +47187,7 @@
         <v>-0.703</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.1973</v>
+        <v>-1.1974</v>
       </c>
       <c r="J77" t="n">
         <v>-1.6415</v>
@@ -47221,7 +47221,7 @@
         <v>-0.703</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2362</v>
+        <v>-1.2363</v>
       </c>
       <c r="J78" t="n">
         <v>-1.575</v>
@@ -47255,7 +47255,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.243</v>
+        <v>-1.2431</v>
       </c>
       <c r="J79" t="n">
         <v>-1.5286</v>
@@ -47323,7 +47323,7 @@
         <v>-0.7735</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.3025</v>
+        <v>-1.3026</v>
       </c>
       <c r="J81" t="n">
         <v>-1.3494</v>
@@ -47425,7 +47425,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.3043</v>
+        <v>-1.3044</v>
       </c>
       <c r="J84" t="n">
         <v>-1.2971</v>
@@ -47527,7 +47527,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.2774</v>
+        <v>-1.2775</v>
       </c>
       <c r="J87" t="n">
         <v>-1.1182</v>
@@ -47595,7 +47595,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.2236</v>
+        <v>-1.2237</v>
       </c>
       <c r="J89" t="n">
         <v>-1.0502</v>
@@ -47629,7 +47629,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I90" t="n">
-        <v>-1.2719</v>
+        <v>-1.272</v>
       </c>
       <c r="J90" t="n">
         <v>-1.0499</v>
@@ -47765,7 +47765,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I94" t="n">
-        <v>-1.2997</v>
+        <v>-1.2998</v>
       </c>
       <c r="J94" t="n">
         <v>-0.8408</v>
@@ -47867,7 +47867,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.1815</v>
+        <v>-1.1816</v>
       </c>
       <c r="J97" t="n">
         <v>-0.7234</v>
@@ -47914,7 +47914,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-0.3006</v>
+        <v>-0.3007</v>
       </c>
       <c r="C99" t="n">
         <v>-0.6171</v>
@@ -48003,7 +48003,7 @@
         <v>-0.47</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8369</v>
+        <v>-0.837</v>
       </c>
       <c r="J101" t="n">
         <v>-0.5199</v>
@@ -48241,7 +48241,7 @@
         <v>-0.1605</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6427</v>
       </c>
       <c r="J108" t="n">
         <v>-0.3957</v>
@@ -48297,7 +48297,7 @@
         <v>0.8838</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.1493</v>
+        <v>-0.1494</v>
       </c>
       <c r="F110" t="n">
         <v>0.8838</v>
@@ -48649,7 +48649,7 @@
         <v>0.3858</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.165</v>
+        <v>-0.1651</v>
       </c>
       <c r="J120" t="n">
         <v>-0.1869</v>
@@ -48955,7 +48955,7 @@
         <v>0.7683</v>
       </c>
       <c r="I129" t="n">
-        <v>0.108</v>
+        <v>0.1081</v>
       </c>
       <c r="J129" t="n">
         <v>-0.045</v>
@@ -49499,7 +49499,7 @@
         <v>1.1068</v>
       </c>
       <c r="I145" t="n">
-        <v>0.023</v>
+        <v>0.0231</v>
       </c>
       <c r="J145" t="n">
         <v>0.3337</v>
@@ -49567,7 +49567,7 @@
         <v>1.1068</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="J147" t="n">
         <v>0.3918</v>
@@ -49886,7 +49886,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.6907</v>
+        <v>0.6908</v>
       </c>
       <c r="C157" t="n">
         <v>-0.527</v>
@@ -49941,7 +49941,7 @@
         <v>1.1579</v>
       </c>
       <c r="I158" t="n">
-        <v>0.064</v>
+        <v>0.0641</v>
       </c>
       <c r="J158" t="n">
         <v>0.8825</v>
@@ -50043,7 +50043,7 @@
         <v>1.1757</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0104</v>
+        <v>-0.0103</v>
       </c>
       <c r="J161" t="n">
         <v>1.0249</v>
@@ -50303,7 +50303,7 @@
         <v>0.6978</v>
       </c>
       <c r="E169" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7365</v>
       </c>
       <c r="F169" t="n">
         <v>0.6978</v>
@@ -50315,7 +50315,7 @@
         <v>1.0767</v>
       </c>
       <c r="I169" t="n">
-        <v>0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="J169" t="n">
         <v>1.3187</v>
@@ -50383,7 +50383,7 @@
         <v>1.0767</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0502</v>
+        <v>-0.0501</v>
       </c>
       <c r="J171" t="n">
         <v>1.4412</v>
@@ -51153,7 +51153,7 @@
         <v>0.1202</v>
       </c>
       <c r="E194" t="n">
-        <v>0.322</v>
+        <v>0.3221</v>
       </c>
       <c r="F194" t="n">
         <v>0.1202</v>
@@ -51255,7 +51255,7 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="E197" t="n">
-        <v>0.2324</v>
+        <v>0.2325</v>
       </c>
       <c r="F197" t="n">
         <v>0.07199999999999999</v>
@@ -51471,7 +51471,7 @@
         <v>0.3607</v>
       </c>
       <c r="I203" t="n">
-        <v>0.37</v>
+        <v>0.3701</v>
       </c>
       <c r="J203" t="n">
         <v>-0.5051</v>
@@ -51607,7 +51607,7 @@
         <v>0.3351</v>
       </c>
       <c r="I207" t="n">
-        <v>0.401</v>
+        <v>0.4011</v>
       </c>
       <c r="J207" t="n">
         <v>-0.3128</v>
@@ -51709,7 +51709,7 @@
         <v>0.1795</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6122</v>
+        <v>0.6123</v>
       </c>
       <c r="J210" t="n">
         <v>-0.2538</v>
@@ -51811,7 +51811,7 @@
         <v>0.2539</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7728</v>
       </c>
       <c r="J213" t="n">
         <v>-0.076</v>
@@ -51845,7 +51845,7 @@
         <v>0.1182</v>
       </c>
       <c r="I214" t="n">
-        <v>0.885</v>
+        <v>0.8851</v>
       </c>
       <c r="J214" t="n">
         <v>0.0026</v>
@@ -51981,7 +51981,7 @@
         <v>0.0137</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6896</v>
+        <v>0.6897</v>
       </c>
       <c r="J218" t="n">
         <v>-0.0031</v>
@@ -52003,7 +52003,7 @@
         <v>1.6779</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4611</v>
+        <v>0.4612</v>
       </c>
       <c r="F219" t="n">
         <v>1.6779</v>
@@ -52028,7 +52028,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.6892</v>
+        <v>0.6893</v>
       </c>
       <c r="C220" t="n">
         <v>-2.405</v>
@@ -52049,7 +52049,7 @@
         <v>-0.049</v>
       </c>
       <c r="I220" t="n">
-        <v>0.7634</v>
+        <v>0.7635</v>
       </c>
       <c r="J220" t="n">
         <v>0.1764</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2972</v>
+        <v>1.2973</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.6089</v>
+        <v>1.609</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52559,7 +52559,7 @@
         <v>0.0292</v>
       </c>
       <c r="I235" t="n">
-        <v>1.672</v>
+        <v>1.6721</v>
       </c>
       <c r="J235" t="n">
         <v>0.5668</v>
@@ -52649,7 +52649,7 @@
         <v>1.2151</v>
       </c>
       <c r="E238" t="n">
-        <v>0.5974</v>
+        <v>0.5975</v>
       </c>
       <c r="F238" t="n">
         <v>1.2151</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4634</v>
+        <v>1.4635</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52717,7 +52717,7 @@
         <v>1.2528</v>
       </c>
       <c r="E240" t="n">
-        <v>0.6952</v>
+        <v>0.6953</v>
       </c>
       <c r="F240" t="n">
         <v>1.2528</v>
@@ -52742,7 +52742,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.7305</v>
+        <v>0.7306</v>
       </c>
       <c r="C241" t="n">
         <v>-1.792</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7367</v>
+        <v>1.7368</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7195</v>
+        <v>1.7196</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6868</v>
+        <v>1.6869</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5572</v>
+        <v>1.5573</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.657</v>
+        <v>1.6571</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52955,7 +52955,7 @@
         <v>1.4554</v>
       </c>
       <c r="E247" t="n">
-        <v>0.5095</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F247" t="n">
         <v>1.4554</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6847</v>
+        <v>1.6848</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9345</v>
+        <v>1.9346</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0936</v>
+        <v>2.0937</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2013</v>
+        <v>2.2014</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2556</v>
+        <v>2.2557</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.601</v>
+        <v>0.6011</v>
       </c>
       <c r="C254" t="n">
         <v>-1.316</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3465</v>
+        <v>2.3466</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4112</v>
+        <v>2.4113</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.434</v>
+        <v>2.4341</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5546</v>
+        <v>2.5547</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53329,7 +53329,7 @@
         <v>0.2918</v>
       </c>
       <c r="E258" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5399</v>
       </c>
       <c r="F258" t="n">
         <v>0.2918</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7005</v>
+        <v>2.7007</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53363,7 +53363,7 @@
         <v>0.3229</v>
       </c>
       <c r="E259" t="n">
-        <v>0.5775</v>
+        <v>0.5776</v>
       </c>
       <c r="F259" t="n">
         <v>0.3229</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8863</v>
+        <v>2.8864</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9319</v>
+        <v>2.932</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9293</v>
+        <v>2.9295</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53465,7 +53465,7 @@
         <v>0.4117</v>
       </c>
       <c r="E262" t="n">
-        <v>0.5682</v>
+        <v>0.5683</v>
       </c>
       <c r="F262" t="n">
         <v>0.4117</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8668</v>
+        <v>2.8669</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5746</v>
+        <v>0.574</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5746</v>
+        <v>0.574</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.8923</v>
+        <v>2.89</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.653</v>
+        <v>1.655</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1.915</v>
+        <v>1.914</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>2.342</v>
+        <v>2.339</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.979</v>
+        <v>2.974</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.039</v>
+        <v>4.035</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.947</v>
+        <v>-0.945</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-0.543</v>
+        <v>-0.544</v>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.479</v>
+        <v>0.474</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66310.757</v>
+        <v>66228.192</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44399,19 +44399,19 @@
         <v>1.043</v>
       </c>
       <c r="C263" t="n">
-        <v>1.6534</v>
+        <v>1.6545</v>
       </c>
       <c r="D263" t="n">
-        <v>1.9151</v>
+        <v>1.9144</v>
       </c>
       <c r="E263" t="n">
-        <v>2.3415</v>
+        <v>2.3387</v>
       </c>
       <c r="F263" t="n">
-        <v>2.9789</v>
+        <v>2.9738</v>
       </c>
       <c r="G263" t="n">
-        <v>4.0394</v>
+        <v>4.0352</v>
       </c>
       <c r="H263" t="n">
         <v>2.6</v>
@@ -44423,13 +44423,13 @@
         <v>2.5</v>
       </c>
       <c r="K263" t="n">
-        <v>-0.9466</v>
+        <v>-0.9455</v>
       </c>
       <c r="L263" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5442</v>
       </c>
       <c r="M263" t="n">
-        <v>0.4789</v>
+        <v>0.4738</v>
       </c>
       <c r="N263" t="n">
         <v>-1.557</v>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>66310.7568</v>
+        <v>66228.1925</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44537,10 +44537,10 @@
         <v>20.552</v>
       </c>
       <c r="AW263" t="n">
-        <v>11.0888</v>
+        <v>11.1596</v>
       </c>
       <c r="AX263" t="n">
-        <v>1.0605</v>
+        <v>1.0614</v>
       </c>
     </row>
   </sheetData>
@@ -44643,7 +44643,7 @@
         <v>-0.358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6319</v>
+        <v>-0.632</v>
       </c>
       <c r="J2" t="n">
         <v>-1.5626</v>
@@ -44671,7 +44671,7 @@
         <v>-0.0577</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5903</v>
+        <v>-0.5904</v>
       </c>
       <c r="J3" t="n">
         <v>-1.5477</v>
@@ -44727,7 +44727,7 @@
         <v>0.2197</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5905</v>
+        <v>-0.5906</v>
       </c>
       <c r="F5" t="n">
         <v>0.2197</v>
@@ -44739,7 +44739,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.5429</v>
       </c>
       <c r="J5" t="n">
         <v>-1.5329</v>
@@ -44761,7 +44761,7 @@
         <v>0.2687</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6044</v>
+        <v>-0.6045</v>
       </c>
       <c r="F6" t="n">
         <v>0.2687</v>
@@ -46248,7 +46248,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.7459</v>
+        <v>-0.746</v>
       </c>
       <c r="C50" t="n">
         <v>-0.3217</v>
@@ -46588,7 +46588,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-1.1372</v>
+        <v>-1.1373</v>
       </c>
       <c r="C60" t="n">
         <v>0.7274</v>
@@ -46677,7 +46677,7 @@
         <v>-2.1922</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.0539</v>
+        <v>-1.054</v>
       </c>
       <c r="J62" t="n">
         <v>-1.2678</v>
@@ -46779,7 +46779,7 @@
         <v>-1.8275</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.0178</v>
+        <v>-1.0179</v>
       </c>
       <c r="J65" t="n">
         <v>-1.777</v>
@@ -47030,7 +47030,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.8607</v>
+        <v>-0.8608</v>
       </c>
       <c r="C73" t="n">
         <v>0.301</v>
@@ -47051,7 +47051,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.1922</v>
+        <v>-1.1923</v>
       </c>
       <c r="J73" t="n">
         <v>-1.8127</v>
@@ -47153,7 +47153,7 @@
         <v>-0.703</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2172</v>
+        <v>-1.2173</v>
       </c>
       <c r="J76" t="n">
         <v>-1.7038</v>
@@ -47391,7 +47391,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.3292</v>
+        <v>-1.3293</v>
       </c>
       <c r="J83" t="n">
         <v>-1.3397</v>
@@ -47710,7 +47710,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-0.4604</v>
+        <v>-0.4605</v>
       </c>
       <c r="C93" t="n">
         <v>-0.3887</v>
@@ -47821,7 +47821,7 @@
         <v>0.2759</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.5554</v>
+        <v>-0.5555</v>
       </c>
       <c r="F96" t="n">
         <v>0.2759</v>
@@ -47855,7 +47855,7 @@
         <v>0.5883</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.581</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="F97" t="n">
         <v>0.5883</v>
@@ -47901,7 +47901,7 @@
         <v>-0.5037</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.0554</v>
+        <v>-1.0555</v>
       </c>
       <c r="J98" t="n">
         <v>-0.5312</v>
@@ -48127,7 +48127,7 @@
         <v>0.5881999999999999</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.2178</v>
+        <v>-0.2179</v>
       </c>
       <c r="F105" t="n">
         <v>0.5881999999999999</v>
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.3439</v>
+        <v>0.3438</v>
       </c>
       <c r="C115" t="n">
         <v>-1.072</v>
@@ -49057,7 +49057,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1029</v>
+        <v>0.103</v>
       </c>
       <c r="J132" t="n">
         <v>-0.1091</v>
@@ -49329,7 +49329,7 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2278</v>
+        <v>-0.2279</v>
       </c>
       <c r="J140" t="n">
         <v>0.1018</v>
@@ -49975,7 +49975,7 @@
         <v>1.1579</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.017</v>
+        <v>-0.0169</v>
       </c>
       <c r="J159" t="n">
         <v>0.837</v>
@@ -50213,7 +50213,7 @@
         <v>1.1104</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1028</v>
+        <v>0.1029</v>
       </c>
       <c r="J166" t="n">
         <v>1.2041</v>
@@ -50349,7 +50349,7 @@
         <v>1.0767</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0716</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J170" t="n">
         <v>1.3994</v>
@@ -50655,7 +50655,7 @@
         <v>0.9385</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1991</v>
+        <v>-0.199</v>
       </c>
       <c r="J179" t="n">
         <v>1.712</v>
@@ -50677,7 +50677,7 @@
         <v>0.6758999999999999</v>
       </c>
       <c r="E180" t="n">
-        <v>0.8015</v>
+        <v>0.8016</v>
       </c>
       <c r="F180" t="n">
         <v>0.6758999999999999</v>
@@ -51335,7 +51335,7 @@
         <v>0.2936</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2487</v>
+        <v>0.2488</v>
       </c>
       <c r="J199" t="n">
         <v>-0.6316000000000001</v>
@@ -51357,7 +51357,7 @@
         <v>0.3387</v>
       </c>
       <c r="E200" t="n">
-        <v>0.1733</v>
+        <v>0.1734</v>
       </c>
       <c r="F200" t="n">
         <v>0.3387</v>
@@ -51369,7 +51369,7 @@
         <v>0.2936</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2533</v>
+        <v>0.2534</v>
       </c>
       <c r="J200" t="n">
         <v>-0.6374</v>
@@ -51403,7 +51403,7 @@
         <v>0.2936</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2617</v>
+        <v>0.2618</v>
       </c>
       <c r="J201" t="n">
         <v>-0.5919</v>
@@ -51437,7 +51437,7 @@
         <v>0.3607</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3463</v>
+        <v>0.3464</v>
       </c>
       <c r="J202" t="n">
         <v>-0.6097</v>
@@ -51641,7 +51641,7 @@
         <v>0.1795</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4499</v>
+        <v>0.45</v>
       </c>
       <c r="J208" t="n">
         <v>-0.2344</v>
@@ -51777,7 +51777,7 @@
         <v>0.2539</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7597</v>
+        <v>0.7598</v>
       </c>
       <c r="J212" t="n">
         <v>-0.1602</v>
@@ -51799,7 +51799,7 @@
         <v>1.5673</v>
       </c>
       <c r="E213" t="n">
-        <v>0.4796</v>
+        <v>0.4797</v>
       </c>
       <c r="F213" t="n">
         <v>1.5673</v>
@@ -51879,7 +51879,7 @@
         <v>0.1182</v>
       </c>
       <c r="I215" t="n">
-        <v>0.9338</v>
+        <v>0.9339</v>
       </c>
       <c r="J215" t="n">
         <v>-0.0459</v>
@@ -52015,7 +52015,7 @@
         <v>0.0137</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7415</v>
+        <v>0.7416</v>
       </c>
       <c r="J219" t="n">
         <v>0.1768</v>
@@ -52105,7 +52105,7 @@
         <v>1.7259</v>
       </c>
       <c r="E222" t="n">
-        <v>0.5073</v>
+        <v>0.5074</v>
       </c>
       <c r="F222" t="n">
         <v>1.7259</v>
@@ -52185,7 +52185,7 @@
         <v>0.0552</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0148</v>
+        <v>1.0149</v>
       </c>
       <c r="J224" t="n">
         <v>0.3571</v>
@@ -52321,7 +52321,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I228" t="n">
-        <v>1.2624</v>
+        <v>1.2625</v>
       </c>
       <c r="J228" t="n">
         <v>0.4137</v>
@@ -52334,7 +52334,7 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.7723</v>
+        <v>0.7724</v>
       </c>
       <c r="C229" t="n">
         <v>-1.989</v>
@@ -52423,7 +52423,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I231" t="n">
-        <v>1.4177</v>
+        <v>1.4178</v>
       </c>
       <c r="J231" t="n">
         <v>0.4676</v>
@@ -52436,7 +52436,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.7853</v>
+        <v>0.7854</v>
       </c>
       <c r="C232" t="n">
         <v>-1.976</v>
@@ -52457,7 +52457,7 @@
         <v>0.0292</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4802</v>
+        <v>1.4803</v>
       </c>
       <c r="J232" t="n">
         <v>0.4269</v>
@@ -52470,7 +52470,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0.7852</v>
+        <v>0.7853</v>
       </c>
       <c r="C233" t="n">
         <v>-1.921</v>
@@ -52491,7 +52491,7 @@
         <v>0.0292</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5505</v>
+        <v>1.5506</v>
       </c>
       <c r="J233" t="n">
         <v>0.5712</v>
@@ -52538,7 +52538,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.8134</v>
+        <v>0.8135</v>
       </c>
       <c r="C235" t="n">
         <v>-1.935</v>
@@ -52593,7 +52593,7 @@
         <v>0.0292</v>
       </c>
       <c r="I236" t="n">
-        <v>1.7045</v>
+        <v>1.7046</v>
       </c>
       <c r="J236" t="n">
         <v>0.6237</v>
@@ -52627,7 +52627,7 @@
         <v>0.0292</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4983</v>
+        <v>1.4984</v>
       </c>
       <c r="J237" t="n">
         <v>0.6604</v>
@@ -52695,7 +52695,7 @@
         <v>0.0548</v>
       </c>
       <c r="I239" t="n">
-        <v>1.6136</v>
+        <v>1.6137</v>
       </c>
       <c r="J239" t="n">
         <v>0.6233</v>
@@ -52729,7 +52729,7 @@
         <v>0.0548</v>
       </c>
       <c r="I240" t="n">
-        <v>1.7001</v>
+        <v>1.7002</v>
       </c>
       <c r="J240" t="n">
         <v>0.7178</v>
@@ -52776,7 +52776,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.7922</v>
+        <v>0.7923</v>
       </c>
       <c r="C242" t="n">
         <v>-1.726</v>
@@ -52878,7 +52878,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.6983</v>
+        <v>0.6984</v>
       </c>
       <c r="C245" t="n">
         <v>-1.645</v>
@@ -52980,7 +52980,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.6575</v>
+        <v>0.6576</v>
       </c>
       <c r="C248" t="n">
         <v>-1.551</v>
@@ -53001,7 +53001,7 @@
         <v>-0.109</v>
       </c>
       <c r="I248" t="n">
-        <v>1.7798</v>
+        <v>1.7799</v>
       </c>
       <c r="J248" t="n">
         <v>0.9144</v>
@@ -53014,7 +53014,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.6704</v>
+        <v>0.6705</v>
       </c>
       <c r="C249" t="n">
         <v>-1.552</v>
@@ -53035,7 +53035,7 @@
         <v>-0.109</v>
       </c>
       <c r="I249" t="n">
-        <v>1.8512</v>
+        <v>1.8513</v>
       </c>
       <c r="J249" t="n">
         <v>0.9329</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0937</v>
+        <v>2.0938</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2014</v>
+        <v>2.2015</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53159,7 +53159,7 @@
         <v>0.0319</v>
       </c>
       <c r="E253" t="n">
-        <v>0.5637</v>
+        <v>0.5638</v>
       </c>
       <c r="F253" t="n">
         <v>0.0319</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2557</v>
+        <v>2.2558</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53193,7 +53193,7 @@
         <v>0.6439</v>
       </c>
       <c r="E254" t="n">
-        <v>0.5903</v>
+        <v>0.5904</v>
       </c>
       <c r="F254" t="n">
         <v>0.6439</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4113</v>
+        <v>2.4114</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5547</v>
+        <v>2.5548</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53320,7 +53320,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.4902</v>
+        <v>0.4903</v>
       </c>
       <c r="C258" t="n">
         <v>-1.517</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8864</v>
+        <v>2.8865</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.932</v>
+        <v>2.9321</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53456,7 +53456,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.5369</v>
+        <v>0.537</v>
       </c>
       <c r="C262" t="n">
         <v>-1.201</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.8669</v>
+        <v>2.867</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.574</v>
+        <v>0.5737</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.574</v>
+        <v>0.5737</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.89</v>
+        <v>2.8886</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>

--- a/Japan_FCI_Tracker.xlsx
+++ b/Japan_FCI_Tracker.xlsx
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="197">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>0.704</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="220">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
     </row>
   </sheetData>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66228.192</v>
+        <v>66088.284</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>4156.29</v>
       </c>
       <c r="Z263" t="n">
-        <v>66228.1925</v>
+        <v>66088.2838</v>
       </c>
       <c r="AA263" t="n">
         <v>156.4171</v>
@@ -44773,7 +44773,7 @@
         <v>-0.0181</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5345</v>
+        <v>-0.5346</v>
       </c>
       <c r="J6" t="n">
         <v>-1.5464</v>
@@ -44875,7 +44875,7 @@
         <v>0.1514</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4159</v>
+        <v>-0.416</v>
       </c>
       <c r="J9" t="n">
         <v>-1.3876</v>
@@ -45249,7 +45249,7 @@
         <v>0.4155</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1595</v>
+        <v>-0.1596</v>
       </c>
       <c r="J20" t="n">
         <v>-0.8268</v>
@@ -45976,7 +45976,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.2984</v>
+        <v>-0.2985</v>
       </c>
       <c r="C42" t="n">
         <v>-0.4032</v>
@@ -46065,7 +46065,7 @@
         <v>-0.4995</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5694</v>
+        <v>-0.5695</v>
       </c>
       <c r="J44" t="n">
         <v>0.4983</v>
@@ -46146,7 +46146,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4044</v>
+        <v>-0.4045</v>
       </c>
       <c r="C47" t="n">
         <v>-0.6151</v>
@@ -46201,7 +46201,7 @@
         <v>-0.9866</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9267</v>
+        <v>-0.9268</v>
       </c>
       <c r="J48" t="n">
         <v>0.7507</v>
@@ -46223,7 +46223,7 @@
         <v>-0.0891</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.0032</v>
+        <v>-1.0033</v>
       </c>
       <c r="F49" t="n">
         <v>-0.0891</v>
@@ -46303,7 +46303,7 @@
         <v>-2.1654</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.092</v>
+        <v>-1.0921</v>
       </c>
       <c r="J51" t="n">
         <v>0.5375</v>
@@ -46337,7 +46337,7 @@
         <v>-3.398</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0096</v>
+        <v>-1.0097</v>
       </c>
       <c r="J52" t="n">
         <v>0.3904</v>
@@ -46439,7 +46439,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.9827</v>
+        <v>-0.9828</v>
       </c>
       <c r="J55" t="n">
         <v>-0.1755</v>
@@ -46486,7 +46486,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-1.2168</v>
+        <v>-1.2169</v>
       </c>
       <c r="C57" t="n">
         <v>0.9268999999999999</v>
@@ -46507,7 +46507,7 @@
         <v>-2.8236</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0161</v>
+        <v>-1.0162</v>
       </c>
       <c r="J57" t="n">
         <v>-0.3974</v>
@@ -46881,7 +46881,7 @@
         <v>-1.362</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1495</v>
+        <v>-1.1496</v>
       </c>
       <c r="J68" t="n">
         <v>-2.0811</v>
@@ -46962,7 +46962,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.8978</v>
+        <v>-0.8979</v>
       </c>
       <c r="C71" t="n">
         <v>0.3843</v>
@@ -47119,7 +47119,7 @@
         <v>-0.9376</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1995</v>
+        <v>-1.1996</v>
       </c>
       <c r="J75" t="n">
         <v>-1.7244</v>
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.7238</v>
+        <v>-0.7239</v>
       </c>
       <c r="C79" t="n">
         <v>-0.0368</v>
@@ -47243,7 +47243,7 @@
         <v>0.1218</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.9352</v>
+        <v>-0.9353</v>
       </c>
       <c r="F79" t="n">
         <v>0.1218</v>
@@ -47357,7 +47357,7 @@
         <v>-0.6178</v>
       </c>
       <c r="I82" t="n">
-        <v>-1.3187</v>
+        <v>-1.3188</v>
       </c>
       <c r="J82" t="n">
         <v>-1.3525</v>
@@ -47493,7 +47493,7 @@
         <v>-0.6001</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.3192</v>
+        <v>-1.3193</v>
       </c>
       <c r="J86" t="n">
         <v>-1.1993</v>
@@ -47506,7 +47506,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.5081</v>
+        <v>-0.5082</v>
       </c>
       <c r="C87" t="n">
         <v>-0.1687</v>
@@ -47561,7 +47561,7 @@
         <v>-0.6731</v>
       </c>
       <c r="I88" t="n">
-        <v>-1.2164</v>
+        <v>-1.2165</v>
       </c>
       <c r="J88" t="n">
         <v>-1.0811</v>
@@ -47583,7 +47583,7 @@
         <v>0.337</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.77</v>
+        <v>-0.7701</v>
       </c>
       <c r="F89" t="n">
         <v>0.337</v>
@@ -47663,7 +47663,7 @@
         <v>-0.421</v>
       </c>
       <c r="I91" t="n">
-        <v>-1.2757</v>
+        <v>-1.2758</v>
       </c>
       <c r="J91" t="n">
         <v>-0.9593</v>
@@ -47697,7 +47697,7 @@
         <v>-0.421</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.2942</v>
+        <v>-1.2943</v>
       </c>
       <c r="J92" t="n">
         <v>-0.9359</v>
@@ -47719,7 +47719,7 @@
         <v>0.1751</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.6193</v>
+        <v>-0.6194</v>
       </c>
       <c r="F93" t="n">
         <v>0.1751</v>
@@ -47833,7 +47833,7 @@
         <v>-0.4522</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.2377</v>
+        <v>-1.2378</v>
       </c>
       <c r="J96" t="n">
         <v>-0.7644</v>
@@ -48071,7 +48071,7 @@
         <v>-0.2906</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.804</v>
+        <v>-0.8041</v>
       </c>
       <c r="J103" t="n">
         <v>-0.427</v>
@@ -48445,7 +48445,7 @@
         <v>0.0859</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5451</v>
+        <v>-0.5452</v>
       </c>
       <c r="J114" t="n">
         <v>-0.1624</v>
@@ -49227,7 +49227,7 @@
         <v>0.9537</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.1474</v>
+        <v>-0.1475</v>
       </c>
       <c r="J137" t="n">
         <v>-0.074</v>
@@ -49385,7 +49385,7 @@
         <v>0.2569</v>
       </c>
       <c r="E142" t="n">
-        <v>0.438</v>
+        <v>0.4379</v>
       </c>
       <c r="F142" t="n">
         <v>0.2569</v>
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6246</v>
       </c>
       <c r="C151" t="n">
         <v>-0.547</v>
@@ -50111,7 +50111,7 @@
         <v>1.1753</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0474</v>
+        <v>0.0475</v>
       </c>
       <c r="J163" t="n">
         <v>1.0621</v>
@@ -50757,7 +50757,7 @@
         <v>0.8421</v>
       </c>
       <c r="I182" t="n">
-        <v>-0.2098</v>
+        <v>-0.2097</v>
       </c>
       <c r="J182" t="n">
         <v>1.9557</v>
@@ -51029,7 +51029,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1556</v>
+        <v>-0.1555</v>
       </c>
       <c r="J190" t="n">
         <v>1.4237</v>
@@ -51063,7 +51063,7 @@
         <v>-0.0247</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1328</v>
+        <v>-0.1327</v>
       </c>
       <c r="J191" t="n">
         <v>1.1851</v>
@@ -51165,7 +51165,7 @@
         <v>0.0005</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="J194" t="n">
         <v>0.5265</v>
@@ -51233,7 +51233,7 @@
         <v>0.2032</v>
       </c>
       <c r="I196" t="n">
-        <v>0.167</v>
+        <v>0.1671</v>
       </c>
       <c r="J196" t="n">
         <v>0.0588</v>
@@ -51267,7 +51267,7 @@
         <v>0.2032</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1958</v>
+        <v>0.1959</v>
       </c>
       <c r="J197" t="n">
         <v>-0.2105</v>
@@ -51301,7 +51301,7 @@
         <v>0.2032</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1984</v>
+        <v>0.1985</v>
       </c>
       <c r="J198" t="n">
         <v>-0.4561</v>
@@ -51450,7 +51450,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.297</v>
+        <v>0.2971</v>
       </c>
       <c r="C203" t="n">
         <v>-0.393</v>
@@ -51505,7 +51505,7 @@
         <v>0.3607</v>
       </c>
       <c r="I204" t="n">
-        <v>0.404</v>
+        <v>0.4041</v>
       </c>
       <c r="J204" t="n">
         <v>-0.4146</v>
@@ -51518,7 +51518,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.5707</v>
+        <v>0.5708</v>
       </c>
       <c r="C205" t="n">
         <v>-0.8159999999999999</v>
@@ -51539,7 +51539,7 @@
         <v>0.3351</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3962</v>
+        <v>0.3963</v>
       </c>
       <c r="J205" t="n">
         <v>-0.4232</v>
@@ -51675,7 +51675,7 @@
         <v>0.1795</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5853</v>
       </c>
       <c r="J209" t="n">
         <v>-0.2528</v>
@@ -51833,7 +51833,7 @@
         <v>1.7331</v>
       </c>
       <c r="E214" t="n">
-        <v>0.4652</v>
+        <v>0.4653</v>
       </c>
       <c r="F214" t="n">
         <v>1.7331</v>
@@ -51892,7 +51892,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.8046</v>
+        <v>0.8047</v>
       </c>
       <c r="C216" t="n">
         <v>-2.302</v>
@@ -52071,7 +52071,7 @@
         <v>1.8125</v>
       </c>
       <c r="E221" t="n">
-        <v>0.431</v>
+        <v>0.4311</v>
       </c>
       <c r="F221" t="n">
         <v>1.8125</v>
@@ -52083,7 +52083,7 @@
         <v>-0.049</v>
       </c>
       <c r="I221" t="n">
-        <v>0.7773</v>
+        <v>0.7774</v>
       </c>
       <c r="J221" t="n">
         <v>0.1687</v>
@@ -52117,7 +52117,7 @@
         <v>-0.049</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8752</v>
+        <v>0.8753</v>
       </c>
       <c r="J222" t="n">
         <v>0.1944</v>
@@ -52151,7 +52151,7 @@
         <v>0.0552</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9873</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="J223" t="n">
         <v>0.3093</v>
@@ -52219,7 +52219,7 @@
         <v>0.0552</v>
       </c>
       <c r="I225" t="n">
-        <v>1.084</v>
+        <v>1.0841</v>
       </c>
       <c r="J225" t="n">
         <v>0.3019</v>
@@ -52253,7 +52253,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I226" t="n">
-        <v>1.1647</v>
+        <v>1.1648</v>
       </c>
       <c r="J226" t="n">
         <v>0.3526</v>
@@ -52287,7 +52287,7 @@
         <v>-0.0494</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2043</v>
+        <v>1.2044</v>
       </c>
       <c r="J227" t="n">
         <v>0.3049</v>
@@ -52355,7 +52355,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I229" t="n">
-        <v>1.1861</v>
+        <v>1.1862</v>
       </c>
       <c r="J229" t="n">
         <v>0.4267</v>
@@ -52377,7 +52377,7 @@
         <v>1.1749</v>
       </c>
       <c r="E230" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="F230" t="n">
         <v>1.1749</v>
@@ -52389,7 +52389,7 @@
         <v>-0.0019</v>
       </c>
       <c r="I230" t="n">
-        <v>1.2973</v>
+        <v>1.2974</v>
       </c>
       <c r="J230" t="n">
         <v>0.5341</v>
@@ -52411,7 +52411,7 @@
         <v>1.4913</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6724</v>
+        <v>0.6725</v>
       </c>
       <c r="F231" t="n">
         <v>1.4913</v>
@@ -52513,7 +52513,7 @@
         <v>1.2985</v>
       </c>
       <c r="E234" t="n">
-        <v>0.7743</v>
+        <v>0.7744</v>
       </c>
       <c r="F234" t="n">
         <v>1.2985</v>
@@ -52525,7 +52525,7 @@
         <v>0.0292</v>
       </c>
       <c r="I234" t="n">
-        <v>1.609</v>
+        <v>1.6091</v>
       </c>
       <c r="J234" t="n">
         <v>0.573</v>
@@ -52547,7 +52547,7 @@
         <v>1.3375</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6824</v>
+        <v>0.6825</v>
       </c>
       <c r="F235" t="n">
         <v>1.3375</v>
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.8519</v>
+        <v>0.852</v>
       </c>
       <c r="C237" t="n">
         <v>-1.785</v>
@@ -52615,7 +52615,7 @@
         <v>1.4216</v>
       </c>
       <c r="E237" t="n">
-        <v>0.7095</v>
+        <v>0.7096</v>
       </c>
       <c r="F237" t="n">
         <v>1.4216</v>
@@ -52661,7 +52661,7 @@
         <v>0.0548</v>
       </c>
       <c r="I238" t="n">
-        <v>1.4635</v>
+        <v>1.4636</v>
       </c>
       <c r="J238" t="n">
         <v>0.6312</v>
@@ -52674,7 +52674,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.7456</v>
+        <v>0.7457</v>
       </c>
       <c r="C239" t="n">
         <v>-1.795</v>
@@ -52763,7 +52763,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I241" t="n">
-        <v>1.7368</v>
+        <v>1.7369</v>
       </c>
       <c r="J241" t="n">
         <v>0.7514</v>
@@ -52797,7 +52797,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7959</v>
+        <v>1.796</v>
       </c>
       <c r="J242" t="n">
         <v>0.7819</v>
@@ -52819,7 +52819,7 @@
         <v>1.3068</v>
       </c>
       <c r="E243" t="n">
-        <v>0.6213</v>
+        <v>0.6214</v>
       </c>
       <c r="F243" t="n">
         <v>1.3068</v>
@@ -52831,7 +52831,7 @@
         <v>-0.0023</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7196</v>
+        <v>1.7197</v>
       </c>
       <c r="J243" t="n">
         <v>0.8072</v>
@@ -52865,7 +52865,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I244" t="n">
-        <v>1.6869</v>
+        <v>1.687</v>
       </c>
       <c r="J244" t="n">
         <v>0.7603</v>
@@ -52899,7 +52899,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I245" t="n">
-        <v>1.5573</v>
+        <v>1.5574</v>
       </c>
       <c r="J245" t="n">
         <v>0.8373</v>
@@ -52933,7 +52933,7 @@
         <v>-0.1146</v>
       </c>
       <c r="I246" t="n">
-        <v>1.6571</v>
+        <v>1.6572</v>
       </c>
       <c r="J246" t="n">
         <v>0.9728</v>
@@ -52946,7 +52946,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.6987</v>
+        <v>0.6988</v>
       </c>
       <c r="C247" t="n">
         <v>-1.552</v>
@@ -52967,7 +52967,7 @@
         <v>-0.109</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6848</v>
+        <v>1.6849</v>
       </c>
       <c r="J247" t="n">
         <v>0.8498</v>
@@ -53057,7 +53057,7 @@
         <v>1.2163</v>
       </c>
       <c r="E250" t="n">
-        <v>0.4803</v>
+        <v>0.4804</v>
       </c>
       <c r="F250" t="n">
         <v>1.2163</v>
@@ -53069,7 +53069,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I250" t="n">
-        <v>1.9346</v>
+        <v>1.9347</v>
       </c>
       <c r="J250" t="n">
         <v>0.9801</v>
@@ -53082,7 +53082,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.7012</v>
+        <v>0.7013</v>
       </c>
       <c r="C251" t="n">
         <v>-1.567</v>
@@ -53103,7 +53103,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I251" t="n">
-        <v>2.0938</v>
+        <v>2.0939</v>
       </c>
       <c r="J251" t="n">
         <v>0.968</v>
@@ -53116,7 +53116,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.7712</v>
+        <v>0.7713</v>
       </c>
       <c r="C252" t="n">
         <v>-1.566</v>
@@ -53125,7 +53125,7 @@
         <v>1.2108</v>
       </c>
       <c r="E252" t="n">
-        <v>0.6613</v>
+        <v>0.6614</v>
       </c>
       <c r="F252" t="n">
         <v>1.2108</v>
@@ -53137,7 +53137,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I252" t="n">
-        <v>2.2015</v>
+        <v>2.2016</v>
       </c>
       <c r="J252" t="n">
         <v>1.0442</v>
@@ -53171,7 +53171,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I253" t="n">
-        <v>2.2558</v>
+        <v>2.2559</v>
       </c>
       <c r="J253" t="n">
         <v>0.9782</v>
@@ -53205,7 +53205,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I254" t="n">
-        <v>2.3466</v>
+        <v>2.3468</v>
       </c>
       <c r="J254" t="n">
         <v>1.0212</v>
@@ -53218,7 +53218,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.5689</v>
+        <v>0.569</v>
       </c>
       <c r="C255" t="n">
         <v>-1.316</v>
@@ -53227,7 +53227,7 @@
         <v>0.4417</v>
       </c>
       <c r="E255" t="n">
-        <v>0.6007</v>
+        <v>0.6008</v>
       </c>
       <c r="F255" t="n">
         <v>0.4417</v>
@@ -53239,7 +53239,7 @@
         <v>-0.1068</v>
       </c>
       <c r="I255" t="n">
-        <v>2.4114</v>
+        <v>2.4115</v>
       </c>
       <c r="J255" t="n">
         <v>1.1523</v>
@@ -53273,7 +53273,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I256" t="n">
-        <v>2.4341</v>
+        <v>2.4342</v>
       </c>
       <c r="J256" t="n">
         <v>1.1221</v>
@@ -53286,7 +53286,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.4849</v>
+        <v>0.485</v>
       </c>
       <c r="C257" t="n">
         <v>-1.517</v>
@@ -53295,7 +53295,7 @@
         <v>0.3205</v>
       </c>
       <c r="E257" t="n">
-        <v>0.526</v>
+        <v>0.5261</v>
       </c>
       <c r="F257" t="n">
         <v>0.3205</v>
@@ -53307,7 +53307,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I257" t="n">
-        <v>2.5548</v>
+        <v>2.5549</v>
       </c>
       <c r="J257" t="n">
         <v>1.1728</v>
@@ -53341,7 +53341,7 @@
         <v>-0.1717</v>
       </c>
       <c r="I258" t="n">
-        <v>2.7007</v>
+        <v>2.7009</v>
       </c>
       <c r="J258" t="n">
         <v>1.1617</v>
@@ -53354,7 +53354,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.5266</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="C259" t="n">
         <v>-1.503</v>
@@ -53375,7 +53375,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I259" t="n">
-        <v>2.8865</v>
+        <v>2.8866</v>
       </c>
       <c r="J259" t="n">
         <v>1.2023</v>
@@ -53397,7 +53397,7 @@
         <v>0.4093</v>
       </c>
       <c r="E260" t="n">
-        <v>0.6163</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="F260" t="n">
         <v>0.4093</v>
@@ -53409,7 +53409,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I260" t="n">
-        <v>2.9321</v>
+        <v>2.9322</v>
       </c>
       <c r="J260" t="n">
         <v>1.2277</v>
@@ -53443,7 +53443,7 @@
         <v>-0.1462</v>
       </c>
       <c r="I261" t="n">
-        <v>2.9295</v>
+        <v>2.9297</v>
       </c>
       <c r="J261" t="n">
         <v>1.1996</v>
@@ -53477,7 +53477,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I262" t="n">
-        <v>2.867</v>
+        <v>2.8671</v>
       </c>
       <c r="J262" t="n">
         <v>1.1996</v>
@@ -53490,13 +53490,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0.5737</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="C263" t="n">
         <v>-1.201</v>
       </c>
       <c r="E263" t="n">
-        <v>0.5737</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="G263" t="n">
         <v>-1.6529</v>
@@ -53505,7 +53505,7 @@
         <v>-0.1405</v>
       </c>
       <c r="I263" t="n">
-        <v>2.8886</v>
+        <v>2.8862</v>
       </c>
       <c r="J263" t="n">
         <v>1.1996</v>
